--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -14,6 +14,28 @@
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14336,17 +14358,17 @@
       </c>
     </row>
     <row r="64" ht="23.25" customHeight="1">
-      <c r="A64" s="18">
+      <c r="A64" s="18" t="str" cm="1">
         <f t="array" ref="A64:A73">_xlfn.LET(_xlpm.u,_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Customer],ComplaintTracker[Issue Type]="Complaint")),_xlfn.TAKE(_xlfn.SORTBY(_xlpm.u,COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlpm.u),-1,_xlpm.u,1),10))</f>
-        <v/>
-      </c>
-      <c r="B64" s="21">
+        <v>Ford</v>
+      </c>
+      <c r="B64" s="21" cm="1">
         <f t="array" ref="B64:B73">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A64))</f>
-        <v/>
-      </c>
-      <c r="C64" s="23">
+        <v>32</v>
+      </c>
+      <c r="C64" s="23" cm="1">
         <f t="array" ref="C64:C73">_xlfn.ANCHORARRAY(B64)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v/>
+        <v>0.43835616438356162</v>
       </c>
       <c r="D64" s="3" t="n"/>
       <c r="E64" s="18" t="inlineStr">
@@ -14363,9 +14385,9 @@
         <v/>
       </c>
       <c r="H64" s="3" t="n"/>
-      <c r="I64" s="18">
+      <c r="I64" s="18" t="str" cm="1">
         <f t="array" ref="I64:L84">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
-        <v/>
+        <v>Bankruptcy</v>
       </c>
       <c r="J64" s="75" t="n">
         <v>9</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1219,10 +1219,10 @@
           </marker>
           <cat>
             <numRef>
-              <f>Dashboard!$A$50:$A$57</f>
+              <f>Dashboard!$A$50:$A$58</f>
               <numCache>
                 <formatCode>mmm\ yyyy</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>46023</v>
                 </pt>
@@ -1247,15 +1247,18 @@
                 <pt idx="7">
                   <v>46235</v>
                 </pt>
+                <pt idx="8">
+                  <v>46266</v>
+                </pt>
               </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>Dashboard!$B$50:$B$57</f>
+              <f>Dashboard!$B$50:$B$58</f>
               <numCache>
                 <formatCode>General</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>4</v>
                 </pt>
@@ -1279,6 +1282,9 @@
                 </pt>
                 <pt idx="7">
                   <v>12</v>
+                </pt>
+                <pt idx="8">
+                  <v>2</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1317,10 +1323,10 @@
           </marker>
           <cat>
             <numRef>
-              <f>Dashboard!$A$50:$A$57</f>
+              <f>Dashboard!$A$50:$A$58</f>
               <numCache>
                 <formatCode>mmm\ yyyy</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>46023</v>
                 </pt>
@@ -1345,15 +1351,18 @@
                 <pt idx="7">
                   <v>46235</v>
                 </pt>
+                <pt idx="8">
+                  <v>46266</v>
+                </pt>
               </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>Dashboard!$C$50:$C$57</f>
+              <f>Dashboard!$C$50:$C$58</f>
               <numCache>
                 <formatCode>General</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0</v>
                 </pt>
@@ -1376,6 +1385,9 @@
                   <v>1</v>
                 </pt>
                 <pt idx="7">
+                  <v>0</v>
+                </pt>
+                <pt idx="8">
                   <v>0</v>
                 </pt>
               </numCache>
@@ -1635,6 +1647,22 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="3"/>
+            <invertIfNegative val="0"/>
+            <bubble3D val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4C78A8"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="4C78A8"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <dLbls>
             <numFmt formatCode="#,##0"/>
             <spPr>
@@ -1679,9 +1707,9 @@
           </dLbls>
           <cat>
             <strRef>
-              <f>Dashboard!$I$50:$I$52</f>
+              <f>Dashboard!$I$50:$I$53</f>
               <strCache>
-                <ptCount val="3"/>
+                <ptCount val="4"/>
                 <pt idx="0">
                   <v>Fixed</v>
                 </pt>
@@ -1691,23 +1719,29 @@
                 <pt idx="2">
                   <v>Clarification Provided</v>
                 </pt>
+                <pt idx="3">
+                  <v>Pending</v>
+                </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>Dashboard!$J$50:$J$52</f>
+              <f>Dashboard!$J$50:$J$53</f>
               <numCache>
                 <formatCode>General</formatCode>
-                <ptCount val="3"/>
+                <ptCount val="4"/>
                 <pt idx="0">
-                  <v>38</v>
+                  <v>39</v>
                 </pt>
                 <pt idx="1">
-                  <v>18</v>
+                  <v>21</v>
                 </pt>
                 <pt idx="2">
                   <v>17</v>
+                </pt>
+                <pt idx="3">
+                  <v>4</v>
                 </pt>
               </numCache>
             </numRef>
@@ -14041,9 +14075,19 @@
         <v/>
       </c>
       <c r="H53" s="3" t="n"/>
-      <c r="I53" s="20" t="n"/>
-      <c r="J53" s="22" t="n"/>
-      <c r="K53" s="24" t="n"/>
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J53" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Short Term Fix Status],I53)</f>
+        <v/>
+      </c>
+      <c r="K53" s="24">
+        <f>J53/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
+        <v/>
+      </c>
       <c r="L53" s="3" t="n"/>
       <c r="M53" s="20" t="inlineStr">
         <is>
@@ -14195,17 +14239,15 @@
       <c r="R57" s="3" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B58" s="26">
-        <f>SUM(B50:B57)</f>
+      <c r="A58" s="19" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B58" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Month_Sort],ROW()-49)</f>
         <v/>
       </c>
-      <c r="C58" s="26">
-        <f>SUM(C50:C57)</f>
+      <c r="C58" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Inquiry",ComplaintTracker[Month_Sort],ROW()-49)</f>
         <v/>
       </c>
       <c r="D58" s="3" t="n"/>
@@ -14225,9 +14267,19 @@
       <c r="R58" s="3" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="3" t="n"/>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B59" s="26">
+        <f>SUM(B50:B58)</f>
+        <v/>
+      </c>
+      <c r="C59" s="26">
+        <f>SUM(C50:C58)</f>
+        <v/>
+      </c>
       <c r="D59" s="3" t="n"/>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -12171,16 +12171,16 @@
         <v>46235</v>
       </c>
       <c r="B89" s="119" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Transport Disruption</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -12188,27 +12188,27 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kandla Port Cargo Congestion – Supplier Impact Notification Clarification (Eaton)</t>
+          <t>Fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Supplier Impact Mapping Clarification</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -12218,27 +12218,27 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Impact-confirmation notification criteria documentation for port/logistics bulletins</t>
+          <t>Chinese regional source coverage for sub-tier automotive lighting suppliers</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-28 (Done). Eaton asked what criteria triggered impact-confirmation notifications to Eaton suppliers on the Kandla Port cargo congestion bulletin, since the bulletin text focused on rice exports.</t>
+          <t>Staged from Jira EAO-25 (Sent to PM). GM reported a fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China (reported July 10) was not found in GM's org; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R89" t="n">
@@ -12249,17 +12249,17 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>EAO-28</t>
+          <t>EAO-25</t>
         </is>
       </c>
     </row>
@@ -12268,16 +12268,16 @@
         <v>46235</v>
       </c>
       <c r="B90" s="119" t="n">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Liberty Blume</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -12285,27 +12285,27 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ciena 400G Optics Counterfeit Risk Intelligence Request (Liberty Blume)</t>
+          <t>Chicago Heights, Illinois Tornado – Trialco Impact Not Identified</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Intelligence/Advisory Request</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Event Identification</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -12320,22 +12320,22 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Counterfeit/grey-market component intelligence briefing capability</t>
+          <t>Escalation automation for localized-impact tornado/storm sub-events and named-facility (Trialco) impact confirmation</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-32 (Open). Liberty Blume requested industry intelligence on counterfeit/grey-market Ciena 400G optical transceivers beyond the supplier scanning report already provided.</t>
+          <t>Staged from Jira EAO-25 (Sent to PM). GM reported no event was created specifically for the July 27 Chicago Heights, Illinois tornado (broader Illinois storm alerts existed) and asked whether Trialco was identified as impacted; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R90" t="n">
@@ -12346,35 +12346,35 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>EAO-32</t>
+          <t>EAO-25</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="118" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="B91" s="119" t="n">
-        <v>46267</v>
+        <v>46251</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Transport Disruption</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -12382,27 +12382,27 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Taiwan Strait Conflict Risk Assessment – Missed EventWatch Notification</t>
+          <t>Kandla Port Cargo Congestion – Supplier Impact Notification Clarification (Eaton)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -12412,66 +12412,66 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Geopolitical conflict risk-assessment scenario monitoring and escalation</t>
+          <t>Impact-confirmation notification criteria documentation for port/logistics bulletins</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-33 (In Progress). Caterpillar reported no notification for “Taiwan Strait Conflict Risk Assessment and Potential Global Supply Chain Impact”; CS found no matching event in the backend.</t>
+          <t>Staged from Jira EAO-28 (Done). Eaton asked what criteria triggered impact-confirmation notifications to Eaton suppliers on the Kandla Port cargo congestion bulletin, since the bulletin text focused on rice exports.</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T91" s="118" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>EAO-33</t>
+          <t>EAO-28</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="118" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="B92" s="119" t="n">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Liberty Blume</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -12479,27 +12479,27 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Western Balkans Truck Driver/EU Border Blockade – August 31 Update Missed Alert (Ford)</t>
+          <t>Ciena 400G Optics Counterfeit Risk Intelligence Request (Liberty Blume)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Intelligence/Advisory Request</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -12514,61 +12514,61 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Recurring/evolving-event WarRoom update monitoring and re-escalation detection</t>
+          <t>Counterfeit/grey-market component intelligence briefing capability</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-34 (Open). Ford reported a missed alert for the August 31 update to Western Balkans/Serbia-EU border blockade disruptions; CS found the original January 2026 event but needs to confirm whether it was updated to cover this development. Related to the January 2026 Eaton row above (same underlying WarRoom, different customer/date).</t>
+          <t>Staged from Jira EAO-32 (Open). Liberty Blume requested industry intelligence on counterfeit/grey-market Ciena 400G optical transceivers beyond the supplier scanning report already provided.</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R92" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T92" s="118" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>EAO-34</t>
+          <t>EAO-32</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="118" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B93" s="119" t="n">
-        <v>46237</v>
+        <v>46267</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China</t>
+          <t>Taiwan Strait Conflict Risk Assessment – Missed EventWatch Notification</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Event Identification</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Chinese regional source coverage for sub-tier automotive lighting suppliers</t>
+          <t>Geopolitical conflict risk-assessment scenario monitoring and escalation</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-25 (Sent to PM). GM reported a fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China (reported July 10) was not found in GM's org; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
+          <t>Staged from Jira EAO-33 (In Progress). Caterpillar reported no notification for “Taiwan Strait Conflict Risk Assessment and Potential Global Supply Chain Impact”; CS found no matching event in the backend.</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -12630,10 +12630,10 @@
         </is>
       </c>
       <c r="R93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T93" s="118" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -12642,30 +12642,30 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>EAO-25</t>
+          <t>EAO-33</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="118" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B94" s="119" t="n">
-        <v>46237</v>
+        <v>46268</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Protest/Riot</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chicago Heights, Illinois Tornado – Trialco Impact Not Identified</t>
+          <t>Western Balkans Truck Driver/EU Border Blockade – August 31 Update Missed Alert (Ford)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Escalation automation for localized-impact tornado/storm sub-events and named-facility (Trialco) impact confirmation</t>
+          <t>Recurring/evolving-event WarRoom update monitoring and re-escalation detection</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-25 (Sent to PM). GM reported no event was created specifically for the July 27 Chicago Heights, Illinois tornado (broader Illinois storm alerts existed) and asked whether Trialco was identified as impacted; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
+          <t>Staged from Jira EAO-34 (Open). Ford reported a missed alert for the August 31 update to Western Balkans/Serbia-EU border blockade disruptions; CS found the original January 2026 event but needs to confirm whether it was updated to cover this development. Related to the January 2026 Eaton row above (same underlying WarRoom, different customer/date).</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -12727,10 +12727,10 @@
         </is>
       </c>
       <c r="R94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T94" s="118" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>EAO-25</t>
+          <t>EAO-34</t>
         </is>
       </c>
     </row>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1278,10 +1278,10 @@
                   <v>8</v>
                 </pt>
                 <pt idx="6">
-                  <v>3</v>
+                  <v>7</v>
                 </pt>
                 <pt idx="7">
-                  <v>12</v>
+                  <v>14</v>
                 </pt>
                 <pt idx="8">
                   <v>2</v>
@@ -1382,10 +1382,10 @@
                   <v>3</v>
                 </pt>
                 <pt idx="6">
-                  <v>1</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="7">
-                  <v>0</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="8">
                   <v>0</v>
@@ -2052,10 +2052,10 @@
                   <v>2</v>
                 </pt>
                 <pt idx="2">
-                  <v>75</v>
+                  <v>83</v>
                 </pt>
                 <pt idx="3">
-                  <v>3</v>
+                  <v>8</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2342,10 +2342,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>38</v>
+                  <v>42</v>
                 </pt>
                 <pt idx="1">
-                  <v>28</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -2600,19 +2600,19 @@
                   <v>GM</v>
                 </pt>
                 <pt idx="5">
+                  <v>Ford/GM</v>
+                </pt>
+                <pt idx="6">
                   <v>Merck</v>
                 </pt>
-                <pt idx="6">
+                <pt idx="7">
                   <v>Schneider Electric</v>
                 </pt>
-                <pt idx="7">
+                <pt idx="8">
                   <v>UVM Health Network</v>
                 </pt>
-                <pt idx="8">
+                <pt idx="9">
                   <v>Bombardier</v>
-                </pt>
-                <pt idx="9">
-                  <v>Fedrigoni Group</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2627,22 +2627,22 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>32</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="1">
-                  <v>10</v>
+                  <v>11</v>
                 </pt>
                 <pt idx="2">
-                  <v>6</v>
+                  <v>7</v>
                 </pt>
                 <pt idx="3">
                   <v>4</v>
                 </pt>
                 <pt idx="4">
-                  <v>2</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="5">
-                  <v>2</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="6">
                   <v>2</v>
@@ -2651,13 +2651,13 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="9">
                   <v>1</v>
                 </pt>
                 <pt idx="10">
-                  <v>11</v>
+                  <v>14</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2945,10 +2945,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
                 <pt idx="0">
-                  <v>22</v>
+                  <v>26</v>
                 </pt>
                 <pt idx="1">
-                  <v>26</v>
+                  <v>30</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -14414,13 +14414,13 @@
         <f t="array" ref="A64:A73">_xlfn.LET(_xlpm.u,_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Customer],ComplaintTracker[Issue Type]="Complaint")),_xlfn.TAKE(_xlfn.SORTBY(_xlpm.u,COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlpm.u),-1,_xlpm.u,1),10))</f>
         <v>Ford</v>
       </c>
-      <c r="B64" s="21" cm="1">
+      <c r="B64" s="21" t="n" cm="1">
         <f t="array" ref="B64:B73">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A64))</f>
-        <v>32</v>
-      </c>
-      <c r="C64" s="23" cm="1">
+        <v>31</v>
+      </c>
+      <c r="C64" s="23" t="n" cm="1">
         <f t="array" ref="C64:C73">_xlfn.ANCHORARRAY(B64)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.43835616438356162</v>
+        <v>0.38271604938271603</v>
       </c>
       <c r="D64" s="3" t="n"/>
       <c r="E64" s="18" t="inlineStr">
@@ -14438,17 +14438,17 @@
       </c>
       <c r="H64" s="3" t="n"/>
       <c r="I64" s="18" t="str" cm="1">
-        <f t="array" ref="I64:L84">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
+        <f t="array" ref="I64:L87">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
         <v>Bankruptcy</v>
       </c>
       <c r="J64" s="75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K64" s="75" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" ht="23.25" customHeight="1">
@@ -14458,10 +14458,10 @@
         </is>
       </c>
       <c r="B65" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C65" s="24" t="n">
-        <v>0.136986301369863</v>
+        <v>0.13580246913580246</v>
       </c>
       <c r="D65" s="3" t="n"/>
       <c r="E65" s="20" t="inlineStr">
@@ -14500,10 +14500,10 @@
         </is>
       </c>
       <c r="B66" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C66" s="24" t="n">
-        <v>0.0821917808219178</v>
+        <v>0.08641975308641975</v>
       </c>
       <c r="D66" s="3" t="n"/>
       <c r="E66" s="20" t="inlineStr">
@@ -14526,13 +14526,13 @@
         </is>
       </c>
       <c r="J66" s="76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K66" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" ht="23.25" customHeight="1">
@@ -14545,7 +14545,7 @@
         <v>4</v>
       </c>
       <c r="C67" s="24" t="n">
-        <v>0.0547945205479452</v>
+        <v>0.04938271604938271</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="20" t="inlineStr">
@@ -14584,10 +14584,10 @@
         </is>
       </c>
       <c r="B68" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.0273972602739726</v>
+        <v>0.04938271604938271</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -14622,14 +14622,14 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Ford/GM</t>
         </is>
       </c>
       <c r="B69" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.0273972602739726</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -14664,14 +14664,14 @@
     <row r="70" ht="23.25" customHeight="1">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="B70" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.0273972602739726</v>
+        <v>0.024691358024691357</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -14706,14 +14706,14 @@
     <row r="71" ht="23.25" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>UVM Health Network</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="B71" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.0273972602739726</v>
+        <v>0.024691358024691357</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -14736,26 +14736,26 @@
         </is>
       </c>
       <c r="J71" s="76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K71" s="76" t="n">
         <v>2</v>
       </c>
       <c r="L71" s="76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>Bombardier</t>
+          <t>UVM Health Network</t>
         </is>
       </c>
       <c r="B72" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.0136986301369863</v>
+        <v>0.024691358024691357</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -14790,14 +14790,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>Fedrigoni Group</t>
+          <t>Bombardier</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
         <v>1</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.0136986301369863</v>
+        <v>0.012345679012345678</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="25" t="inlineStr">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="J73" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K73" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" ht="23.25" customHeight="1">
@@ -14932,17 +14932,17 @@
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Litigation/Legal</t>
         </is>
       </c>
       <c r="J77" s="76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K77" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14956,17 +14956,17 @@
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="J78" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="K78" s="76" t="n">
-        <v>1</v>
-      </c>
       <c r="L78" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" ht="23.25" customHeight="1">
@@ -14980,17 +14980,17 @@
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="J79" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K79" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L79" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" ht="23.25" customHeight="1">
@@ -15004,17 +15004,17 @@
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="20" t="inlineStr">
         <is>
-          <t>Regulatory Change</t>
+          <t>Protest/Riot</t>
         </is>
       </c>
       <c r="J80" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K80" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -15028,17 +15028,17 @@
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Regulatory Change</t>
         </is>
       </c>
       <c r="J81" s="76" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K81" s="76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" ht="23.25" customHeight="1">
@@ -15052,17 +15052,17 @@
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="20" t="inlineStr">
         <is>
-          <t>Transport Disruption</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="J82" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K82" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L82" s="76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" ht="23.25" customHeight="1">
@@ -15076,17 +15076,17 @@
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="J83" s="76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K83" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="76" t="n">
         <v>1</v>
-      </c>
-      <c r="L83" s="76" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15098,19 +15098,19 @@
       <c r="F84" s="3" t="n"/>
       <c r="G84" s="3" t="n"/>
       <c r="H84" s="3" t="n"/>
-      <c r="I84" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J84" s="77" t="n">
-        <v>73</v>
-      </c>
-      <c r="K84" s="77" t="n">
-        <v>7</v>
-      </c>
-      <c r="L84" s="77" t="n">
-        <v>80</v>
+      <c r="I84" s="20" t="inlineStr">
+        <is>
+          <t>Transport Disruption</t>
+        </is>
+      </c>
+      <c r="J84" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="76" t="n">
+        <v>2</v>
       </c>
       <c r="M84" s="3" t="n"/>
       <c r="N84" s="3" t="n"/>
@@ -15128,10 +15128,20 @@
       <c r="F85" s="3" t="n"/>
       <c r="G85" s="3" t="n"/>
       <c r="H85" s="3" t="n"/>
-      <c r="I85" s="3" t="n"/>
-      <c r="J85" s="78" t="n"/>
-      <c r="K85" s="78" t="n"/>
-      <c r="L85" s="78" t="n"/>
+      <c r="I85" s="20" t="inlineStr">
+        <is>
+          <t>WarRoom Operations</t>
+        </is>
+      </c>
+      <c r="J85" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" s="76" t="n">
+        <v>1</v>
+      </c>
       <c r="M85" s="3" t="n"/>
       <c r="N85" s="3" t="n"/>
       <c r="O85" s="3" t="n"/>
@@ -15148,10 +15158,20 @@
       <c r="F86" s="3" t="n"/>
       <c r="G86" s="3" t="n"/>
       <c r="H86" s="3" t="n"/>
-      <c r="I86" s="3" t="n"/>
-      <c r="J86" s="78" t="n"/>
-      <c r="K86" s="78" t="n"/>
-      <c r="L86" s="78" t="n"/>
+      <c r="I86" s="20" t="inlineStr">
+        <is>
+          <t>Wildfire</t>
+        </is>
+      </c>
+      <c r="J86" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K86" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="76" t="n">
+        <v>4</v>
+      </c>
       <c r="M86" s="3" t="n"/>
       <c r="N86" s="3" t="n"/>
       <c r="O86" s="3" t="n"/>
@@ -15168,10 +15188,20 @@
       <c r="F87" s="3" t="n"/>
       <c r="G87" s="3" t="n"/>
       <c r="H87" s="3" t="n"/>
-      <c r="I87" s="3" t="n"/>
-      <c r="J87" s="78" t="n"/>
-      <c r="K87" s="78" t="n"/>
-      <c r="L87" s="78" t="n"/>
+      <c r="I87" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J87" s="77" t="n">
+        <v>81</v>
+      </c>
+      <c r="K87" s="77" t="n">
+        <v>12</v>
+      </c>
+      <c r="L87" s="77" t="n">
+        <v>93</v>
+      </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
       <c r="O87" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -10007,7 +10007,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="W66" s="33" t="inlineStr">
         <is>
           <t>EAO-12</t>
         </is>
@@ -10106,7 +10106,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="W67" s="33" t="inlineStr">
         <is>
           <t>EAO-13</t>
         </is>
@@ -10205,7 +10205,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="W68" s="33" t="inlineStr">
         <is>
           <t>EAO-14</t>
         </is>
@@ -10308,7 +10308,7 @@
           <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="W69" s="33" t="inlineStr">
         <is>
           <t>EAO-15</t>
         </is>
@@ -10316,19 +10316,19 @@
     </row>
     <row r="70">
       <c r="A70" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="B70" s="37" t="n">
-        <v>46245</v>
+        <v>46213</v>
       </c>
       <c r="C70" s="33" t="inlineStr">
         <is>
-          <t>Regulatory Change</t>
+          <t>WarRoom Operations</t>
         </is>
       </c>
       <c r="D70" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E70" s="39" t="n">
@@ -10336,27 +10336,27 @@
       </c>
       <c r="F70" s="33" t="inlineStr">
         <is>
-          <t>China MOFCOM Announcement No. 30 of 2026 (Export Control Watchlist)</t>
+          <t>Super Typhoon Bavi WarRoom Timing Clarification (Taiwan)</t>
         </is>
       </c>
       <c r="G70" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H70" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>WarRoom Timing/Trigger Criteria Clarification</t>
         </is>
       </c>
       <c r="I70" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J70" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K70" s="33" t="inlineStr">
@@ -10366,40 +10366,38 @@
       </c>
       <c r="L70" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M70" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful Decision Validation</t>
+          <t>WarRoom trigger-criteria explanation template for post-peak activations</t>
         </is>
       </c>
       <c r="N70" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O70" s="33" t="inlineStr">
         <is>
-          <t>EAO-23: News was captured but initially classified as Not Impactful by AI. Human-in-the-loop review did not escalate the event. RCA shared based on the investigation trail.</t>
-        </is>
-      </c>
-      <c r="P70" s="33" t="n"/>
+          <t>Staged from Jira EAO-16 (Done). Eaton asked why the WarRoom for Super Typhoon Bavi (Taiwan) was activated on 9-Jul after the storm had already peaked, and what triggering criteria were used.</t>
+        </is>
+      </c>
       <c r="Q70" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R70" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="S70" s="39" t="n"/>
+        <v>7</v>
+      </c>
       <c r="T70" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="U70" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V70" s="33" t="inlineStr">
@@ -10407,27 +10405,27 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>EAO-23</t>
+      <c r="W70" s="33" t="inlineStr">
+        <is>
+          <t>EAO-16</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="B71" s="37" t="n">
-        <v>46237</v>
+        <v>46213</v>
       </c>
       <c r="C71" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Litigation/Legal</t>
         </is>
       </c>
       <c r="D71" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Micron</t>
         </is>
       </c>
       <c r="E71" s="39" t="n">
@@ -10435,7 +10433,7 @@
       </c>
       <c r="F71" s="33" t="inlineStr">
         <is>
-          <t>TOHOKU Chemical Japan Fire – Sub-tier Cashew Dust Supplier</t>
+          <t>Jacobs Engineering/CH2M Hill Forced Labor Lawsuit – Missed EventWatch Notification (Micron)</t>
         </is>
       </c>
       <c r="G71" s="33" t="inlineStr">
@@ -10470,91 +10468,89 @@
       </c>
       <c r="M71" s="33" t="inlineStr">
         <is>
+          <t>Legal/labor-litigation source coverage and entity-linking for supplier-adjacent lawsuits</t>
+        </is>
+      </c>
+      <c r="N71" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O71" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-17 (Done). Micron reported a forced-labor lawsuit against Jacobs Engineering/CH2M Hill was not captured in EventWatch and requested RCA if it was in scope.</t>
+        </is>
+      </c>
+      <c r="Q71" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R71" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="T71" s="35" t="n">
+        <v>46204</v>
+      </c>
+      <c r="U71" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V71" s="33" t="inlineStr">
+        <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="N71" s="33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O71" s="33" t="inlineStr">
-        <is>
-          <t>EAO-24: No proactive alert was generated for the July 21 fire. Customer requested RCA, ICA, and PCA for the missed coverage. RCA shared.</t>
-        </is>
-      </c>
-      <c r="P71" s="33" t="n"/>
-      <c r="Q71" s="33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R71" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="S71" s="39" t="n"/>
-      <c r="T71" s="35" t="n">
-        <v>46235</v>
-      </c>
-      <c r="U71" s="33" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V71" s="33" t="inlineStr">
-        <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>EAO-24</t>
+      <c r="W71" s="33" t="inlineStr">
+        <is>
+          <t>EAO-17</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="B72" s="37" t="n">
-        <v>46255</v>
+        <v>46216</v>
       </c>
       <c r="C72" s="33" t="inlineStr">
         <is>
-          <t>Transport Disruption</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D72" s="33" t="inlineStr">
         <is>
-          <t>Ford/GM</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="E72" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="33" t="inlineStr">
         <is>
-          <t>World Trade Bridge Closed in Laredo, Texas</t>
+          <t>Suspension Baseplate Supply Risk Monitoring Request (Fujita Plating/NHK/OSK)</t>
         </is>
       </c>
       <c r="G72" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H72" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I72" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J72" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K72" s="33" t="inlineStr">
@@ -10564,96 +10560,94 @@
       </c>
       <c r="L72" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M72" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Supplier decommitment/capacity-risk monitoring for sub-tier component makers</t>
         </is>
       </c>
       <c r="N72" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O72" s="33" t="inlineStr">
         <is>
-          <t>EAO-25: Event was missed due to a keyword gap. Keyword was added and the article is now being captured.</t>
-        </is>
-      </c>
-      <c r="P72" s="33" t="n"/>
+          <t>Staged from Jira EAO-18 (Done). Western Digital asked whether EventWatch has published or is monitoring a reported Suspension Baseplate supply risk tied to Fujita Plating/NHK/OSK decommitments; CS found no matching event in the backend.</t>
+        </is>
+      </c>
       <c r="Q72" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R72" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="S72" s="39" t="n"/>
+        <v>7</v>
+      </c>
       <c r="T72" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="U72" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V72" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>EAO-25</t>
+          <t>Other Control Automation</t>
+        </is>
+      </c>
+      <c r="W72" s="33" t="inlineStr">
+        <is>
+          <t>EAO-18</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="B73" s="37" t="n">
-        <v>46258</v>
+        <v>46217</v>
       </c>
       <c r="C73" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D73" s="33" t="inlineStr">
         <is>
-          <t>Ford/GM</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E73" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" s="33" t="inlineStr">
         <is>
-          <t>Fire at Nemak Factory in Monterrey, Mexico</t>
+          <t>RFI – Power Grid Failure Monitoring Strategy</t>
         </is>
       </c>
       <c r="G73" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H73" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Monitoring Strategy RFI</t>
         </is>
       </c>
       <c r="I73" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J73" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K73" s="33" t="inlineStr">
@@ -10663,76 +10657,74 @@
       </c>
       <c r="L73" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M73" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful Decision Validation</t>
+          <t>Published monitoring-scope documentation for power-grid/infrastructure failure events</t>
         </is>
       </c>
       <c r="N73" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O73" s="33" t="inlineStr">
         <is>
-          <t>EAO-25: News processing captured the article and attached it to an updated factory-fire cluster. The event was later marked Not Impactful by the analyst. RCA shared based on the investigation trail.</t>
-        </is>
-      </c>
-      <c r="P73" s="33" t="n"/>
+          <t>Staged from Jira EAO-19 (Done). Ford requested an explanation of Resilinc's monitoring strategy for power grid failure events after multiple incidents affected suppliers in the US and Europe.</t>
+        </is>
+      </c>
       <c r="Q73" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R73" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="S73" s="39" t="n"/>
+        <v>7</v>
+      </c>
       <c r="T73" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="U73" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V73" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>EAO-25</t>
+          <t>Other Control Automation</t>
+        </is>
+      </c>
+      <c r="W73" s="33" t="inlineStr">
+        <is>
+          <t>EAO-19</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="B74" s="37" t="n">
-        <v>46255</v>
+        <v>46220</v>
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D74" s="33" t="inlineStr">
         <is>
-          <t>Ford/GM</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="E74" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" s="33" t="inlineStr">
         <is>
-          <t>Fire at FXI de Cuautitlán, S.A. de C.V.</t>
+          <t>ASSMANN WSW Components GmbH Bankruptcy Filing – Missed Coverage (Honeywell Tier 1 Supplier)</t>
         </is>
       </c>
       <c r="G74" s="33" t="inlineStr">
@@ -10742,7 +10734,7 @@
       </c>
       <c r="H74" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="I74" s="33" t="inlineStr">
@@ -10762,63 +10754,61 @@
       </c>
       <c r="L74" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M74" s="33" t="inlineStr">
         <is>
+          <t>Tier-1 supplier bankruptcy/insolvency filing source coverage expansion (EU registries)</t>
+        </is>
+      </c>
+      <c r="N74" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O74" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-20 (Done). Honeywell reported ASSMANN WSW Components GmbH's July 6 insolvency filing (a mapped Tier-1 supplier) was never published as an EventWatch bulletin or WarRoom; RCA requested.</t>
+        </is>
+      </c>
+      <c r="Q74" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R74" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="T74" s="35" t="n">
+        <v>46204</v>
+      </c>
+      <c r="U74" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V74" s="33" t="inlineStr">
+        <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="N74" s="33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O74" s="33" t="inlineStr">
-        <is>
-          <t>EAO-25: Event was not captured by the vendor due to a source coverage gap. Vendor was asked to add the sources to its network. RCA shared based on the investigation trail.</t>
-        </is>
-      </c>
-      <c r="P74" s="33" t="n"/>
-      <c r="Q74" s="33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R74" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="S74" s="39" t="n"/>
-      <c r="T74" s="35" t="n">
-        <v>46235</v>
-      </c>
-      <c r="U74" s="33" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V74" s="33" t="inlineStr">
-        <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>EAO-25</t>
+      <c r="W74" s="33" t="inlineStr">
+        <is>
+          <t>EAO-20</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="B75" s="37" t="n">
-        <v>46252</v>
+        <v>46220</v>
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="D75" s="33" t="inlineStr">
@@ -10831,7 +10821,7 @@
       </c>
       <c r="F75" s="33" t="inlineStr">
         <is>
-          <t>Sasol Polyethylene Plant Fire / Shutdown</t>
+          <t>Severe Air Quality Degradation – Canadian Wildfires Missed Alert (Midwest/Northeast US)</t>
         </is>
       </c>
       <c r="G75" s="33" t="inlineStr">
@@ -10846,12 +10836,12 @@
       </c>
       <c r="I75" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J75" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Event Identification</t>
         </is>
       </c>
       <c r="K75" s="33" t="inlineStr">
@@ -10866,7 +10856,7 @@
       </c>
       <c r="M75" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Escalation automation for environmental-hazard advisories</t>
         </is>
       </c>
       <c r="N75" s="33" t="inlineStr">
@@ -10876,21 +10866,19 @@
       </c>
       <c r="O75" s="33" t="inlineStr">
         <is>
-          <t>EAO-26: Customer reported a missed EventWatch alert for the Sasol polyethylene plant fire and shutdown. Investigation and RCA were requested; RCA shared.</t>
-        </is>
-      </c>
-      <c r="P75" s="33" t="n"/>
+          <t>Staged from Jira EAO-21 (Done). Ford reported no EventWatch alert/WarRoom was generated for July 15-17 wildfire smoke air-quality degradation across the US Midwest/Northeast; CS confirmed no matching notification was found.</t>
+        </is>
+      </c>
       <c r="Q75" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="R75" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="S75" s="39" t="n"/>
+        <v>7</v>
+      </c>
       <c r="T75" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="U75" s="33" t="inlineStr">
         <is>
@@ -10899,30 +10887,30 @@
       </c>
       <c r="V75" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>EAO-26</t>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W75" s="33" t="inlineStr">
+        <is>
+          <t>EAO-21</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="B76" s="37" t="n">
-        <v>46251</v>
+        <v>46230</v>
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E76" s="39" t="n">
@@ -10930,7 +10918,7 @@
       </c>
       <c r="F76" s="33" t="inlineStr">
         <is>
-          <t>Ceuta Border Security &amp; Humanitarian Crisis</t>
+          <t>Romania ANCPI Cyberattack – Missed EventWatch Notification</t>
         </is>
       </c>
       <c r="G76" s="33" t="inlineStr">
@@ -10945,12 +10933,12 @@
       </c>
       <c r="I76" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J76" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K76" s="33" t="inlineStr">
@@ -10965,7 +10953,7 @@
       </c>
       <c r="M76" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Trigger Automation</t>
+          <t>Government/public-sector cyberattack source coverage expansion (regional-language sources)</t>
         </is>
       </c>
       <c r="N76" s="33" t="inlineStr">
@@ -10975,21 +10963,19 @@
       </c>
       <c r="O76" s="33" t="inlineStr">
         <is>
-          <t>EAO-27: Customer reported a missed EventWatch alert and requested an update. RCA shared following review of the event.</t>
-        </is>
-      </c>
-      <c r="P76" s="33" t="n"/>
+          <t>Staged from Jira EAO-22 (Done). Eaton reported the July 14-16 ANCPI (Romania land registry) cyberattack had no corresponding WarRoom or news on the portal; RCA requested if it was in scope.</t>
+        </is>
+      </c>
       <c r="Q76" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="R76" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="S76" s="39" t="n"/>
+        <v>7</v>
+      </c>
       <c r="T76" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="U76" s="33" t="inlineStr">
         <is>
@@ -10998,12 +10984,12 @@
       </c>
       <c r="V76" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>EAO-27</t>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W76" s="33" t="inlineStr">
+        <is>
+          <t>EAO-22</t>
         </is>
       </c>
     </row>
@@ -11012,11 +10998,11 @@
         <v>46235</v>
       </c>
       <c r="B77" s="37" t="n">
-        <v>46254</v>
+        <v>46237</v>
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
@@ -11029,7 +11015,7 @@
       </c>
       <c r="F77" s="33" t="inlineStr">
         <is>
-          <t>Typhoon Dolphin Bulletins Distributed Across Two WarRooms</t>
+          <t>TOHOKU Chemical Japan Fire – Sub-tier Cashew Dust Supplier</t>
         </is>
       </c>
       <c r="G77" s="33" t="inlineStr">
@@ -11039,7 +11025,7 @@
       </c>
       <c r="H77" s="33" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I77" s="33" t="inlineStr">
@@ -11049,7 +11035,7 @@
       </c>
       <c r="J77" s="33" t="inlineStr">
         <is>
-          <t>Duplication</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K77" s="33" t="inlineStr">
@@ -11064,7 +11050,7 @@
       </c>
       <c r="M77" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="N77" s="33" t="inlineStr">
@@ -11074,13 +11060,13 @@
       </c>
       <c r="O77" s="33" t="inlineStr">
         <is>
-          <t>EAO-29: Bulletins were distributed across two WarRooms, resulting in gaps in the update sequence. Customer requested RCA; RCA shared.</t>
+          <t>EAO-24: No proactive alert was generated for the July 21 fire. Customer requested RCA, ICA, and PCA for the missed coverage. RCA shared.</t>
         </is>
       </c>
       <c r="P77" s="33" t="n"/>
       <c r="Q77" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R77" s="39" t="n">
@@ -11092,17 +11078,17 @@
       </c>
       <c r="U77" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V77" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>EAO-29</t>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W77" s="33" t="inlineStr">
+        <is>
+          <t>EAO-24</t>
         </is>
       </c>
     </row>
@@ -11111,16 +11097,16 @@
         <v>46235</v>
       </c>
       <c r="B78" s="37" t="n">
-        <v>46258</v>
+        <v>46237</v>
       </c>
       <c r="C78" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D78" s="33" t="inlineStr">
         <is>
-          <t>The American National Red Cross</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="E78" s="39" t="n">
@@ -11128,7 +11114,7 @@
       </c>
       <c r="F78" s="33" t="inlineStr">
         <is>
-          <t>Uber Freight Investigates Reported Cyberattack After Hackers Claim Data Breach</t>
+          <t>Fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China</t>
         </is>
       </c>
       <c r="G78" s="33" t="inlineStr">
@@ -11138,17 +11124,17 @@
       </c>
       <c r="H78" s="33" t="inlineStr">
         <is>
-          <t>WarRoom not visible in customer profile</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I78" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J78" s="33" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K78" s="33" t="inlineStr">
@@ -11158,25 +11144,24 @@
       </c>
       <c r="L78" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="M78" s="33" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>Chinese regional source coverage for sub-tier automotive lighting suppliers</t>
         </is>
       </c>
       <c r="N78" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O78" s="33" t="inlineStr">
         <is>
-          <t>EAO-30: EventWatch news was published on August 13 but was not visible on the customer portal. Portal visibility investigation completed and clarification provided.</t>
-        </is>
-      </c>
-      <c r="P78" s="33" t="n"/>
+          <t>Staged from Jira EAO-25 (Sent to PM). GM reported a fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China (reported July 10) was not found in GM's org; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
+        </is>
+      </c>
       <c r="Q78" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11185,7 +11170,6 @@
       <c r="R78" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="S78" s="39" t="n"/>
       <c r="T78" s="35" t="n">
         <v>46235</v>
       </c>
@@ -11196,7 +11180,12 @@
       </c>
       <c r="V78" s="33" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W78" s="33" t="inlineStr">
+        <is>
+          <t>EAO-25</t>
         </is>
       </c>
     </row>
@@ -11205,16 +11194,16 @@
         <v>46235</v>
       </c>
       <c r="B79" s="37" t="n">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="E79" s="39" t="n">
@@ -11222,7 +11211,7 @@
       </c>
       <c r="F79" s="33" t="inlineStr">
         <is>
-          <t>Gindre India Data Breach – EventWatch Alert/WarRoom Missing</t>
+          <t>Chicago Heights, Illinois Tornado – Trialco Impact Not Identified</t>
         </is>
       </c>
       <c r="G79" s="33" t="inlineStr">
@@ -11237,12 +11226,12 @@
       </c>
       <c r="I79" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J79" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Event Identification</t>
         </is>
       </c>
       <c r="K79" s="33" t="inlineStr">
@@ -11252,12 +11241,12 @@
       </c>
       <c r="L79" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="M79" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Escalation automation for localized-impact tornado/storm sub-events and named-facility (Trialco) impact confirmation</t>
         </is>
       </c>
       <c r="N79" s="33" t="inlineStr">
@@ -11267,10 +11256,9 @@
       </c>
       <c r="O79" s="33" t="inlineStr">
         <is>
-          <t>EAO-31: No corresponding EventWatch event or WarRoom was found for the reported data breach. Source coverage review completed and RCA shared.</t>
-        </is>
-      </c>
-      <c r="P79" s="33" t="n"/>
+          <t>Staged from Jira EAO-25 (Sent to PM). GM reported no event was created specifically for the July 27 Chicago Heights, Illinois tornado (broader Illinois storm alerts existed) and asked whether Trialco was identified as impacted; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
+        </is>
+      </c>
       <c r="Q79" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11279,7 +11267,6 @@
       <c r="R79" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="S79" s="39" t="n"/>
       <c r="T79" s="35" t="n">
         <v>46235</v>
       </c>
@@ -11290,12 +11277,12 @@
       </c>
       <c r="V79" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>EAO-31</t>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W79" s="33" t="inlineStr">
+        <is>
+          <t>EAO-25</t>
         </is>
       </c>
     </row>
@@ -11304,16 +11291,16 @@
         <v>46235</v>
       </c>
       <c r="B80" s="37" t="n">
-        <v>46265</v>
+        <v>46245</v>
       </c>
       <c r="C80" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Regulatory Change</t>
         </is>
       </c>
       <c r="D80" s="33" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E80" s="39" t="n">
@@ -11321,7 +11308,7 @@
       </c>
       <c r="F80" s="33" t="inlineStr">
         <is>
-          <t>Baxter International Reports a Cybersecurity Incident</t>
+          <t>China MOFCOM Announcement No. 30 of 2026 (Export Control Watchlist)</t>
         </is>
       </c>
       <c r="G80" s="33" t="inlineStr">
@@ -11366,7 +11353,7 @@
       </c>
       <c r="O80" s="33" t="inlineStr">
         <is>
-          <t>Customer reported the missed Baxter ransomware incident. EventWatch captured the report on August 14, but human review incorrectly marked it Not Impactful; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+          <t>EAO-23: News was captured but initially classified as Not Impactful by AI. Human-in-the-loop review did not escalate the event. RCA shared based on the investigation trail.</t>
         </is>
       </c>
       <c r="P80" s="33" t="n"/>
@@ -11392,22 +11379,27 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="W80" s="33" t="inlineStr">
+        <is>
+          <t>EAO-23</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="B81" s="37" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="D81" s="33" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E81" s="39" t="n">
@@ -11415,7 +11407,7 @@
       </c>
       <c r="F81" s="33" t="inlineStr">
         <is>
-          <t>McKesson Corporation Confirms Data Breach Following a Cybersecurity Incident</t>
+          <t>Ceuta Border Security &amp; Humanitarian Crisis</t>
         </is>
       </c>
       <c r="G81" s="33" t="inlineStr">
@@ -11450,7 +11442,7 @@
       </c>
       <c r="M81" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Duplicate Decision Validation</t>
+          <t>WarRoom Trigger Automation</t>
         </is>
       </c>
       <c r="N81" s="33" t="inlineStr">
@@ -11460,7 +11452,7 @@
       </c>
       <c r="O81" s="33" t="inlineStr">
         <is>
-          <t>Customer reported the missed McKesson data-breach incident. EventWatch captured the report on August 28, but human review assumed it was already covered; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+          <t>EAO-27: Customer reported a missed EventWatch alert and requested an update. RCA shared following review of the event.</t>
         </is>
       </c>
       <c r="P81" s="33" t="n"/>
@@ -11486,1069 +11478,1077 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="W81" s="33" t="inlineStr">
+        <is>
+          <t>EAO-27</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B82" s="119" t="n">
-        <v>46213</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>WarRoom Operations</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+      <c r="A82" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B82" s="37" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C82" s="33" t="inlineStr">
+        <is>
+          <t>Transport Disruption</t>
+        </is>
+      </c>
+      <c r="D82" s="33" t="inlineStr">
         <is>
           <t>Eaton</t>
         </is>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Super Typhoon Bavi WarRoom Timing Clarification (Taiwan)</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F82" s="33" t="inlineStr">
+        <is>
+          <t>Kandla Port Cargo Congestion – Supplier Impact Notification Clarification (Eaton)</t>
+        </is>
+      </c>
+      <c r="G82" s="33" t="inlineStr">
         <is>
           <t>Inquiry</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>WarRoom Timing/Trigger Criteria Clarification</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>Supplier Impact Mapping Clarification</t>
+        </is>
+      </c>
+      <c r="I82" s="33" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J82" s="33" t="inlineStr">
+        <is>
+          <t>Mapping</t>
+        </is>
+      </c>
+      <c r="K82" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L82" s="33" t="inlineStr">
+        <is>
+          <t>Clarification Provided</t>
+        </is>
+      </c>
+      <c r="M82" s="33" t="inlineStr">
+        <is>
+          <t>Impact-confirmation notification criteria documentation for port/logistics bulletins</t>
+        </is>
+      </c>
+      <c r="N82" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O82" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-28 (Done). Eaton asked what criteria triggered impact-confirmation notifications to Eaton suppliers on the Kandla Port cargo congestion bulletin, since the bulletin text focused on rice exports.</t>
+        </is>
+      </c>
+      <c r="Q82" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R82" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="T82" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="U82" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="V82" s="33" t="inlineStr">
+        <is>
+          <t>Entity &amp; Supplier Resolution</t>
+        </is>
+      </c>
+      <c r="W82" s="33" t="inlineStr">
+        <is>
+          <t>EAO-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B83" s="37" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C83" s="33" t="inlineStr">
+        <is>
+          <t>Factory Fire</t>
+        </is>
+      </c>
+      <c r="D83" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E83" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="33" t="inlineStr">
+        <is>
+          <t>Sasol Polyethylene Plant Fire / Shutdown</t>
+        </is>
+      </c>
+      <c r="G83" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H83" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I83" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J83" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K83" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L83" s="33" t="inlineStr">
+        <is>
+          <t>RCA Shared</t>
+        </is>
+      </c>
+      <c r="M83" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="N83" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O83" s="33" t="inlineStr">
+        <is>
+          <t>EAO-26: Customer reported a missed EventWatch alert for the Sasol polyethylene plant fire and shutdown. Investigation and RCA were requested; RCA shared.</t>
+        </is>
+      </c>
+      <c r="P83" s="33" t="n"/>
+      <c r="Q83" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R83" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="S83" s="39" t="n"/>
+      <c r="T83" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="U83" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V83" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W83" s="33" t="inlineStr">
+        <is>
+          <t>EAO-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B84" s="37" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C84" s="33" t="inlineStr">
+        <is>
+          <t>Hurricane/Typhoon</t>
+        </is>
+      </c>
+      <c r="D84" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E84" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="33" t="inlineStr">
+        <is>
+          <t>Typhoon Dolphin Bulletins Distributed Across Two WarRooms</t>
+        </is>
+      </c>
+      <c r="G84" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H84" s="33" t="inlineStr">
+        <is>
+          <t>Duplicate WarRooms</t>
+        </is>
+      </c>
+      <c r="I84" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J84" s="33" t="inlineStr">
+        <is>
+          <t>Duplication</t>
+        </is>
+      </c>
+      <c r="K84" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L84" s="33" t="inlineStr">
+        <is>
+          <t>RCA Shared</t>
+        </is>
+      </c>
+      <c r="M84" s="33" t="inlineStr">
+        <is>
+          <t>Cluster Integrity Validation</t>
+        </is>
+      </c>
+      <c r="N84" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O84" s="33" t="inlineStr">
+        <is>
+          <t>EAO-29: Bulletins were distributed across two WarRooms, resulting in gaps in the update sequence. Customer requested RCA; RCA shared.</t>
+        </is>
+      </c>
+      <c r="P84" s="33" t="n"/>
+      <c r="Q84" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R84" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="S84" s="39" t="n"/>
+      <c r="T84" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="U84" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="V84" s="33" t="inlineStr">
+        <is>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+        </is>
+      </c>
+      <c r="W84" s="33" t="inlineStr">
+        <is>
+          <t>EAO-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B85" s="37" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C85" s="33" t="inlineStr">
+        <is>
+          <t>Transport Disruption</t>
+        </is>
+      </c>
+      <c r="D85" s="33" t="inlineStr">
+        <is>
+          <t>Ford/GM</t>
+        </is>
+      </c>
+      <c r="E85" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="33" t="inlineStr">
+        <is>
+          <t>World Trade Bridge Closed in Laredo, Texas</t>
+        </is>
+      </c>
+      <c r="G85" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H85" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I85" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J85" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K85" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L85" s="33" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="M85" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="N85" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O85" s="33" t="inlineStr">
+        <is>
+          <t>EAO-25: Event was missed due to a keyword gap. Keyword was added and the article is now being captured.</t>
+        </is>
+      </c>
+      <c r="P85" s="33" t="n"/>
+      <c r="Q85" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R85" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="S85" s="39" t="n"/>
+      <c r="T85" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="U85" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V85" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W85" s="33" t="inlineStr">
+        <is>
+          <t>EAO-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B86" s="37" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C86" s="33" t="inlineStr">
+        <is>
+          <t>Factory Fire</t>
+        </is>
+      </c>
+      <c r="D86" s="33" t="inlineStr">
+        <is>
+          <t>Ford/GM</t>
+        </is>
+      </c>
+      <c r="E86" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="33" t="inlineStr">
+        <is>
+          <t>Fire at FXI de Cuautitlán, S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="G86" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H86" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I86" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J86" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K86" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L86" s="33" t="inlineStr">
+        <is>
+          <t>RCA Shared</t>
+        </is>
+      </c>
+      <c r="M86" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="N86" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O86" s="33" t="inlineStr">
+        <is>
+          <t>EAO-25: Event was not captured by the vendor due to a source coverage gap. Vendor was asked to add the sources to its network. RCA shared based on the investigation trail.</t>
+        </is>
+      </c>
+      <c r="P86" s="33" t="n"/>
+      <c r="Q86" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R86" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="S86" s="39" t="n"/>
+      <c r="T86" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="U86" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V86" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W86" s="33" t="inlineStr">
+        <is>
+          <t>EAO-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B87" s="37" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C87" s="33" t="inlineStr">
+        <is>
+          <t>Factory Fire</t>
+        </is>
+      </c>
+      <c r="D87" s="33" t="inlineStr">
+        <is>
+          <t>Ford/GM</t>
+        </is>
+      </c>
+      <c r="E87" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" s="33" t="inlineStr">
+        <is>
+          <t>Fire at Nemak Factory in Monterrey, Mexico</t>
+        </is>
+      </c>
+      <c r="G87" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H87" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I87" s="33" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="J87" s="33" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K87" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L87" s="33" t="inlineStr">
+        <is>
+          <t>RCA Shared</t>
+        </is>
+      </c>
+      <c r="M87" s="33" t="inlineStr">
+        <is>
+          <t>Not Impactful Decision Validation</t>
+        </is>
+      </c>
+      <c r="N87" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O87" s="33" t="inlineStr">
+        <is>
+          <t>EAO-25: News processing captured the article and attached it to an updated factory-fire cluster. The event was later marked Not Impactful by the analyst. RCA shared based on the investigation trail.</t>
+        </is>
+      </c>
+      <c r="P87" s="33" t="n"/>
+      <c r="Q87" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R87" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="S87" s="39" t="n"/>
+      <c r="T87" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="U87" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V87" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W87" s="33" t="inlineStr">
+        <is>
+          <t>EAO-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B88" s="37" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C88" s="33" t="inlineStr">
+        <is>
+          <t>Cyber Attack</t>
+        </is>
+      </c>
+      <c r="D88" s="33" t="inlineStr">
+        <is>
+          <t>The American National Red Cross</t>
+        </is>
+      </c>
+      <c r="E88" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="33" t="inlineStr">
+        <is>
+          <t>Uber Freight Investigates Reported Cyberattack After Hackers Claim Data Breach</t>
+        </is>
+      </c>
+      <c r="G88" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H88" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom not visible in customer profile</t>
+        </is>
+      </c>
+      <c r="I88" s="33" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="J88" s="33" t="inlineStr">
+        <is>
+          <t>Visibility</t>
+        </is>
+      </c>
+      <c r="K88" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L88" s="33" t="inlineStr">
+        <is>
+          <t>RCA Shared</t>
+        </is>
+      </c>
+      <c r="M88" s="33" t="inlineStr">
+        <is>
+          <t>Notification Visibility Monitoring</t>
+        </is>
+      </c>
+      <c r="N88" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O88" s="33" t="inlineStr">
+        <is>
+          <t>EAO-30: EventWatch news was published on August 13 but was not visible on the customer portal. Portal visibility investigation completed and clarification provided.</t>
+        </is>
+      </c>
+      <c r="P88" s="33" t="n"/>
+      <c r="Q88" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R88" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="S88" s="39" t="n"/>
+      <c r="T88" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="U88" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V88" s="33" t="inlineStr">
+        <is>
+          <t>Notification Visibility Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B89" s="37" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C89" s="33" t="inlineStr">
+        <is>
+          <t>Cyber Attack</t>
+        </is>
+      </c>
+      <c r="D89" s="33" t="inlineStr">
+        <is>
+          <t>Schneider Electric</t>
+        </is>
+      </c>
+      <c r="E89" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="33" t="inlineStr">
+        <is>
+          <t>Gindre India Data Breach – EventWatch Alert/WarRoom Missing</t>
+        </is>
+      </c>
+      <c r="G89" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H89" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I89" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J89" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K89" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L89" s="33" t="inlineStr">
+        <is>
+          <t>RCA Shared</t>
+        </is>
+      </c>
+      <c r="M89" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="N89" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O89" s="33" t="inlineStr">
+        <is>
+          <t>EAO-31: No corresponding EventWatch event or WarRoom was found for the reported data breach. Source coverage review completed and RCA shared.</t>
+        </is>
+      </c>
+      <c r="P89" s="33" t="n"/>
+      <c r="Q89" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R89" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="S89" s="39" t="n"/>
+      <c r="T89" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="U89" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V89" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W89" s="33" t="inlineStr">
+        <is>
+          <t>EAO-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B90" s="37" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C90" s="33" t="inlineStr">
+        <is>
+          <t>Cyber Attack</t>
+        </is>
+      </c>
+      <c r="D90" s="33" t="inlineStr">
+        <is>
+          <t>Merck</t>
+        </is>
+      </c>
+      <c r="E90" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="33" t="inlineStr">
+        <is>
+          <t>Baxter International Reports a Cybersecurity Incident</t>
+        </is>
+      </c>
+      <c r="G90" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H90" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I90" s="33" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="J90" s="33" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K90" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L90" s="33" t="inlineStr">
+        <is>
+          <t>RCA Shared</t>
+        </is>
+      </c>
+      <c r="M90" s="33" t="inlineStr">
+        <is>
+          <t>Not Impactful Decision Validation</t>
+        </is>
+      </c>
+      <c r="N90" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O90" s="33" t="inlineStr">
+        <is>
+          <t>Customer reported the missed Baxter ransomware incident. EventWatch captured the report on August 14, but human review incorrectly marked it Not Impactful; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+        </is>
+      </c>
+      <c r="P90" s="33" t="n"/>
+      <c r="Q90" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R90" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="S90" s="39" t="n"/>
+      <c r="T90" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="U90" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V90" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B91" s="37" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C91" s="33" t="inlineStr">
+        <is>
+          <t>Cyber Attack</t>
+        </is>
+      </c>
+      <c r="D91" s="33" t="inlineStr">
+        <is>
+          <t>Merck</t>
+        </is>
+      </c>
+      <c r="E91" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="33" t="inlineStr">
+        <is>
+          <t>McKesson Corporation Confirms Data Breach Following a Cybersecurity Incident</t>
+        </is>
+      </c>
+      <c r="G91" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H91" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I91" s="33" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="J91" s="33" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K91" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L91" s="33" t="inlineStr">
+        <is>
+          <t>RCA Shared</t>
+        </is>
+      </c>
+      <c r="M91" s="33" t="inlineStr">
+        <is>
+          <t>Entity &amp; Duplicate Decision Validation</t>
+        </is>
+      </c>
+      <c r="N91" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O91" s="33" t="inlineStr">
+        <is>
+          <t>Customer reported the missed McKesson data-breach incident. EventWatch captured the report on August 28, but human review assumed it was already covered; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+        </is>
+      </c>
+      <c r="P91" s="33" t="n"/>
+      <c r="Q91" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R91" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="S91" s="39" t="n"/>
+      <c r="T91" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="U91" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V91" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B92" s="37" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C92" s="33" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D92" s="33" t="inlineStr">
+        <is>
+          <t>Liberty Blume</t>
+        </is>
+      </c>
+      <c r="E92" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="33" t="inlineStr">
+        <is>
+          <t>Ciena 400G Optics Counterfeit Risk Intelligence Request (Liberty Blume)</t>
+        </is>
+      </c>
+      <c r="G92" s="33" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="H92" s="33" t="inlineStr">
+        <is>
+          <t>Intelligence/Advisory Request</t>
+        </is>
+      </c>
+      <c r="I92" s="33" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="J92" s="33" t="inlineStr">
         <is>
           <t>Process Clarification</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="K92" s="33" t="inlineStr">
         <is>
           <t>Improvement</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Clarification Provided</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>WarRoom trigger-criteria explanation template for post-peak activations</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
+      <c r="L92" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M92" s="33" t="inlineStr">
+        <is>
+          <t>Counterfeit/grey-market component intelligence briefing capability</t>
+        </is>
+      </c>
+      <c r="N92" s="33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-16 (Done). Eaton asked why the WarRoom for Super Typhoon Bavi (Taiwan) was activated on 9-Jul after the storm had already peaked, and what triggering criteria were used.</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
+      <c r="O92" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-32 (Open). Liberty Blume requested industry intelligence on counterfeit/grey-market Ciena 400G optical transceivers beyond the supplier scanning report already provided.</t>
+        </is>
+      </c>
+      <c r="Q92" s="33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R82" t="n">
-        <v>7</v>
-      </c>
-      <c r="T82" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="U82" t="inlineStr">
+      <c r="R92" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="T92" s="35" t="n">
+        <v>46235</v>
+      </c>
+      <c r="U92" s="33" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>EAO-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B83" s="119" t="n">
-        <v>46213</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Litigation/Legal</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Micron</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Jacobs Engineering/CH2M Hill Forced Labor Lawsuit – Missed EventWatch Notification (Micron)</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Complaint</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Missed Event</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Source Coverage</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>RCA Shared</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Legal/labor-litigation source coverage and entity-linking for supplier-adjacent lawsuits</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-17 (Done). Micron reported a forced-labor lawsuit against Jacobs Engineering/CH2M Hill was not captured in EventWatch and requested RCA if it was in scope.</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R83" t="n">
-        <v>7</v>
-      </c>
-      <c r="T83" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>EAO-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B84" s="119" t="n">
-        <v>46216</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Supply Shortage</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Western Digital</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Suspension Baseplate Supply Risk Monitoring Request (Fujita Plating/NHK/OSK)</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Inquiry</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Coverage Verification Request</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Process Clarification</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Clarification Provided</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>Supplier decommitment/capacity-risk monitoring for sub-tier component makers</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-18 (Done). Western Digital asked whether EventWatch has published or is monitoring a reported Suspension Baseplate supply risk tied to Fujita Plating/NHK/OSK decommitments; CS found no matching event in the backend.</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R84" t="n">
-        <v>7</v>
-      </c>
-      <c r="T84" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
+      <c r="V92" s="33" t="inlineStr">
         <is>
           <t>Other Control Automation</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>EAO-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B85" s="119" t="n">
-        <v>46217</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Ford</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>RFI – Power Grid Failure Monitoring Strategy</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Inquiry</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Monitoring Strategy RFI</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Process Clarification</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Clarification Provided</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>Published monitoring-scope documentation for power-grid/infrastructure failure events</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-19 (Done). Ford requested an explanation of Resilinc's monitoring strategy for power grid failure events after multiple incidents affected suppliers in the US and Europe.</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R85" t="n">
-        <v>7</v>
-      </c>
-      <c r="T85" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Other Control Automation</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>EAO-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B86" s="119" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Bankruptcy</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>ASSMANN WSW Components GmbH Bankruptcy Filing – Missed Coverage (Honeywell Tier 1 Supplier)</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Complaint</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Missed insolvency alert</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Source Coverage</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>Tier-1 supplier bankruptcy/insolvency filing source coverage expansion (EU registries)</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-20 (Done). Honeywell reported ASSMANN WSW Components GmbH's July 6 insolvency filing (a mapped Tier-1 supplier) was never published as an EventWatch bulletin or WarRoom; RCA requested.</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R86" t="n">
-        <v>7</v>
-      </c>
-      <c r="T86" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>EAO-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B87" s="119" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Wildfire</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Ford</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Severe Air Quality Degradation – Canadian Wildfires Missed Alert (Midwest/Northeast US)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Complaint</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Missed Event</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>People</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Event Identification</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>RCA Shared</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>Escalation automation for environmental-hazard advisories</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-21 (Done). Ford reported no EventWatch alert/WarRoom was generated for July 15-17 wildfire smoke air-quality degradation across the US Midwest/Northeast; CS confirmed no matching notification was found.</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R87" t="n">
-        <v>7</v>
-      </c>
-      <c r="T87" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>EAO-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B88" s="119" t="n">
-        <v>46230</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Cyber Attack</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Romania ANCPI Cyberattack – Missed EventWatch Notification</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Complaint</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Missed Event</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Source Coverage</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>RCA Shared</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>Government/public-sector cyberattack source coverage expansion (regional-language sources)</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-22 (Done). Eaton reported the July 14-16 ANCPI (Romania land registry) cyberattack had no corresponding WarRoom or news on the portal; RCA requested if it was in scope.</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R88" t="n">
-        <v>7</v>
-      </c>
-      <c r="T88" s="118" t="n">
-        <v>46204</v>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>EAO-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="118" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B89" s="119" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Factory Fire</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Complaint</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Missed Event</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Source Coverage</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>Chinese regional source coverage for sub-tier automotive lighting suppliers</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-25 (Sent to PM). GM reported a fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China (reported July 10) was not found in GM's org; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R89" t="n">
-        <v>8</v>
-      </c>
-      <c r="T89" s="118" t="n">
-        <v>46235</v>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>EAO-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="118" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B90" s="119" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Tornado</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Chicago Heights, Illinois Tornado – Trialco Impact Not Identified</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Complaint</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Missed Event</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>People</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Event Identification</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>Escalation automation for localized-impact tornado/storm sub-events and named-facility (Trialco) impact confirmation</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-25 (Sent to PM). GM reported no event was created specifically for the July 27 Chicago Heights, Illinois tornado (broader Illinois storm alerts existed) and asked whether Trialco was identified as impacted; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R90" t="n">
-        <v>8</v>
-      </c>
-      <c r="T90" s="118" t="n">
-        <v>46235</v>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>EAO-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="118" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B91" s="119" t="n">
-        <v>46251</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Transport Disruption</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Kandla Port Cargo Congestion – Supplier Impact Notification Clarification (Eaton)</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Inquiry</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Supplier Impact Mapping Clarification</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Mapping</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Clarification Provided</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>Impact-confirmation notification criteria documentation for port/logistics bulletins</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-28 (Done). Eaton asked what criteria triggered impact-confirmation notifications to Eaton suppliers on the Kandla Port cargo congestion bulletin, since the bulletin text focused on rice exports.</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R91" t="n">
-        <v>8</v>
-      </c>
-      <c r="T91" s="118" t="n">
-        <v>46235</v>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Entity &amp; Supplier Resolution</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>EAO-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="118" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B92" s="119" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Liberty Blume</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Ciena 400G Optics Counterfeit Risk Intelligence Request (Liberty Blume)</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Inquiry</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Intelligence/Advisory Request</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Process Clarification</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>Counterfeit/grey-market component intelligence briefing capability</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-32 (Open). Liberty Blume requested industry intelligence on counterfeit/grey-market Ciena 400G optical transceivers beyond the supplier scanning report already provided.</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R92" t="n">
-        <v>8</v>
-      </c>
-      <c r="T92" s="118" t="n">
-        <v>46235</v>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Other Control Automation</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
+      <c r="W92" s="33" t="inlineStr">
         <is>
           <t>EAO-32</t>
         </is>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -8731,197 +8731,197 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="35" t="n">
+    <row r="54" customFormat="1" s="29">
+      <c r="A54" s="36" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B54" s="38" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C54" s="34" t="inlineStr">
+        <is>
+          <t>Wildfire</t>
+        </is>
+      </c>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E54" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="34" t="inlineStr">
+        <is>
+          <t>Supplier Impact Mapping Clarification – Sandy Fire (Simi Valley, California, USA)</t>
+        </is>
+      </c>
+      <c r="G54" s="34" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="H54" s="34" t="inlineStr">
+        <is>
+          <t>Supplier Impact Mapping Clarification</t>
+        </is>
+      </c>
+      <c r="I54" s="34" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="J54" s="34" t="inlineStr">
+        <is>
+          <t>Mapping</t>
+        </is>
+      </c>
+      <c r="K54" s="34" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L54" s="34" t="inlineStr">
+        <is>
+          <t>Clarification Provided</t>
+        </is>
+      </c>
+      <c r="M54" s="34" t="inlineStr">
+        <is>
+          <t>Geofencing validation enhancement</t>
+        </is>
+      </c>
+      <c r="N54" s="34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O54" s="34" t="inlineStr">
+        <is>
+          <t>Customer questioned why Helium Leak Testing Inc. was mapped as impacted while Meggitt Safety Systems and Pacific Scientific were not mapped. Investigation confirmed no publicly reported evacuations, shutdowns, or operational disruptions for the Royal Ave and Voyager Ave industrial corridors. Helium Leak Testing Inc. remained within the WarRoom because the impact area had previously been expanded based on broader regional effects including wildfire smoke, reduced visibility, and air quality concerns. Geofencing methodology, supplier mapping logic, and future AI-assisted impact polygon improvements were explained to the customer.</t>
+        </is>
+      </c>
+      <c r="P54" s="34" t="inlineStr">
+        <is>
+          <t>~22.5 hours</t>
+        </is>
+      </c>
+      <c r="Q54" s="34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R54" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="S54" s="40" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="T54" s="36" t="n">
+        <v>46143</v>
+      </c>
+      <c r="U54" s="34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="V54" s="34" t="inlineStr">
+        <is>
+          <t>AI-Assisted Geofencing</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="35" t="n">
         <v>46174</v>
       </c>
-      <c r="B54" s="37" t="n">
-        <v>46177</v>
-      </c>
-      <c r="C54" s="33" t="inlineStr">
-        <is>
-          <t>Protest/Riot</t>
-        </is>
-      </c>
-      <c r="D54" s="34" t="inlineStr">
+      <c r="B55" s="37" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C55" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D55" s="33" t="inlineStr">
         <is>
           <t>Ford</t>
         </is>
       </c>
-      <c r="E54" s="39" t="n">
+      <c r="E55" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="33" t="inlineStr">
-        <is>
-          <t>ANTAC Transport Blockades in Mexico</t>
-        </is>
-      </c>
-      <c r="G54" s="33" t="inlineStr">
+      <c r="F55" s="33" t="inlineStr">
+        <is>
+          <t>CROMTRYCK s.r.o. Insolvency (Czech Republic)</t>
+        </is>
+      </c>
+      <c r="G55" s="33" t="inlineStr">
         <is>
           <t>Complaint</t>
         </is>
       </c>
-      <c r="H54" s="33" t="inlineStr">
+      <c r="H55" s="33" t="inlineStr">
         <is>
           <t>Missed Event</t>
         </is>
       </c>
-      <c r="I54" s="33" t="inlineStr">
+      <c r="I55" s="33" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="J54" s="33" t="inlineStr">
-        <is>
-          <t>Keyword Update</t>
-        </is>
-      </c>
-      <c r="K54" s="33" t="inlineStr">
+      <c r="J55" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K55" s="33" t="inlineStr">
         <is>
           <t>Improvement</t>
         </is>
       </c>
-      <c r="L54" s="33" t="inlineStr">
-        <is>
-          <t>RCA Shared</t>
-        </is>
-      </c>
-      <c r="M54" s="33" t="inlineStr">
+      <c r="L55" s="33" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="M55" s="33" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="N54" s="33" t="inlineStr">
+      <c r="N55" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O54" s="33" t="inlineStr">
-        <is>
-          <t>RCA completed; keyword gap identified and corrective actions implemented. Spanish-language detection logic did not recognize transportation disruption and protest terminology. Relevant keywords were added.</t>
-        </is>
-      </c>
-      <c r="P54" s="33" t="n"/>
-      <c r="Q54" s="33" t="inlineStr">
+      <c r="O55" s="33" t="inlineStr">
+        <is>
+          <t>Missed insolvency event due to regional insolvency source coverage limitations and restricted/paywalled source visibility. Vendor source expansion requested.</t>
+        </is>
+      </c>
+      <c r="P55" s="33" t="n"/>
+      <c r="Q55" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R54" s="39" t="n">
+      <c r="R55" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="S54" s="39" t="n"/>
-      <c r="T54" s="35" t="n">
+      <c r="S55" s="39" t="n"/>
+      <c r="T55" s="35" t="n">
         <v>46174</v>
       </c>
-      <c r="U54" s="33" t="inlineStr">
+      <c r="U55" s="33" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="V54" s="33" t="inlineStr">
+      <c r="V55" s="33" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" customFormat="1" s="29">
-      <c r="A55" s="36" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B55" s="38" t="n">
-        <v>46164</v>
-      </c>
-      <c r="C55" s="34" t="inlineStr">
-        <is>
-          <t>Wildfire</t>
-        </is>
-      </c>
-      <c r="D55" s="34" t="inlineStr">
-        <is>
-          <t>Ford</t>
-        </is>
-      </c>
-      <c r="E55" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="34" t="inlineStr">
-        <is>
-          <t>Supplier Impact Mapping Clarification – Sandy Fire (Simi Valley, California, USA)</t>
-        </is>
-      </c>
-      <c r="G55" s="34" t="inlineStr">
-        <is>
-          <t>Inquiry</t>
-        </is>
-      </c>
-      <c r="H55" s="34" t="inlineStr">
-        <is>
-          <t>Supplier Impact Mapping Clarification</t>
-        </is>
-      </c>
-      <c r="I55" s="34" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="J55" s="34" t="inlineStr">
-        <is>
-          <t>Mapping</t>
-        </is>
-      </c>
-      <c r="K55" s="34" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L55" s="34" t="inlineStr">
-        <is>
-          <t>Clarification Provided</t>
-        </is>
-      </c>
-      <c r="M55" s="34" t="inlineStr">
-        <is>
-          <t>Geofencing validation enhancement</t>
-        </is>
-      </c>
-      <c r="N55" s="34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O55" s="34" t="inlineStr">
-        <is>
-          <t>Customer questioned why Helium Leak Testing Inc. was mapped as impacted while Meggitt Safety Systems and Pacific Scientific were not mapped. Investigation confirmed no publicly reported evacuations, shutdowns, or operational disruptions for the Royal Ave and Voyager Ave industrial corridors. Helium Leak Testing Inc. remained within the WarRoom because the impact area had previously been expanded based on broader regional effects including wildfire smoke, reduced visibility, and air quality concerns. Geofencing methodology, supplier mapping logic, and future AI-assisted impact polygon improvements were explained to the customer.</t>
-        </is>
-      </c>
-      <c r="P55" s="34" t="inlineStr">
-        <is>
-          <t>~22.5 hours</t>
-        </is>
-      </c>
-      <c r="Q55" s="34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R55" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="S55" s="40" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="T55" s="36" t="n">
-        <v>46143</v>
-      </c>
-      <c r="U55" s="34" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="V55" s="34" t="inlineStr">
-        <is>
-          <t>AI-Assisted Geofencing</t>
         </is>
       </c>
     </row>
@@ -8930,14 +8930,14 @@
         <v>46174</v>
       </c>
       <c r="B56" s="37" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="C56" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
-        </is>
-      </c>
-      <c r="D56" s="33" t="inlineStr">
+          <t>Protest/Riot</t>
+        </is>
+      </c>
+      <c r="D56" s="34" t="inlineStr">
         <is>
           <t>Ford</t>
         </is>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="F56" s="33" t="inlineStr">
         <is>
-          <t>CROMTRYCK s.r.o. Insolvency (Czech Republic)</t>
+          <t>ANTAC Transport Blockades in Mexico</t>
         </is>
       </c>
       <c r="G56" s="33" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="J56" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K56" s="33" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="L56" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M56" s="33" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="O56" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency event due to regional insolvency source coverage limitations and restricted/paywalled source visibility. Vendor source expansion requested.</t>
+          <t>RCA completed; keyword gap identified and corrective actions implemented. Spanish-language detection logic did not recognize transportation disruption and protest terminology. Relevant keywords were added.</t>
         </is>
       </c>
       <c r="P56" s="33" t="n"/>
@@ -9112,7 +9112,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="W57" s="33" t="inlineStr">
         <is>
           <t>EAO-1</t>
         </is>
@@ -9211,7 +9211,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="W58" s="33" t="inlineStr">
         <is>
           <t>EAO-4</t>
         </is>
@@ -9222,16 +9222,16 @@
         <v>46174</v>
       </c>
       <c r="B59" s="37" t="n">
-        <v>46196</v>
+        <v>46188</v>
       </c>
       <c r="C59" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D59" s="33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="E59" s="39" t="n">
@@ -9239,27 +9239,27 @@
       </c>
       <c r="F59" s="33" t="inlineStr">
         <is>
-          <t>Dana Incorporated to Merge with Eaton's Mobility Business</t>
+          <t>MLCC Supply Chain Alert Related to AI Demand Growth</t>
         </is>
       </c>
       <c r="G59" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H59" s="33" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I59" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J59" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K59" s="33" t="inlineStr">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="L59" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M59" s="33" t="inlineStr">
         <is>
-          <t>Supplier relationship validation + impacted entity completeness checks</t>
+          <t>Forecast vs Event differentiation</t>
         </is>
       </c>
       <c r="N59" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O59" s="33" t="inlineStr">
         <is>
-          <t>Customer-facing RCA requested and RCA document prepared. Dana Holding Corporation was not included in impacted supplier selection during initial WarRoom creation and was subsequently added.</t>
+          <t>Article was an investment and market outlook discussing future MLCC demand and did not meet EventWatch reporting thresholds.</t>
         </is>
       </c>
       <c r="P59" s="33" t="n"/>
@@ -9307,12 +9307,12 @@
       </c>
       <c r="V59" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>EAO-6</t>
+          <t>Other Control Automation</t>
+        </is>
+      </c>
+      <c r="W59" s="33" t="inlineStr">
+        <is>
+          <t>EAO-8</t>
         </is>
       </c>
     </row>
@@ -9325,12 +9325,12 @@
       </c>
       <c r="C60" s="33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="D60" s="33" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E60" s="39" t="n">
@@ -9338,27 +9338,27 @@
       </c>
       <c r="F60" s="33" t="inlineStr">
         <is>
-          <t>Inquiry on Route Disruption – Sepone Bridge, Laos</t>
+          <t>Dana Incorporated to Merge with Eaton's Mobility Business</t>
         </is>
       </c>
       <c r="G60" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H60" s="33" t="inlineStr">
         <is>
-          <t>Customer Requested Verification</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="I60" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J60" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K60" s="33" t="inlineStr">
@@ -9368,22 +9368,22 @@
       </c>
       <c r="L60" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M60" s="33" t="inlineStr">
         <is>
-          <t>Route-risk monitoring enhancement</t>
+          <t>Supplier relationship validation + impacted entity completeness checks</t>
         </is>
       </c>
       <c r="N60" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O60" s="33" t="inlineStr">
         <is>
-          <t>Review of English and local-language sources did not identify any verified disruption, closure, or logistic impact.</t>
+          <t>Customer-facing RCA requested and RCA document prepared. Dana Holding Corporation was not included in impacted supplier selection during initial WarRoom creation and was subsequently added.</t>
         </is>
       </c>
       <c r="P60" s="33" t="n"/>
@@ -9406,12 +9406,12 @@
       </c>
       <c r="V60" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>EAO-7</t>
+          <t>Entity &amp; Supplier Resolution</t>
+        </is>
+      </c>
+      <c r="W60" s="33" t="inlineStr">
+        <is>
+          <t>EAO-6</t>
         </is>
       </c>
     </row>
@@ -9420,16 +9420,16 @@
         <v>46174</v>
       </c>
       <c r="B61" s="37" t="n">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="C61" s="33" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D61" s="33" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="E61" s="39" t="n">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F61" s="33" t="inlineStr">
         <is>
-          <t>MLCC Supply Chain Alert Related to AI Demand Growth</t>
+          <t>Inquiry on Route Disruption – Sepone Bridge, Laos</t>
         </is>
       </c>
       <c r="G61" s="33" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="H61" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Customer Requested Verification</t>
         </is>
       </c>
       <c r="I61" s="33" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="M61" s="33" t="inlineStr">
         <is>
-          <t>Forecast vs Event differentiation</t>
+          <t>Route-risk monitoring enhancement</t>
         </is>
       </c>
       <c r="N61" s="33" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="O61" s="33" t="inlineStr">
         <is>
-          <t>Article was an investment and market outlook discussing future MLCC demand and did not meet EventWatch reporting thresholds.</t>
+          <t>Review of English and local-language sources did not identify any verified disruption, closure, or logistic impact.</t>
         </is>
       </c>
       <c r="P61" s="33" t="n"/>
@@ -9508,9 +9508,9 @@
           <t>Other Control Automation</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>EAO-8</t>
+      <c r="W61" s="33" t="inlineStr">
+        <is>
+          <t>EAO-7</t>
         </is>
       </c>
     </row>
@@ -9519,16 +9519,16 @@
         <v>46174</v>
       </c>
       <c r="B62" s="37" t="n">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D62" s="33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="E62" s="39" t="n">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="F62" s="33" t="inlineStr">
         <is>
-          <t>Fire at the Isselguss GmbH Facility in Isselburg, Germany</t>
+          <t>Nidec Chaun Choung Technology Suffers Ransomware Attack</t>
         </is>
       </c>
       <c r="G62" s="33" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="I62" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J62" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K62" s="33" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="M62" s="33" t="inlineStr">
         <is>
-          <t>Entity-location-aware clustering + cluster separation validation</t>
+          <t>Supplier-aware cyber incident escalation model</t>
         </is>
       </c>
       <c r="N62" s="33" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="O62" s="33" t="inlineStr">
         <is>
-          <t>RCA PDF prepared and approved for customer sharing. Event was captured by feeds but incorrectly clustered with another unrelated factory fire in Germany, preventing separate WarRoom creation.</t>
+          <t>RCA prepared; analyst impact-assessment failure identified. Event was captured successfully but incorrectly assessed as Not Impactful during analyst review and therefore not escalated.</t>
         </is>
       </c>
       <c r="P62" s="33" t="n"/>
@@ -9604,12 +9604,12 @@
       </c>
       <c r="V62" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>EAO-9</t>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W62" s="33" t="inlineStr">
+        <is>
+          <t>EAO-10</t>
         </is>
       </c>
     </row>
@@ -9618,16 +9618,16 @@
         <v>46174</v>
       </c>
       <c r="B63" s="37" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C63" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D63" s="33" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E63" s="39" t="n">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="F63" s="33" t="inlineStr">
         <is>
-          <t>Nidec Chaun Choung Technology Suffers Ransomware Attack</t>
+          <t>Fire at the Isselguss GmbH Facility in Isselburg, Germany</t>
         </is>
       </c>
       <c r="G63" s="33" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="I63" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J63" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Event Identification</t>
         </is>
       </c>
       <c r="K63" s="33" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="M63" s="33" t="inlineStr">
         <is>
-          <t>Supplier-aware cyber incident escalation model</t>
+          <t>Entity-location-aware clustering + cluster separation validation</t>
         </is>
       </c>
       <c r="N63" s="33" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="O63" s="33" t="inlineStr">
         <is>
-          <t>RCA prepared; analyst impact-assessment failure identified. Event was captured successfully but incorrectly assessed as Not Impactful during analyst review and therefore not escalated.</t>
+          <t>RCA PDF prepared and approved for customer sharing. Event was captured by feeds but incorrectly clustered with another unrelated factory fire in Germany, preventing separate WarRoom creation.</t>
         </is>
       </c>
       <c r="P63" s="33" t="n"/>
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V63" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>EAO-10</t>
+          <t>Entity &amp; Supplier Resolution</t>
+        </is>
+      </c>
+      <c r="W63" s="33" t="inlineStr">
+        <is>
+          <t>EAO-9</t>
         </is>
       </c>
     </row>
@@ -9805,7 +9805,7 @@
           <t>AI-Assisted Geofencing</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="W64" s="33" t="inlineStr">
         <is>
           <t>EAO-5</t>
         </is>
@@ -9904,7 +9904,7 @@
           <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="W65" s="33" t="inlineStr">
         <is>
           <t>EAO-11</t>
         </is>
@@ -12555,194 +12555,194 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="118" t="n">
+      <c r="A93" s="35" t="n">
         <v>46266</v>
       </c>
-      <c r="B93" s="119" t="n">
+      <c r="B93" s="37" t="n">
         <v>46267</v>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="33" t="inlineStr">
         <is>
           <t>Geopolitical</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" s="33" t="inlineStr">
         <is>
           <t>Caterpillar</t>
         </is>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" s="33" t="inlineStr">
         <is>
           <t>Taiwan Strait Conflict Risk Assessment – Missed EventWatch Notification</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G93" s="33" t="inlineStr">
         <is>
           <t>Complaint</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H93" s="33" t="inlineStr">
         <is>
           <t>Missed Event</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I93" s="33" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J93" s="33" t="inlineStr">
         <is>
           <t>Event Identification</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="K93" s="33" t="inlineStr">
         <is>
           <t>Improvement</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="L93" s="33" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="M93" s="33" t="inlineStr">
         <is>
           <t>Geopolitical conflict risk-assessment scenario monitoring and escalation</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="N93" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="O93" s="33" t="inlineStr">
         <is>
           <t>Staged from Jira EAO-33 (In Progress). Caterpillar reported no notification for “Taiwan Strait Conflict Risk Assessment and Potential Global Supply Chain Impact”; CS found no matching event in the backend.</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="Q93" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R93" t="n">
+      <c r="R93" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="T93" s="118" t="n">
+      <c r="T93" s="35" t="n">
         <v>46266</v>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="U93" s="33" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr">
+      <c r="V93" s="33" t="inlineStr">
         <is>
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="W93" t="inlineStr">
+      <c r="W93" s="33" t="inlineStr">
         <is>
           <t>EAO-33</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="118" t="n">
+      <c r="A94" s="35" t="n">
         <v>46266</v>
       </c>
-      <c r="B94" s="119" t="n">
+      <c r="B94" s="37" t="n">
         <v>46268</v>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="33" t="inlineStr">
         <is>
           <t>Protest/Riot</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="33" t="inlineStr">
         <is>
           <t>Ford</t>
         </is>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="33" t="inlineStr">
         <is>
           <t>Western Balkans Truck Driver/EU Border Blockade – August 31 Update Missed Alert (Ford)</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G94" s="33" t="inlineStr">
         <is>
           <t>Complaint</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H94" s="33" t="inlineStr">
         <is>
           <t>Missed Event</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I94" s="33" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J94" s="33" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="K94" s="33" t="inlineStr">
         <is>
           <t>Improvement</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="L94" s="33" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="M94" s="33" t="inlineStr">
         <is>
           <t>Recurring/evolving-event WarRoom update monitoring and re-escalation detection</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="N94" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="O94" s="33" t="inlineStr">
         <is>
           <t>Staged from Jira EAO-34 (Open). Ford reported a missed alert for the August 31 update to Western Balkans/Serbia-EU border blockade disruptions; CS found the original January 2026 event but needs to confirm whether it was updated to cover this development. Related to the January 2026 Eaton row above (same underlying WarRoom, different customer/date).</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="Q94" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R94" t="n">
+      <c r="R94" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="T94" s="118" t="n">
+      <c r="T94" s="35" t="n">
         <v>46266</v>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="U94" s="33" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="V94" t="inlineStr">
+      <c r="V94" s="33" t="inlineStr">
         <is>
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="W94" t="inlineStr">
+      <c r="W94" s="33" t="inlineStr">
         <is>
           <t>EAO-34</t>
         </is>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -3337,8 +3337,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E136" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A3:E136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E137" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A3:E137"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
     <tableColumn id="2" name="Term / Field" dataDxfId="3"/>
@@ -15739,7 +15739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16384,30 +16384,30 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="30.75" customHeight="1">
+    <row r="26">
       <c r="A26" s="42" t="inlineStr">
         <is>
-          <t>Operational term</t>
+          <t>Field definition</t>
         </is>
       </c>
       <c r="B26" s="41" t="inlineStr">
         <is>
-          <t>EventWatch</t>
+          <t>Jira Key</t>
         </is>
       </c>
       <c r="C26" s="41" t="inlineStr">
         <is>
-          <t>Operational monitoring service that identifies, assesses, and reports events relevant to customers.</t>
+          <t>Atlassian issue key linking the record to the ticket that tracks it.</t>
         </is>
       </c>
       <c r="D26" s="41" t="inlineStr">
         <is>
-          <t>Common EventWatch terminology</t>
+          <t>EAO-&lt;n&gt; for the EventWatch_AI_Ops project; older records may carry DATA, TS, BI or TENAR keys. Blank where no ticket was raised.</t>
         </is>
       </c>
       <c r="E26" s="41" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>Jira Key</t>
         </is>
       </c>
     </row>
@@ -16419,12 +16419,12 @@
       </c>
       <c r="B27" s="41" t="inlineStr">
         <is>
-          <t>WarRoom</t>
+          <t>EventWatch</t>
         </is>
       </c>
       <c r="C27" s="41" t="inlineStr">
         <is>
-          <t>Central event workspace used to publish, organize, and update an operational event.</t>
+          <t>Operational monitoring service that identifies, assesses, and reports events relevant to customers.</t>
         </is>
       </c>
       <c r="D27" s="41" t="inlineStr">
@@ -16446,12 +16446,12 @@
       </c>
       <c r="B28" s="41" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>WarRoom</t>
         </is>
       </c>
       <c r="C28" s="41" t="inlineStr">
         <is>
-          <t>Root Cause Analysis; a documented explanation of why an issue occurred and the corrective/preventive actions.</t>
+          <t>Central event workspace used to publish, organize, and update an operational event.</t>
         </is>
       </c>
       <c r="D28" s="41" t="inlineStr">
@@ -16473,12 +16473,12 @@
       </c>
       <c r="B29" s="41" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="C29" s="41" t="inlineStr">
         <is>
-          <t>Non-Conformance; an internal quality record raised when required process or control performance was not met.</t>
+          <t>Root Cause Analysis; a documented explanation of why an issue occurred and the corrective/preventive actions.</t>
         </is>
       </c>
       <c r="D29" s="41" t="inlineStr">
@@ -16500,12 +16500,12 @@
       </c>
       <c r="B30" s="41" t="inlineStr">
         <is>
-          <t>Not Impactful</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
-          <t>Review outcome indicating that available evidence did not meet the threshold for EventWatch escalation.</t>
+          <t>Non-Conformance; an internal quality record raised when required process or control performance was not met.</t>
         </is>
       </c>
       <c r="D30" s="41" t="inlineStr">
@@ -16527,12 +16527,12 @@
       </c>
       <c r="B31" s="41" t="inlineStr">
         <is>
-          <t>Feed harvesting</t>
+          <t>Not Impactful</t>
         </is>
       </c>
       <c r="C31" s="41" t="inlineStr">
         <is>
-          <t>Automated collection of articles or reports from monitored information sources.</t>
+          <t>Review outcome indicating that available evidence did not meet the threshold for EventWatch escalation.</t>
         </is>
       </c>
       <c r="D31" s="41" t="inlineStr">
@@ -16554,12 +16554,12 @@
       </c>
       <c r="B32" s="41" t="inlineStr">
         <is>
-          <t>Source coverage</t>
+          <t>Feed harvesting</t>
         </is>
       </c>
       <c r="C32" s="41" t="inlineStr">
         <is>
-          <t>Availability and monitoring of relevant websites, feeds, registries, or publications.</t>
+          <t>Automated collection of articles or reports from monitored information sources.</t>
         </is>
       </c>
       <c r="D32" s="41" t="inlineStr">
@@ -16581,12 +16581,12 @@
       </c>
       <c r="B33" s="41" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Source coverage</t>
         </is>
       </c>
       <c r="C33" s="41" t="inlineStr">
         <is>
-          <t>Addition or refinement of search terms when available content was not identified correctly.</t>
+          <t>Availability and monitoring of relevant websites, feeds, registries, or publications.</t>
         </is>
       </c>
       <c r="D33" s="41" t="inlineStr">
@@ -16608,12 +16608,12 @@
       </c>
       <c r="B34" s="41" t="inlineStr">
         <is>
-          <t>Geofencing</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="C34" s="41" t="inlineStr">
         <is>
-          <t>Geographic impact logic used to associate an event area with customer or supplier locations.</t>
+          <t>Addition or refinement of search terms when available content was not identified correctly.</t>
         </is>
       </c>
       <c r="D34" s="41" t="inlineStr">
@@ -16635,12 +16635,12 @@
       </c>
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>Cluster</t>
+          <t>Geofencing</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
         <is>
-          <t>Grouping of related articles or bulletins into one event record or WarRoom.</t>
+          <t>Geographic impact logic used to associate an event area with customer or supplier locations.</t>
         </is>
       </c>
       <c r="D35" s="41" t="inlineStr">
@@ -16662,12 +16662,12 @@
       </c>
       <c r="B36" s="41" t="inlineStr">
         <is>
-          <t>Human-in-the-loop review</t>
+          <t>Cluster</t>
         </is>
       </c>
       <c r="C36" s="41" t="inlineStr">
         <is>
-          <t>Analyst review that validates automated detection and decides whether to escalate or publish.</t>
+          <t>Grouping of related articles or bulletins into one event record or WarRoom.</t>
         </is>
       </c>
       <c r="D36" s="41" t="inlineStr">
@@ -16689,12 +16689,12 @@
       </c>
       <c r="B37" s="41" t="inlineStr">
         <is>
-          <t>Impacted supplier</t>
+          <t>Human-in-the-loop review</t>
         </is>
       </c>
       <c r="C37" s="41" t="inlineStr">
         <is>
-          <t>Customer-mapped supplier assessed as potentially affected by an event.</t>
+          <t>Analyst review that validates automated detection and decides whether to escalate or publish.</t>
         </is>
       </c>
       <c r="D37" s="41" t="inlineStr">
@@ -16711,233 +16711,233 @@
     <row r="38" ht="30.75" customHeight="1">
       <c r="A38" s="42" t="inlineStr">
         <is>
+          <t>Operational term</t>
+        </is>
+      </c>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>Impacted supplier</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t>Customer-mapped supplier assessed as potentially affected by an event.</t>
+        </is>
+      </c>
+      <c r="D38" s="41" t="inlineStr">
+        <is>
+          <t>Common EventWatch terminology</t>
+        </is>
+      </c>
+      <c r="E38" s="41" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30.75" customHeight="1">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B38" s="41" t="inlineStr">
+      <c r="B39" s="41" t="inlineStr">
         <is>
           <t>Bankruptcy</t>
         </is>
       </c>
-      <c r="C38" s="41" t="inlineStr">
+      <c r="C39" s="41" t="inlineStr">
         <is>
           <t>Formal insolvency, bankruptcy filing, restructuring, or equivalent proceeding.</t>
         </is>
       </c>
-      <c r="D38" s="41" t="inlineStr">
+      <c r="D39" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E38" s="41" t="inlineStr">
+      <c r="E39" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="42" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B39" s="41" t="inlineStr">
+      <c r="B40" s="41" t="inlineStr">
         <is>
           <t>Chemical Spill</t>
         </is>
       </c>
-      <c r="C39" s="41" t="inlineStr">
+      <c r="C40" s="41" t="inlineStr">
         <is>
           <t>Release or leak of a hazardous chemical substance.</t>
         </is>
       </c>
-      <c r="D39" s="41" t="inlineStr">
+      <c r="D40" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E39" s="41" t="inlineStr">
+      <c r="E40" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30.75" customHeight="1">
-      <c r="A40" s="42" t="inlineStr">
+    <row r="41" ht="30.75" customHeight="1">
+      <c r="A41" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B40" s="41" t="inlineStr">
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>Cyber Attack</t>
         </is>
       </c>
-      <c r="C40" s="41" t="inlineStr">
+      <c r="C41" s="41" t="inlineStr">
         <is>
           <t>Cybersecurity incident such as ransomware, intrusion, compromise, or data breach.</t>
         </is>
       </c>
-      <c r="D40" s="41" t="inlineStr">
+      <c r="D41" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E40" s="41" t="inlineStr">
+      <c r="E41" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="42" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B41" s="41" t="inlineStr">
+      <c r="B42" s="41" t="inlineStr">
         <is>
           <t>Earthquake</t>
         </is>
       </c>
-      <c r="C41" s="41" t="inlineStr">
+      <c r="C42" s="41" t="inlineStr">
         <is>
           <t>Seismic event with potential operational or supply-chain impact.</t>
         </is>
       </c>
-      <c r="D41" s="41" t="inlineStr">
+      <c r="D42" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E41" s="41" t="inlineStr">
+      <c r="E42" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30.75" customHeight="1">
-      <c r="A42" s="42" t="inlineStr">
+    <row r="43" ht="30.75" customHeight="1">
+      <c r="A43" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B42" s="41" t="inlineStr">
+      <c r="B43" s="41" t="inlineStr">
         <is>
           <t>Extreme Weather</t>
         </is>
       </c>
-      <c r="C42" s="41" t="inlineStr">
+      <c r="C43" s="41" t="inlineStr">
         <is>
           <t>Severe weather such as storms, tornadoes, typhoons, flooding, or snowstorms.</t>
         </is>
       </c>
-      <c r="D42" s="41" t="inlineStr">
+      <c r="D43" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E42" s="41" t="inlineStr">
+      <c r="E43" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="42" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B43" s="41" t="inlineStr">
+      <c r="B44" s="41" t="inlineStr">
         <is>
           <t>Factory Closure</t>
         </is>
       </c>
-      <c r="C43" s="41" t="inlineStr">
+      <c r="C44" s="41" t="inlineStr">
         <is>
           <t>Planned or unplanned closure of a manufacturing facility.</t>
         </is>
       </c>
-      <c r="D43" s="41" t="inlineStr">
+      <c r="D44" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E43" s="41" t="inlineStr">
+      <c r="E44" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30.75" customHeight="1">
-      <c r="A44" s="42" t="inlineStr">
+    <row r="45" ht="30.75" customHeight="1">
+      <c r="A45" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B44" s="41" t="inlineStr">
+      <c r="B45" s="41" t="inlineStr">
         <is>
           <t>Factory Disruption</t>
         </is>
       </c>
-      <c r="C44" s="41" t="inlineStr">
+      <c r="C45" s="41" t="inlineStr">
         <is>
           <t>Operational interruption at a manufacturing facility that is not classified as closure or fire.</t>
         </is>
       </c>
-      <c r="D44" s="41" t="inlineStr">
+      <c r="D45" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E44" s="41" t="inlineStr">
+      <c r="E45" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="42" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B45" s="41" t="inlineStr">
+      <c r="B46" s="41" t="inlineStr">
         <is>
           <t>Factory Fire</t>
         </is>
       </c>
-      <c r="C45" s="41" t="inlineStr">
+      <c r="C46" s="41" t="inlineStr">
         <is>
           <t>Fire affecting a manufacturing, production, or storage facility.</t>
-        </is>
-      </c>
-      <c r="D45" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category</t>
-        </is>
-      </c>
-      <c r="E45" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30.75" customHeight="1">
-      <c r="A46" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B46" s="41" t="inlineStr">
-        <is>
-          <t>Financial Distress</t>
-        </is>
-      </c>
-      <c r="C46" s="41" t="inlineStr">
-        <is>
-          <t>Material financial difficulty that does not yet constitute a formal bankruptcy event.</t>
         </is>
       </c>
       <c r="D46" s="41" t="inlineStr">
@@ -16959,39 +16959,39 @@
       </c>
       <c r="B47" s="41" t="inlineStr">
         <is>
+          <t>Financial Distress</t>
+        </is>
+      </c>
+      <c r="C47" s="41" t="inlineStr">
+        <is>
+          <t>Material financial difficulty that does not yet constitute a formal bankruptcy event.</t>
+        </is>
+      </c>
+      <c r="D47" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category</t>
+        </is>
+      </c>
+      <c r="E47" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30.75" customHeight="1">
+      <c r="A48" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B48" s="41" t="inlineStr">
+        <is>
           <t>Geopolitical</t>
         </is>
       </c>
-      <c r="C47" s="41" t="inlineStr">
+      <c r="C48" s="41" t="inlineStr">
         <is>
           <t>Political, border, security, conflict, or humanitarian development affecting operations.</t>
-        </is>
-      </c>
-      <c r="D47" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category</t>
-        </is>
-      </c>
-      <c r="E47" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B48" s="41" t="inlineStr">
-        <is>
-          <t>Labor Disruption</t>
-        </is>
-      </c>
-      <c r="C48" s="41" t="inlineStr">
-        <is>
-          <t>Strike, work stoppage, industrial action, or labor-related disruption.</t>
         </is>
       </c>
       <c r="D48" s="41" t="inlineStr">
@@ -17013,12 +17013,12 @@
       </c>
       <c r="B49" s="41" t="inlineStr">
         <is>
-          <t>Leadership Transition</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="C49" s="41" t="inlineStr">
         <is>
-          <t>Change in senior executive or organizational leadership.</t>
+          <t>Strike, work stoppage, industrial action, or labor-related disruption.</t>
         </is>
       </c>
       <c r="D49" s="41" t="inlineStr">
@@ -17040,12 +17040,12 @@
       </c>
       <c r="B50" s="41" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Leadership Transition</t>
         </is>
       </c>
       <c r="C50" s="41" t="inlineStr">
         <is>
-          <t>Merger, acquisition, divestiture, or comparable corporate transaction.</t>
+          <t>Change in senior executive or organizational leadership.</t>
         </is>
       </c>
       <c r="D50" s="41" t="inlineStr">
@@ -17067,12 +17067,12 @@
       </c>
       <c r="B51" s="41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>No applicable event category, generally used for non-event inquiries.</t>
+          <t>Merger, acquisition, divestiture, or comparable corporate transaction.</t>
         </is>
       </c>
       <c r="D51" s="41" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="B52" s="41" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C52" s="41" t="inlineStr">
         <is>
-          <t>Demonstration, civil unrest, riot, or blockade driven by protest activity.</t>
+          <t>No applicable event category, generally used for non-event inquiries.</t>
         </is>
       </c>
       <c r="D52" s="41" t="inlineStr">
@@ -17121,93 +17121,93 @@
       </c>
       <c r="B53" s="41" t="inlineStr">
         <is>
+          <t>Protest/Riot</t>
+        </is>
+      </c>
+      <c r="C53" s="41" t="inlineStr">
+        <is>
+          <t>Demonstration, civil unrest, riot, or blockade driven by protest activity.</t>
+        </is>
+      </c>
+      <c r="D53" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category</t>
+        </is>
+      </c>
+      <c r="E53" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B54" s="41" t="inlineStr">
+        <is>
           <t>Regulatory Change</t>
         </is>
       </c>
-      <c r="C53" s="41" t="inlineStr">
+      <c r="C54" s="41" t="inlineStr">
         <is>
           <t>Government rule, sanction, export control, or regulatory action.</t>
         </is>
       </c>
-      <c r="D53" s="41" t="inlineStr">
+      <c r="D54" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E53" s="41" t="inlineStr">
+      <c r="E54" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30.75" customHeight="1">
-      <c r="A54" s="42" t="inlineStr">
+    <row r="55" ht="30.75" customHeight="1">
+      <c r="A55" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B54" s="41" t="inlineStr">
+      <c r="B55" s="41" t="inlineStr">
         <is>
           <t>Supply Shortage</t>
         </is>
       </c>
-      <c r="C54" s="41" t="inlineStr">
+      <c r="C55" s="41" t="inlineStr">
         <is>
           <t>Shortage or constrained availability of materials, components, energy, or goods.</t>
         </is>
       </c>
-      <c r="D54" s="41" t="inlineStr">
+      <c r="D55" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E54" s="41" t="inlineStr">
+      <c r="E55" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="42" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B55" s="41" t="inlineStr">
+      <c r="B56" s="41" t="inlineStr">
         <is>
           <t>Transport Disruption</t>
         </is>
       </c>
-      <c r="C55" s="41" t="inlineStr">
+      <c r="C56" s="41" t="inlineStr">
         <is>
           <t>Disruption to roads, bridges, ports, rail, air, or logistics routes.</t>
-        </is>
-      </c>
-      <c r="D55" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category</t>
-        </is>
-      </c>
-      <c r="E55" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30.75" customHeight="1">
-      <c r="A56" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B56" s="41" t="inlineStr">
-        <is>
-          <t>Wildfire</t>
-        </is>
-      </c>
-      <c r="C56" s="41" t="inlineStr">
-        <is>
-          <t>Uncontrolled vegetation fire with potential geographic or operational impact.</t>
         </is>
       </c>
       <c r="D56" s="41" t="inlineStr">
@@ -17224,27 +17224,27 @@
     <row r="57" ht="30.75" customHeight="1">
       <c r="A57" s="42" t="inlineStr">
         <is>
-          <t>Issue type</t>
+          <t>Event type</t>
         </is>
       </c>
       <c r="B57" s="41" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="C57" s="41" t="inlineStr">
         <is>
-          <t>Customer reports a service failure, miss, delay, incorrect action, or other concern.</t>
+          <t>Uncontrolled vegetation fire with potential geographic or operational impact.</t>
         </is>
       </c>
       <c r="D57" s="41" t="inlineStr">
         <is>
-          <t>Included in complaint metrics</t>
+          <t>Standard event category</t>
         </is>
       </c>
       <c r="E57" s="41" t="inlineStr">
         <is>
-          <t>Issue Type</t>
+          <t>Event type</t>
         </is>
       </c>
     </row>
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B58" s="41" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="C58" s="41" t="inlineStr">
         <is>
-          <t>Customer requests verification, explanation, or information without a confirmed service failure.</t>
+          <t>Customer reports a service failure, miss, delay, incorrect action, or other concern.</t>
         </is>
       </c>
       <c r="D58" s="41" t="inlineStr">
         <is>
-          <t>Tracked separately from complaints</t>
+          <t>Included in complaint metrics</t>
         </is>
       </c>
       <c r="E58" s="41" t="inlineStr">
@@ -17278,27 +17278,27 @@
     <row r="59" ht="30.75" customHeight="1">
       <c r="A59" s="42" t="inlineStr">
         <is>
-          <t>Root cause</t>
+          <t>Issue type</t>
         </is>
       </c>
       <c r="B59" s="41" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="C59" s="41" t="inlineStr">
         <is>
-          <t>Human judgment, review, prioritization, publishing, or execution was the primary cause.</t>
+          <t>Customer requests verification, explanation, or information without a confirmed service failure.</t>
         </is>
       </c>
       <c r="D59" s="41" t="inlineStr">
         <is>
-          <t>Primary cause domain</t>
+          <t>Tracked separately from complaints</t>
         </is>
       </c>
       <c r="E59" s="41" t="inlineStr">
         <is>
-          <t>Root Cause</t>
+          <t>Issue Type</t>
         </is>
       </c>
     </row>
@@ -17310,12 +17310,12 @@
       </c>
       <c r="B60" s="41" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="C60" s="41" t="inlineStr">
         <is>
-          <t>Policy, workflow, threshold, mapping method, or procedural design was the primary cause.</t>
+          <t>Human judgment, review, prioritization, publishing, or execution was the primary cause.</t>
         </is>
       </c>
       <c r="D60" s="41" t="inlineStr">
@@ -17337,49 +17337,49 @@
       </c>
       <c r="B61" s="41" t="inlineStr">
         <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C61" s="41" t="inlineStr">
+        <is>
+          <t>Policy, workflow, threshold, mapping method, or procedural design was the primary cause.</t>
+        </is>
+      </c>
+      <c r="D61" s="41" t="inlineStr">
+        <is>
+          <t>Primary cause domain</t>
+        </is>
+      </c>
+      <c r="E61" s="41" t="inlineStr">
+        <is>
+          <t>Root Cause</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30.75" customHeight="1">
+      <c r="A62" s="42" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+      <c r="B62" s="41" t="inlineStr">
+        <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="C61" s="41" t="inlineStr">
+      <c r="C62" s="41" t="inlineStr">
         <is>
           <t>Technology, data ingestion, source coverage, detection, clustering, or platform behavior was the primary cause.</t>
         </is>
       </c>
-      <c r="D61" s="41" t="inlineStr">
+      <c r="D62" s="41" t="inlineStr">
         <is>
           <t>Primary cause domain</t>
         </is>
       </c>
-      <c r="E61" s="41" t="inlineStr">
+      <c r="E62" s="41" t="inlineStr">
         <is>
           <t>Root Cause</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B62" s="41" t="inlineStr">
-        <is>
-          <t>Captured Late</t>
-        </is>
-      </c>
-      <c r="C62" s="41" t="inlineStr">
-        <is>
-          <t>Relevant information entered the workflow later than required.</t>
-        </is>
-      </c>
-      <c r="D62" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E62" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
         </is>
       </c>
     </row>
@@ -17391,66 +17391,66 @@
       </c>
       <c r="B63" s="41" t="inlineStr">
         <is>
+          <t>Captured Late</t>
+        </is>
+      </c>
+      <c r="C63" s="41" t="inlineStr">
+        <is>
+          <t>Relevant information entered the workflow later than required.</t>
+        </is>
+      </c>
+      <c r="D63" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E63" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B64" s="41" t="inlineStr">
+        <is>
           <t>Duplication</t>
         </is>
       </c>
-      <c r="C63" s="41" t="inlineStr">
+      <c r="C64" s="41" t="inlineStr">
         <is>
           <t>Related content was split into duplicate WarRooms or event records.</t>
         </is>
       </c>
-      <c r="D63" s="41" t="inlineStr">
+      <c r="D64" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E63" s="41" t="inlineStr">
+      <c r="E64" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="30.75" customHeight="1">
-      <c r="A64" s="42" t="inlineStr">
+    <row r="65" ht="30.75" customHeight="1">
+      <c r="A65" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B64" s="41" t="inlineStr">
+      <c r="B65" s="41" t="inlineStr">
         <is>
           <t>Event Identification</t>
         </is>
       </c>
-      <c r="C64" s="41" t="inlineStr">
+      <c r="C65" s="41" t="inlineStr">
         <is>
           <t>The relevant event was not recognized or converted into reportable coverage.</t>
-        </is>
-      </c>
-      <c r="D64" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E64" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B65" s="41" t="inlineStr">
-        <is>
-          <t>Industry selection</t>
-        </is>
-      </c>
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>An incorrect or missing industry classification affected tracking.</t>
         </is>
       </c>
       <c r="D65" s="41" t="inlineStr">
@@ -17472,66 +17472,66 @@
       </c>
       <c r="B66" s="41" t="inlineStr">
         <is>
+          <t>Industry selection</t>
+        </is>
+      </c>
+      <c r="C66" s="41" t="inlineStr">
+        <is>
+          <t>An incorrect or missing industry classification affected tracking.</t>
+        </is>
+      </c>
+      <c r="D66" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E66" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B67" s="41" t="inlineStr">
+        <is>
           <t>Keyword Update</t>
         </is>
       </c>
-      <c r="C66" s="41" t="inlineStr">
+      <c r="C67" s="41" t="inlineStr">
         <is>
           <t>Search or detection terms required addition or refinement.</t>
         </is>
       </c>
-      <c r="D66" s="41" t="inlineStr">
+      <c r="D67" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E66" s="41" t="inlineStr">
+      <c r="E67" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="30.75" customHeight="1">
-      <c r="A67" s="42" t="inlineStr">
+    <row r="68" ht="30.75" customHeight="1">
+      <c r="A68" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B67" s="41" t="inlineStr">
+      <c r="B68" s="41" t="inlineStr">
         <is>
           <t>Mapping</t>
         </is>
       </c>
-      <c r="C67" s="41" t="inlineStr">
+      <c r="C68" s="41" t="inlineStr">
         <is>
           <t>Customer, supplier, company, facility, or impact relationship was missing or incorrect.</t>
-        </is>
-      </c>
-      <c r="D67" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E67" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B68" s="41" t="inlineStr">
-        <is>
-          <t>Policy/Logic</t>
-        </is>
-      </c>
-      <c r="C68" s="41" t="inlineStr">
-        <is>
-          <t>A rule, threshold, or decision logic produced or explained the outcome.</t>
         </is>
       </c>
       <c r="D68" s="41" t="inlineStr">
@@ -17553,39 +17553,39 @@
       </c>
       <c r="B69" s="41" t="inlineStr">
         <is>
+          <t>Policy/Logic</t>
+        </is>
+      </c>
+      <c r="C69" s="41" t="inlineStr">
+        <is>
+          <t>A rule, threshold, or decision logic produced or explained the outcome.</t>
+        </is>
+      </c>
+      <c r="D69" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E69" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B70" s="41" t="inlineStr">
+        <is>
           <t>Prioritization</t>
         </is>
       </c>
-      <c r="C69" s="41" t="inlineStr">
+      <c r="C70" s="41" t="inlineStr">
         <is>
           <t>A detected item was not handled with the required urgency.</t>
-        </is>
-      </c>
-      <c r="D69" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E69" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="30.75" customHeight="1">
-      <c r="A70" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B70" s="41" t="inlineStr">
-        <is>
-          <t>Process Clarification</t>
-        </is>
-      </c>
-      <c r="C70" s="41" t="inlineStr">
-        <is>
-          <t>The case required explanation of policy, thresholds, or workflow rather than defect correction.</t>
         </is>
       </c>
       <c r="D70" s="41" t="inlineStr">
@@ -17607,93 +17607,93 @@
       </c>
       <c r="B71" s="41" t="inlineStr">
         <is>
+          <t>Process Clarification</t>
+        </is>
+      </c>
+      <c r="C71" s="41" t="inlineStr">
+        <is>
+          <t>The case required explanation of policy, thresholds, or workflow rather than defect correction.</t>
+        </is>
+      </c>
+      <c r="D71" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E71" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30.75" customHeight="1">
+      <c r="A72" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B72" s="41" t="inlineStr">
+        <is>
           <t>Relevancy</t>
         </is>
       </c>
-      <c r="C71" s="41" t="inlineStr">
+      <c r="C72" s="41" t="inlineStr">
         <is>
           <t>The item’s relevance to the customer or EventWatch scope was disputed or incorrectly assessed.</t>
         </is>
       </c>
-      <c r="D71" s="41" t="inlineStr">
+      <c r="D72" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E71" s="41" t="inlineStr">
+      <c r="E72" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="42" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B72" s="41" t="inlineStr">
+      <c r="B73" s="41" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="C72" s="41" t="inlineStr">
+      <c r="C73" s="41" t="inlineStr">
         <is>
           <t>Human assessment or quality review led to the issue.</t>
         </is>
       </c>
-      <c r="D72" s="41" t="inlineStr">
+      <c r="D73" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E72" s="41" t="inlineStr">
+      <c r="E73" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="30.75" customHeight="1">
-      <c r="A73" s="42" t="inlineStr">
+    <row r="74" ht="30.75" customHeight="1">
+      <c r="A74" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B73" s="41" t="inlineStr">
+      <c r="B74" s="41" t="inlineStr">
         <is>
           <t>Source Coverage</t>
         </is>
       </c>
-      <c r="C73" s="41" t="inlineStr">
+      <c r="C74" s="41" t="inlineStr">
         <is>
           <t>The relevant source was unavailable, unmonitored, restricted, or not harvested.</t>
-        </is>
-      </c>
-      <c r="D73" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E73" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B74" s="41" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="C74" s="41" t="inlineStr">
-        <is>
-          <t>The concern relates to reporting or consolidation strategy.</t>
         </is>
       </c>
       <c r="D74" s="41" t="inlineStr">
@@ -17715,39 +17715,39 @@
       </c>
       <c r="B75" s="41" t="inlineStr">
         <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="C75" s="41" t="inlineStr">
+        <is>
+          <t>The concern relates to reporting or consolidation strategy.</t>
+        </is>
+      </c>
+      <c r="D75" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E75" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B76" s="41" t="inlineStr">
+        <is>
           <t>Tagging</t>
         </is>
       </c>
-      <c r="C75" s="41" t="inlineStr">
+      <c r="C76" s="41" t="inlineStr">
         <is>
           <t>A required category or industry tag was missing or incorrect.</t>
-        </is>
-      </c>
-      <c r="D75" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E75" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="30.75" customHeight="1">
-      <c r="A76" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B76" s="41" t="inlineStr">
-        <is>
-          <t>Visibility</t>
-        </is>
-      </c>
-      <c r="C76" s="41" t="inlineStr">
-        <is>
-          <t>Published content was not visible because of profile, portal, notification, or display conditions.</t>
         </is>
       </c>
       <c r="D76" s="41" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="B77" s="41" t="inlineStr">
         <is>
-          <t>WarRoom Creation</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="C77" s="41" t="inlineStr">
         <is>
-          <t>A required WarRoom was not created despite available EventWatch coverage.</t>
+          <t>Published content was not visible because of profile, portal, notification, or display conditions.</t>
         </is>
       </c>
       <c r="D77" s="41" t="inlineStr">
@@ -17791,27 +17791,27 @@
     <row r="78" ht="30.75" customHeight="1">
       <c r="A78" s="42" t="inlineStr">
         <is>
-          <t>Improvement classification</t>
+          <t>Sub-type</t>
         </is>
       </c>
       <c r="B78" s="41" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>WarRoom Creation</t>
         </is>
       </c>
       <c r="C78" s="41" t="inlineStr">
         <is>
-          <t>Control, workflow, model, or monitoring enhancement rather than correction of a confirmed defect.</t>
+          <t>A required WarRoom was not created despite available EventWatch coverage.</t>
         </is>
       </c>
       <c r="D78" s="41" t="inlineStr">
         <is>
-          <t>Enhancement</t>
+          <t>Detailed cause/handling category</t>
         </is>
       </c>
       <c r="E78" s="41" t="inlineStr">
         <is>
-          <t>Improvement VS Bug</t>
+          <t>Sub-type</t>
         </is>
       </c>
     </row>
@@ -17823,49 +17823,49 @@
       </c>
       <c r="B79" s="41" t="inlineStr">
         <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="C79" s="41" t="inlineStr">
+        <is>
+          <t>Control, workflow, model, or monitoring enhancement rather than correction of a confirmed defect.</t>
+        </is>
+      </c>
+      <c r="D79" s="41" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E79" s="41" t="inlineStr">
+        <is>
+          <t>Improvement VS Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30.75" customHeight="1">
+      <c r="A80" s="42" t="inlineStr">
+        <is>
+          <t>Improvement classification</t>
+        </is>
+      </c>
+      <c r="B80" s="41" t="inlineStr">
+        <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="C79" s="41" t="inlineStr">
+      <c r="C80" s="41" t="inlineStr">
         <is>
           <t>Confirmed product or engineering defect requiring correction.</t>
         </is>
       </c>
-      <c r="D79" s="41" t="inlineStr">
+      <c r="D80" s="41" t="inlineStr">
         <is>
           <t>Defect</t>
         </is>
       </c>
-      <c r="E79" s="41" t="inlineStr">
+      <c r="E80" s="41" t="inlineStr">
         <is>
           <t>Improvement VS Bug</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="42" t="inlineStr">
-        <is>
-          <t>Fix status</t>
-        </is>
-      </c>
-      <c r="B80" s="41" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C80" s="41" t="inlineStr">
-        <is>
-          <t>Immediate corrective action was completed.</t>
-        </is>
-      </c>
-      <c r="D80" s="41" t="inlineStr">
-        <is>
-          <t>Current resolution state</t>
-        </is>
-      </c>
-      <c r="E80" s="41" t="inlineStr">
-        <is>
-          <t>Short Term Fix Status</t>
         </is>
       </c>
     </row>
@@ -17877,76 +17877,76 @@
       </c>
       <c r="B81" s="41" t="inlineStr">
         <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C81" s="41" t="inlineStr">
+        <is>
+          <t>Immediate corrective action was completed.</t>
+        </is>
+      </c>
+      <c r="D81" s="41" t="inlineStr">
+        <is>
+          <t>Current resolution state</t>
+        </is>
+      </c>
+      <c r="E81" s="41" t="inlineStr">
+        <is>
+          <t>Short Term Fix Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="42" t="inlineStr">
+        <is>
+          <t>Fix status</t>
+        </is>
+      </c>
+      <c r="B82" s="41" t="inlineStr">
+        <is>
           <t>RCA Shared</t>
         </is>
       </c>
-      <c r="C81" s="41" t="inlineStr">
+      <c r="C82" s="41" t="inlineStr">
         <is>
           <t>The root cause analysis was completed and shared with the customer.</t>
         </is>
       </c>
-      <c r="D81" s="41" t="inlineStr">
+      <c r="D82" s="41" t="inlineStr">
         <is>
           <t>Current resolution state</t>
         </is>
       </c>
-      <c r="E81" s="41" t="inlineStr">
+      <c r="E82" s="41" t="inlineStr">
         <is>
           <t>Short Term Fix Status</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="30.75" customHeight="1">
-      <c r="A82" s="42" t="inlineStr">
+    <row r="83" ht="30.75" customHeight="1">
+      <c r="A83" s="42" t="inlineStr">
         <is>
           <t>Fix status</t>
         </is>
       </c>
-      <c r="B82" s="41" t="inlineStr">
+      <c r="B83" s="41" t="inlineStr">
         <is>
           <t>Clarification Provided</t>
         </is>
       </c>
-      <c r="C82" s="41" t="inlineStr">
+      <c r="C83" s="41" t="inlineStr">
         <is>
           <t>The customer received an explanation, verification result, or policy/process clarification.</t>
         </is>
       </c>
-      <c r="D82" s="41" t="inlineStr">
+      <c r="D83" s="41" t="inlineStr">
         <is>
           <t>Current resolution state</t>
         </is>
       </c>
-      <c r="E82" s="41" t="inlineStr">
+      <c r="E83" s="41" t="inlineStr">
         <is>
           <t>Short Term Fix Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="42" t="inlineStr">
-        <is>
-          <t>Boolean flag</t>
-        </is>
-      </c>
-      <c r="B83" s="41" t="inlineStr">
-        <is>
-          <t>Yes — RCA Requested</t>
-        </is>
-      </c>
-      <c r="C83" s="41" t="inlineStr">
-        <is>
-          <t>A formal root cause analysis was requested.</t>
-        </is>
-      </c>
-      <c r="D83" s="41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E83" s="41" t="inlineStr">
-        <is>
-          <t>RCA Requested</t>
         </is>
       </c>
     </row>
@@ -17958,49 +17958,49 @@
       </c>
       <c r="B84" s="41" t="inlineStr">
         <is>
+          <t>Yes — RCA Requested</t>
+        </is>
+      </c>
+      <c r="C84" s="41" t="inlineStr">
+        <is>
+          <t>A formal root cause analysis was requested.</t>
+        </is>
+      </c>
+      <c r="D84" s="41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E84" s="41" t="inlineStr">
+        <is>
+          <t>RCA Requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="42" t="inlineStr">
+        <is>
+          <t>Boolean flag</t>
+        </is>
+      </c>
+      <c r="B85" s="41" t="inlineStr">
+        <is>
           <t>No — RCA Requested</t>
         </is>
       </c>
-      <c r="C84" s="41" t="inlineStr">
+      <c r="C85" s="41" t="inlineStr">
         <is>
           <t>No formal root cause analysis was requested.</t>
         </is>
       </c>
-      <c r="D84" s="41" t="inlineStr">
+      <c r="D85" s="41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E84" s="41" t="inlineStr">
+      <c r="E85" s="41" t="inlineStr">
         <is>
           <t>RCA Requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="30.75" customHeight="1">
-      <c r="A85" s="42" t="inlineStr">
-        <is>
-          <t>Boolean flag</t>
-        </is>
-      </c>
-      <c r="B85" s="41" t="inlineStr">
-        <is>
-          <t>Yes — Missed_Flag</t>
-        </is>
-      </c>
-      <c r="C85" s="41" t="inlineStr">
-        <is>
-          <t>Expected coverage, alerting, escalation, or WarRoom action was missed or materially delayed.</t>
-        </is>
-      </c>
-      <c r="D85" s="41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E85" s="41" t="inlineStr">
-        <is>
-          <t>Missed_Flag</t>
         </is>
       </c>
     </row>
@@ -18012,49 +18012,49 @@
       </c>
       <c r="B86" s="41" t="inlineStr">
         <is>
+          <t>Yes — Missed_Flag</t>
+        </is>
+      </c>
+      <c r="C86" s="41" t="inlineStr">
+        <is>
+          <t>Expected coverage, alerting, escalation, or WarRoom action was missed or materially delayed.</t>
+        </is>
+      </c>
+      <c r="D86" s="41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E86" s="41" t="inlineStr">
+        <is>
+          <t>Missed_Flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30.75" customHeight="1">
+      <c r="A87" s="42" t="inlineStr">
+        <is>
+          <t>Boolean flag</t>
+        </is>
+      </c>
+      <c r="B87" s="41" t="inlineStr">
+        <is>
           <t>No — Missed_Flag</t>
         </is>
       </c>
-      <c r="C86" s="41" t="inlineStr">
+      <c r="C87" s="41" t="inlineStr">
         <is>
           <t>No confirmed reporting miss; the case concerns clarification, relevancy, mapping, duplication, or another non-miss issue.</t>
         </is>
       </c>
-      <c r="D86" s="41" t="inlineStr">
+      <c r="D87" s="41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E86" s="41" t="inlineStr">
+      <c r="E87" s="41" t="inlineStr">
         <is>
           <t>Missed_Flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="42" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="B87" s="41" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C87" s="41" t="inlineStr">
-        <is>
-          <t>Material impact or priority requiring elevated management attention.</t>
-        </is>
-      </c>
-      <c r="D87" s="41" t="inlineStr">
-        <is>
-          <t>Priority level</t>
-        </is>
-      </c>
-      <c r="E87" s="41" t="inlineStr">
-        <is>
-          <t>Severity</t>
         </is>
       </c>
     </row>
@@ -18066,12 +18066,12 @@
       </c>
       <c r="B88" s="41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C88" s="41" t="inlineStr">
         <is>
-          <t>Standard operational complaint or issue requiring tracked response.</t>
+          <t>Material impact or priority requiring elevated management attention.</t>
         </is>
       </c>
       <c r="D88" s="41" t="inlineStr">
@@ -18093,12 +18093,12 @@
       </c>
       <c r="B89" s="41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C89" s="41" t="inlineStr">
         <is>
-          <t>Limited-impact inquiry or quality issue with lower operational urgency.</t>
+          <t>Standard operational complaint or issue requiring tracked response.</t>
         </is>
       </c>
       <c r="D89" s="41" t="inlineStr">
@@ -18115,27 +18115,27 @@
     <row r="90">
       <c r="A90" s="42" t="inlineStr">
         <is>
-          <t>Automation focus</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="B90" s="41" t="inlineStr">
         <is>
-          <t>AI-Assisted Geofencing</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>Automate or improve impact-area creation and location validation.</t>
+          <t>Limited-impact inquiry or quality issue with lower operational urgency.</t>
         </is>
       </c>
       <c r="D90" s="41" t="inlineStr">
         <is>
-          <t>Standardized dashboard category</t>
+          <t>Priority level</t>
         </is>
       </c>
       <c r="E90" s="41" t="inlineStr">
         <is>
-          <t>Standard Automation Focus</t>
+          <t>Severity</t>
         </is>
       </c>
     </row>
@@ -18147,93 +18147,93 @@
       </c>
       <c r="B91" s="41" t="inlineStr">
         <is>
+          <t>AI-Assisted Geofencing</t>
+        </is>
+      </c>
+      <c r="C91" s="41" t="inlineStr">
+        <is>
+          <t>Automate or improve impact-area creation and location validation.</t>
+        </is>
+      </c>
+      <c r="D91" s="41" t="inlineStr">
+        <is>
+          <t>Standardized dashboard category</t>
+        </is>
+      </c>
+      <c r="E91" s="41" t="inlineStr">
+        <is>
+          <t>Standard Automation Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="42" t="inlineStr">
+        <is>
+          <t>Automation focus</t>
+        </is>
+      </c>
+      <c r="B92" s="41" t="inlineStr">
+        <is>
           <t>Automated Industry Tagging</t>
         </is>
       </c>
-      <c r="C91" s="41" t="inlineStr">
+      <c r="C92" s="41" t="inlineStr">
         <is>
           <t>Automatically assign and validate industry classifications.</t>
         </is>
       </c>
-      <c r="D91" s="41" t="inlineStr">
+      <c r="D92" s="41" t="inlineStr">
         <is>
           <t>Standardized dashboard category</t>
         </is>
       </c>
-      <c r="E91" s="41" t="inlineStr">
+      <c r="E92" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="30.75" customHeight="1">
-      <c r="A92" s="42" t="inlineStr">
+    <row r="93" ht="30.75" customHeight="1">
+      <c r="A93" s="42" t="inlineStr">
         <is>
           <t>Automation focus</t>
         </is>
       </c>
-      <c r="B92" s="41" t="inlineStr">
+      <c r="B93" s="41" t="inlineStr">
         <is>
           <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
-      <c r="C92" s="41" t="inlineStr">
+      <c r="C93" s="41" t="inlineStr">
         <is>
           <t>Detect duplicate/split clusters and preserve one coherent event sequence.</t>
         </is>
       </c>
-      <c r="D92" s="41" t="inlineStr">
+      <c r="D93" s="41" t="inlineStr">
         <is>
           <t>Standardized dashboard category</t>
         </is>
       </c>
-      <c r="E92" s="41" t="inlineStr">
+      <c r="E93" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="42" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="42" t="inlineStr">
         <is>
           <t>Automation focus</t>
         </is>
       </c>
-      <c r="B93" s="41" t="inlineStr">
+      <c r="B94" s="41" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="C93" s="41" t="inlineStr">
+      <c r="C94" s="41" t="inlineStr">
         <is>
           <t>Identify, onboard, and monitor new or missing sources dynamically.</t>
-        </is>
-      </c>
-      <c r="D93" s="41" t="inlineStr">
-        <is>
-          <t>Standardized dashboard category</t>
-        </is>
-      </c>
-      <c r="E93" s="41" t="inlineStr">
-        <is>
-          <t>Standard Automation Focus</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="30.75" customHeight="1">
-      <c r="A94" s="42" t="inlineStr">
-        <is>
-          <t>Automation focus</t>
-        </is>
-      </c>
-      <c r="B94" s="41" t="inlineStr">
-        <is>
-          <t>Entity &amp; Supplier Resolution</t>
-        </is>
-      </c>
-      <c r="C94" s="41" t="inlineStr">
-        <is>
-          <t>Resolve company, facility, supplier, and customer relationships accurately.</t>
         </is>
       </c>
       <c r="D94" s="41" t="inlineStr">
@@ -18255,12 +18255,12 @@
       </c>
       <c r="B95" s="41" t="inlineStr">
         <is>
-          <t>Multilingual Keyword Expansion</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="C95" s="41" t="inlineStr">
         <is>
-          <t>Expand and maintain detection terms across languages and regional variations.</t>
+          <t>Resolve company, facility, supplier, and customer relationships accurately.</t>
         </is>
       </c>
       <c r="D95" s="41" t="inlineStr">
@@ -18282,66 +18282,66 @@
       </c>
       <c r="B96" s="41" t="inlineStr">
         <is>
+          <t>Multilingual Keyword Expansion</t>
+        </is>
+      </c>
+      <c r="C96" s="41" t="inlineStr">
+        <is>
+          <t>Expand and maintain detection terms across languages and regional variations.</t>
+        </is>
+      </c>
+      <c r="D96" s="41" t="inlineStr">
+        <is>
+          <t>Standardized dashboard category</t>
+        </is>
+      </c>
+      <c r="E96" s="41" t="inlineStr">
+        <is>
+          <t>Standard Automation Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30.75" customHeight="1">
+      <c r="A97" s="42" t="inlineStr">
+        <is>
+          <t>Automation focus</t>
+        </is>
+      </c>
+      <c r="B97" s="41" t="inlineStr">
+        <is>
           <t>Notification Visibility Monitoring</t>
         </is>
       </c>
-      <c r="C96" s="41" t="inlineStr">
+      <c r="C97" s="41" t="inlineStr">
         <is>
           <t>Monitor whether published alerts and WarRooms are visible and delivered to the customer.</t>
         </is>
       </c>
-      <c r="D96" s="41" t="inlineStr">
+      <c r="D97" s="41" t="inlineStr">
         <is>
           <t>Standardized dashboard category</t>
         </is>
       </c>
-      <c r="E96" s="41" t="inlineStr">
+      <c r="E97" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="42" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="42" t="inlineStr">
         <is>
           <t>Automation focus</t>
         </is>
       </c>
-      <c r="B97" s="41" t="inlineStr">
+      <c r="B98" s="41" t="inlineStr">
         <is>
           <t>Other Control Automation</t>
         </is>
       </c>
-      <c r="C97" s="41" t="inlineStr">
+      <c r="C98" s="41" t="inlineStr">
         <is>
           <t>Automation that does not fit another standardized focus category.</t>
-        </is>
-      </c>
-      <c r="D97" s="41" t="inlineStr">
-        <is>
-          <t>Standardized dashboard category</t>
-        </is>
-      </c>
-      <c r="E97" s="41" t="inlineStr">
-        <is>
-          <t>Standard Automation Focus</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30.75" customHeight="1">
-      <c r="A98" s="42" t="inlineStr">
-        <is>
-          <t>Automation focus</t>
-        </is>
-      </c>
-      <c r="B98" s="41" t="inlineStr">
-        <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="C98" s="41" t="inlineStr">
-        <is>
-          <t>Validate impact decisions, escalation, publishing, and WarRoom creation.</t>
         </is>
       </c>
       <c r="D98" s="41" t="inlineStr">
@@ -18358,27 +18358,27 @@
     <row r="99" ht="30.75" customHeight="1">
       <c r="A99" s="42" t="inlineStr">
         <is>
-          <t>Reason label</t>
+          <t>Automation focus</t>
         </is>
       </c>
       <c r="B99" s="41" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="C99" s="41" t="inlineStr">
         <is>
-          <t>Customer requested confirmation of coverage, facts, or system behavior.</t>
+          <t>Validate impact decisions, escalation, publishing, and WarRoom creation.</t>
         </is>
       </c>
       <c r="D99" s="41" t="inlineStr">
         <is>
-          <t>Use only when supported by Comments and Missed_Flag</t>
+          <t>Standardized dashboard category</t>
         </is>
       </c>
       <c r="E99" s="41" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
@@ -18390,7 +18390,7 @@
       </c>
       <c r="B100" s="41" t="inlineStr">
         <is>
-          <t>Customer Requested Verification</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="C100" s="41" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="B101" s="41" t="inlineStr">
         <is>
-          <t>Customer Terminology Preference</t>
+          <t>Customer Requested Verification</t>
         </is>
       </c>
       <c r="C101" s="41" t="inlineStr">
         <is>
-          <t>Customer requested wording or naming alignment rather than correction of a reporting failure.</t>
+          <t>Customer requested confirmation of coverage, facts, or system behavior.</t>
         </is>
       </c>
       <c r="D101" s="41" t="inlineStr">
@@ -18444,12 +18444,12 @@
       </c>
       <c r="B102" s="41" t="inlineStr">
         <is>
-          <t>Delay in creating separate WarRoom / delayed escalation</t>
+          <t>Customer Terminology Preference</t>
         </is>
       </c>
       <c r="C102" s="41" t="inlineStr">
         <is>
-          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
+          <t>Customer requested wording or naming alignment rather than correction of a reporting failure.</t>
         </is>
       </c>
       <c r="D102" s="41" t="inlineStr">
@@ -18471,7 +18471,7 @@
       </c>
       <c r="B103" s="41" t="inlineStr">
         <is>
-          <t>Delayed / Missing WarRoom</t>
+          <t>Delay in creating separate WarRoom / delayed escalation</t>
         </is>
       </c>
       <c r="C103" s="41" t="inlineStr">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="B104" s="41" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Delayed / Missing WarRoom</t>
         </is>
       </c>
       <c r="C104" s="41" t="inlineStr">
@@ -18525,7 +18525,7 @@
       </c>
       <c r="B105" s="41" t="inlineStr">
         <is>
-          <t>Delayed WarRoom</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="C105" s="41" t="inlineStr">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B106" s="41" t="inlineStr">
         <is>
-          <t>Delayed alert / WarRoom created late</t>
+          <t>Delayed WarRoom</t>
         </is>
       </c>
       <c r="C106" s="41" t="inlineStr">
@@ -18579,12 +18579,12 @@
       </c>
       <c r="B107" s="41" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms</t>
+          <t>Delayed alert / WarRoom created late</t>
         </is>
       </c>
       <c r="C107" s="41" t="inlineStr">
         <is>
-          <t>Related content was distributed across more than one WarRoom.</t>
+          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
         </is>
       </c>
       <c r="D107" s="41" t="inlineStr">
@@ -18606,12 +18606,12 @@
       </c>
       <c r="B108" s="41" t="inlineStr">
         <is>
-          <t>Event not triggered / not notified</t>
+          <t>Duplicate WarRooms</t>
         </is>
       </c>
       <c r="C108" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>Related content was distributed across more than one WarRoom.</t>
         </is>
       </c>
       <c r="D108" s="41" t="inlineStr">
@@ -18633,12 +18633,12 @@
       </c>
       <c r="B109" s="41" t="inlineStr">
         <is>
-          <t>Geographic Coverage Clarification</t>
+          <t>Event not triggered / not notified</t>
         </is>
       </c>
       <c r="C109" s="41" t="inlineStr">
         <is>
-          <t>Customer requested explanation of the geographic scope or impact-area method.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D109" s="41" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="B110" s="41" t="inlineStr">
         <is>
-          <t>Geographic Misclassification</t>
+          <t>Geographic Coverage Clarification</t>
         </is>
       </c>
       <c r="C110" s="41" t="inlineStr">
         <is>
-          <t>An event or location was assigned to an incorrect geographic impact area.</t>
+          <t>Customer requested explanation of the geographic scope or impact-area method.</t>
         </is>
       </c>
       <c r="D110" s="41" t="inlineStr">
@@ -18687,12 +18687,12 @@
       </c>
       <c r="B111" s="41" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Geographic Misclassification</t>
         </is>
       </c>
       <c r="C111" s="41" t="inlineStr">
         <is>
-          <t>A relevant mapped supplier was omitted from the impacted-supplier selection.</t>
+          <t>An event or location was assigned to an incorrect geographic impact area.</t>
         </is>
       </c>
       <c r="D111" s="41" t="inlineStr">
@@ -18714,12 +18714,12 @@
       </c>
       <c r="B112" s="41" t="inlineStr">
         <is>
-          <t>Incorrect Action</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="C112" s="41" t="inlineStr">
         <is>
-          <t>EventWatch action or handling was incorrect even though the event itself may not have been missed.</t>
+          <t>A relevant mapped supplier was omitted from the impacted-supplier selection.</t>
         </is>
       </c>
       <c r="D112" s="41" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="B113" s="41" t="inlineStr">
         <is>
-          <t>Incorrect Industry selection</t>
+          <t>Incorrect Action</t>
         </is>
       </c>
       <c r="C113" s="41" t="inlineStr">
         <is>
-          <t>The expected industry classification was missing or incorrect.</t>
+          <t>EventWatch action or handling was incorrect even though the event itself may not have been missed.</t>
         </is>
       </c>
       <c r="D113" s="41" t="inlineStr">
@@ -18768,12 +18768,12 @@
       </c>
       <c r="B114" s="41" t="inlineStr">
         <is>
-          <t>Missed + Delayed Reporting</t>
+          <t>Incorrect Industry selection</t>
         </is>
       </c>
       <c r="C114" s="41" t="inlineStr">
         <is>
-          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
+          <t>The expected industry classification was missing or incorrect.</t>
         </is>
       </c>
       <c r="D114" s="41" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="B115" s="41" t="inlineStr">
         <is>
-          <t>Missed / Delayed Event</t>
+          <t>Missed + Delayed Reporting</t>
         </is>
       </c>
       <c r="C115" s="41" t="inlineStr">
@@ -18822,12 +18822,12 @@
       </c>
       <c r="B116" s="41" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed / Delayed Event</t>
         </is>
       </c>
       <c r="C116" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
         </is>
       </c>
       <c r="D116" s="41" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="B117" s="41" t="inlineStr">
         <is>
-          <t>Missed Relevant Event</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="C117" s="41" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="B118" s="41" t="inlineStr">
         <is>
-          <t>Missed WarRoom</t>
+          <t>Missed Relevant Event</t>
         </is>
       </c>
       <c r="C118" s="41" t="inlineStr">
@@ -18903,7 +18903,7 @@
       </c>
       <c r="B119" s="41" t="inlineStr">
         <is>
-          <t>Missed WarRoom / No notification</t>
+          <t>Missed WarRoom</t>
         </is>
       </c>
       <c r="C119" s="41" t="inlineStr">
@@ -18930,7 +18930,7 @@
       </c>
       <c r="B120" s="41" t="inlineStr">
         <is>
-          <t>Missed alert / event not captured</t>
+          <t>Missed WarRoom / No notification</t>
         </is>
       </c>
       <c r="C120" s="41" t="inlineStr">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="B121" s="41" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Missed alert / event not captured</t>
         </is>
       </c>
       <c r="C121" s="41" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="B122" s="41" t="inlineStr">
         <is>
-          <t>Missed insolvency event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="C122" s="41" t="inlineStr">
@@ -19011,7 +19011,7 @@
       </c>
       <c r="B123" s="41" t="inlineStr">
         <is>
-          <t>Missed severe weather alert</t>
+          <t>Missed insolvency event</t>
         </is>
       </c>
       <c r="C123" s="41" t="inlineStr">
@@ -19038,12 +19038,12 @@
       </c>
       <c r="B124" s="41" t="inlineStr">
         <is>
-          <t>Missing Automotive industry tag (customer tracking missed it)</t>
+          <t>Missed severe weather alert</t>
         </is>
       </c>
       <c r="C124" s="41" t="inlineStr">
         <is>
-          <t>The expected industry classification was missing or incorrect.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D124" s="41" t="inlineStr">
@@ -19065,12 +19065,12 @@
       </c>
       <c r="B125" s="41" t="inlineStr">
         <is>
-          <t>Missing EventWatch coverage / feeds not captured</t>
+          <t>Missing Automotive industry tag (customer tracking missed it)</t>
         </is>
       </c>
       <c r="C125" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>The expected industry classification was missing or incorrect.</t>
         </is>
       </c>
       <c r="D125" s="41" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="B126" s="41" t="inlineStr">
         <is>
-          <t>Missing Resilinc alert / insolvency not captured</t>
+          <t>Missing EventWatch coverage / feeds not captured</t>
         </is>
       </c>
       <c r="C126" s="41" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="B127" s="41" t="inlineStr">
         <is>
-          <t>SEC notification not captured/provided on time</t>
+          <t>Missing Resilinc alert / insolvency not captured</t>
         </is>
       </c>
       <c r="C127" s="41" t="inlineStr">
         <is>
-          <t>Specific customer-reported reason recorded in the tracker.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D127" s="41" t="inlineStr">
@@ -19146,12 +19146,12 @@
       </c>
       <c r="B128" s="41" t="inlineStr">
         <is>
-          <t>Severity / consolidation handling concern</t>
+          <t>SEC notification not captured/provided on time</t>
         </is>
       </c>
       <c r="C128" s="41" t="inlineStr">
         <is>
-          <t>Customer questioned the severity level or consolidation of event coverage.</t>
+          <t>Specific customer-reported reason recorded in the tracker.</t>
         </is>
       </c>
       <c r="D128" s="41" t="inlineStr">
@@ -19173,12 +19173,12 @@
       </c>
       <c r="B129" s="41" t="inlineStr">
         <is>
-          <t>Supplier Impact Mapping Clarification</t>
+          <t>Severity / consolidation handling concern</t>
         </is>
       </c>
       <c r="C129" s="41" t="inlineStr">
         <is>
-          <t>Customer requested explanation of why suppliers were included or excluded from the impact area.</t>
+          <t>Customer questioned the severity level or consolidation of event coverage.</t>
         </is>
       </c>
       <c r="D129" s="41" t="inlineStr">
@@ -19200,12 +19200,12 @@
       </c>
       <c r="B130" s="41" t="inlineStr">
         <is>
-          <t>WarRoom not created despite nationwide disruption</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="C130" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>Customer requested explanation of why suppliers were included or excluded from the impact area.</t>
         </is>
       </c>
       <c r="D130" s="41" t="inlineStr">
@@ -19227,12 +19227,12 @@
       </c>
       <c r="B131" s="41" t="inlineStr">
         <is>
-          <t>WarRoom not visible in customer profile</t>
+          <t>WarRoom not created despite nationwide disruption</t>
         </is>
       </c>
       <c r="C131" s="41" t="inlineStr">
         <is>
-          <t>Published content was not visible in the customer profile or portal.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D131" s="41" t="inlineStr">
@@ -19254,12 +19254,12 @@
       </c>
       <c r="B132" s="41" t="inlineStr">
         <is>
-          <t>WarRoom should have been created but was not</t>
+          <t>WarRoom not visible in customer profile</t>
         </is>
       </c>
       <c r="C132" s="41" t="inlineStr">
         <is>
-          <t>Available information met the escalation criteria, but the required WarRoom was not created.</t>
+          <t>Published content was not visible in the customer profile or portal.</t>
         </is>
       </c>
       <c r="D132" s="41" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="B133" s="41" t="inlineStr">
         <is>
-          <t>WarRoom visibility affected by customer profile filters</t>
+          <t>WarRoom should have been created but was not</t>
         </is>
       </c>
       <c r="C133" s="41" t="inlineStr">
         <is>
-          <t>Published content was not visible in the customer profile or portal.</t>
+          <t>Available information met the escalation criteria, but the required WarRoom was not created.</t>
         </is>
       </c>
       <c r="D133" s="41" t="inlineStr">
@@ -19308,12 +19308,12 @@
       </c>
       <c r="B134" s="41" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>WarRoom visibility affected by customer profile filters</t>
         </is>
       </c>
       <c r="C134" s="41" t="inlineStr">
         <is>
-          <t>The relevance classification of an event or alert was disputed or incorrect.</t>
+          <t>Published content was not visible in the customer profile or portal.</t>
         </is>
       </c>
       <c r="D134" s="41" t="inlineStr">
@@ -19330,27 +19330,27 @@
     <row r="135" ht="30.75" customHeight="1">
       <c r="A135" s="42" t="inlineStr">
         <is>
-          <t>Event type</t>
+          <t>Reason label</t>
         </is>
       </c>
       <c r="B135" s="41" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="C135" s="41" t="inlineStr">
         <is>
-          <t>Tropical cyclone classified as a hurricane or typhoon, with potential geographic, operational, or supply-chain impact.</t>
+          <t>The relevance classification of an event or alert was disputed or incorrect.</t>
         </is>
       </c>
       <c r="D135" s="41" t="inlineStr">
         <is>
-          <t>Use specifically for hurricanes and typhoons rather than the broader Extreme Weather category.</t>
+          <t>Use only when supported by Comments and Missed_Flag</t>
         </is>
       </c>
       <c r="E135" s="41" t="inlineStr">
         <is>
-          <t>Event type</t>
+          <t>Reason</t>
         </is>
       </c>
     </row>
@@ -19362,20 +19362,47 @@
       </c>
       <c r="B136" s="41" t="inlineStr">
         <is>
+          <t>Hurricane/Typhoon</t>
+        </is>
+      </c>
+      <c r="C136" s="41" t="inlineStr">
+        <is>
+          <t>Tropical cyclone classified as a hurricane or typhoon, with potential geographic, operational, or supply-chain impact.</t>
+        </is>
+      </c>
+      <c r="D136" s="41" t="inlineStr">
+        <is>
+          <t>Use specifically for hurricanes and typhoons rather than the broader Extreme Weather category.</t>
+        </is>
+      </c>
+      <c r="E136" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="30.75" customHeight="1">
+      <c r="A137" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B137" s="41" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C136" s="41" t="inlineStr">
+      <c r="C137" s="41" t="inlineStr">
         <is>
           <t>Event or inquiry category that does not fit any available standardized Event type.</t>
         </is>
       </c>
-      <c r="D136" s="41" t="inlineStr">
+      <c r="D137" s="41" t="inlineStr">
         <is>
           <t>Use only when no specific standard category applies; explain the subject in the title and comments.</t>
         </is>
       </c>
-      <c r="E136" s="41" t="inlineStr">
+      <c r="E137" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1388,7 +1388,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>0</v>
+                  <v>1</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2052,7 +2052,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="2">
-                  <v>83</v>
+                  <v>84</v>
                 </pt>
                 <pt idx="3">
                   <v>8</v>
@@ -3282,8 +3282,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:W94" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
-  <autoFilter ref="A1:W94"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:W95" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="A1:W95"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Month" dataDxfId="28">
       <calculatedColumnFormula>DATE(YEAR(B2),MONTH(B2),1)</calculatedColumnFormula>
@@ -3641,7 +3641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W94"/>
+  <dimension ref="A1:W95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -12745,6 +12745,107 @@
       <c r="W94" s="33" t="inlineStr">
         <is>
           <t>EAO-34</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B95" s="37" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C95" s="33" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D95" s="33" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="E95" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="33" t="inlineStr">
+        <is>
+          <t>Supplier and Site Mapping Clarification – Punjab Region Risk Event (Eaton)</t>
+        </is>
+      </c>
+      <c r="G95" s="33" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="H95" s="33" t="inlineStr">
+        <is>
+          <t>Supplier Impact Mapping Clarification</t>
+        </is>
+      </c>
+      <c r="I95" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J95" s="33" t="inlineStr">
+        <is>
+          <t>Mapping</t>
+        </is>
+      </c>
+      <c r="K95" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L95" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M95" s="33" t="inlineStr">
+        <is>
+          <t>Supplier site geocode validation before polygon-based impact mapping, so sites outside the affected region cannot be attached to an event</t>
+        </is>
+      </c>
+      <c r="N95" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O95" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-35 (Open). Eaton queried why four Tier 1 suppliers, including a logistics partner, were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab; Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) were also attached, with Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). The geofence polygon over the affected Punjab region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of the supplier site coordinates rather than an operator or polygon error. Awaiting confirmation from the mapping-logic review.</t>
+        </is>
+      </c>
+      <c r="P95" s="33" t="n"/>
+      <c r="Q95" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R95" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S95" s="39" t="n"/>
+      <c r="T95" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U95" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V95" s="33" t="inlineStr">
+        <is>
+          <t>AI-Assisted Geofencing</t>
+        </is>
+      </c>
+      <c r="W95" s="33" t="inlineStr">
+        <is>
+          <t>EAO-35</t>
         </is>
       </c>
     </row>
@@ -14987,10 +15088,10 @@
         <v>0</v>
       </c>
       <c r="K79" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L79" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" ht="23.25" customHeight="1">
@@ -15197,10 +15298,10 @@
         <v>81</v>
       </c>
       <c r="K87" s="77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L87" s="77" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -12169,6 +12169,11 @@
           <t>Notification Visibility Monitoring</t>
         </is>
       </c>
+      <c r="W88" s="33" t="inlineStr">
+        <is>
+          <t>TS-22695</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="35" t="n">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -3282,9 +3282,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:W95" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
-  <autoFilter ref="A1:W95"/>
-  <tableColumns count="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:X95" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="A1:X95"/>
+  <tableColumns count="24">
     <tableColumn id="1" name="Month" dataDxfId="28">
       <calculatedColumnFormula>DATE(YEAR(B2),MONTH(B2),1)</calculatedColumnFormula>
     </tableColumn>
@@ -3331,14 +3331,15 @@
       <calculatedColumnFormula>IF(OR(ISNUMBER(SEARCH("keyword",M2)),ISNUMBER(SEARCH("language",M2))),"Multilingual Keyword Expansion",IF(OR(ISNUMBER(SEARCH("source",M2)),ISNUMBER(SEARCH("feed",M2)),ISNUMBER(SEARCH("vendor",M2))),"Dynamic Source Discovery",IF(OR(ISNUMBER(SEARCH("escalat",M2)),ISNUMBER(SEARCH("warroom",M2)),ISNUMBER(SEARCH("not impactful",M2)),ISNUMBER(SEARCH("priorit",M2)),ISNUMBER(SEARCH("reviewer",M2)),ISNUMBER(SEARCH("validation automation",M2))),"WarRoom &amp; Decision Validation",IF(ISNUMBER(SEARCH("tag",M2)),"Automated Industry Tagging",IF(OR(ISNUMBER(SEARCH("map",M2)),ISNUMBER(SEARCH("supplier",M2)),ISNUMBER(SEARCH("entity",M2)),ISNUMBER(SEARCH("alias",M2)),ISNUMBER(SEARCH("facility",M2)),ISNUMBER(SEARCH("company",M2))),"Entity &amp; Supplier Resolution",IF(OR(ISNUMBER(SEARCH("geo",M2)),ISNUMBER(SEARCH("location",M2))),"AI-Assisted Geofencing",IF(OR(ISNUMBER(SEARCH("duplicate",M2)),ISNUMBER(SEARCH("cluster",M2))),"Cluster Integrity &amp; Duplicate Prevention",IF(OR(ISNUMBER(SEARCH("visibility",M2)),ISNUMBER(SEARCH("notification",M2))),"Notification Visibility Monitoring",IF(OR(ISNUMBER(SEARCH("rca",M2)),ISNUMBER(SEARCH("complaint",M2)),ISNUMBER(SEARCH("process control",M2))),"RCA &amp; Workflow Automation","Other Control Automation")))))))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="23" name="Jira Key"/>
+    <tableColumn id="24" name="RCA Details"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E137" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A3:E137"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E138" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A3:E138"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
     <tableColumn id="2" name="Term / Field" dataDxfId="3"/>
@@ -3641,7 +3642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W95"/>
+  <dimension ref="A1:X95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -3770,6 +3771,11 @@
           <t>Jira Key</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>RCA Details</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="35" t="n">
@@ -3864,6 +3870,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X2" s="33" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="35" t="n">
@@ -3958,6 +3965,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X3" s="33" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="35" t="n">
@@ -4052,6 +4060,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X4" s="33" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="n">
@@ -4152,6 +4161,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X5" s="33" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="n">
@@ -4246,6 +4256,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X6" s="33" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="n">
@@ -4340,6 +4351,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X7" s="33" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="n">
@@ -4434,6 +4446,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X8" s="33" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="n">
@@ -4528,6 +4541,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X9" s="33" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="n">
@@ -4622,6 +4636,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X10" s="33" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="n">
@@ -4716,6 +4731,7 @@
           <t>Notification Visibility Monitoring</t>
         </is>
       </c>
+      <c r="X11" s="33" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="35" t="n">
@@ -4810,6 +4826,7 @@
           <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
+      <c r="X12" s="33" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="35" t="n">
@@ -4904,6 +4921,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X13" s="33" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="35" t="n">
@@ -4998,6 +5016,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X14" s="33" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="35" t="n">
@@ -5092,6 +5111,7 @@
           <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
+      <c r="X15" s="33" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="35" t="n">
@@ -5186,6 +5206,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X16" s="33" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="35" t="n">
@@ -5280,6 +5301,7 @@
           <t>Notification Visibility Monitoring</t>
         </is>
       </c>
+      <c r="X17" s="33" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="35" t="n">
@@ -5374,6 +5396,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X18" s="33" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="35" t="n">
@@ -5468,6 +5491,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X19" s="33" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="35" t="n">
@@ -5562,6 +5586,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X20" s="33" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="35" t="n">
@@ -5656,6 +5681,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X21" s="33" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="35" t="n">
@@ -5750,6 +5776,7 @@
           <t>Automated Industry Tagging</t>
         </is>
       </c>
+      <c r="X22" s="33" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="35" t="n">
@@ -5844,6 +5871,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X23" s="33" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="35" t="n">
@@ -5944,6 +5972,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X24" s="33" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="35" t="n">
@@ -6044,6 +6073,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X25" s="33" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="35" t="n">
@@ -6138,6 +6168,7 @@
           <t>Automated Industry Tagging</t>
         </is>
       </c>
+      <c r="X26" s="33" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="35" t="n">
@@ -6232,6 +6263,7 @@
           <t>AI-Assisted Geofencing</t>
         </is>
       </c>
+      <c r="X27" s="33" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="35" t="n">
@@ -6326,6 +6358,7 @@
           <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
+      <c r="X28" s="33" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="35" t="n">
@@ -6420,6 +6453,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X29" s="33" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="35" t="n">
@@ -6514,6 +6548,7 @@
           <t>Multilingual Keyword Expansion</t>
         </is>
       </c>
+      <c r="X30" s="33" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="35" t="n">
@@ -6608,6 +6643,7 @@
           <t>Multilingual Keyword Expansion</t>
         </is>
       </c>
+      <c r="X31" s="33" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="35" t="n">
@@ -6702,6 +6738,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X32" s="33" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="35" t="n">
@@ -6796,6 +6833,7 @@
           <t>AI-Assisted Geofencing</t>
         </is>
       </c>
+      <c r="X33" s="33" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="35" t="n">
@@ -6890,6 +6928,7 @@
           <t>Multilingual Keyword Expansion</t>
         </is>
       </c>
+      <c r="X34" s="33" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="35" t="n">
@@ -6990,6 +7029,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X35" s="33" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="35" t="n">
@@ -7090,6 +7130,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X36" s="33" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="35" t="n">
@@ -7190,6 +7231,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X37" s="33" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="35" t="n">
@@ -7290,6 +7332,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X38" s="33" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="35" t="n">
@@ -7384,6 +7427,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X39" s="33" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="35" t="n">
@@ -7478,6 +7522,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X40" s="33" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="35" t="n">
@@ -7572,6 +7617,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X41" s="33" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="35" t="n">
@@ -7666,6 +7712,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X42" s="33" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="35" t="n">
@@ -7760,6 +7807,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X43" s="33" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="35" t="n">
@@ -7860,6 +7908,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X44" s="33" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="35" t="n">
@@ -7960,6 +8009,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X45" s="33" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="35" t="n">
@@ -8054,6 +8104,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X46" s="33" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="35" t="n">
@@ -8148,6 +8199,7 @@
           <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
+      <c r="X47" s="33" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="35" t="n">
@@ -8242,6 +8294,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X48" s="33" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="35" t="n">
@@ -8336,6 +8389,7 @@
           <t>AI-Assisted Geofencing</t>
         </is>
       </c>
+      <c r="X49" s="33" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="35" t="n">
@@ -8436,6 +8490,7 @@
           <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
+      <c r="X50" s="33" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="35" t="n">
@@ -8536,6 +8591,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X51" s="33" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="35" t="n">
@@ -8636,6 +8692,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X52" s="33" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="35" t="n">
@@ -8730,6 +8787,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X53" s="33" t="n"/>
     </row>
     <row r="54" customFormat="1" s="29">
       <c r="A54" s="36" t="n">
@@ -8830,6 +8888,7 @@
           <t>AI-Assisted Geofencing</t>
         </is>
       </c>
+      <c r="X54" s="33" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="35" t="n">
@@ -8924,6 +8983,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X55" s="33" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="35" t="n">
@@ -9018,6 +9078,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X56" s="33" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="35" t="n">
@@ -9117,6 +9178,11 @@
           <t>EAO-1</t>
         </is>
       </c>
+      <c r="X57" s="33" t="inlineStr">
+        <is>
+          <t>Articles on the Burnstein von Seelen disruption did reach the portal, but the analyst classified the event Not Impactful and did not escalate it, so it never reached WarRoom consideration. Corrective: analyst coaching on law-enforcement, regulatory and workforce disruptions, plus an internal non-conformance raised against the reporting workflow. Preventive: extra review controls before a Not Impactful call on a monitored supplier, stronger supplier-context visibility during review, expanded audits of analyst overrides, and AI-assisted relevance work with Product/Data Science.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="35" t="n">
@@ -9216,6 +9282,11 @@
           <t>EAO-4</t>
         </is>
       </c>
+      <c r="X58" s="33" t="inlineStr">
+        <is>
+          <t>RCA approved and sent to the customer on 15-Jun-2026 as a PDF attached to EAO-4; the document text is not in the ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="35" t="n">
@@ -9315,6 +9386,7 @@
           <t>EAO-8</t>
         </is>
       </c>
+      <c r="X59" s="33" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="35" t="n">
@@ -9414,6 +9486,11 @@
           <t>EAO-6</t>
         </is>
       </c>
+      <c r="X60" s="33" t="inlineStr">
+        <is>
+          <t>The primary transaction participants were identified correctly, but Dana Holdings was omitted during the initial review of related corporate entities and supplier relationships; a WarRoom update was issued to add it. Preventive: mandatory secondary review for impacted-supplier assessments involving mergers, acquisitions, restructurings and other multi-entity transactions. RCA shared 13-Jul-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="35" t="n">
@@ -9513,6 +9590,7 @@
           <t>EAO-7</t>
         </is>
       </c>
+      <c r="X61" s="33" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="35" t="n">
@@ -9612,6 +9690,11 @@
           <t>EAO-10</t>
         </is>
       </c>
+      <c r="X62" s="33" t="inlineStr">
+        <is>
+          <t>RCA reviewed and sent to the customer as a PDF attached to EAO-10 (29-Jun-2026); the document text is not in the ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="35" t="n">
@@ -9711,6 +9794,11 @@
           <t>EAO-9</t>
         </is>
       </c>
+      <c r="X63" s="33" t="inlineStr">
+        <is>
+          <t>RCA approved and sent to the customer on 25-Jun-2026 as a PDF attached to EAO-9; the document text is not in the ticket. The WarRoom itself was published before the RCA was issued.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="35" t="n">
@@ -9810,6 +9898,7 @@
           <t>EAO-5</t>
         </is>
       </c>
+      <c r="X64" s="33" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="35" t="n">
@@ -9909,6 +9998,7 @@
           <t>EAO-11</t>
         </is>
       </c>
+      <c r="X65" s="33" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="35" t="n">
@@ -10012,6 +10102,11 @@
           <t>EAO-12</t>
         </is>
       </c>
+      <c r="X66" s="33" t="inlineStr">
+        <is>
+          <t>Feeds covering the BorgWarner Vigo indefinite strike were in the public domain from 26-Jun-2026 but were not captured on the portal until 1 July; Engineering was asked to investigate why the 26-27 June sources were missed. RCA approved and shared 09-Jul-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="35" t="n">
@@ -10111,6 +10206,7 @@
           <t>EAO-13</t>
         </is>
       </c>
+      <c r="X67" s="33" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="35" t="n">
@@ -10210,6 +10306,11 @@
           <t>EAO-14</t>
         </is>
       </c>
+      <c r="X68" s="33" t="inlineStr">
+        <is>
+          <t>RCA approved and sent to the customer on 13-Jul-2026 as a PDF attached to EAO-14; the document text is not in the ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="35" t="n">
@@ -10313,6 +10414,11 @@
           <t>EAO-15</t>
         </is>
       </c>
+      <c r="X69" s="33" t="inlineStr">
+        <is>
+          <t>The event met the Price Fluctuation reporting threshold and did qualify for a WarRoom; the failure came later, in customer-specific supplier normalization. The Samsung Electronics sites are normalized under Samsung for the affected customer, and that normalization was not applied during the impacted-site assessment, so the sites were never associated with the event and no customer WarRoom was created. This was not a parent-child modelling issue. Normalization is maintained outside the EventWatch editorial workflow, so the response is strengthened validation controls plus AI-assisted WarRoom generation rather than a guarantee. RCA shared 15-Jul-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="35" t="n">
@@ -10410,6 +10516,11 @@
           <t>EAO-16</t>
         </is>
       </c>
+      <c r="X70" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch captured multiple Philippines articles before the dedicated Philippines WarRoom was created, but they were assessed Not Impactful during reporting review, when available reports still described preparedness and localized impacts. Root cause: human assessment error underestimating the significance of the evolving Philippines impacts, which delayed WarRoom creation. Preventive: multi-country weather events assessed independently for each affected geography rather than inferred from the wider storm.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="35" t="n">
@@ -10507,6 +10618,11 @@
           <t>EAO-17</t>
         </is>
       </c>
+      <c r="X71" s="33" t="inlineStr">
+        <is>
+          <t>RCA reviewed and sent to the customer on 14-Jul-2026 as a PDF attached to EAO-17; the document text is not in the ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="35" t="n">
@@ -10604,6 +10720,7 @@
           <t>EAO-18</t>
         </is>
       </c>
+      <c r="X72" s="33" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="35" t="n">
@@ -10701,6 +10818,11 @@
           <t>EAO-19</t>
         </is>
       </c>
+      <c r="X73" s="33" t="inlineStr">
+        <is>
+          <t>Not a miss - an inquiry answered in full. EventWatch monitors power infrastructure continuously across utilities and transmission operators, government and emergency agencies, grid operators, news sources and official outage maps. Reporting is risk-based rather than every outage: mapped supplier sites in the affected region, impact on manufacturing hubs, ports, warehouses and logistics, expected outage duration, and public confirmation of operational disruption, all against regional reporting thresholds.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="35" t="n">
@@ -10798,6 +10920,11 @@
           <t>EAO-20</t>
         </is>
       </c>
+      <c r="X74" s="33" t="inlineStr">
+        <is>
+          <t>German-language sources reporting the ASSMANN WSW Components insolvency were not captured by the portal; Engineering was asked to investigate the feed gap. RCA reviewed and shared with the customer 20-Jul-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="35" t="n">
@@ -10895,6 +11022,11 @@
           <t>EAO-21</t>
         </is>
       </c>
+      <c r="X75" s="33" t="inlineStr">
+        <is>
+          <t>RCA approved and sent to the customer on 21-Jul-2026 as a PDF attached to EAO-21; the document text is not in the ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="35" t="n">
@@ -10992,6 +11124,7 @@
           <t>EAO-22</t>
         </is>
       </c>
+      <c r="X76" s="33" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="35" t="n">
@@ -11091,6 +11224,7 @@
           <t>EAO-24</t>
         </is>
       </c>
+      <c r="X77" s="33" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="35" t="n">
@@ -11188,6 +11322,11 @@
           <t>EAO-25</t>
         </is>
       </c>
+      <c r="X78" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="35" t="n">
@@ -11285,6 +11424,11 @@
           <t>EAO-25</t>
         </is>
       </c>
+      <c r="X79" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="35" t="n">
@@ -11384,6 +11528,11 @@
           <t>EAO-23</t>
         </is>
       </c>
+      <c r="X80" s="33" t="inlineStr">
+        <is>
+          <t>RCA approved and sent to the customer on 05-Aug-2026 as a PDF attached to EAO-23; the document text is not in the ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="35" t="n">
@@ -11483,6 +11632,11 @@
           <t>EAO-27</t>
         </is>
       </c>
+      <c r="X81" s="33" t="inlineStr">
+        <is>
+          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-27; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="35" t="n">
@@ -11580,6 +11734,11 @@
           <t>EAO-28</t>
         </is>
       </c>
+      <c r="X82" s="33" t="inlineStr">
+        <is>
+          <t>No RCA document issued - the team shares one only where there was a miss. Clarification given instead: EventWatch published the Kandla congestion event on reports of clearance delays up to 40 days and container shortages. The source article highlighted rice exports, but nothing indicated the congestion was confined to rice cargo, so mapped supplier sites within the impact area were sent Supplier Impact Confirmation requests as proactive validation. The outreach was not a statement that those suppliers were already impacted.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="35" t="n">
@@ -11679,6 +11838,11 @@
           <t>EAO-26</t>
         </is>
       </c>
+      <c r="X83" s="33" t="inlineStr">
+        <is>
+          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-26; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="35" t="n">
@@ -11778,6 +11942,7 @@
           <t>EAO-29</t>
         </is>
       </c>
+      <c r="X84" s="33" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="35" t="n">
@@ -11877,6 +12042,11 @@
           <t>EAO-25</t>
         </is>
       </c>
+      <c r="X85" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="35" t="n">
@@ -11976,6 +12146,11 @@
           <t>EAO-25</t>
         </is>
       </c>
+      <c r="X86" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="35" t="n">
@@ -12075,6 +12250,11 @@
           <t>EAO-25</t>
         </is>
       </c>
+      <c r="X87" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="35" t="n">
@@ -12174,6 +12354,7 @@
           <t>TS-22695</t>
         </is>
       </c>
+      <c r="X88" s="33" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="35" t="n">
@@ -12273,6 +12454,11 @@
           <t>EAO-31</t>
         </is>
       </c>
+      <c r="X89" s="33" t="inlineStr">
+        <is>
+          <t>Feeds reporting the Qilin ransomware breach at Gindre India were not captured on the EventWatch portal; Engineering investigation requested 31-Aug-2026. RCA reviewed and shared with the customer 03-Sep-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="35" t="n">
@@ -12367,6 +12553,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X90" s="33" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="35" t="n">
@@ -12461,6 +12648,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X91" s="33" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="35" t="n">
@@ -12558,6 +12746,7 @@
           <t>EAO-32</t>
         </is>
       </c>
+      <c r="X92" s="33" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="35" t="n">
@@ -12655,6 +12844,7 @@
           <t>EAO-33</t>
         </is>
       </c>
+      <c r="X93" s="33" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="35" t="n">
@@ -12752,6 +12942,7 @@
           <t>EAO-34</t>
         </is>
       </c>
+      <c r="X94" s="33" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="35" t="n">
@@ -12853,6 +13044,7 @@
           <t>EAO-35</t>
         </is>
       </c>
+      <c r="X95" s="33" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -15845,7 +16037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16517,30 +16709,30 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="30.75" customHeight="1">
+    <row r="27">
       <c r="A27" s="42" t="inlineStr">
         <is>
-          <t>Operational term</t>
+          <t>Field definition</t>
         </is>
       </c>
       <c r="B27" s="41" t="inlineStr">
         <is>
-          <t>EventWatch</t>
+          <t>RCA Details</t>
         </is>
       </c>
       <c r="C27" s="41" t="inlineStr">
         <is>
-          <t>Operational monitoring service that identifies, assesses, and reports events relevant to customers.</t>
+          <t>Root cause summary for the record, taken from the RCA shared on the linked Jira ticket.</t>
         </is>
       </c>
       <c r="D27" s="41" t="inlineStr">
         <is>
-          <t>Common EventWatch terminology</t>
+          <t>Free text. Blank where no RCA was requested or none has been issued yet. Where the RCA went out only as a PDF attachment the entry says so, rather than paraphrasing a document that is not in the ticket.</t>
         </is>
       </c>
       <c r="E27" s="41" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>RCA Details</t>
         </is>
       </c>
     </row>
@@ -16552,12 +16744,12 @@
       </c>
       <c r="B28" s="41" t="inlineStr">
         <is>
-          <t>WarRoom</t>
+          <t>EventWatch</t>
         </is>
       </c>
       <c r="C28" s="41" t="inlineStr">
         <is>
-          <t>Central event workspace used to publish, organize, and update an operational event.</t>
+          <t>Operational monitoring service that identifies, assesses, and reports events relevant to customers.</t>
         </is>
       </c>
       <c r="D28" s="41" t="inlineStr">
@@ -16579,12 +16771,12 @@
       </c>
       <c r="B29" s="41" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>WarRoom</t>
         </is>
       </c>
       <c r="C29" s="41" t="inlineStr">
         <is>
-          <t>Root Cause Analysis; a documented explanation of why an issue occurred and the corrective/preventive actions.</t>
+          <t>Central event workspace used to publish, organize, and update an operational event.</t>
         </is>
       </c>
       <c r="D29" s="41" t="inlineStr">
@@ -16606,12 +16798,12 @@
       </c>
       <c r="B30" s="41" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
-          <t>Non-Conformance; an internal quality record raised when required process or control performance was not met.</t>
+          <t>Root Cause Analysis; a documented explanation of why an issue occurred and the corrective/preventive actions.</t>
         </is>
       </c>
       <c r="D30" s="41" t="inlineStr">
@@ -16633,12 +16825,12 @@
       </c>
       <c r="B31" s="41" t="inlineStr">
         <is>
-          <t>Not Impactful</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="C31" s="41" t="inlineStr">
         <is>
-          <t>Review outcome indicating that available evidence did not meet the threshold for EventWatch escalation.</t>
+          <t>Non-Conformance; an internal quality record raised when required process or control performance was not met.</t>
         </is>
       </c>
       <c r="D31" s="41" t="inlineStr">
@@ -16660,12 +16852,12 @@
       </c>
       <c r="B32" s="41" t="inlineStr">
         <is>
-          <t>Feed harvesting</t>
+          <t>Not Impactful</t>
         </is>
       </c>
       <c r="C32" s="41" t="inlineStr">
         <is>
-          <t>Automated collection of articles or reports from monitored information sources.</t>
+          <t>Review outcome indicating that available evidence did not meet the threshold for EventWatch escalation.</t>
         </is>
       </c>
       <c r="D32" s="41" t="inlineStr">
@@ -16687,12 +16879,12 @@
       </c>
       <c r="B33" s="41" t="inlineStr">
         <is>
-          <t>Source coverage</t>
+          <t>Feed harvesting</t>
         </is>
       </c>
       <c r="C33" s="41" t="inlineStr">
         <is>
-          <t>Availability and monitoring of relevant websites, feeds, registries, or publications.</t>
+          <t>Automated collection of articles or reports from monitored information sources.</t>
         </is>
       </c>
       <c r="D33" s="41" t="inlineStr">
@@ -16714,12 +16906,12 @@
       </c>
       <c r="B34" s="41" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Source coverage</t>
         </is>
       </c>
       <c r="C34" s="41" t="inlineStr">
         <is>
-          <t>Addition or refinement of search terms when available content was not identified correctly.</t>
+          <t>Availability and monitoring of relevant websites, feeds, registries, or publications.</t>
         </is>
       </c>
       <c r="D34" s="41" t="inlineStr">
@@ -16741,12 +16933,12 @@
       </c>
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>Geofencing</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
         <is>
-          <t>Geographic impact logic used to associate an event area with customer or supplier locations.</t>
+          <t>Addition or refinement of search terms when available content was not identified correctly.</t>
         </is>
       </c>
       <c r="D35" s="41" t="inlineStr">
@@ -16768,12 +16960,12 @@
       </c>
       <c r="B36" s="41" t="inlineStr">
         <is>
-          <t>Cluster</t>
+          <t>Geofencing</t>
         </is>
       </c>
       <c r="C36" s="41" t="inlineStr">
         <is>
-          <t>Grouping of related articles or bulletins into one event record or WarRoom.</t>
+          <t>Geographic impact logic used to associate an event area with customer or supplier locations.</t>
         </is>
       </c>
       <c r="D36" s="41" t="inlineStr">
@@ -16795,12 +16987,12 @@
       </c>
       <c r="B37" s="41" t="inlineStr">
         <is>
-          <t>Human-in-the-loop review</t>
+          <t>Cluster</t>
         </is>
       </c>
       <c r="C37" s="41" t="inlineStr">
         <is>
-          <t>Analyst review that validates automated detection and decides whether to escalate or publish.</t>
+          <t>Grouping of related articles or bulletins into one event record or WarRoom.</t>
         </is>
       </c>
       <c r="D37" s="41" t="inlineStr">
@@ -16822,12 +17014,12 @@
       </c>
       <c r="B38" s="41" t="inlineStr">
         <is>
-          <t>Impacted supplier</t>
+          <t>Human-in-the-loop review</t>
         </is>
       </c>
       <c r="C38" s="41" t="inlineStr">
         <is>
-          <t>Customer-mapped supplier assessed as potentially affected by an event.</t>
+          <t>Analyst review that validates automated detection and decides whether to escalate or publish.</t>
         </is>
       </c>
       <c r="D38" s="41" t="inlineStr">
@@ -16844,233 +17036,233 @@
     <row r="39" ht="30.75" customHeight="1">
       <c r="A39" s="42" t="inlineStr">
         <is>
+          <t>Operational term</t>
+        </is>
+      </c>
+      <c r="B39" s="41" t="inlineStr">
+        <is>
+          <t>Impacted supplier</t>
+        </is>
+      </c>
+      <c r="C39" s="41" t="inlineStr">
+        <is>
+          <t>Customer-mapped supplier assessed as potentially affected by an event.</t>
+        </is>
+      </c>
+      <c r="D39" s="41" t="inlineStr">
+        <is>
+          <t>Common EventWatch terminology</t>
+        </is>
+      </c>
+      <c r="E39" s="41" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30.75" customHeight="1">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B39" s="41" t="inlineStr">
+      <c r="B40" s="41" t="inlineStr">
         <is>
           <t>Bankruptcy</t>
         </is>
       </c>
-      <c r="C39" s="41" t="inlineStr">
+      <c r="C40" s="41" t="inlineStr">
         <is>
           <t>Formal insolvency, bankruptcy filing, restructuring, or equivalent proceeding.</t>
         </is>
       </c>
-      <c r="D39" s="41" t="inlineStr">
+      <c r="D40" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E39" s="41" t="inlineStr">
+      <c r="E40" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="42" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B40" s="41" t="inlineStr">
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>Chemical Spill</t>
         </is>
       </c>
-      <c r="C40" s="41" t="inlineStr">
+      <c r="C41" s="41" t="inlineStr">
         <is>
           <t>Release or leak of a hazardous chemical substance.</t>
         </is>
       </c>
-      <c r="D40" s="41" t="inlineStr">
+      <c r="D41" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E40" s="41" t="inlineStr">
+      <c r="E41" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30.75" customHeight="1">
-      <c r="A41" s="42" t="inlineStr">
+    <row r="42" ht="30.75" customHeight="1">
+      <c r="A42" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B41" s="41" t="inlineStr">
+      <c r="B42" s="41" t="inlineStr">
         <is>
           <t>Cyber Attack</t>
         </is>
       </c>
-      <c r="C41" s="41" t="inlineStr">
+      <c r="C42" s="41" t="inlineStr">
         <is>
           <t>Cybersecurity incident such as ransomware, intrusion, compromise, or data breach.</t>
         </is>
       </c>
-      <c r="D41" s="41" t="inlineStr">
+      <c r="D42" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E41" s="41" t="inlineStr">
+      <c r="E42" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="42" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B42" s="41" t="inlineStr">
+      <c r="B43" s="41" t="inlineStr">
         <is>
           <t>Earthquake</t>
         </is>
       </c>
-      <c r="C42" s="41" t="inlineStr">
+      <c r="C43" s="41" t="inlineStr">
         <is>
           <t>Seismic event with potential operational or supply-chain impact.</t>
         </is>
       </c>
-      <c r="D42" s="41" t="inlineStr">
+      <c r="D43" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E42" s="41" t="inlineStr">
+      <c r="E43" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30.75" customHeight="1">
-      <c r="A43" s="42" t="inlineStr">
+    <row r="44" ht="30.75" customHeight="1">
+      <c r="A44" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B43" s="41" t="inlineStr">
+      <c r="B44" s="41" t="inlineStr">
         <is>
           <t>Extreme Weather</t>
         </is>
       </c>
-      <c r="C43" s="41" t="inlineStr">
+      <c r="C44" s="41" t="inlineStr">
         <is>
           <t>Severe weather such as storms, tornadoes, typhoons, flooding, or snowstorms.</t>
         </is>
       </c>
-      <c r="D43" s="41" t="inlineStr">
+      <c r="D44" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E43" s="41" t="inlineStr">
+      <c r="E44" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="42" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B44" s="41" t="inlineStr">
+      <c r="B45" s="41" t="inlineStr">
         <is>
           <t>Factory Closure</t>
         </is>
       </c>
-      <c r="C44" s="41" t="inlineStr">
+      <c r="C45" s="41" t="inlineStr">
         <is>
           <t>Planned or unplanned closure of a manufacturing facility.</t>
         </is>
       </c>
-      <c r="D44" s="41" t="inlineStr">
+      <c r="D45" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E44" s="41" t="inlineStr">
+      <c r="E45" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30.75" customHeight="1">
-      <c r="A45" s="42" t="inlineStr">
+    <row r="46" ht="30.75" customHeight="1">
+      <c r="A46" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B45" s="41" t="inlineStr">
+      <c r="B46" s="41" t="inlineStr">
         <is>
           <t>Factory Disruption</t>
         </is>
       </c>
-      <c r="C45" s="41" t="inlineStr">
+      <c r="C46" s="41" t="inlineStr">
         <is>
           <t>Operational interruption at a manufacturing facility that is not classified as closure or fire.</t>
         </is>
       </c>
-      <c r="D45" s="41" t="inlineStr">
+      <c r="D46" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E45" s="41" t="inlineStr">
+      <c r="E46" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="42" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B46" s="41" t="inlineStr">
+      <c r="B47" s="41" t="inlineStr">
         <is>
           <t>Factory Fire</t>
         </is>
       </c>
-      <c r="C46" s="41" t="inlineStr">
+      <c r="C47" s="41" t="inlineStr">
         <is>
           <t>Fire affecting a manufacturing, production, or storage facility.</t>
-        </is>
-      </c>
-      <c r="D46" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category</t>
-        </is>
-      </c>
-      <c r="E46" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30.75" customHeight="1">
-      <c r="A47" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B47" s="41" t="inlineStr">
-        <is>
-          <t>Financial Distress</t>
-        </is>
-      </c>
-      <c r="C47" s="41" t="inlineStr">
-        <is>
-          <t>Material financial difficulty that does not yet constitute a formal bankruptcy event.</t>
         </is>
       </c>
       <c r="D47" s="41" t="inlineStr">
@@ -17092,39 +17284,39 @@
       </c>
       <c r="B48" s="41" t="inlineStr">
         <is>
+          <t>Financial Distress</t>
+        </is>
+      </c>
+      <c r="C48" s="41" t="inlineStr">
+        <is>
+          <t>Material financial difficulty that does not yet constitute a formal bankruptcy event.</t>
+        </is>
+      </c>
+      <c r="D48" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category</t>
+        </is>
+      </c>
+      <c r="E48" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30.75" customHeight="1">
+      <c r="A49" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B49" s="41" t="inlineStr">
+        <is>
           <t>Geopolitical</t>
         </is>
       </c>
-      <c r="C48" s="41" t="inlineStr">
+      <c r="C49" s="41" t="inlineStr">
         <is>
           <t>Political, border, security, conflict, or humanitarian development affecting operations.</t>
-        </is>
-      </c>
-      <c r="D48" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category</t>
-        </is>
-      </c>
-      <c r="E48" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B49" s="41" t="inlineStr">
-        <is>
-          <t>Labor Disruption</t>
-        </is>
-      </c>
-      <c r="C49" s="41" t="inlineStr">
-        <is>
-          <t>Strike, work stoppage, industrial action, or labor-related disruption.</t>
         </is>
       </c>
       <c r="D49" s="41" t="inlineStr">
@@ -17146,12 +17338,12 @@
       </c>
       <c r="B50" s="41" t="inlineStr">
         <is>
-          <t>Leadership Transition</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="C50" s="41" t="inlineStr">
         <is>
-          <t>Change in senior executive or organizational leadership.</t>
+          <t>Strike, work stoppage, industrial action, or labor-related disruption.</t>
         </is>
       </c>
       <c r="D50" s="41" t="inlineStr">
@@ -17173,12 +17365,12 @@
       </c>
       <c r="B51" s="41" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Leadership Transition</t>
         </is>
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>Merger, acquisition, divestiture, or comparable corporate transaction.</t>
+          <t>Change in senior executive or organizational leadership.</t>
         </is>
       </c>
       <c r="D51" s="41" t="inlineStr">
@@ -17200,12 +17392,12 @@
       </c>
       <c r="B52" s="41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="C52" s="41" t="inlineStr">
         <is>
-          <t>No applicable event category, generally used for non-event inquiries.</t>
+          <t>Merger, acquisition, divestiture, or comparable corporate transaction.</t>
         </is>
       </c>
       <c r="D52" s="41" t="inlineStr">
@@ -17227,12 +17419,12 @@
       </c>
       <c r="B53" s="41" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C53" s="41" t="inlineStr">
         <is>
-          <t>Demonstration, civil unrest, riot, or blockade driven by protest activity.</t>
+          <t>No applicable event category, generally used for non-event inquiries.</t>
         </is>
       </c>
       <c r="D53" s="41" t="inlineStr">
@@ -17254,93 +17446,93 @@
       </c>
       <c r="B54" s="41" t="inlineStr">
         <is>
+          <t>Protest/Riot</t>
+        </is>
+      </c>
+      <c r="C54" s="41" t="inlineStr">
+        <is>
+          <t>Demonstration, civil unrest, riot, or blockade driven by protest activity.</t>
+        </is>
+      </c>
+      <c r="D54" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category</t>
+        </is>
+      </c>
+      <c r="E54" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B55" s="41" t="inlineStr">
+        <is>
           <t>Regulatory Change</t>
         </is>
       </c>
-      <c r="C54" s="41" t="inlineStr">
+      <c r="C55" s="41" t="inlineStr">
         <is>
           <t>Government rule, sanction, export control, or regulatory action.</t>
         </is>
       </c>
-      <c r="D54" s="41" t="inlineStr">
+      <c r="D55" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E54" s="41" t="inlineStr">
+      <c r="E55" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="30.75" customHeight="1">
-      <c r="A55" s="42" t="inlineStr">
+    <row r="56" ht="30.75" customHeight="1">
+      <c r="A56" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B55" s="41" t="inlineStr">
+      <c r="B56" s="41" t="inlineStr">
         <is>
           <t>Supply Shortage</t>
         </is>
       </c>
-      <c r="C55" s="41" t="inlineStr">
+      <c r="C56" s="41" t="inlineStr">
         <is>
           <t>Shortage or constrained availability of materials, components, energy, or goods.</t>
         </is>
       </c>
-      <c r="D55" s="41" t="inlineStr">
+      <c r="D56" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E55" s="41" t="inlineStr">
+      <c r="E56" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="42" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B56" s="41" t="inlineStr">
+      <c r="B57" s="41" t="inlineStr">
         <is>
           <t>Transport Disruption</t>
         </is>
       </c>
-      <c r="C56" s="41" t="inlineStr">
+      <c r="C57" s="41" t="inlineStr">
         <is>
           <t>Disruption to roads, bridges, ports, rail, air, or logistics routes.</t>
-        </is>
-      </c>
-      <c r="D56" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category</t>
-        </is>
-      </c>
-      <c r="E56" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30.75" customHeight="1">
-      <c r="A57" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B57" s="41" t="inlineStr">
-        <is>
-          <t>Wildfire</t>
-        </is>
-      </c>
-      <c r="C57" s="41" t="inlineStr">
-        <is>
-          <t>Uncontrolled vegetation fire with potential geographic or operational impact.</t>
         </is>
       </c>
       <c r="D57" s="41" t="inlineStr">
@@ -17357,27 +17549,27 @@
     <row r="58" ht="30.75" customHeight="1">
       <c r="A58" s="42" t="inlineStr">
         <is>
-          <t>Issue type</t>
+          <t>Event type</t>
         </is>
       </c>
       <c r="B58" s="41" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="C58" s="41" t="inlineStr">
         <is>
-          <t>Customer reports a service failure, miss, delay, incorrect action, or other concern.</t>
+          <t>Uncontrolled vegetation fire with potential geographic or operational impact.</t>
         </is>
       </c>
       <c r="D58" s="41" t="inlineStr">
         <is>
-          <t>Included in complaint metrics</t>
+          <t>Standard event category</t>
         </is>
       </c>
       <c r="E58" s="41" t="inlineStr">
         <is>
-          <t>Issue Type</t>
+          <t>Event type</t>
         </is>
       </c>
     </row>
@@ -17389,17 +17581,17 @@
       </c>
       <c r="B59" s="41" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="C59" s="41" t="inlineStr">
         <is>
-          <t>Customer requests verification, explanation, or information without a confirmed service failure.</t>
+          <t>Customer reports a service failure, miss, delay, incorrect action, or other concern.</t>
         </is>
       </c>
       <c r="D59" s="41" t="inlineStr">
         <is>
-          <t>Tracked separately from complaints</t>
+          <t>Included in complaint metrics</t>
         </is>
       </c>
       <c r="E59" s="41" t="inlineStr">
@@ -17411,27 +17603,27 @@
     <row r="60" ht="30.75" customHeight="1">
       <c r="A60" s="42" t="inlineStr">
         <is>
-          <t>Root cause</t>
+          <t>Issue type</t>
         </is>
       </c>
       <c r="B60" s="41" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="C60" s="41" t="inlineStr">
         <is>
-          <t>Human judgment, review, prioritization, publishing, or execution was the primary cause.</t>
+          <t>Customer requests verification, explanation, or information without a confirmed service failure.</t>
         </is>
       </c>
       <c r="D60" s="41" t="inlineStr">
         <is>
-          <t>Primary cause domain</t>
+          <t>Tracked separately from complaints</t>
         </is>
       </c>
       <c r="E60" s="41" t="inlineStr">
         <is>
-          <t>Root Cause</t>
+          <t>Issue Type</t>
         </is>
       </c>
     </row>
@@ -17443,12 +17635,12 @@
       </c>
       <c r="B61" s="41" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="C61" s="41" t="inlineStr">
         <is>
-          <t>Policy, workflow, threshold, mapping method, or procedural design was the primary cause.</t>
+          <t>Human judgment, review, prioritization, publishing, or execution was the primary cause.</t>
         </is>
       </c>
       <c r="D61" s="41" t="inlineStr">
@@ -17470,49 +17662,49 @@
       </c>
       <c r="B62" s="41" t="inlineStr">
         <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C62" s="41" t="inlineStr">
+        <is>
+          <t>Policy, workflow, threshold, mapping method, or procedural design was the primary cause.</t>
+        </is>
+      </c>
+      <c r="D62" s="41" t="inlineStr">
+        <is>
+          <t>Primary cause domain</t>
+        </is>
+      </c>
+      <c r="E62" s="41" t="inlineStr">
+        <is>
+          <t>Root Cause</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30.75" customHeight="1">
+      <c r="A63" s="42" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+      <c r="B63" s="41" t="inlineStr">
+        <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="C62" s="41" t="inlineStr">
+      <c r="C63" s="41" t="inlineStr">
         <is>
           <t>Technology, data ingestion, source coverage, detection, clustering, or platform behavior was the primary cause.</t>
         </is>
       </c>
-      <c r="D62" s="41" t="inlineStr">
+      <c r="D63" s="41" t="inlineStr">
         <is>
           <t>Primary cause domain</t>
         </is>
       </c>
-      <c r="E62" s="41" t="inlineStr">
+      <c r="E63" s="41" t="inlineStr">
         <is>
           <t>Root Cause</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B63" s="41" t="inlineStr">
-        <is>
-          <t>Captured Late</t>
-        </is>
-      </c>
-      <c r="C63" s="41" t="inlineStr">
-        <is>
-          <t>Relevant information entered the workflow later than required.</t>
-        </is>
-      </c>
-      <c r="D63" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E63" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
         </is>
       </c>
     </row>
@@ -17524,66 +17716,66 @@
       </c>
       <c r="B64" s="41" t="inlineStr">
         <is>
+          <t>Captured Late</t>
+        </is>
+      </c>
+      <c r="C64" s="41" t="inlineStr">
+        <is>
+          <t>Relevant information entered the workflow later than required.</t>
+        </is>
+      </c>
+      <c r="D64" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E64" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B65" s="41" t="inlineStr">
+        <is>
           <t>Duplication</t>
         </is>
       </c>
-      <c r="C64" s="41" t="inlineStr">
+      <c r="C65" s="41" t="inlineStr">
         <is>
           <t>Related content was split into duplicate WarRooms or event records.</t>
         </is>
       </c>
-      <c r="D64" s="41" t="inlineStr">
+      <c r="D65" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E64" s="41" t="inlineStr">
+      <c r="E65" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="30.75" customHeight="1">
-      <c r="A65" s="42" t="inlineStr">
+    <row r="66" ht="30.75" customHeight="1">
+      <c r="A66" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B65" s="41" t="inlineStr">
+      <c r="B66" s="41" t="inlineStr">
         <is>
           <t>Event Identification</t>
         </is>
       </c>
-      <c r="C65" s="41" t="inlineStr">
+      <c r="C66" s="41" t="inlineStr">
         <is>
           <t>The relevant event was not recognized or converted into reportable coverage.</t>
-        </is>
-      </c>
-      <c r="D65" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E65" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B66" s="41" t="inlineStr">
-        <is>
-          <t>Industry selection</t>
-        </is>
-      </c>
-      <c r="C66" s="41" t="inlineStr">
-        <is>
-          <t>An incorrect or missing industry classification affected tracking.</t>
         </is>
       </c>
       <c r="D66" s="41" t="inlineStr">
@@ -17605,66 +17797,66 @@
       </c>
       <c r="B67" s="41" t="inlineStr">
         <is>
+          <t>Industry selection</t>
+        </is>
+      </c>
+      <c r="C67" s="41" t="inlineStr">
+        <is>
+          <t>An incorrect or missing industry classification affected tracking.</t>
+        </is>
+      </c>
+      <c r="D67" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E67" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B68" s="41" t="inlineStr">
+        <is>
           <t>Keyword Update</t>
         </is>
       </c>
-      <c r="C67" s="41" t="inlineStr">
+      <c r="C68" s="41" t="inlineStr">
         <is>
           <t>Search or detection terms required addition or refinement.</t>
         </is>
       </c>
-      <c r="D67" s="41" t="inlineStr">
+      <c r="D68" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E67" s="41" t="inlineStr">
+      <c r="E68" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="30.75" customHeight="1">
-      <c r="A68" s="42" t="inlineStr">
+    <row r="69" ht="30.75" customHeight="1">
+      <c r="A69" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B68" s="41" t="inlineStr">
+      <c r="B69" s="41" t="inlineStr">
         <is>
           <t>Mapping</t>
         </is>
       </c>
-      <c r="C68" s="41" t="inlineStr">
+      <c r="C69" s="41" t="inlineStr">
         <is>
           <t>Customer, supplier, company, facility, or impact relationship was missing or incorrect.</t>
-        </is>
-      </c>
-      <c r="D68" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E68" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B69" s="41" t="inlineStr">
-        <is>
-          <t>Policy/Logic</t>
-        </is>
-      </c>
-      <c r="C69" s="41" t="inlineStr">
-        <is>
-          <t>A rule, threshold, or decision logic produced or explained the outcome.</t>
         </is>
       </c>
       <c r="D69" s="41" t="inlineStr">
@@ -17686,39 +17878,39 @@
       </c>
       <c r="B70" s="41" t="inlineStr">
         <is>
+          <t>Policy/Logic</t>
+        </is>
+      </c>
+      <c r="C70" s="41" t="inlineStr">
+        <is>
+          <t>A rule, threshold, or decision logic produced or explained the outcome.</t>
+        </is>
+      </c>
+      <c r="D70" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E70" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B71" s="41" t="inlineStr">
+        <is>
           <t>Prioritization</t>
         </is>
       </c>
-      <c r="C70" s="41" t="inlineStr">
+      <c r="C71" s="41" t="inlineStr">
         <is>
           <t>A detected item was not handled with the required urgency.</t>
-        </is>
-      </c>
-      <c r="D70" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E70" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="30.75" customHeight="1">
-      <c r="A71" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B71" s="41" t="inlineStr">
-        <is>
-          <t>Process Clarification</t>
-        </is>
-      </c>
-      <c r="C71" s="41" t="inlineStr">
-        <is>
-          <t>The case required explanation of policy, thresholds, or workflow rather than defect correction.</t>
         </is>
       </c>
       <c r="D71" s="41" t="inlineStr">
@@ -17740,93 +17932,93 @@
       </c>
       <c r="B72" s="41" t="inlineStr">
         <is>
+          <t>Process Clarification</t>
+        </is>
+      </c>
+      <c r="C72" s="41" t="inlineStr">
+        <is>
+          <t>The case required explanation of policy, thresholds, or workflow rather than defect correction.</t>
+        </is>
+      </c>
+      <c r="D72" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E72" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30.75" customHeight="1">
+      <c r="A73" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B73" s="41" t="inlineStr">
+        <is>
           <t>Relevancy</t>
         </is>
       </c>
-      <c r="C72" s="41" t="inlineStr">
+      <c r="C73" s="41" t="inlineStr">
         <is>
           <t>The item’s relevance to the customer or EventWatch scope was disputed or incorrectly assessed.</t>
         </is>
       </c>
-      <c r="D72" s="41" t="inlineStr">
+      <c r="D73" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E72" s="41" t="inlineStr">
+      <c r="E73" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="42" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B73" s="41" t="inlineStr">
+      <c r="B74" s="41" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="C73" s="41" t="inlineStr">
+      <c r="C74" s="41" t="inlineStr">
         <is>
           <t>Human assessment or quality review led to the issue.</t>
         </is>
       </c>
-      <c r="D73" s="41" t="inlineStr">
+      <c r="D74" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E73" s="41" t="inlineStr">
+      <c r="E74" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="30.75" customHeight="1">
-      <c r="A74" s="42" t="inlineStr">
+    <row r="75" ht="30.75" customHeight="1">
+      <c r="A75" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B74" s="41" t="inlineStr">
+      <c r="B75" s="41" t="inlineStr">
         <is>
           <t>Source Coverage</t>
         </is>
       </c>
-      <c r="C74" s="41" t="inlineStr">
+      <c r="C75" s="41" t="inlineStr">
         <is>
           <t>The relevant source was unavailable, unmonitored, restricted, or not harvested.</t>
-        </is>
-      </c>
-      <c r="D74" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E74" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B75" s="41" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="C75" s="41" t="inlineStr">
-        <is>
-          <t>The concern relates to reporting or consolidation strategy.</t>
         </is>
       </c>
       <c r="D75" s="41" t="inlineStr">
@@ -17848,39 +18040,39 @@
       </c>
       <c r="B76" s="41" t="inlineStr">
         <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="C76" s="41" t="inlineStr">
+        <is>
+          <t>The concern relates to reporting or consolidation strategy.</t>
+        </is>
+      </c>
+      <c r="D76" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E76" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B77" s="41" t="inlineStr">
+        <is>
           <t>Tagging</t>
         </is>
       </c>
-      <c r="C76" s="41" t="inlineStr">
+      <c r="C77" s="41" t="inlineStr">
         <is>
           <t>A required category or industry tag was missing or incorrect.</t>
-        </is>
-      </c>
-      <c r="D76" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E76" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30.75" customHeight="1">
-      <c r="A77" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B77" s="41" t="inlineStr">
-        <is>
-          <t>Visibility</t>
-        </is>
-      </c>
-      <c r="C77" s="41" t="inlineStr">
-        <is>
-          <t>Published content was not visible because of profile, portal, notification, or display conditions.</t>
         </is>
       </c>
       <c r="D77" s="41" t="inlineStr">
@@ -17902,12 +18094,12 @@
       </c>
       <c r="B78" s="41" t="inlineStr">
         <is>
-          <t>WarRoom Creation</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="C78" s="41" t="inlineStr">
         <is>
-          <t>A required WarRoom was not created despite available EventWatch coverage.</t>
+          <t>Published content was not visible because of profile, portal, notification, or display conditions.</t>
         </is>
       </c>
       <c r="D78" s="41" t="inlineStr">
@@ -17924,27 +18116,27 @@
     <row r="79" ht="30.75" customHeight="1">
       <c r="A79" s="42" t="inlineStr">
         <is>
-          <t>Improvement classification</t>
+          <t>Sub-type</t>
         </is>
       </c>
       <c r="B79" s="41" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>WarRoom Creation</t>
         </is>
       </c>
       <c r="C79" s="41" t="inlineStr">
         <is>
-          <t>Control, workflow, model, or monitoring enhancement rather than correction of a confirmed defect.</t>
+          <t>A required WarRoom was not created despite available EventWatch coverage.</t>
         </is>
       </c>
       <c r="D79" s="41" t="inlineStr">
         <is>
-          <t>Enhancement</t>
+          <t>Detailed cause/handling category</t>
         </is>
       </c>
       <c r="E79" s="41" t="inlineStr">
         <is>
-          <t>Improvement VS Bug</t>
+          <t>Sub-type</t>
         </is>
       </c>
     </row>
@@ -17956,49 +18148,49 @@
       </c>
       <c r="B80" s="41" t="inlineStr">
         <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="C80" s="41" t="inlineStr">
+        <is>
+          <t>Control, workflow, model, or monitoring enhancement rather than correction of a confirmed defect.</t>
+        </is>
+      </c>
+      <c r="D80" s="41" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E80" s="41" t="inlineStr">
+        <is>
+          <t>Improvement VS Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="30.75" customHeight="1">
+      <c r="A81" s="42" t="inlineStr">
+        <is>
+          <t>Improvement classification</t>
+        </is>
+      </c>
+      <c r="B81" s="41" t="inlineStr">
+        <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="C80" s="41" t="inlineStr">
+      <c r="C81" s="41" t="inlineStr">
         <is>
           <t>Confirmed product or engineering defect requiring correction.</t>
         </is>
       </c>
-      <c r="D80" s="41" t="inlineStr">
+      <c r="D81" s="41" t="inlineStr">
         <is>
           <t>Defect</t>
         </is>
       </c>
-      <c r="E80" s="41" t="inlineStr">
+      <c r="E81" s="41" t="inlineStr">
         <is>
           <t>Improvement VS Bug</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="42" t="inlineStr">
-        <is>
-          <t>Fix status</t>
-        </is>
-      </c>
-      <c r="B81" s="41" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C81" s="41" t="inlineStr">
-        <is>
-          <t>Immediate corrective action was completed.</t>
-        </is>
-      </c>
-      <c r="D81" s="41" t="inlineStr">
-        <is>
-          <t>Current resolution state</t>
-        </is>
-      </c>
-      <c r="E81" s="41" t="inlineStr">
-        <is>
-          <t>Short Term Fix Status</t>
         </is>
       </c>
     </row>
@@ -18010,76 +18202,76 @@
       </c>
       <c r="B82" s="41" t="inlineStr">
         <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C82" s="41" t="inlineStr">
+        <is>
+          <t>Immediate corrective action was completed.</t>
+        </is>
+      </c>
+      <c r="D82" s="41" t="inlineStr">
+        <is>
+          <t>Current resolution state</t>
+        </is>
+      </c>
+      <c r="E82" s="41" t="inlineStr">
+        <is>
+          <t>Short Term Fix Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="42" t="inlineStr">
+        <is>
+          <t>Fix status</t>
+        </is>
+      </c>
+      <c r="B83" s="41" t="inlineStr">
+        <is>
           <t>RCA Shared</t>
         </is>
       </c>
-      <c r="C82" s="41" t="inlineStr">
+      <c r="C83" s="41" t="inlineStr">
         <is>
           <t>The root cause analysis was completed and shared with the customer.</t>
         </is>
       </c>
-      <c r="D82" s="41" t="inlineStr">
+      <c r="D83" s="41" t="inlineStr">
         <is>
           <t>Current resolution state</t>
         </is>
       </c>
-      <c r="E82" s="41" t="inlineStr">
+      <c r="E83" s="41" t="inlineStr">
         <is>
           <t>Short Term Fix Status</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="30.75" customHeight="1">
-      <c r="A83" s="42" t="inlineStr">
+    <row r="84" ht="30.75" customHeight="1">
+      <c r="A84" s="42" t="inlineStr">
         <is>
           <t>Fix status</t>
         </is>
       </c>
-      <c r="B83" s="41" t="inlineStr">
+      <c r="B84" s="41" t="inlineStr">
         <is>
           <t>Clarification Provided</t>
         </is>
       </c>
-      <c r="C83" s="41" t="inlineStr">
+      <c r="C84" s="41" t="inlineStr">
         <is>
           <t>The customer received an explanation, verification result, or policy/process clarification.</t>
         </is>
       </c>
-      <c r="D83" s="41" t="inlineStr">
+      <c r="D84" s="41" t="inlineStr">
         <is>
           <t>Current resolution state</t>
         </is>
       </c>
-      <c r="E83" s="41" t="inlineStr">
+      <c r="E84" s="41" t="inlineStr">
         <is>
           <t>Short Term Fix Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="42" t="inlineStr">
-        <is>
-          <t>Boolean flag</t>
-        </is>
-      </c>
-      <c r="B84" s="41" t="inlineStr">
-        <is>
-          <t>Yes — RCA Requested</t>
-        </is>
-      </c>
-      <c r="C84" s="41" t="inlineStr">
-        <is>
-          <t>A formal root cause analysis was requested.</t>
-        </is>
-      </c>
-      <c r="D84" s="41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E84" s="41" t="inlineStr">
-        <is>
-          <t>RCA Requested</t>
         </is>
       </c>
     </row>
@@ -18091,49 +18283,49 @@
       </c>
       <c r="B85" s="41" t="inlineStr">
         <is>
+          <t>Yes — RCA Requested</t>
+        </is>
+      </c>
+      <c r="C85" s="41" t="inlineStr">
+        <is>
+          <t>A formal root cause analysis was requested.</t>
+        </is>
+      </c>
+      <c r="D85" s="41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E85" s="41" t="inlineStr">
+        <is>
+          <t>RCA Requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="42" t="inlineStr">
+        <is>
+          <t>Boolean flag</t>
+        </is>
+      </c>
+      <c r="B86" s="41" t="inlineStr">
+        <is>
           <t>No — RCA Requested</t>
         </is>
       </c>
-      <c r="C85" s="41" t="inlineStr">
+      <c r="C86" s="41" t="inlineStr">
         <is>
           <t>No formal root cause analysis was requested.</t>
         </is>
       </c>
-      <c r="D85" s="41" t="inlineStr">
+      <c r="D86" s="41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E85" s="41" t="inlineStr">
+      <c r="E86" s="41" t="inlineStr">
         <is>
           <t>RCA Requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="30.75" customHeight="1">
-      <c r="A86" s="42" t="inlineStr">
-        <is>
-          <t>Boolean flag</t>
-        </is>
-      </c>
-      <c r="B86" s="41" t="inlineStr">
-        <is>
-          <t>Yes — Missed_Flag</t>
-        </is>
-      </c>
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>Expected coverage, alerting, escalation, or WarRoom action was missed or materially delayed.</t>
-        </is>
-      </c>
-      <c r="D86" s="41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E86" s="41" t="inlineStr">
-        <is>
-          <t>Missed_Flag</t>
         </is>
       </c>
     </row>
@@ -18145,49 +18337,49 @@
       </c>
       <c r="B87" s="41" t="inlineStr">
         <is>
+          <t>Yes — Missed_Flag</t>
+        </is>
+      </c>
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>Expected coverage, alerting, escalation, or WarRoom action was missed or materially delayed.</t>
+        </is>
+      </c>
+      <c r="D87" s="41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E87" s="41" t="inlineStr">
+        <is>
+          <t>Missed_Flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="30.75" customHeight="1">
+      <c r="A88" s="42" t="inlineStr">
+        <is>
+          <t>Boolean flag</t>
+        </is>
+      </c>
+      <c r="B88" s="41" t="inlineStr">
+        <is>
           <t>No — Missed_Flag</t>
         </is>
       </c>
-      <c r="C87" s="41" t="inlineStr">
+      <c r="C88" s="41" t="inlineStr">
         <is>
           <t>No confirmed reporting miss; the case concerns clarification, relevancy, mapping, duplication, or another non-miss issue.</t>
         </is>
       </c>
-      <c r="D87" s="41" t="inlineStr">
+      <c r="D88" s="41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E87" s="41" t="inlineStr">
+      <c r="E88" s="41" t="inlineStr">
         <is>
           <t>Missed_Flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="42" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="B88" s="41" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C88" s="41" t="inlineStr">
-        <is>
-          <t>Material impact or priority requiring elevated management attention.</t>
-        </is>
-      </c>
-      <c r="D88" s="41" t="inlineStr">
-        <is>
-          <t>Priority level</t>
-        </is>
-      </c>
-      <c r="E88" s="41" t="inlineStr">
-        <is>
-          <t>Severity</t>
         </is>
       </c>
     </row>
@@ -18199,12 +18391,12 @@
       </c>
       <c r="B89" s="41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C89" s="41" t="inlineStr">
         <is>
-          <t>Standard operational complaint or issue requiring tracked response.</t>
+          <t>Material impact or priority requiring elevated management attention.</t>
         </is>
       </c>
       <c r="D89" s="41" t="inlineStr">
@@ -18226,12 +18418,12 @@
       </c>
       <c r="B90" s="41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>Limited-impact inquiry or quality issue with lower operational urgency.</t>
+          <t>Standard operational complaint or issue requiring tracked response.</t>
         </is>
       </c>
       <c r="D90" s="41" t="inlineStr">
@@ -18248,27 +18440,27 @@
     <row r="91">
       <c r="A91" s="42" t="inlineStr">
         <is>
-          <t>Automation focus</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="B91" s="41" t="inlineStr">
         <is>
-          <t>AI-Assisted Geofencing</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C91" s="41" t="inlineStr">
         <is>
-          <t>Automate or improve impact-area creation and location validation.</t>
+          <t>Limited-impact inquiry or quality issue with lower operational urgency.</t>
         </is>
       </c>
       <c r="D91" s="41" t="inlineStr">
         <is>
-          <t>Standardized dashboard category</t>
+          <t>Priority level</t>
         </is>
       </c>
       <c r="E91" s="41" t="inlineStr">
         <is>
-          <t>Standard Automation Focus</t>
+          <t>Severity</t>
         </is>
       </c>
     </row>
@@ -18280,93 +18472,93 @@
       </c>
       <c r="B92" s="41" t="inlineStr">
         <is>
+          <t>AI-Assisted Geofencing</t>
+        </is>
+      </c>
+      <c r="C92" s="41" t="inlineStr">
+        <is>
+          <t>Automate or improve impact-area creation and location validation.</t>
+        </is>
+      </c>
+      <c r="D92" s="41" t="inlineStr">
+        <is>
+          <t>Standardized dashboard category</t>
+        </is>
+      </c>
+      <c r="E92" s="41" t="inlineStr">
+        <is>
+          <t>Standard Automation Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="42" t="inlineStr">
+        <is>
+          <t>Automation focus</t>
+        </is>
+      </c>
+      <c r="B93" s="41" t="inlineStr">
+        <is>
           <t>Automated Industry Tagging</t>
         </is>
       </c>
-      <c r="C92" s="41" t="inlineStr">
+      <c r="C93" s="41" t="inlineStr">
         <is>
           <t>Automatically assign and validate industry classifications.</t>
         </is>
       </c>
-      <c r="D92" s="41" t="inlineStr">
+      <c r="D93" s="41" t="inlineStr">
         <is>
           <t>Standardized dashboard category</t>
         </is>
       </c>
-      <c r="E92" s="41" t="inlineStr">
+      <c r="E93" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="30.75" customHeight="1">
-      <c r="A93" s="42" t="inlineStr">
+    <row r="94" ht="30.75" customHeight="1">
+      <c r="A94" s="42" t="inlineStr">
         <is>
           <t>Automation focus</t>
         </is>
       </c>
-      <c r="B93" s="41" t="inlineStr">
+      <c r="B94" s="41" t="inlineStr">
         <is>
           <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
-      <c r="C93" s="41" t="inlineStr">
+      <c r="C94" s="41" t="inlineStr">
         <is>
           <t>Detect duplicate/split clusters and preserve one coherent event sequence.</t>
         </is>
       </c>
-      <c r="D93" s="41" t="inlineStr">
+      <c r="D94" s="41" t="inlineStr">
         <is>
           <t>Standardized dashboard category</t>
         </is>
       </c>
-      <c r="E93" s="41" t="inlineStr">
+      <c r="E94" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="42" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="42" t="inlineStr">
         <is>
           <t>Automation focus</t>
         </is>
       </c>
-      <c r="B94" s="41" t="inlineStr">
+      <c r="B95" s="41" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="C94" s="41" t="inlineStr">
+      <c r="C95" s="41" t="inlineStr">
         <is>
           <t>Identify, onboard, and monitor new or missing sources dynamically.</t>
-        </is>
-      </c>
-      <c r="D94" s="41" t="inlineStr">
-        <is>
-          <t>Standardized dashboard category</t>
-        </is>
-      </c>
-      <c r="E94" s="41" t="inlineStr">
-        <is>
-          <t>Standard Automation Focus</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="30.75" customHeight="1">
-      <c r="A95" s="42" t="inlineStr">
-        <is>
-          <t>Automation focus</t>
-        </is>
-      </c>
-      <c r="B95" s="41" t="inlineStr">
-        <is>
-          <t>Entity &amp; Supplier Resolution</t>
-        </is>
-      </c>
-      <c r="C95" s="41" t="inlineStr">
-        <is>
-          <t>Resolve company, facility, supplier, and customer relationships accurately.</t>
         </is>
       </c>
       <c r="D95" s="41" t="inlineStr">
@@ -18388,12 +18580,12 @@
       </c>
       <c r="B96" s="41" t="inlineStr">
         <is>
-          <t>Multilingual Keyword Expansion</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="C96" s="41" t="inlineStr">
         <is>
-          <t>Expand and maintain detection terms across languages and regional variations.</t>
+          <t>Resolve company, facility, supplier, and customer relationships accurately.</t>
         </is>
       </c>
       <c r="D96" s="41" t="inlineStr">
@@ -18415,66 +18607,66 @@
       </c>
       <c r="B97" s="41" t="inlineStr">
         <is>
+          <t>Multilingual Keyword Expansion</t>
+        </is>
+      </c>
+      <c r="C97" s="41" t="inlineStr">
+        <is>
+          <t>Expand and maintain detection terms across languages and regional variations.</t>
+        </is>
+      </c>
+      <c r="D97" s="41" t="inlineStr">
+        <is>
+          <t>Standardized dashboard category</t>
+        </is>
+      </c>
+      <c r="E97" s="41" t="inlineStr">
+        <is>
+          <t>Standard Automation Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="30.75" customHeight="1">
+      <c r="A98" s="42" t="inlineStr">
+        <is>
+          <t>Automation focus</t>
+        </is>
+      </c>
+      <c r="B98" s="41" t="inlineStr">
+        <is>
           <t>Notification Visibility Monitoring</t>
         </is>
       </c>
-      <c r="C97" s="41" t="inlineStr">
+      <c r="C98" s="41" t="inlineStr">
         <is>
           <t>Monitor whether published alerts and WarRooms are visible and delivered to the customer.</t>
         </is>
       </c>
-      <c r="D97" s="41" t="inlineStr">
+      <c r="D98" s="41" t="inlineStr">
         <is>
           <t>Standardized dashboard category</t>
         </is>
       </c>
-      <c r="E97" s="41" t="inlineStr">
+      <c r="E98" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="42" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="42" t="inlineStr">
         <is>
           <t>Automation focus</t>
         </is>
       </c>
-      <c r="B98" s="41" t="inlineStr">
+      <c r="B99" s="41" t="inlineStr">
         <is>
           <t>Other Control Automation</t>
         </is>
       </c>
-      <c r="C98" s="41" t="inlineStr">
+      <c r="C99" s="41" t="inlineStr">
         <is>
           <t>Automation that does not fit another standardized focus category.</t>
-        </is>
-      </c>
-      <c r="D98" s="41" t="inlineStr">
-        <is>
-          <t>Standardized dashboard category</t>
-        </is>
-      </c>
-      <c r="E98" s="41" t="inlineStr">
-        <is>
-          <t>Standard Automation Focus</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="30.75" customHeight="1">
-      <c r="A99" s="42" t="inlineStr">
-        <is>
-          <t>Automation focus</t>
-        </is>
-      </c>
-      <c r="B99" s="41" t="inlineStr">
-        <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="C99" s="41" t="inlineStr">
-        <is>
-          <t>Validate impact decisions, escalation, publishing, and WarRoom creation.</t>
         </is>
       </c>
       <c r="D99" s="41" t="inlineStr">
@@ -18491,27 +18683,27 @@
     <row r="100" ht="30.75" customHeight="1">
       <c r="A100" s="42" t="inlineStr">
         <is>
-          <t>Reason label</t>
+          <t>Automation focus</t>
         </is>
       </c>
       <c r="B100" s="41" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="C100" s="41" t="inlineStr">
         <is>
-          <t>Customer requested confirmation of coverage, facts, or system behavior.</t>
+          <t>Validate impact decisions, escalation, publishing, and WarRoom creation.</t>
         </is>
       </c>
       <c r="D100" s="41" t="inlineStr">
         <is>
-          <t>Use only when supported by Comments and Missed_Flag</t>
+          <t>Standardized dashboard category</t>
         </is>
       </c>
       <c r="E100" s="41" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
@@ -18523,7 +18715,7 @@
       </c>
       <c r="B101" s="41" t="inlineStr">
         <is>
-          <t>Customer Requested Verification</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="C101" s="41" t="inlineStr">
@@ -18550,12 +18742,12 @@
       </c>
       <c r="B102" s="41" t="inlineStr">
         <is>
-          <t>Customer Terminology Preference</t>
+          <t>Customer Requested Verification</t>
         </is>
       </c>
       <c r="C102" s="41" t="inlineStr">
         <is>
-          <t>Customer requested wording or naming alignment rather than correction of a reporting failure.</t>
+          <t>Customer requested confirmation of coverage, facts, or system behavior.</t>
         </is>
       </c>
       <c r="D102" s="41" t="inlineStr">
@@ -18577,12 +18769,12 @@
       </c>
       <c r="B103" s="41" t="inlineStr">
         <is>
-          <t>Delay in creating separate WarRoom / delayed escalation</t>
+          <t>Customer Terminology Preference</t>
         </is>
       </c>
       <c r="C103" s="41" t="inlineStr">
         <is>
-          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
+          <t>Customer requested wording or naming alignment rather than correction of a reporting failure.</t>
         </is>
       </c>
       <c r="D103" s="41" t="inlineStr">
@@ -18604,7 +18796,7 @@
       </c>
       <c r="B104" s="41" t="inlineStr">
         <is>
-          <t>Delayed / Missing WarRoom</t>
+          <t>Delay in creating separate WarRoom / delayed escalation</t>
         </is>
       </c>
       <c r="C104" s="41" t="inlineStr">
@@ -18631,7 +18823,7 @@
       </c>
       <c r="B105" s="41" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Delayed / Missing WarRoom</t>
         </is>
       </c>
       <c r="C105" s="41" t="inlineStr">
@@ -18658,7 +18850,7 @@
       </c>
       <c r="B106" s="41" t="inlineStr">
         <is>
-          <t>Delayed WarRoom</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="C106" s="41" t="inlineStr">
@@ -18685,7 +18877,7 @@
       </c>
       <c r="B107" s="41" t="inlineStr">
         <is>
-          <t>Delayed alert / WarRoom created late</t>
+          <t>Delayed WarRoom</t>
         </is>
       </c>
       <c r="C107" s="41" t="inlineStr">
@@ -18712,12 +18904,12 @@
       </c>
       <c r="B108" s="41" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms</t>
+          <t>Delayed alert / WarRoom created late</t>
         </is>
       </c>
       <c r="C108" s="41" t="inlineStr">
         <is>
-          <t>Related content was distributed across more than one WarRoom.</t>
+          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
         </is>
       </c>
       <c r="D108" s="41" t="inlineStr">
@@ -18739,12 +18931,12 @@
       </c>
       <c r="B109" s="41" t="inlineStr">
         <is>
-          <t>Event not triggered / not notified</t>
+          <t>Duplicate WarRooms</t>
         </is>
       </c>
       <c r="C109" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>Related content was distributed across more than one WarRoom.</t>
         </is>
       </c>
       <c r="D109" s="41" t="inlineStr">
@@ -18766,12 +18958,12 @@
       </c>
       <c r="B110" s="41" t="inlineStr">
         <is>
-          <t>Geographic Coverage Clarification</t>
+          <t>Event not triggered / not notified</t>
         </is>
       </c>
       <c r="C110" s="41" t="inlineStr">
         <is>
-          <t>Customer requested explanation of the geographic scope or impact-area method.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D110" s="41" t="inlineStr">
@@ -18793,12 +18985,12 @@
       </c>
       <c r="B111" s="41" t="inlineStr">
         <is>
-          <t>Geographic Misclassification</t>
+          <t>Geographic Coverage Clarification</t>
         </is>
       </c>
       <c r="C111" s="41" t="inlineStr">
         <is>
-          <t>An event or location was assigned to an incorrect geographic impact area.</t>
+          <t>Customer requested explanation of the geographic scope or impact-area method.</t>
         </is>
       </c>
       <c r="D111" s="41" t="inlineStr">
@@ -18820,12 +19012,12 @@
       </c>
       <c r="B112" s="41" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Geographic Misclassification</t>
         </is>
       </c>
       <c r="C112" s="41" t="inlineStr">
         <is>
-          <t>A relevant mapped supplier was omitted from the impacted-supplier selection.</t>
+          <t>An event or location was assigned to an incorrect geographic impact area.</t>
         </is>
       </c>
       <c r="D112" s="41" t="inlineStr">
@@ -18847,12 +19039,12 @@
       </c>
       <c r="B113" s="41" t="inlineStr">
         <is>
-          <t>Incorrect Action</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="C113" s="41" t="inlineStr">
         <is>
-          <t>EventWatch action or handling was incorrect even though the event itself may not have been missed.</t>
+          <t>A relevant mapped supplier was omitted from the impacted-supplier selection.</t>
         </is>
       </c>
       <c r="D113" s="41" t="inlineStr">
@@ -18874,12 +19066,12 @@
       </c>
       <c r="B114" s="41" t="inlineStr">
         <is>
-          <t>Incorrect Industry selection</t>
+          <t>Incorrect Action</t>
         </is>
       </c>
       <c r="C114" s="41" t="inlineStr">
         <is>
-          <t>The expected industry classification was missing or incorrect.</t>
+          <t>EventWatch action or handling was incorrect even though the event itself may not have been missed.</t>
         </is>
       </c>
       <c r="D114" s="41" t="inlineStr">
@@ -18901,12 +19093,12 @@
       </c>
       <c r="B115" s="41" t="inlineStr">
         <is>
-          <t>Missed + Delayed Reporting</t>
+          <t>Incorrect Industry selection</t>
         </is>
       </c>
       <c r="C115" s="41" t="inlineStr">
         <is>
-          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
+          <t>The expected industry classification was missing or incorrect.</t>
         </is>
       </c>
       <c r="D115" s="41" t="inlineStr">
@@ -18928,7 +19120,7 @@
       </c>
       <c r="B116" s="41" t="inlineStr">
         <is>
-          <t>Missed / Delayed Event</t>
+          <t>Missed + Delayed Reporting</t>
         </is>
       </c>
       <c r="C116" s="41" t="inlineStr">
@@ -18955,12 +19147,12 @@
       </c>
       <c r="B117" s="41" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed / Delayed Event</t>
         </is>
       </c>
       <c r="C117" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
         </is>
       </c>
       <c r="D117" s="41" t="inlineStr">
@@ -18982,7 +19174,7 @@
       </c>
       <c r="B118" s="41" t="inlineStr">
         <is>
-          <t>Missed Relevant Event</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="C118" s="41" t="inlineStr">
@@ -19009,7 +19201,7 @@
       </c>
       <c r="B119" s="41" t="inlineStr">
         <is>
-          <t>Missed WarRoom</t>
+          <t>Missed Relevant Event</t>
         </is>
       </c>
       <c r="C119" s="41" t="inlineStr">
@@ -19036,7 +19228,7 @@
       </c>
       <c r="B120" s="41" t="inlineStr">
         <is>
-          <t>Missed WarRoom / No notification</t>
+          <t>Missed WarRoom</t>
         </is>
       </c>
       <c r="C120" s="41" t="inlineStr">
@@ -19063,7 +19255,7 @@
       </c>
       <c r="B121" s="41" t="inlineStr">
         <is>
-          <t>Missed alert / event not captured</t>
+          <t>Missed WarRoom / No notification</t>
         </is>
       </c>
       <c r="C121" s="41" t="inlineStr">
@@ -19090,7 +19282,7 @@
       </c>
       <c r="B122" s="41" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Missed alert / event not captured</t>
         </is>
       </c>
       <c r="C122" s="41" t="inlineStr">
@@ -19117,7 +19309,7 @@
       </c>
       <c r="B123" s="41" t="inlineStr">
         <is>
-          <t>Missed insolvency event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="C123" s="41" t="inlineStr">
@@ -19144,7 +19336,7 @@
       </c>
       <c r="B124" s="41" t="inlineStr">
         <is>
-          <t>Missed severe weather alert</t>
+          <t>Missed insolvency event</t>
         </is>
       </c>
       <c r="C124" s="41" t="inlineStr">
@@ -19171,12 +19363,12 @@
       </c>
       <c r="B125" s="41" t="inlineStr">
         <is>
-          <t>Missing Automotive industry tag (customer tracking missed it)</t>
+          <t>Missed severe weather alert</t>
         </is>
       </c>
       <c r="C125" s="41" t="inlineStr">
         <is>
-          <t>The expected industry classification was missing or incorrect.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D125" s="41" t="inlineStr">
@@ -19198,12 +19390,12 @@
       </c>
       <c r="B126" s="41" t="inlineStr">
         <is>
-          <t>Missing EventWatch coverage / feeds not captured</t>
+          <t>Missing Automotive industry tag (customer tracking missed it)</t>
         </is>
       </c>
       <c r="C126" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>The expected industry classification was missing or incorrect.</t>
         </is>
       </c>
       <c r="D126" s="41" t="inlineStr">
@@ -19225,7 +19417,7 @@
       </c>
       <c r="B127" s="41" t="inlineStr">
         <is>
-          <t>Missing Resilinc alert / insolvency not captured</t>
+          <t>Missing EventWatch coverage / feeds not captured</t>
         </is>
       </c>
       <c r="C127" s="41" t="inlineStr">
@@ -19252,12 +19444,12 @@
       </c>
       <c r="B128" s="41" t="inlineStr">
         <is>
-          <t>SEC notification not captured/provided on time</t>
+          <t>Missing Resilinc alert / insolvency not captured</t>
         </is>
       </c>
       <c r="C128" s="41" t="inlineStr">
         <is>
-          <t>Specific customer-reported reason recorded in the tracker.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D128" s="41" t="inlineStr">
@@ -19279,12 +19471,12 @@
       </c>
       <c r="B129" s="41" t="inlineStr">
         <is>
-          <t>Severity / consolidation handling concern</t>
+          <t>SEC notification not captured/provided on time</t>
         </is>
       </c>
       <c r="C129" s="41" t="inlineStr">
         <is>
-          <t>Customer questioned the severity level or consolidation of event coverage.</t>
+          <t>Specific customer-reported reason recorded in the tracker.</t>
         </is>
       </c>
       <c r="D129" s="41" t="inlineStr">
@@ -19306,12 +19498,12 @@
       </c>
       <c r="B130" s="41" t="inlineStr">
         <is>
-          <t>Supplier Impact Mapping Clarification</t>
+          <t>Severity / consolidation handling concern</t>
         </is>
       </c>
       <c r="C130" s="41" t="inlineStr">
         <is>
-          <t>Customer requested explanation of why suppliers were included or excluded from the impact area.</t>
+          <t>Customer questioned the severity level or consolidation of event coverage.</t>
         </is>
       </c>
       <c r="D130" s="41" t="inlineStr">
@@ -19333,12 +19525,12 @@
       </c>
       <c r="B131" s="41" t="inlineStr">
         <is>
-          <t>WarRoom not created despite nationwide disruption</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="C131" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>Customer requested explanation of why suppliers were included or excluded from the impact area.</t>
         </is>
       </c>
       <c r="D131" s="41" t="inlineStr">
@@ -19360,12 +19552,12 @@
       </c>
       <c r="B132" s="41" t="inlineStr">
         <is>
-          <t>WarRoom not visible in customer profile</t>
+          <t>WarRoom not created despite nationwide disruption</t>
         </is>
       </c>
       <c r="C132" s="41" t="inlineStr">
         <is>
-          <t>Published content was not visible in the customer profile or portal.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D132" s="41" t="inlineStr">
@@ -19387,12 +19579,12 @@
       </c>
       <c r="B133" s="41" t="inlineStr">
         <is>
-          <t>WarRoom should have been created but was not</t>
+          <t>WarRoom not visible in customer profile</t>
         </is>
       </c>
       <c r="C133" s="41" t="inlineStr">
         <is>
-          <t>Available information met the escalation criteria, but the required WarRoom was not created.</t>
+          <t>Published content was not visible in the customer profile or portal.</t>
         </is>
       </c>
       <c r="D133" s="41" t="inlineStr">
@@ -19414,12 +19606,12 @@
       </c>
       <c r="B134" s="41" t="inlineStr">
         <is>
-          <t>WarRoom visibility affected by customer profile filters</t>
+          <t>WarRoom should have been created but was not</t>
         </is>
       </c>
       <c r="C134" s="41" t="inlineStr">
         <is>
-          <t>Published content was not visible in the customer profile or portal.</t>
+          <t>Available information met the escalation criteria, but the required WarRoom was not created.</t>
         </is>
       </c>
       <c r="D134" s="41" t="inlineStr">
@@ -19441,12 +19633,12 @@
       </c>
       <c r="B135" s="41" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>WarRoom visibility affected by customer profile filters</t>
         </is>
       </c>
       <c r="C135" s="41" t="inlineStr">
         <is>
-          <t>The relevance classification of an event or alert was disputed or incorrect.</t>
+          <t>Published content was not visible in the customer profile or portal.</t>
         </is>
       </c>
       <c r="D135" s="41" t="inlineStr">
@@ -19463,27 +19655,27 @@
     <row r="136" ht="30.75" customHeight="1">
       <c r="A136" s="42" t="inlineStr">
         <is>
-          <t>Event type</t>
+          <t>Reason label</t>
         </is>
       </c>
       <c r="B136" s="41" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="C136" s="41" t="inlineStr">
         <is>
-          <t>Tropical cyclone classified as a hurricane or typhoon, with potential geographic, operational, or supply-chain impact.</t>
+          <t>The relevance classification of an event or alert was disputed or incorrect.</t>
         </is>
       </c>
       <c r="D136" s="41" t="inlineStr">
         <is>
-          <t>Use specifically for hurricanes and typhoons rather than the broader Extreme Weather category.</t>
+          <t>Use only when supported by Comments and Missed_Flag</t>
         </is>
       </c>
       <c r="E136" s="41" t="inlineStr">
         <is>
-          <t>Event type</t>
+          <t>Reason</t>
         </is>
       </c>
     </row>
@@ -19495,20 +19687,47 @@
       </c>
       <c r="B137" s="41" t="inlineStr">
         <is>
+          <t>Hurricane/Typhoon</t>
+        </is>
+      </c>
+      <c r="C137" s="41" t="inlineStr">
+        <is>
+          <t>Tropical cyclone classified as a hurricane or typhoon, with potential geographic, operational, or supply-chain impact.</t>
+        </is>
+      </c>
+      <c r="D137" s="41" t="inlineStr">
+        <is>
+          <t>Use specifically for hurricanes and typhoons rather than the broader Extreme Weather category.</t>
+        </is>
+      </c>
+      <c r="E137" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="30.75" customHeight="1">
+      <c r="A138" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B138" s="41" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C137" s="41" t="inlineStr">
+      <c r="C138" s="41" t="inlineStr">
         <is>
           <t>Event or inquiry category that does not fit any available standardized Event type.</t>
         </is>
       </c>
-      <c r="D137" s="41" t="inlineStr">
+      <c r="D138" s="41" t="inlineStr">
         <is>
           <t>Use only when no specific standard category applies; explain the subject in the title and comments.</t>
         </is>
       </c>
-      <c r="E137" s="41" t="inlineStr">
+      <c r="E138" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -3282,9 +3282,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:W95" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
-  <autoFilter ref="A1:W95"/>
-  <tableColumns count="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:X95" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="A1:X95"/>
+  <tableColumns count="24">
     <tableColumn id="1" name="Month" dataDxfId="28">
       <calculatedColumnFormula>DATE(YEAR(B2),MONTH(B2),1)</calculatedColumnFormula>
     </tableColumn>
@@ -3331,14 +3331,15 @@
       <calculatedColumnFormula>IF(OR(ISNUMBER(SEARCH("keyword",M2)),ISNUMBER(SEARCH("language",M2))),"Multilingual Keyword Expansion",IF(OR(ISNUMBER(SEARCH("source",M2)),ISNUMBER(SEARCH("feed",M2)),ISNUMBER(SEARCH("vendor",M2))),"Dynamic Source Discovery",IF(OR(ISNUMBER(SEARCH("escalat",M2)),ISNUMBER(SEARCH("warroom",M2)),ISNUMBER(SEARCH("not impactful",M2)),ISNUMBER(SEARCH("priorit",M2)),ISNUMBER(SEARCH("reviewer",M2)),ISNUMBER(SEARCH("validation automation",M2))),"WarRoom &amp; Decision Validation",IF(ISNUMBER(SEARCH("tag",M2)),"Automated Industry Tagging",IF(OR(ISNUMBER(SEARCH("map",M2)),ISNUMBER(SEARCH("supplier",M2)),ISNUMBER(SEARCH("entity",M2)),ISNUMBER(SEARCH("alias",M2)),ISNUMBER(SEARCH("facility",M2)),ISNUMBER(SEARCH("company",M2))),"Entity &amp; Supplier Resolution",IF(OR(ISNUMBER(SEARCH("geo",M2)),ISNUMBER(SEARCH("location",M2))),"AI-Assisted Geofencing",IF(OR(ISNUMBER(SEARCH("duplicate",M2)),ISNUMBER(SEARCH("cluster",M2))),"Cluster Integrity &amp; Duplicate Prevention",IF(OR(ISNUMBER(SEARCH("visibility",M2)),ISNUMBER(SEARCH("notification",M2))),"Notification Visibility Monitoring",IF(OR(ISNUMBER(SEARCH("rca",M2)),ISNUMBER(SEARCH("complaint",M2)),ISNUMBER(SEARCH("process control",M2))),"RCA &amp; Workflow Automation","Other Control Automation")))))))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="23" name="Jira Key"/>
+    <tableColumn id="24" name="RCA Details"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E137" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A3:E137"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E138" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A3:E138"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
     <tableColumn id="2" name="Term / Field" dataDxfId="3"/>
@@ -3641,7 +3642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W95"/>
+  <dimension ref="A1:X95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -3770,6 +3771,11 @@
           <t>Jira Key</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>RCA Details</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="35" t="n">
@@ -3864,6 +3870,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X2" s="33" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="35" t="n">
@@ -3958,6 +3965,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X3" s="33" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="35" t="n">
@@ -4052,6 +4060,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X4" s="33" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="n">
@@ -4152,6 +4161,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X5" s="33" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="n">
@@ -4246,6 +4256,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X6" s="33" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="n">
@@ -4340,6 +4351,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X7" s="33" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="n">
@@ -4434,6 +4446,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X8" s="33" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="n">
@@ -4528,6 +4541,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X9" s="33" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="n">
@@ -4622,6 +4636,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X10" s="33" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="n">
@@ -4716,6 +4731,7 @@
           <t>Notification Visibility Monitoring</t>
         </is>
       </c>
+      <c r="X11" s="33" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="35" t="n">
@@ -4810,6 +4826,7 @@
           <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
+      <c r="X12" s="33" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="35" t="n">
@@ -4904,6 +4921,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X13" s="33" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="35" t="n">
@@ -4998,6 +5016,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X14" s="33" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="35" t="n">
@@ -5092,6 +5111,7 @@
           <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
+      <c r="X15" s="33" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="35" t="n">
@@ -5186,6 +5206,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X16" s="33" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="35" t="n">
@@ -5280,6 +5301,7 @@
           <t>Notification Visibility Monitoring</t>
         </is>
       </c>
+      <c r="X17" s="33" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="35" t="n">
@@ -5374,6 +5396,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X18" s="33" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="35" t="n">
@@ -5468,6 +5491,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X19" s="33" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="35" t="n">
@@ -5562,6 +5586,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X20" s="33" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="35" t="n">
@@ -5656,6 +5681,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X21" s="33" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="35" t="n">
@@ -5750,6 +5776,7 @@
           <t>Automated Industry Tagging</t>
         </is>
       </c>
+      <c r="X22" s="33" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="35" t="n">
@@ -5844,6 +5871,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X23" s="33" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="35" t="n">
@@ -5944,6 +5972,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X24" s="33" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="35" t="n">
@@ -6044,6 +6073,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X25" s="33" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="35" t="n">
@@ -6138,6 +6168,7 @@
           <t>Automated Industry Tagging</t>
         </is>
       </c>
+      <c r="X26" s="33" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="35" t="n">
@@ -6232,6 +6263,7 @@
           <t>AI-Assisted Geofencing</t>
         </is>
       </c>
+      <c r="X27" s="33" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="35" t="n">
@@ -6326,6 +6358,7 @@
           <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
+      <c r="X28" s="33" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="35" t="n">
@@ -6420,6 +6453,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X29" s="33" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="35" t="n">
@@ -6514,6 +6548,7 @@
           <t>Multilingual Keyword Expansion</t>
         </is>
       </c>
+      <c r="X30" s="33" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="35" t="n">
@@ -6608,6 +6643,7 @@
           <t>Multilingual Keyword Expansion</t>
         </is>
       </c>
+      <c r="X31" s="33" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="35" t="n">
@@ -6702,6 +6738,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X32" s="33" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="35" t="n">
@@ -6796,6 +6833,7 @@
           <t>AI-Assisted Geofencing</t>
         </is>
       </c>
+      <c r="X33" s="33" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="35" t="n">
@@ -6890,6 +6928,7 @@
           <t>Multilingual Keyword Expansion</t>
         </is>
       </c>
+      <c r="X34" s="33" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="35" t="n">
@@ -6990,6 +7029,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X35" s="33" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="35" t="n">
@@ -7090,6 +7130,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X36" s="33" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="35" t="n">
@@ -7190,6 +7231,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X37" s="33" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="35" t="n">
@@ -7290,6 +7332,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X38" s="33" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="35" t="n">
@@ -7384,6 +7427,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X39" s="33" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="35" t="n">
@@ -7478,6 +7522,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X40" s="33" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="35" t="n">
@@ -7572,6 +7617,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X41" s="33" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="35" t="n">
@@ -7666,6 +7712,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X42" s="33" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="35" t="n">
@@ -7760,6 +7807,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X43" s="33" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="35" t="n">
@@ -7860,6 +7908,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X44" s="33" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="35" t="n">
@@ -7960,6 +8009,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X45" s="33" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="35" t="n">
@@ -8054,6 +8104,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X46" s="33" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="35" t="n">
@@ -8148,6 +8199,7 @@
           <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
+      <c r="X47" s="33" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="35" t="n">
@@ -8242,6 +8294,7 @@
           <t>Other Control Automation</t>
         </is>
       </c>
+      <c r="X48" s="33" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="35" t="n">
@@ -8336,6 +8389,7 @@
           <t>AI-Assisted Geofencing</t>
         </is>
       </c>
+      <c r="X49" s="33" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="35" t="n">
@@ -8436,6 +8490,7 @@
           <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
+      <c r="X50" s="33" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="35" t="n">
@@ -8536,6 +8591,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X51" s="33" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="35" t="n">
@@ -8636,6 +8692,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X52" s="33" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="35" t="n">
@@ -8730,6 +8787,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X53" s="33" t="n"/>
     </row>
     <row r="54" customFormat="1" s="29">
       <c r="A54" s="36" t="n">
@@ -8830,6 +8888,7 @@
           <t>AI-Assisted Geofencing</t>
         </is>
       </c>
+      <c r="X54" s="33" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="35" t="n">
@@ -8924,6 +8983,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X55" s="33" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="35" t="n">
@@ -9018,6 +9078,7 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
+      <c r="X56" s="33" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="35" t="n">
@@ -9117,6 +9178,11 @@
           <t>EAO-1</t>
         </is>
       </c>
+      <c r="X57" s="33" t="inlineStr">
+        <is>
+          <t>Articles on the Burnstein von Seelen disruption did reach the portal, but the analyst classified the event Not Impactful and did not escalate it, so it never reached WarRoom consideration. Corrective: analyst coaching on law-enforcement, regulatory and workforce disruptions, plus an internal non-conformance raised against the reporting workflow. Preventive: extra review controls before a Not Impactful call on a monitored supplier, stronger supplier-context visibility during review, expanded audits of analyst overrides, and AI-assisted relevance work with Product/Data Science.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="35" t="n">
@@ -9216,6 +9282,11 @@
           <t>EAO-4</t>
         </is>
       </c>
+      <c r="X58" s="33" t="inlineStr">
+        <is>
+          <t>RCA approved and sent to the customer on 15-Jun-2026 as a PDF attached to EAO-4; the document text is not in the ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="35" t="n">
@@ -9315,6 +9386,7 @@
           <t>EAO-8</t>
         </is>
       </c>
+      <c r="X59" s="33" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="35" t="n">
@@ -9414,6 +9486,11 @@
           <t>EAO-6</t>
         </is>
       </c>
+      <c r="X60" s="33" t="inlineStr">
+        <is>
+          <t>The primary transaction participants were identified correctly, but Dana Holdings was omitted during the initial review of related corporate entities and supplier relationships; a WarRoom update was issued to add it. Preventive: mandatory secondary review for impacted-supplier assessments involving mergers, acquisitions, restructurings and other multi-entity transactions. RCA shared 13-Jul-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="35" t="n">
@@ -9513,6 +9590,7 @@
           <t>EAO-7</t>
         </is>
       </c>
+      <c r="X61" s="33" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="35" t="n">
@@ -9612,6 +9690,11 @@
           <t>EAO-10</t>
         </is>
       </c>
+      <c r="X62" s="33" t="inlineStr">
+        <is>
+          <t>RCA reviewed and sent to the customer as a PDF attached to EAO-10 (29-Jun-2026); the document text is not in the ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="35" t="n">
@@ -9711,6 +9794,11 @@
           <t>EAO-9</t>
         </is>
       </c>
+      <c r="X63" s="33" t="inlineStr">
+        <is>
+          <t>RCA approved and sent to the customer on 25-Jun-2026 as a PDF attached to EAO-9; the document text is not in the ticket. The WarRoom itself was published before the RCA was issued.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="35" t="n">
@@ -9810,6 +9898,7 @@
           <t>EAO-5</t>
         </is>
       </c>
+      <c r="X64" s="33" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="35" t="n">
@@ -9909,6 +9998,7 @@
           <t>EAO-11</t>
         </is>
       </c>
+      <c r="X65" s="33" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="35" t="n">
@@ -10012,6 +10102,11 @@
           <t>EAO-12</t>
         </is>
       </c>
+      <c r="X66" s="33" t="inlineStr">
+        <is>
+          <t>Feeds covering the BorgWarner Vigo indefinite strike were in the public domain from 26-Jun-2026 but were not captured on the portal until 1 July; Engineering was asked to investigate why the 26-27 June sources were missed. RCA approved and shared 09-Jul-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="35" t="n">
@@ -10111,6 +10206,7 @@
           <t>EAO-13</t>
         </is>
       </c>
+      <c r="X67" s="33" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="35" t="n">
@@ -10210,6 +10306,11 @@
           <t>EAO-14</t>
         </is>
       </c>
+      <c r="X68" s="33" t="inlineStr">
+        <is>
+          <t>RCA approved and sent to the customer on 13-Jul-2026 as a PDF attached to EAO-14; the document text is not in the ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="35" t="n">
@@ -10313,6 +10414,11 @@
           <t>EAO-15</t>
         </is>
       </c>
+      <c r="X69" s="33" t="inlineStr">
+        <is>
+          <t>The event met the Price Fluctuation reporting threshold and did qualify for a WarRoom; the failure came later, in customer-specific supplier normalization. The Samsung Electronics sites are normalized under Samsung for the affected customer, and that normalization was not applied during the impacted-site assessment, so the sites were never associated with the event and no customer WarRoom was created. This was not a parent-child modelling issue. Normalization is maintained outside the EventWatch editorial workflow, so the response is strengthened validation controls plus AI-assisted WarRoom generation rather than a guarantee. RCA shared 15-Jul-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="35" t="n">
@@ -10410,6 +10516,11 @@
           <t>EAO-16</t>
         </is>
       </c>
+      <c r="X70" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch captured multiple Philippines articles before the dedicated Philippines WarRoom was created, but they were assessed Not Impactful during reporting review, when available reports still described preparedness and localized impacts. Root cause: human assessment error underestimating the significance of the evolving Philippines impacts, which delayed WarRoom creation. Preventive: multi-country weather events assessed independently for each affected geography rather than inferred from the wider storm.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="35" t="n">
@@ -10507,6 +10618,11 @@
           <t>EAO-17</t>
         </is>
       </c>
+      <c r="X71" s="33" t="inlineStr">
+        <is>
+          <t>RCA reviewed and sent to the customer on 14-Jul-2026 as a PDF attached to EAO-17; the document text is not in the ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="35" t="n">
@@ -10604,6 +10720,7 @@
           <t>EAO-18</t>
         </is>
       </c>
+      <c r="X72" s="33" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="35" t="n">
@@ -10701,6 +10818,11 @@
           <t>EAO-19</t>
         </is>
       </c>
+      <c r="X73" s="33" t="inlineStr">
+        <is>
+          <t>Not a miss - an inquiry answered in full. EventWatch monitors power infrastructure continuously across utilities and transmission operators, government and emergency agencies, grid operators, news sources and official outage maps. Reporting is risk-based rather than every outage: mapped supplier sites in the affected region, impact on manufacturing hubs, ports, warehouses and logistics, expected outage duration, and public confirmation of operational disruption, all against regional reporting thresholds.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="35" t="n">
@@ -10798,6 +10920,11 @@
           <t>EAO-20</t>
         </is>
       </c>
+      <c r="X74" s="33" t="inlineStr">
+        <is>
+          <t>German-language sources reporting the ASSMANN WSW Components insolvency were not captured by the portal; Engineering was asked to investigate the feed gap. RCA reviewed and shared with the customer 20-Jul-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="35" t="n">
@@ -10895,6 +11022,11 @@
           <t>EAO-21</t>
         </is>
       </c>
+      <c r="X75" s="33" t="inlineStr">
+        <is>
+          <t>RCA approved and sent to the customer on 21-Jul-2026 as a PDF attached to EAO-21; the document text is not in the ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="35" t="n">
@@ -10992,6 +11124,7 @@
           <t>EAO-22</t>
         </is>
       </c>
+      <c r="X76" s="33" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="35" t="n">
@@ -11091,6 +11224,7 @@
           <t>EAO-24</t>
         </is>
       </c>
+      <c r="X77" s="33" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="35" t="n">
@@ -11188,6 +11322,11 @@
           <t>EAO-25</t>
         </is>
       </c>
+      <c r="X78" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="35" t="n">
@@ -11285,6 +11424,11 @@
           <t>EAO-25</t>
         </is>
       </c>
+      <c r="X79" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="35" t="n">
@@ -11384,6 +11528,11 @@
           <t>EAO-23</t>
         </is>
       </c>
+      <c r="X80" s="33" t="inlineStr">
+        <is>
+          <t>RCA approved and sent to the customer on 05-Aug-2026 as a PDF attached to EAO-23; the document text is not in the ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="35" t="n">
@@ -11483,6 +11632,11 @@
           <t>EAO-27</t>
         </is>
       </c>
+      <c r="X81" s="33" t="inlineStr">
+        <is>
+          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-27; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="35" t="n">
@@ -11580,6 +11734,11 @@
           <t>EAO-28</t>
         </is>
       </c>
+      <c r="X82" s="33" t="inlineStr">
+        <is>
+          <t>No RCA document issued - the team shares one only where there was a miss. Clarification given instead: EventWatch published the Kandla congestion event on reports of clearance delays up to 40 days and container shortages. The source article highlighted rice exports, but nothing indicated the congestion was confined to rice cargo, so mapped supplier sites within the impact area were sent Supplier Impact Confirmation requests as proactive validation. The outreach was not a statement that those suppliers were already impacted.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="35" t="n">
@@ -11679,6 +11838,11 @@
           <t>EAO-26</t>
         </is>
       </c>
+      <c r="X83" s="33" t="inlineStr">
+        <is>
+          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-26; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="35" t="n">
@@ -11778,6 +11942,7 @@
           <t>EAO-29</t>
         </is>
       </c>
+      <c r="X84" s="33" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="35" t="n">
@@ -11877,6 +12042,11 @@
           <t>EAO-25</t>
         </is>
       </c>
+      <c r="X85" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="35" t="n">
@@ -11976,6 +12146,11 @@
           <t>EAO-25</t>
         </is>
       </c>
+      <c r="X86" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="35" t="n">
@@ -12075,6 +12250,11 @@
           <t>EAO-25</t>
         </is>
       </c>
+      <c r="X87" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="35" t="n">
@@ -12169,6 +12349,12 @@
           <t>Notification Visibility Monitoring</t>
         </is>
       </c>
+      <c r="W88" s="33" t="inlineStr">
+        <is>
+          <t>TS-22695</t>
+        </is>
+      </c>
+      <c r="X88" s="33" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="35" t="n">
@@ -12268,6 +12454,11 @@
           <t>EAO-31</t>
         </is>
       </c>
+      <c r="X89" s="33" t="inlineStr">
+        <is>
+          <t>Feeds reporting the Qilin ransomware breach at Gindre India were not captured on the EventWatch portal; Engineering investigation requested 31-Aug-2026. RCA reviewed and shared with the customer 03-Sep-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="35" t="n">
@@ -12362,6 +12553,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X90" s="33" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="35" t="n">
@@ -12456,6 +12648,7 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
+      <c r="X91" s="33" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="35" t="n">
@@ -12553,6 +12746,7 @@
           <t>EAO-32</t>
         </is>
       </c>
+      <c r="X92" s="33" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="35" t="n">
@@ -12650,6 +12844,7 @@
           <t>EAO-33</t>
         </is>
       </c>
+      <c r="X93" s="33" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="35" t="n">
@@ -12747,6 +12942,7 @@
           <t>EAO-34</t>
         </is>
       </c>
+      <c r="X94" s="33" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="35" t="n">
@@ -12848,6 +13044,7 @@
           <t>EAO-35</t>
         </is>
       </c>
+      <c r="X95" s="33" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -15840,7 +16037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16512,30 +16709,30 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="30.75" customHeight="1">
+    <row r="27">
       <c r="A27" s="42" t="inlineStr">
         <is>
-          <t>Operational term</t>
+          <t>Field definition</t>
         </is>
       </c>
       <c r="B27" s="41" t="inlineStr">
         <is>
-          <t>EventWatch</t>
+          <t>RCA Details</t>
         </is>
       </c>
       <c r="C27" s="41" t="inlineStr">
         <is>
-          <t>Operational monitoring service that identifies, assesses, and reports events relevant to customers.</t>
+          <t>Root cause summary for the record, taken from the RCA shared on the linked Jira ticket.</t>
         </is>
       </c>
       <c r="D27" s="41" t="inlineStr">
         <is>
-          <t>Common EventWatch terminology</t>
+          <t>Free text. Blank where no RCA was requested or none has been issued yet. Where the RCA went out only as a PDF attachment the entry says so, rather than paraphrasing a document that is not in the ticket.</t>
         </is>
       </c>
       <c r="E27" s="41" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>RCA Details</t>
         </is>
       </c>
     </row>
@@ -16547,12 +16744,12 @@
       </c>
       <c r="B28" s="41" t="inlineStr">
         <is>
-          <t>WarRoom</t>
+          <t>EventWatch</t>
         </is>
       </c>
       <c r="C28" s="41" t="inlineStr">
         <is>
-          <t>Central event workspace used to publish, organize, and update an operational event.</t>
+          <t>Operational monitoring service that identifies, assesses, and reports events relevant to customers.</t>
         </is>
       </c>
       <c r="D28" s="41" t="inlineStr">
@@ -16574,12 +16771,12 @@
       </c>
       <c r="B29" s="41" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>WarRoom</t>
         </is>
       </c>
       <c r="C29" s="41" t="inlineStr">
         <is>
-          <t>Root Cause Analysis; a documented explanation of why an issue occurred and the corrective/preventive actions.</t>
+          <t>Central event workspace used to publish, organize, and update an operational event.</t>
         </is>
       </c>
       <c r="D29" s="41" t="inlineStr">
@@ -16601,12 +16798,12 @@
       </c>
       <c r="B30" s="41" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
-          <t>Non-Conformance; an internal quality record raised when required process or control performance was not met.</t>
+          <t>Root Cause Analysis; a documented explanation of why an issue occurred and the corrective/preventive actions.</t>
         </is>
       </c>
       <c r="D30" s="41" t="inlineStr">
@@ -16628,12 +16825,12 @@
       </c>
       <c r="B31" s="41" t="inlineStr">
         <is>
-          <t>Not Impactful</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="C31" s="41" t="inlineStr">
         <is>
-          <t>Review outcome indicating that available evidence did not meet the threshold for EventWatch escalation.</t>
+          <t>Non-Conformance; an internal quality record raised when required process or control performance was not met.</t>
         </is>
       </c>
       <c r="D31" s="41" t="inlineStr">
@@ -16655,12 +16852,12 @@
       </c>
       <c r="B32" s="41" t="inlineStr">
         <is>
-          <t>Feed harvesting</t>
+          <t>Not Impactful</t>
         </is>
       </c>
       <c r="C32" s="41" t="inlineStr">
         <is>
-          <t>Automated collection of articles or reports from monitored information sources.</t>
+          <t>Review outcome indicating that available evidence did not meet the threshold for EventWatch escalation.</t>
         </is>
       </c>
       <c r="D32" s="41" t="inlineStr">
@@ -16682,12 +16879,12 @@
       </c>
       <c r="B33" s="41" t="inlineStr">
         <is>
-          <t>Source coverage</t>
+          <t>Feed harvesting</t>
         </is>
       </c>
       <c r="C33" s="41" t="inlineStr">
         <is>
-          <t>Availability and monitoring of relevant websites, feeds, registries, or publications.</t>
+          <t>Automated collection of articles or reports from monitored information sources.</t>
         </is>
       </c>
       <c r="D33" s="41" t="inlineStr">
@@ -16709,12 +16906,12 @@
       </c>
       <c r="B34" s="41" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Source coverage</t>
         </is>
       </c>
       <c r="C34" s="41" t="inlineStr">
         <is>
-          <t>Addition or refinement of search terms when available content was not identified correctly.</t>
+          <t>Availability and monitoring of relevant websites, feeds, registries, or publications.</t>
         </is>
       </c>
       <c r="D34" s="41" t="inlineStr">
@@ -16736,12 +16933,12 @@
       </c>
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>Geofencing</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
         <is>
-          <t>Geographic impact logic used to associate an event area with customer or supplier locations.</t>
+          <t>Addition or refinement of search terms when available content was not identified correctly.</t>
         </is>
       </c>
       <c r="D35" s="41" t="inlineStr">
@@ -16763,12 +16960,12 @@
       </c>
       <c r="B36" s="41" t="inlineStr">
         <is>
-          <t>Cluster</t>
+          <t>Geofencing</t>
         </is>
       </c>
       <c r="C36" s="41" t="inlineStr">
         <is>
-          <t>Grouping of related articles or bulletins into one event record or WarRoom.</t>
+          <t>Geographic impact logic used to associate an event area with customer or supplier locations.</t>
         </is>
       </c>
       <c r="D36" s="41" t="inlineStr">
@@ -16790,12 +16987,12 @@
       </c>
       <c r="B37" s="41" t="inlineStr">
         <is>
-          <t>Human-in-the-loop review</t>
+          <t>Cluster</t>
         </is>
       </c>
       <c r="C37" s="41" t="inlineStr">
         <is>
-          <t>Analyst review that validates automated detection and decides whether to escalate or publish.</t>
+          <t>Grouping of related articles or bulletins into one event record or WarRoom.</t>
         </is>
       </c>
       <c r="D37" s="41" t="inlineStr">
@@ -16817,12 +17014,12 @@
       </c>
       <c r="B38" s="41" t="inlineStr">
         <is>
-          <t>Impacted supplier</t>
+          <t>Human-in-the-loop review</t>
         </is>
       </c>
       <c r="C38" s="41" t="inlineStr">
         <is>
-          <t>Customer-mapped supplier assessed as potentially affected by an event.</t>
+          <t>Analyst review that validates automated detection and decides whether to escalate or publish.</t>
         </is>
       </c>
       <c r="D38" s="41" t="inlineStr">
@@ -16839,233 +17036,233 @@
     <row r="39" ht="30.75" customHeight="1">
       <c r="A39" s="42" t="inlineStr">
         <is>
+          <t>Operational term</t>
+        </is>
+      </c>
+      <c r="B39" s="41" t="inlineStr">
+        <is>
+          <t>Impacted supplier</t>
+        </is>
+      </c>
+      <c r="C39" s="41" t="inlineStr">
+        <is>
+          <t>Customer-mapped supplier assessed as potentially affected by an event.</t>
+        </is>
+      </c>
+      <c r="D39" s="41" t="inlineStr">
+        <is>
+          <t>Common EventWatch terminology</t>
+        </is>
+      </c>
+      <c r="E39" s="41" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30.75" customHeight="1">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B39" s="41" t="inlineStr">
+      <c r="B40" s="41" t="inlineStr">
         <is>
           <t>Bankruptcy</t>
         </is>
       </c>
-      <c r="C39" s="41" t="inlineStr">
+      <c r="C40" s="41" t="inlineStr">
         <is>
           <t>Formal insolvency, bankruptcy filing, restructuring, or equivalent proceeding.</t>
         </is>
       </c>
-      <c r="D39" s="41" t="inlineStr">
+      <c r="D40" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E39" s="41" t="inlineStr">
+      <c r="E40" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="42" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B40" s="41" t="inlineStr">
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>Chemical Spill</t>
         </is>
       </c>
-      <c r="C40" s="41" t="inlineStr">
+      <c r="C41" s="41" t="inlineStr">
         <is>
           <t>Release or leak of a hazardous chemical substance.</t>
         </is>
       </c>
-      <c r="D40" s="41" t="inlineStr">
+      <c r="D41" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E40" s="41" t="inlineStr">
+      <c r="E41" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30.75" customHeight="1">
-      <c r="A41" s="42" t="inlineStr">
+    <row r="42" ht="30.75" customHeight="1">
+      <c r="A42" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B41" s="41" t="inlineStr">
+      <c r="B42" s="41" t="inlineStr">
         <is>
           <t>Cyber Attack</t>
         </is>
       </c>
-      <c r="C41" s="41" t="inlineStr">
+      <c r="C42" s="41" t="inlineStr">
         <is>
           <t>Cybersecurity incident such as ransomware, intrusion, compromise, or data breach.</t>
         </is>
       </c>
-      <c r="D41" s="41" t="inlineStr">
+      <c r="D42" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E41" s="41" t="inlineStr">
+      <c r="E42" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="42" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B42" s="41" t="inlineStr">
+      <c r="B43" s="41" t="inlineStr">
         <is>
           <t>Earthquake</t>
         </is>
       </c>
-      <c r="C42" s="41" t="inlineStr">
+      <c r="C43" s="41" t="inlineStr">
         <is>
           <t>Seismic event with potential operational or supply-chain impact.</t>
         </is>
       </c>
-      <c r="D42" s="41" t="inlineStr">
+      <c r="D43" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E42" s="41" t="inlineStr">
+      <c r="E43" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30.75" customHeight="1">
-      <c r="A43" s="42" t="inlineStr">
+    <row r="44" ht="30.75" customHeight="1">
+      <c r="A44" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B43" s="41" t="inlineStr">
+      <c r="B44" s="41" t="inlineStr">
         <is>
           <t>Extreme Weather</t>
         </is>
       </c>
-      <c r="C43" s="41" t="inlineStr">
+      <c r="C44" s="41" t="inlineStr">
         <is>
           <t>Severe weather such as storms, tornadoes, typhoons, flooding, or snowstorms.</t>
         </is>
       </c>
-      <c r="D43" s="41" t="inlineStr">
+      <c r="D44" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E43" s="41" t="inlineStr">
+      <c r="E44" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="42" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B44" s="41" t="inlineStr">
+      <c r="B45" s="41" t="inlineStr">
         <is>
           <t>Factory Closure</t>
         </is>
       </c>
-      <c r="C44" s="41" t="inlineStr">
+      <c r="C45" s="41" t="inlineStr">
         <is>
           <t>Planned or unplanned closure of a manufacturing facility.</t>
         </is>
       </c>
-      <c r="D44" s="41" t="inlineStr">
+      <c r="D45" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E44" s="41" t="inlineStr">
+      <c r="E45" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30.75" customHeight="1">
-      <c r="A45" s="42" t="inlineStr">
+    <row r="46" ht="30.75" customHeight="1">
+      <c r="A46" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B45" s="41" t="inlineStr">
+      <c r="B46" s="41" t="inlineStr">
         <is>
           <t>Factory Disruption</t>
         </is>
       </c>
-      <c r="C45" s="41" t="inlineStr">
+      <c r="C46" s="41" t="inlineStr">
         <is>
           <t>Operational interruption at a manufacturing facility that is not classified as closure or fire.</t>
         </is>
       </c>
-      <c r="D45" s="41" t="inlineStr">
+      <c r="D46" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E45" s="41" t="inlineStr">
+      <c r="E46" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="42" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B46" s="41" t="inlineStr">
+      <c r="B47" s="41" t="inlineStr">
         <is>
           <t>Factory Fire</t>
         </is>
       </c>
-      <c r="C46" s="41" t="inlineStr">
+      <c r="C47" s="41" t="inlineStr">
         <is>
           <t>Fire affecting a manufacturing, production, or storage facility.</t>
-        </is>
-      </c>
-      <c r="D46" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category</t>
-        </is>
-      </c>
-      <c r="E46" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30.75" customHeight="1">
-      <c r="A47" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B47" s="41" t="inlineStr">
-        <is>
-          <t>Financial Distress</t>
-        </is>
-      </c>
-      <c r="C47" s="41" t="inlineStr">
-        <is>
-          <t>Material financial difficulty that does not yet constitute a formal bankruptcy event.</t>
         </is>
       </c>
       <c r="D47" s="41" t="inlineStr">
@@ -17087,39 +17284,39 @@
       </c>
       <c r="B48" s="41" t="inlineStr">
         <is>
+          <t>Financial Distress</t>
+        </is>
+      </c>
+      <c r="C48" s="41" t="inlineStr">
+        <is>
+          <t>Material financial difficulty that does not yet constitute a formal bankruptcy event.</t>
+        </is>
+      </c>
+      <c r="D48" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category</t>
+        </is>
+      </c>
+      <c r="E48" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30.75" customHeight="1">
+      <c r="A49" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B49" s="41" t="inlineStr">
+        <is>
           <t>Geopolitical</t>
         </is>
       </c>
-      <c r="C48" s="41" t="inlineStr">
+      <c r="C49" s="41" t="inlineStr">
         <is>
           <t>Political, border, security, conflict, or humanitarian development affecting operations.</t>
-        </is>
-      </c>
-      <c r="D48" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category</t>
-        </is>
-      </c>
-      <c r="E48" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B49" s="41" t="inlineStr">
-        <is>
-          <t>Labor Disruption</t>
-        </is>
-      </c>
-      <c r="C49" s="41" t="inlineStr">
-        <is>
-          <t>Strike, work stoppage, industrial action, or labor-related disruption.</t>
         </is>
       </c>
       <c r="D49" s="41" t="inlineStr">
@@ -17141,12 +17338,12 @@
       </c>
       <c r="B50" s="41" t="inlineStr">
         <is>
-          <t>Leadership Transition</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="C50" s="41" t="inlineStr">
         <is>
-          <t>Change in senior executive or organizational leadership.</t>
+          <t>Strike, work stoppage, industrial action, or labor-related disruption.</t>
         </is>
       </c>
       <c r="D50" s="41" t="inlineStr">
@@ -17168,12 +17365,12 @@
       </c>
       <c r="B51" s="41" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Leadership Transition</t>
         </is>
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>Merger, acquisition, divestiture, or comparable corporate transaction.</t>
+          <t>Change in senior executive or organizational leadership.</t>
         </is>
       </c>
       <c r="D51" s="41" t="inlineStr">
@@ -17195,12 +17392,12 @@
       </c>
       <c r="B52" s="41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="C52" s="41" t="inlineStr">
         <is>
-          <t>No applicable event category, generally used for non-event inquiries.</t>
+          <t>Merger, acquisition, divestiture, or comparable corporate transaction.</t>
         </is>
       </c>
       <c r="D52" s="41" t="inlineStr">
@@ -17222,12 +17419,12 @@
       </c>
       <c r="B53" s="41" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C53" s="41" t="inlineStr">
         <is>
-          <t>Demonstration, civil unrest, riot, or blockade driven by protest activity.</t>
+          <t>No applicable event category, generally used for non-event inquiries.</t>
         </is>
       </c>
       <c r="D53" s="41" t="inlineStr">
@@ -17249,93 +17446,93 @@
       </c>
       <c r="B54" s="41" t="inlineStr">
         <is>
+          <t>Protest/Riot</t>
+        </is>
+      </c>
+      <c r="C54" s="41" t="inlineStr">
+        <is>
+          <t>Demonstration, civil unrest, riot, or blockade driven by protest activity.</t>
+        </is>
+      </c>
+      <c r="D54" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category</t>
+        </is>
+      </c>
+      <c r="E54" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B55" s="41" t="inlineStr">
+        <is>
           <t>Regulatory Change</t>
         </is>
       </c>
-      <c r="C54" s="41" t="inlineStr">
+      <c r="C55" s="41" t="inlineStr">
         <is>
           <t>Government rule, sanction, export control, or regulatory action.</t>
         </is>
       </c>
-      <c r="D54" s="41" t="inlineStr">
+      <c r="D55" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E54" s="41" t="inlineStr">
+      <c r="E55" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="30.75" customHeight="1">
-      <c r="A55" s="42" t="inlineStr">
+    <row r="56" ht="30.75" customHeight="1">
+      <c r="A56" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B55" s="41" t="inlineStr">
+      <c r="B56" s="41" t="inlineStr">
         <is>
           <t>Supply Shortage</t>
         </is>
       </c>
-      <c r="C55" s="41" t="inlineStr">
+      <c r="C56" s="41" t="inlineStr">
         <is>
           <t>Shortage or constrained availability of materials, components, energy, or goods.</t>
         </is>
       </c>
-      <c r="D55" s="41" t="inlineStr">
+      <c r="D56" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E55" s="41" t="inlineStr">
+      <c r="E56" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="42" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B56" s="41" t="inlineStr">
+      <c r="B57" s="41" t="inlineStr">
         <is>
           <t>Transport Disruption</t>
         </is>
       </c>
-      <c r="C56" s="41" t="inlineStr">
+      <c r="C57" s="41" t="inlineStr">
         <is>
           <t>Disruption to roads, bridges, ports, rail, air, or logistics routes.</t>
-        </is>
-      </c>
-      <c r="D56" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category</t>
-        </is>
-      </c>
-      <c r="E56" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30.75" customHeight="1">
-      <c r="A57" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B57" s="41" t="inlineStr">
-        <is>
-          <t>Wildfire</t>
-        </is>
-      </c>
-      <c r="C57" s="41" t="inlineStr">
-        <is>
-          <t>Uncontrolled vegetation fire with potential geographic or operational impact.</t>
         </is>
       </c>
       <c r="D57" s="41" t="inlineStr">
@@ -17352,27 +17549,27 @@
     <row r="58" ht="30.75" customHeight="1">
       <c r="A58" s="42" t="inlineStr">
         <is>
-          <t>Issue type</t>
+          <t>Event type</t>
         </is>
       </c>
       <c r="B58" s="41" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="C58" s="41" t="inlineStr">
         <is>
-          <t>Customer reports a service failure, miss, delay, incorrect action, or other concern.</t>
+          <t>Uncontrolled vegetation fire with potential geographic or operational impact.</t>
         </is>
       </c>
       <c r="D58" s="41" t="inlineStr">
         <is>
-          <t>Included in complaint metrics</t>
+          <t>Standard event category</t>
         </is>
       </c>
       <c r="E58" s="41" t="inlineStr">
         <is>
-          <t>Issue Type</t>
+          <t>Event type</t>
         </is>
       </c>
     </row>
@@ -17384,17 +17581,17 @@
       </c>
       <c r="B59" s="41" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="C59" s="41" t="inlineStr">
         <is>
-          <t>Customer requests verification, explanation, or information without a confirmed service failure.</t>
+          <t>Customer reports a service failure, miss, delay, incorrect action, or other concern.</t>
         </is>
       </c>
       <c r="D59" s="41" t="inlineStr">
         <is>
-          <t>Tracked separately from complaints</t>
+          <t>Included in complaint metrics</t>
         </is>
       </c>
       <c r="E59" s="41" t="inlineStr">
@@ -17406,27 +17603,27 @@
     <row r="60" ht="30.75" customHeight="1">
       <c r="A60" s="42" t="inlineStr">
         <is>
-          <t>Root cause</t>
+          <t>Issue type</t>
         </is>
       </c>
       <c r="B60" s="41" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="C60" s="41" t="inlineStr">
         <is>
-          <t>Human judgment, review, prioritization, publishing, or execution was the primary cause.</t>
+          <t>Customer requests verification, explanation, or information without a confirmed service failure.</t>
         </is>
       </c>
       <c r="D60" s="41" t="inlineStr">
         <is>
-          <t>Primary cause domain</t>
+          <t>Tracked separately from complaints</t>
         </is>
       </c>
       <c r="E60" s="41" t="inlineStr">
         <is>
-          <t>Root Cause</t>
+          <t>Issue Type</t>
         </is>
       </c>
     </row>
@@ -17438,12 +17635,12 @@
       </c>
       <c r="B61" s="41" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="C61" s="41" t="inlineStr">
         <is>
-          <t>Policy, workflow, threshold, mapping method, or procedural design was the primary cause.</t>
+          <t>Human judgment, review, prioritization, publishing, or execution was the primary cause.</t>
         </is>
       </c>
       <c r="D61" s="41" t="inlineStr">
@@ -17465,49 +17662,49 @@
       </c>
       <c r="B62" s="41" t="inlineStr">
         <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C62" s="41" t="inlineStr">
+        <is>
+          <t>Policy, workflow, threshold, mapping method, or procedural design was the primary cause.</t>
+        </is>
+      </c>
+      <c r="D62" s="41" t="inlineStr">
+        <is>
+          <t>Primary cause domain</t>
+        </is>
+      </c>
+      <c r="E62" s="41" t="inlineStr">
+        <is>
+          <t>Root Cause</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30.75" customHeight="1">
+      <c r="A63" s="42" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+      <c r="B63" s="41" t="inlineStr">
+        <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="C62" s="41" t="inlineStr">
+      <c r="C63" s="41" t="inlineStr">
         <is>
           <t>Technology, data ingestion, source coverage, detection, clustering, or platform behavior was the primary cause.</t>
         </is>
       </c>
-      <c r="D62" s="41" t="inlineStr">
+      <c r="D63" s="41" t="inlineStr">
         <is>
           <t>Primary cause domain</t>
         </is>
       </c>
-      <c r="E62" s="41" t="inlineStr">
+      <c r="E63" s="41" t="inlineStr">
         <is>
           <t>Root Cause</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B63" s="41" t="inlineStr">
-        <is>
-          <t>Captured Late</t>
-        </is>
-      </c>
-      <c r="C63" s="41" t="inlineStr">
-        <is>
-          <t>Relevant information entered the workflow later than required.</t>
-        </is>
-      </c>
-      <c r="D63" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E63" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
         </is>
       </c>
     </row>
@@ -17519,66 +17716,66 @@
       </c>
       <c r="B64" s="41" t="inlineStr">
         <is>
+          <t>Captured Late</t>
+        </is>
+      </c>
+      <c r="C64" s="41" t="inlineStr">
+        <is>
+          <t>Relevant information entered the workflow later than required.</t>
+        </is>
+      </c>
+      <c r="D64" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E64" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B65" s="41" t="inlineStr">
+        <is>
           <t>Duplication</t>
         </is>
       </c>
-      <c r="C64" s="41" t="inlineStr">
+      <c r="C65" s="41" t="inlineStr">
         <is>
           <t>Related content was split into duplicate WarRooms or event records.</t>
         </is>
       </c>
-      <c r="D64" s="41" t="inlineStr">
+      <c r="D65" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E64" s="41" t="inlineStr">
+      <c r="E65" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="30.75" customHeight="1">
-      <c r="A65" s="42" t="inlineStr">
+    <row r="66" ht="30.75" customHeight="1">
+      <c r="A66" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B65" s="41" t="inlineStr">
+      <c r="B66" s="41" t="inlineStr">
         <is>
           <t>Event Identification</t>
         </is>
       </c>
-      <c r="C65" s="41" t="inlineStr">
+      <c r="C66" s="41" t="inlineStr">
         <is>
           <t>The relevant event was not recognized or converted into reportable coverage.</t>
-        </is>
-      </c>
-      <c r="D65" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E65" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B66" s="41" t="inlineStr">
-        <is>
-          <t>Industry selection</t>
-        </is>
-      </c>
-      <c r="C66" s="41" t="inlineStr">
-        <is>
-          <t>An incorrect or missing industry classification affected tracking.</t>
         </is>
       </c>
       <c r="D66" s="41" t="inlineStr">
@@ -17600,66 +17797,66 @@
       </c>
       <c r="B67" s="41" t="inlineStr">
         <is>
+          <t>Industry selection</t>
+        </is>
+      </c>
+      <c r="C67" s="41" t="inlineStr">
+        <is>
+          <t>An incorrect or missing industry classification affected tracking.</t>
+        </is>
+      </c>
+      <c r="D67" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E67" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B68" s="41" t="inlineStr">
+        <is>
           <t>Keyword Update</t>
         </is>
       </c>
-      <c r="C67" s="41" t="inlineStr">
+      <c r="C68" s="41" t="inlineStr">
         <is>
           <t>Search or detection terms required addition or refinement.</t>
         </is>
       </c>
-      <c r="D67" s="41" t="inlineStr">
+      <c r="D68" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E67" s="41" t="inlineStr">
+      <c r="E68" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="30.75" customHeight="1">
-      <c r="A68" s="42" t="inlineStr">
+    <row r="69" ht="30.75" customHeight="1">
+      <c r="A69" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B68" s="41" t="inlineStr">
+      <c r="B69" s="41" t="inlineStr">
         <is>
           <t>Mapping</t>
         </is>
       </c>
-      <c r="C68" s="41" t="inlineStr">
+      <c r="C69" s="41" t="inlineStr">
         <is>
           <t>Customer, supplier, company, facility, or impact relationship was missing or incorrect.</t>
-        </is>
-      </c>
-      <c r="D68" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E68" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B69" s="41" t="inlineStr">
-        <is>
-          <t>Policy/Logic</t>
-        </is>
-      </c>
-      <c r="C69" s="41" t="inlineStr">
-        <is>
-          <t>A rule, threshold, or decision logic produced or explained the outcome.</t>
         </is>
       </c>
       <c r="D69" s="41" t="inlineStr">
@@ -17681,39 +17878,39 @@
       </c>
       <c r="B70" s="41" t="inlineStr">
         <is>
+          <t>Policy/Logic</t>
+        </is>
+      </c>
+      <c r="C70" s="41" t="inlineStr">
+        <is>
+          <t>A rule, threshold, or decision logic produced or explained the outcome.</t>
+        </is>
+      </c>
+      <c r="D70" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E70" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B71" s="41" t="inlineStr">
+        <is>
           <t>Prioritization</t>
         </is>
       </c>
-      <c r="C70" s="41" t="inlineStr">
+      <c r="C71" s="41" t="inlineStr">
         <is>
           <t>A detected item was not handled with the required urgency.</t>
-        </is>
-      </c>
-      <c r="D70" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E70" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="30.75" customHeight="1">
-      <c r="A71" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B71" s="41" t="inlineStr">
-        <is>
-          <t>Process Clarification</t>
-        </is>
-      </c>
-      <c r="C71" s="41" t="inlineStr">
-        <is>
-          <t>The case required explanation of policy, thresholds, or workflow rather than defect correction.</t>
         </is>
       </c>
       <c r="D71" s="41" t="inlineStr">
@@ -17735,93 +17932,93 @@
       </c>
       <c r="B72" s="41" t="inlineStr">
         <is>
+          <t>Process Clarification</t>
+        </is>
+      </c>
+      <c r="C72" s="41" t="inlineStr">
+        <is>
+          <t>The case required explanation of policy, thresholds, or workflow rather than defect correction.</t>
+        </is>
+      </c>
+      <c r="D72" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E72" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30.75" customHeight="1">
+      <c r="A73" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B73" s="41" t="inlineStr">
+        <is>
           <t>Relevancy</t>
         </is>
       </c>
-      <c r="C72" s="41" t="inlineStr">
+      <c r="C73" s="41" t="inlineStr">
         <is>
           <t>The item’s relevance to the customer or EventWatch scope was disputed or incorrectly assessed.</t>
         </is>
       </c>
-      <c r="D72" s="41" t="inlineStr">
+      <c r="D73" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E72" s="41" t="inlineStr">
+      <c r="E73" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="42" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B73" s="41" t="inlineStr">
+      <c r="B74" s="41" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="C73" s="41" t="inlineStr">
+      <c r="C74" s="41" t="inlineStr">
         <is>
           <t>Human assessment or quality review led to the issue.</t>
         </is>
       </c>
-      <c r="D73" s="41" t="inlineStr">
+      <c r="D74" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E73" s="41" t="inlineStr">
+      <c r="E74" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="30.75" customHeight="1">
-      <c r="A74" s="42" t="inlineStr">
+    <row r="75" ht="30.75" customHeight="1">
+      <c r="A75" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B74" s="41" t="inlineStr">
+      <c r="B75" s="41" t="inlineStr">
         <is>
           <t>Source Coverage</t>
         </is>
       </c>
-      <c r="C74" s="41" t="inlineStr">
+      <c r="C75" s="41" t="inlineStr">
         <is>
           <t>The relevant source was unavailable, unmonitored, restricted, or not harvested.</t>
-        </is>
-      </c>
-      <c r="D74" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E74" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B75" s="41" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="C75" s="41" t="inlineStr">
-        <is>
-          <t>The concern relates to reporting or consolidation strategy.</t>
         </is>
       </c>
       <c r="D75" s="41" t="inlineStr">
@@ -17843,39 +18040,39 @@
       </c>
       <c r="B76" s="41" t="inlineStr">
         <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="C76" s="41" t="inlineStr">
+        <is>
+          <t>The concern relates to reporting or consolidation strategy.</t>
+        </is>
+      </c>
+      <c r="D76" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E76" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B77" s="41" t="inlineStr">
+        <is>
           <t>Tagging</t>
         </is>
       </c>
-      <c r="C76" s="41" t="inlineStr">
+      <c r="C77" s="41" t="inlineStr">
         <is>
           <t>A required category or industry tag was missing or incorrect.</t>
-        </is>
-      </c>
-      <c r="D76" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E76" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30.75" customHeight="1">
-      <c r="A77" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B77" s="41" t="inlineStr">
-        <is>
-          <t>Visibility</t>
-        </is>
-      </c>
-      <c r="C77" s="41" t="inlineStr">
-        <is>
-          <t>Published content was not visible because of profile, portal, notification, or display conditions.</t>
         </is>
       </c>
       <c r="D77" s="41" t="inlineStr">
@@ -17897,12 +18094,12 @@
       </c>
       <c r="B78" s="41" t="inlineStr">
         <is>
-          <t>WarRoom Creation</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="C78" s="41" t="inlineStr">
         <is>
-          <t>A required WarRoom was not created despite available EventWatch coverage.</t>
+          <t>Published content was not visible because of profile, portal, notification, or display conditions.</t>
         </is>
       </c>
       <c r="D78" s="41" t="inlineStr">
@@ -17919,27 +18116,27 @@
     <row r="79" ht="30.75" customHeight="1">
       <c r="A79" s="42" t="inlineStr">
         <is>
-          <t>Improvement classification</t>
+          <t>Sub-type</t>
         </is>
       </c>
       <c r="B79" s="41" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>WarRoom Creation</t>
         </is>
       </c>
       <c r="C79" s="41" t="inlineStr">
         <is>
-          <t>Control, workflow, model, or monitoring enhancement rather than correction of a confirmed defect.</t>
+          <t>A required WarRoom was not created despite available EventWatch coverage.</t>
         </is>
       </c>
       <c r="D79" s="41" t="inlineStr">
         <is>
-          <t>Enhancement</t>
+          <t>Detailed cause/handling category</t>
         </is>
       </c>
       <c r="E79" s="41" t="inlineStr">
         <is>
-          <t>Improvement VS Bug</t>
+          <t>Sub-type</t>
         </is>
       </c>
     </row>
@@ -17951,49 +18148,49 @@
       </c>
       <c r="B80" s="41" t="inlineStr">
         <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="C80" s="41" t="inlineStr">
+        <is>
+          <t>Control, workflow, model, or monitoring enhancement rather than correction of a confirmed defect.</t>
+        </is>
+      </c>
+      <c r="D80" s="41" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E80" s="41" t="inlineStr">
+        <is>
+          <t>Improvement VS Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="30.75" customHeight="1">
+      <c r="A81" s="42" t="inlineStr">
+        <is>
+          <t>Improvement classification</t>
+        </is>
+      </c>
+      <c r="B81" s="41" t="inlineStr">
+        <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="C80" s="41" t="inlineStr">
+      <c r="C81" s="41" t="inlineStr">
         <is>
           <t>Confirmed product or engineering defect requiring correction.</t>
         </is>
       </c>
-      <c r="D80" s="41" t="inlineStr">
+      <c r="D81" s="41" t="inlineStr">
         <is>
           <t>Defect</t>
         </is>
       </c>
-      <c r="E80" s="41" t="inlineStr">
+      <c r="E81" s="41" t="inlineStr">
         <is>
           <t>Improvement VS Bug</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="42" t="inlineStr">
-        <is>
-          <t>Fix status</t>
-        </is>
-      </c>
-      <c r="B81" s="41" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C81" s="41" t="inlineStr">
-        <is>
-          <t>Immediate corrective action was completed.</t>
-        </is>
-      </c>
-      <c r="D81" s="41" t="inlineStr">
-        <is>
-          <t>Current resolution state</t>
-        </is>
-      </c>
-      <c r="E81" s="41" t="inlineStr">
-        <is>
-          <t>Short Term Fix Status</t>
         </is>
       </c>
     </row>
@@ -18005,76 +18202,76 @@
       </c>
       <c r="B82" s="41" t="inlineStr">
         <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C82" s="41" t="inlineStr">
+        <is>
+          <t>Immediate corrective action was completed.</t>
+        </is>
+      </c>
+      <c r="D82" s="41" t="inlineStr">
+        <is>
+          <t>Current resolution state</t>
+        </is>
+      </c>
+      <c r="E82" s="41" t="inlineStr">
+        <is>
+          <t>Short Term Fix Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="42" t="inlineStr">
+        <is>
+          <t>Fix status</t>
+        </is>
+      </c>
+      <c r="B83" s="41" t="inlineStr">
+        <is>
           <t>RCA Shared</t>
         </is>
       </c>
-      <c r="C82" s="41" t="inlineStr">
+      <c r="C83" s="41" t="inlineStr">
         <is>
           <t>The root cause analysis was completed and shared with the customer.</t>
         </is>
       </c>
-      <c r="D82" s="41" t="inlineStr">
+      <c r="D83" s="41" t="inlineStr">
         <is>
           <t>Current resolution state</t>
         </is>
       </c>
-      <c r="E82" s="41" t="inlineStr">
+      <c r="E83" s="41" t="inlineStr">
         <is>
           <t>Short Term Fix Status</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="30.75" customHeight="1">
-      <c r="A83" s="42" t="inlineStr">
+    <row r="84" ht="30.75" customHeight="1">
+      <c r="A84" s="42" t="inlineStr">
         <is>
           <t>Fix status</t>
         </is>
       </c>
-      <c r="B83" s="41" t="inlineStr">
+      <c r="B84" s="41" t="inlineStr">
         <is>
           <t>Clarification Provided</t>
         </is>
       </c>
-      <c r="C83" s="41" t="inlineStr">
+      <c r="C84" s="41" t="inlineStr">
         <is>
           <t>The customer received an explanation, verification result, or policy/process clarification.</t>
         </is>
       </c>
-      <c r="D83" s="41" t="inlineStr">
+      <c r="D84" s="41" t="inlineStr">
         <is>
           <t>Current resolution state</t>
         </is>
       </c>
-      <c r="E83" s="41" t="inlineStr">
+      <c r="E84" s="41" t="inlineStr">
         <is>
           <t>Short Term Fix Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="42" t="inlineStr">
-        <is>
-          <t>Boolean flag</t>
-        </is>
-      </c>
-      <c r="B84" s="41" t="inlineStr">
-        <is>
-          <t>Yes — RCA Requested</t>
-        </is>
-      </c>
-      <c r="C84" s="41" t="inlineStr">
-        <is>
-          <t>A formal root cause analysis was requested.</t>
-        </is>
-      </c>
-      <c r="D84" s="41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E84" s="41" t="inlineStr">
-        <is>
-          <t>RCA Requested</t>
         </is>
       </c>
     </row>
@@ -18086,49 +18283,49 @@
       </c>
       <c r="B85" s="41" t="inlineStr">
         <is>
+          <t>Yes — RCA Requested</t>
+        </is>
+      </c>
+      <c r="C85" s="41" t="inlineStr">
+        <is>
+          <t>A formal root cause analysis was requested.</t>
+        </is>
+      </c>
+      <c r="D85" s="41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E85" s="41" t="inlineStr">
+        <is>
+          <t>RCA Requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="42" t="inlineStr">
+        <is>
+          <t>Boolean flag</t>
+        </is>
+      </c>
+      <c r="B86" s="41" t="inlineStr">
+        <is>
           <t>No — RCA Requested</t>
         </is>
       </c>
-      <c r="C85" s="41" t="inlineStr">
+      <c r="C86" s="41" t="inlineStr">
         <is>
           <t>No formal root cause analysis was requested.</t>
         </is>
       </c>
-      <c r="D85" s="41" t="inlineStr">
+      <c r="D86" s="41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E85" s="41" t="inlineStr">
+      <c r="E86" s="41" t="inlineStr">
         <is>
           <t>RCA Requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="30.75" customHeight="1">
-      <c r="A86" s="42" t="inlineStr">
-        <is>
-          <t>Boolean flag</t>
-        </is>
-      </c>
-      <c r="B86" s="41" t="inlineStr">
-        <is>
-          <t>Yes — Missed_Flag</t>
-        </is>
-      </c>
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>Expected coverage, alerting, escalation, or WarRoom action was missed or materially delayed.</t>
-        </is>
-      </c>
-      <c r="D86" s="41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E86" s="41" t="inlineStr">
-        <is>
-          <t>Missed_Flag</t>
         </is>
       </c>
     </row>
@@ -18140,49 +18337,49 @@
       </c>
       <c r="B87" s="41" t="inlineStr">
         <is>
+          <t>Yes — Missed_Flag</t>
+        </is>
+      </c>
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>Expected coverage, alerting, escalation, or WarRoom action was missed or materially delayed.</t>
+        </is>
+      </c>
+      <c r="D87" s="41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E87" s="41" t="inlineStr">
+        <is>
+          <t>Missed_Flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="30.75" customHeight="1">
+      <c r="A88" s="42" t="inlineStr">
+        <is>
+          <t>Boolean flag</t>
+        </is>
+      </c>
+      <c r="B88" s="41" t="inlineStr">
+        <is>
           <t>No — Missed_Flag</t>
         </is>
       </c>
-      <c r="C87" s="41" t="inlineStr">
+      <c r="C88" s="41" t="inlineStr">
         <is>
           <t>No confirmed reporting miss; the case concerns clarification, relevancy, mapping, duplication, or another non-miss issue.</t>
         </is>
       </c>
-      <c r="D87" s="41" t="inlineStr">
+      <c r="D88" s="41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E87" s="41" t="inlineStr">
+      <c r="E88" s="41" t="inlineStr">
         <is>
           <t>Missed_Flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="42" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="B88" s="41" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C88" s="41" t="inlineStr">
-        <is>
-          <t>Material impact or priority requiring elevated management attention.</t>
-        </is>
-      </c>
-      <c r="D88" s="41" t="inlineStr">
-        <is>
-          <t>Priority level</t>
-        </is>
-      </c>
-      <c r="E88" s="41" t="inlineStr">
-        <is>
-          <t>Severity</t>
         </is>
       </c>
     </row>
@@ -18194,12 +18391,12 @@
       </c>
       <c r="B89" s="41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C89" s="41" t="inlineStr">
         <is>
-          <t>Standard operational complaint or issue requiring tracked response.</t>
+          <t>Material impact or priority requiring elevated management attention.</t>
         </is>
       </c>
       <c r="D89" s="41" t="inlineStr">
@@ -18221,12 +18418,12 @@
       </c>
       <c r="B90" s="41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>Limited-impact inquiry or quality issue with lower operational urgency.</t>
+          <t>Standard operational complaint or issue requiring tracked response.</t>
         </is>
       </c>
       <c r="D90" s="41" t="inlineStr">
@@ -18243,27 +18440,27 @@
     <row r="91">
       <c r="A91" s="42" t="inlineStr">
         <is>
-          <t>Automation focus</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="B91" s="41" t="inlineStr">
         <is>
-          <t>AI-Assisted Geofencing</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C91" s="41" t="inlineStr">
         <is>
-          <t>Automate or improve impact-area creation and location validation.</t>
+          <t>Limited-impact inquiry or quality issue with lower operational urgency.</t>
         </is>
       </c>
       <c r="D91" s="41" t="inlineStr">
         <is>
-          <t>Standardized dashboard category</t>
+          <t>Priority level</t>
         </is>
       </c>
       <c r="E91" s="41" t="inlineStr">
         <is>
-          <t>Standard Automation Focus</t>
+          <t>Severity</t>
         </is>
       </c>
     </row>
@@ -18275,93 +18472,93 @@
       </c>
       <c r="B92" s="41" t="inlineStr">
         <is>
+          <t>AI-Assisted Geofencing</t>
+        </is>
+      </c>
+      <c r="C92" s="41" t="inlineStr">
+        <is>
+          <t>Automate or improve impact-area creation and location validation.</t>
+        </is>
+      </c>
+      <c r="D92" s="41" t="inlineStr">
+        <is>
+          <t>Standardized dashboard category</t>
+        </is>
+      </c>
+      <c r="E92" s="41" t="inlineStr">
+        <is>
+          <t>Standard Automation Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="42" t="inlineStr">
+        <is>
+          <t>Automation focus</t>
+        </is>
+      </c>
+      <c r="B93" s="41" t="inlineStr">
+        <is>
           <t>Automated Industry Tagging</t>
         </is>
       </c>
-      <c r="C92" s="41" t="inlineStr">
+      <c r="C93" s="41" t="inlineStr">
         <is>
           <t>Automatically assign and validate industry classifications.</t>
         </is>
       </c>
-      <c r="D92" s="41" t="inlineStr">
+      <c r="D93" s="41" t="inlineStr">
         <is>
           <t>Standardized dashboard category</t>
         </is>
       </c>
-      <c r="E92" s="41" t="inlineStr">
+      <c r="E93" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="30.75" customHeight="1">
-      <c r="A93" s="42" t="inlineStr">
+    <row r="94" ht="30.75" customHeight="1">
+      <c r="A94" s="42" t="inlineStr">
         <is>
           <t>Automation focus</t>
         </is>
       </c>
-      <c r="B93" s="41" t="inlineStr">
+      <c r="B94" s="41" t="inlineStr">
         <is>
           <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
-      <c r="C93" s="41" t="inlineStr">
+      <c r="C94" s="41" t="inlineStr">
         <is>
           <t>Detect duplicate/split clusters and preserve one coherent event sequence.</t>
         </is>
       </c>
-      <c r="D93" s="41" t="inlineStr">
+      <c r="D94" s="41" t="inlineStr">
         <is>
           <t>Standardized dashboard category</t>
         </is>
       </c>
-      <c r="E93" s="41" t="inlineStr">
+      <c r="E94" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="42" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="42" t="inlineStr">
         <is>
           <t>Automation focus</t>
         </is>
       </c>
-      <c r="B94" s="41" t="inlineStr">
+      <c r="B95" s="41" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="C94" s="41" t="inlineStr">
+      <c r="C95" s="41" t="inlineStr">
         <is>
           <t>Identify, onboard, and monitor new or missing sources dynamically.</t>
-        </is>
-      </c>
-      <c r="D94" s="41" t="inlineStr">
-        <is>
-          <t>Standardized dashboard category</t>
-        </is>
-      </c>
-      <c r="E94" s="41" t="inlineStr">
-        <is>
-          <t>Standard Automation Focus</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="30.75" customHeight="1">
-      <c r="A95" s="42" t="inlineStr">
-        <is>
-          <t>Automation focus</t>
-        </is>
-      </c>
-      <c r="B95" s="41" t="inlineStr">
-        <is>
-          <t>Entity &amp; Supplier Resolution</t>
-        </is>
-      </c>
-      <c r="C95" s="41" t="inlineStr">
-        <is>
-          <t>Resolve company, facility, supplier, and customer relationships accurately.</t>
         </is>
       </c>
       <c r="D95" s="41" t="inlineStr">
@@ -18383,12 +18580,12 @@
       </c>
       <c r="B96" s="41" t="inlineStr">
         <is>
-          <t>Multilingual Keyword Expansion</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="C96" s="41" t="inlineStr">
         <is>
-          <t>Expand and maintain detection terms across languages and regional variations.</t>
+          <t>Resolve company, facility, supplier, and customer relationships accurately.</t>
         </is>
       </c>
       <c r="D96" s="41" t="inlineStr">
@@ -18410,66 +18607,66 @@
       </c>
       <c r="B97" s="41" t="inlineStr">
         <is>
+          <t>Multilingual Keyword Expansion</t>
+        </is>
+      </c>
+      <c r="C97" s="41" t="inlineStr">
+        <is>
+          <t>Expand and maintain detection terms across languages and regional variations.</t>
+        </is>
+      </c>
+      <c r="D97" s="41" t="inlineStr">
+        <is>
+          <t>Standardized dashboard category</t>
+        </is>
+      </c>
+      <c r="E97" s="41" t="inlineStr">
+        <is>
+          <t>Standard Automation Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="30.75" customHeight="1">
+      <c r="A98" s="42" t="inlineStr">
+        <is>
+          <t>Automation focus</t>
+        </is>
+      </c>
+      <c r="B98" s="41" t="inlineStr">
+        <is>
           <t>Notification Visibility Monitoring</t>
         </is>
       </c>
-      <c r="C97" s="41" t="inlineStr">
+      <c r="C98" s="41" t="inlineStr">
         <is>
           <t>Monitor whether published alerts and WarRooms are visible and delivered to the customer.</t>
         </is>
       </c>
-      <c r="D97" s="41" t="inlineStr">
+      <c r="D98" s="41" t="inlineStr">
         <is>
           <t>Standardized dashboard category</t>
         </is>
       </c>
-      <c r="E97" s="41" t="inlineStr">
+      <c r="E98" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="42" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="42" t="inlineStr">
         <is>
           <t>Automation focus</t>
         </is>
       </c>
-      <c r="B98" s="41" t="inlineStr">
+      <c r="B99" s="41" t="inlineStr">
         <is>
           <t>Other Control Automation</t>
         </is>
       </c>
-      <c r="C98" s="41" t="inlineStr">
+      <c r="C99" s="41" t="inlineStr">
         <is>
           <t>Automation that does not fit another standardized focus category.</t>
-        </is>
-      </c>
-      <c r="D98" s="41" t="inlineStr">
-        <is>
-          <t>Standardized dashboard category</t>
-        </is>
-      </c>
-      <c r="E98" s="41" t="inlineStr">
-        <is>
-          <t>Standard Automation Focus</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="30.75" customHeight="1">
-      <c r="A99" s="42" t="inlineStr">
-        <is>
-          <t>Automation focus</t>
-        </is>
-      </c>
-      <c r="B99" s="41" t="inlineStr">
-        <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="C99" s="41" t="inlineStr">
-        <is>
-          <t>Validate impact decisions, escalation, publishing, and WarRoom creation.</t>
         </is>
       </c>
       <c r="D99" s="41" t="inlineStr">
@@ -18486,27 +18683,27 @@
     <row r="100" ht="30.75" customHeight="1">
       <c r="A100" s="42" t="inlineStr">
         <is>
-          <t>Reason label</t>
+          <t>Automation focus</t>
         </is>
       </c>
       <c r="B100" s="41" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="C100" s="41" t="inlineStr">
         <is>
-          <t>Customer requested confirmation of coverage, facts, or system behavior.</t>
+          <t>Validate impact decisions, escalation, publishing, and WarRoom creation.</t>
         </is>
       </c>
       <c r="D100" s="41" t="inlineStr">
         <is>
-          <t>Use only when supported by Comments and Missed_Flag</t>
+          <t>Standardized dashboard category</t>
         </is>
       </c>
       <c r="E100" s="41" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
@@ -18518,7 +18715,7 @@
       </c>
       <c r="B101" s="41" t="inlineStr">
         <is>
-          <t>Customer Requested Verification</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="C101" s="41" t="inlineStr">
@@ -18545,12 +18742,12 @@
       </c>
       <c r="B102" s="41" t="inlineStr">
         <is>
-          <t>Customer Terminology Preference</t>
+          <t>Customer Requested Verification</t>
         </is>
       </c>
       <c r="C102" s="41" t="inlineStr">
         <is>
-          <t>Customer requested wording or naming alignment rather than correction of a reporting failure.</t>
+          <t>Customer requested confirmation of coverage, facts, or system behavior.</t>
         </is>
       </c>
       <c r="D102" s="41" t="inlineStr">
@@ -18572,12 +18769,12 @@
       </c>
       <c r="B103" s="41" t="inlineStr">
         <is>
-          <t>Delay in creating separate WarRoom / delayed escalation</t>
+          <t>Customer Terminology Preference</t>
         </is>
       </c>
       <c r="C103" s="41" t="inlineStr">
         <is>
-          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
+          <t>Customer requested wording or naming alignment rather than correction of a reporting failure.</t>
         </is>
       </c>
       <c r="D103" s="41" t="inlineStr">
@@ -18599,7 +18796,7 @@
       </c>
       <c r="B104" s="41" t="inlineStr">
         <is>
-          <t>Delayed / Missing WarRoom</t>
+          <t>Delay in creating separate WarRoom / delayed escalation</t>
         </is>
       </c>
       <c r="C104" s="41" t="inlineStr">
@@ -18626,7 +18823,7 @@
       </c>
       <c r="B105" s="41" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Delayed / Missing WarRoom</t>
         </is>
       </c>
       <c r="C105" s="41" t="inlineStr">
@@ -18653,7 +18850,7 @@
       </c>
       <c r="B106" s="41" t="inlineStr">
         <is>
-          <t>Delayed WarRoom</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="C106" s="41" t="inlineStr">
@@ -18680,7 +18877,7 @@
       </c>
       <c r="B107" s="41" t="inlineStr">
         <is>
-          <t>Delayed alert / WarRoom created late</t>
+          <t>Delayed WarRoom</t>
         </is>
       </c>
       <c r="C107" s="41" t="inlineStr">
@@ -18707,12 +18904,12 @@
       </c>
       <c r="B108" s="41" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms</t>
+          <t>Delayed alert / WarRoom created late</t>
         </is>
       </c>
       <c r="C108" s="41" t="inlineStr">
         <is>
-          <t>Related content was distributed across more than one WarRoom.</t>
+          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
         </is>
       </c>
       <c r="D108" s="41" t="inlineStr">
@@ -18734,12 +18931,12 @@
       </c>
       <c r="B109" s="41" t="inlineStr">
         <is>
-          <t>Event not triggered / not notified</t>
+          <t>Duplicate WarRooms</t>
         </is>
       </c>
       <c r="C109" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>Related content was distributed across more than one WarRoom.</t>
         </is>
       </c>
       <c r="D109" s="41" t="inlineStr">
@@ -18761,12 +18958,12 @@
       </c>
       <c r="B110" s="41" t="inlineStr">
         <is>
-          <t>Geographic Coverage Clarification</t>
+          <t>Event not triggered / not notified</t>
         </is>
       </c>
       <c r="C110" s="41" t="inlineStr">
         <is>
-          <t>Customer requested explanation of the geographic scope or impact-area method.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D110" s="41" t="inlineStr">
@@ -18788,12 +18985,12 @@
       </c>
       <c r="B111" s="41" t="inlineStr">
         <is>
-          <t>Geographic Misclassification</t>
+          <t>Geographic Coverage Clarification</t>
         </is>
       </c>
       <c r="C111" s="41" t="inlineStr">
         <is>
-          <t>An event or location was assigned to an incorrect geographic impact area.</t>
+          <t>Customer requested explanation of the geographic scope or impact-area method.</t>
         </is>
       </c>
       <c r="D111" s="41" t="inlineStr">
@@ -18815,12 +19012,12 @@
       </c>
       <c r="B112" s="41" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Geographic Misclassification</t>
         </is>
       </c>
       <c r="C112" s="41" t="inlineStr">
         <is>
-          <t>A relevant mapped supplier was omitted from the impacted-supplier selection.</t>
+          <t>An event or location was assigned to an incorrect geographic impact area.</t>
         </is>
       </c>
       <c r="D112" s="41" t="inlineStr">
@@ -18842,12 +19039,12 @@
       </c>
       <c r="B113" s="41" t="inlineStr">
         <is>
-          <t>Incorrect Action</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="C113" s="41" t="inlineStr">
         <is>
-          <t>EventWatch action or handling was incorrect even though the event itself may not have been missed.</t>
+          <t>A relevant mapped supplier was omitted from the impacted-supplier selection.</t>
         </is>
       </c>
       <c r="D113" s="41" t="inlineStr">
@@ -18869,12 +19066,12 @@
       </c>
       <c r="B114" s="41" t="inlineStr">
         <is>
-          <t>Incorrect Industry selection</t>
+          <t>Incorrect Action</t>
         </is>
       </c>
       <c r="C114" s="41" t="inlineStr">
         <is>
-          <t>The expected industry classification was missing or incorrect.</t>
+          <t>EventWatch action or handling was incorrect even though the event itself may not have been missed.</t>
         </is>
       </c>
       <c r="D114" s="41" t="inlineStr">
@@ -18896,12 +19093,12 @@
       </c>
       <c r="B115" s="41" t="inlineStr">
         <is>
-          <t>Missed + Delayed Reporting</t>
+          <t>Incorrect Industry selection</t>
         </is>
       </c>
       <c r="C115" s="41" t="inlineStr">
         <is>
-          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
+          <t>The expected industry classification was missing or incorrect.</t>
         </is>
       </c>
       <c r="D115" s="41" t="inlineStr">
@@ -18923,7 +19120,7 @@
       </c>
       <c r="B116" s="41" t="inlineStr">
         <is>
-          <t>Missed / Delayed Event</t>
+          <t>Missed + Delayed Reporting</t>
         </is>
       </c>
       <c r="C116" s="41" t="inlineStr">
@@ -18950,12 +19147,12 @@
       </c>
       <c r="B117" s="41" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed / Delayed Event</t>
         </is>
       </c>
       <c r="C117" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
         </is>
       </c>
       <c r="D117" s="41" t="inlineStr">
@@ -18977,7 +19174,7 @@
       </c>
       <c r="B118" s="41" t="inlineStr">
         <is>
-          <t>Missed Relevant Event</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="C118" s="41" t="inlineStr">
@@ -19004,7 +19201,7 @@
       </c>
       <c r="B119" s="41" t="inlineStr">
         <is>
-          <t>Missed WarRoom</t>
+          <t>Missed Relevant Event</t>
         </is>
       </c>
       <c r="C119" s="41" t="inlineStr">
@@ -19031,7 +19228,7 @@
       </c>
       <c r="B120" s="41" t="inlineStr">
         <is>
-          <t>Missed WarRoom / No notification</t>
+          <t>Missed WarRoom</t>
         </is>
       </c>
       <c r="C120" s="41" t="inlineStr">
@@ -19058,7 +19255,7 @@
       </c>
       <c r="B121" s="41" t="inlineStr">
         <is>
-          <t>Missed alert / event not captured</t>
+          <t>Missed WarRoom / No notification</t>
         </is>
       </c>
       <c r="C121" s="41" t="inlineStr">
@@ -19085,7 +19282,7 @@
       </c>
       <c r="B122" s="41" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Missed alert / event not captured</t>
         </is>
       </c>
       <c r="C122" s="41" t="inlineStr">
@@ -19112,7 +19309,7 @@
       </c>
       <c r="B123" s="41" t="inlineStr">
         <is>
-          <t>Missed insolvency event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="C123" s="41" t="inlineStr">
@@ -19139,7 +19336,7 @@
       </c>
       <c r="B124" s="41" t="inlineStr">
         <is>
-          <t>Missed severe weather alert</t>
+          <t>Missed insolvency event</t>
         </is>
       </c>
       <c r="C124" s="41" t="inlineStr">
@@ -19166,12 +19363,12 @@
       </c>
       <c r="B125" s="41" t="inlineStr">
         <is>
-          <t>Missing Automotive industry tag (customer tracking missed it)</t>
+          <t>Missed severe weather alert</t>
         </is>
       </c>
       <c r="C125" s="41" t="inlineStr">
         <is>
-          <t>The expected industry classification was missing or incorrect.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D125" s="41" t="inlineStr">
@@ -19193,12 +19390,12 @@
       </c>
       <c r="B126" s="41" t="inlineStr">
         <is>
-          <t>Missing EventWatch coverage / feeds not captured</t>
+          <t>Missing Automotive industry tag (customer tracking missed it)</t>
         </is>
       </c>
       <c r="C126" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>The expected industry classification was missing or incorrect.</t>
         </is>
       </c>
       <c r="D126" s="41" t="inlineStr">
@@ -19220,7 +19417,7 @@
       </c>
       <c r="B127" s="41" t="inlineStr">
         <is>
-          <t>Missing Resilinc alert / insolvency not captured</t>
+          <t>Missing EventWatch coverage / feeds not captured</t>
         </is>
       </c>
       <c r="C127" s="41" t="inlineStr">
@@ -19247,12 +19444,12 @@
       </c>
       <c r="B128" s="41" t="inlineStr">
         <is>
-          <t>SEC notification not captured/provided on time</t>
+          <t>Missing Resilinc alert / insolvency not captured</t>
         </is>
       </c>
       <c r="C128" s="41" t="inlineStr">
         <is>
-          <t>Specific customer-reported reason recorded in the tracker.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D128" s="41" t="inlineStr">
@@ -19274,12 +19471,12 @@
       </c>
       <c r="B129" s="41" t="inlineStr">
         <is>
-          <t>Severity / consolidation handling concern</t>
+          <t>SEC notification not captured/provided on time</t>
         </is>
       </c>
       <c r="C129" s="41" t="inlineStr">
         <is>
-          <t>Customer questioned the severity level or consolidation of event coverage.</t>
+          <t>Specific customer-reported reason recorded in the tracker.</t>
         </is>
       </c>
       <c r="D129" s="41" t="inlineStr">
@@ -19301,12 +19498,12 @@
       </c>
       <c r="B130" s="41" t="inlineStr">
         <is>
-          <t>Supplier Impact Mapping Clarification</t>
+          <t>Severity / consolidation handling concern</t>
         </is>
       </c>
       <c r="C130" s="41" t="inlineStr">
         <is>
-          <t>Customer requested explanation of why suppliers were included or excluded from the impact area.</t>
+          <t>Customer questioned the severity level or consolidation of event coverage.</t>
         </is>
       </c>
       <c r="D130" s="41" t="inlineStr">
@@ -19328,12 +19525,12 @@
       </c>
       <c r="B131" s="41" t="inlineStr">
         <is>
-          <t>WarRoom not created despite nationwide disruption</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="C131" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>Customer requested explanation of why suppliers were included or excluded from the impact area.</t>
         </is>
       </c>
       <c r="D131" s="41" t="inlineStr">
@@ -19355,12 +19552,12 @@
       </c>
       <c r="B132" s="41" t="inlineStr">
         <is>
-          <t>WarRoom not visible in customer profile</t>
+          <t>WarRoom not created despite nationwide disruption</t>
         </is>
       </c>
       <c r="C132" s="41" t="inlineStr">
         <is>
-          <t>Published content was not visible in the customer profile or portal.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D132" s="41" t="inlineStr">
@@ -19382,12 +19579,12 @@
       </c>
       <c r="B133" s="41" t="inlineStr">
         <is>
-          <t>WarRoom should have been created but was not</t>
+          <t>WarRoom not visible in customer profile</t>
         </is>
       </c>
       <c r="C133" s="41" t="inlineStr">
         <is>
-          <t>Available information met the escalation criteria, but the required WarRoom was not created.</t>
+          <t>Published content was not visible in the customer profile or portal.</t>
         </is>
       </c>
       <c r="D133" s="41" t="inlineStr">
@@ -19409,12 +19606,12 @@
       </c>
       <c r="B134" s="41" t="inlineStr">
         <is>
-          <t>WarRoom visibility affected by customer profile filters</t>
+          <t>WarRoom should have been created but was not</t>
         </is>
       </c>
       <c r="C134" s="41" t="inlineStr">
         <is>
-          <t>Published content was not visible in the customer profile or portal.</t>
+          <t>Available information met the escalation criteria, but the required WarRoom was not created.</t>
         </is>
       </c>
       <c r="D134" s="41" t="inlineStr">
@@ -19436,12 +19633,12 @@
       </c>
       <c r="B135" s="41" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>WarRoom visibility affected by customer profile filters</t>
         </is>
       </c>
       <c r="C135" s="41" t="inlineStr">
         <is>
-          <t>The relevance classification of an event or alert was disputed or incorrect.</t>
+          <t>Published content was not visible in the customer profile or portal.</t>
         </is>
       </c>
       <c r="D135" s="41" t="inlineStr">
@@ -19458,27 +19655,27 @@
     <row r="136" ht="30.75" customHeight="1">
       <c r="A136" s="42" t="inlineStr">
         <is>
-          <t>Event type</t>
+          <t>Reason label</t>
         </is>
       </c>
       <c r="B136" s="41" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="C136" s="41" t="inlineStr">
         <is>
-          <t>Tropical cyclone classified as a hurricane or typhoon, with potential geographic, operational, or supply-chain impact.</t>
+          <t>The relevance classification of an event or alert was disputed or incorrect.</t>
         </is>
       </c>
       <c r="D136" s="41" t="inlineStr">
         <is>
-          <t>Use specifically for hurricanes and typhoons rather than the broader Extreme Weather category.</t>
+          <t>Use only when supported by Comments and Missed_Flag</t>
         </is>
       </c>
       <c r="E136" s="41" t="inlineStr">
         <is>
-          <t>Event type</t>
+          <t>Reason</t>
         </is>
       </c>
     </row>
@@ -19490,20 +19687,47 @@
       </c>
       <c r="B137" s="41" t="inlineStr">
         <is>
+          <t>Hurricane/Typhoon</t>
+        </is>
+      </c>
+      <c r="C137" s="41" t="inlineStr">
+        <is>
+          <t>Tropical cyclone classified as a hurricane or typhoon, with potential geographic, operational, or supply-chain impact.</t>
+        </is>
+      </c>
+      <c r="D137" s="41" t="inlineStr">
+        <is>
+          <t>Use specifically for hurricanes and typhoons rather than the broader Extreme Weather category.</t>
+        </is>
+      </c>
+      <c r="E137" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="30.75" customHeight="1">
+      <c r="A138" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B138" s="41" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C137" s="41" t="inlineStr">
+      <c r="C138" s="41" t="inlineStr">
         <is>
           <t>Event or inquiry category that does not fit any available standardized Event type.</t>
         </is>
       </c>
-      <c r="D137" s="41" t="inlineStr">
+      <c r="D138" s="41" t="inlineStr">
         <is>
           <t>Use only when no specific standard category applies; explain the subject in the title and comments.</t>
         </is>
       </c>
-      <c r="E137" s="41" t="inlineStr">
+      <c r="E138" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1284,7 +1284,7 @@
                   <v>14</v>
                 </pt>
                 <pt idx="8">
-                  <v>2</v>
+                  <v>4</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1388,7 +1388,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1741,7 +1741,7 @@
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>4</v>
+                  <v>6</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2052,10 +2052,10 @@
                   <v>2</v>
                 </pt>
                 <pt idx="2">
-                  <v>84</v>
+                  <v>86</v>
                 </pt>
                 <pt idx="3">
-                  <v>8</v>
+                  <v>9</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2342,7 +2342,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>42</v>
+                  <v>44</v>
                 </pt>
                 <pt idx="1">
                   <v>32</v>
@@ -2627,7 +2627,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>31</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="1">
                   <v>11</v>
@@ -2657,7 +2657,7 @@
                   <v>1</v>
                 </pt>
                 <pt idx="10">
-                  <v>14</v>
+                  <v>15</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2948,7 +2948,7 @@
                   <v>26</v>
                 </pt>
                 <pt idx="1">
-                  <v>30</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -2960,7 +2960,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="5">
-                  <v>4</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="6">
                   <v>2</v>
@@ -3282,8 +3282,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:X95" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
-  <autoFilter ref="A1:X95"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:X98" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="A1:X98"/>
   <tableColumns count="24">
     <tableColumn id="1" name="Month" dataDxfId="28">
       <calculatedColumnFormula>DATE(YEAR(B2),MONTH(B2),1)</calculatedColumnFormula>
@@ -3642,7 +3642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X95"/>
+  <dimension ref="A1:X98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -13045,6 +13045,312 @@
         </is>
       </c>
       <c r="X95" s="33" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B96" s="37" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C96" s="33" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D96" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E96" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="33" t="inlineStr">
+        <is>
+          <t>Prolonged Power Cuts in Punjab, India – Haryana Supplier Site Notified for Impact Confirmation (Ford)</t>
+        </is>
+      </c>
+      <c r="G96" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H96" s="33" t="inlineStr">
+        <is>
+          <t>Geographic Misclassification</t>
+        </is>
+      </c>
+      <c r="I96" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J96" s="33" t="inlineStr">
+        <is>
+          <t>Mapping</t>
+        </is>
+      </c>
+      <c r="K96" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L96" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M96" s="33" t="inlineStr">
+        <is>
+          <t>Geographic validation of supplier sites against the event impact polygon before impact-confirmation requests are issued</t>
+        </is>
+      </c>
+      <c r="N96" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O96" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-36 (Open). A WarRoom for prolonged power cuts in Punjab sent an impact-confirmation request to one Ford Tier 1 supplier, SMI AMTEK CRANKSHAFT, whose site is in Dharuhera, Rewari, Haryana rather than Punjab. SNAP validation shows no active direct Tier 1 suppliers in Punjab at all, so the outreach was wasted effort. Ford asked for RCA, immediate corrective action and preventive corrective action, and asked that it be prioritised. Same defect class as EAO-35 (Eaton): supplier sites outside the impact polygon being attached to the event.</t>
+        </is>
+      </c>
+      <c r="P96" s="33" t="n"/>
+      <c r="Q96" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R96" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S96" s="39" t="n"/>
+      <c r="T96" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U96" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V96" s="33" t="inlineStr">
+        <is>
+          <t>AI-Assisted Geofencing</t>
+        </is>
+      </c>
+      <c r="W96" s="33" t="inlineStr">
+        <is>
+          <t>EAO-36</t>
+        </is>
+      </c>
+      <c r="X96" s="33" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B97" s="37" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C97" s="33" t="inlineStr">
+        <is>
+          <t>Extreme Weather</t>
+        </is>
+      </c>
+      <c r="D97" s="33" t="inlineStr">
+        <is>
+          <t>Sandisk</t>
+        </is>
+      </c>
+      <c r="E97" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="33" t="inlineStr">
+        <is>
+          <t>Record Heavy Rain in Yokkaichi City, Japan – No EventWatch Notification (Sandisk)</t>
+        </is>
+      </c>
+      <c r="G97" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H97" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I97" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J97" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K97" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L97" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M97" s="33" t="inlineStr">
+        <is>
+          <t>Japanese-language and regional weather source coverage for localized record-rainfall events</t>
+        </is>
+      </c>
+      <c r="N97" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O97" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-37 (Open). Sandisk was alerted internally to record heavy rain in Yokkaichi city, Japan and could find no news item or WarRoom for it, despite having loaded their own Yokkaichi sites as suppliers. The customer supplied no public source. CS verified the Sandisk org and then the database across all customer orgs and found no evidence the notification was ever generated, so the event did not enter the system at all rather than being filtered out. RCA requested.</t>
+        </is>
+      </c>
+      <c r="P97" s="33" t="n"/>
+      <c r="Q97" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R97" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S97" s="39" t="n"/>
+      <c r="T97" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U97" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V97" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W97" s="33" t="inlineStr">
+        <is>
+          <t>EAO-37</t>
+        </is>
+      </c>
+      <c r="X97" s="33" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B98" s="37" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C98" s="33" t="inlineStr">
+        <is>
+          <t>Merger &amp; Acquisition</t>
+        </is>
+      </c>
+      <c r="D98" s="33" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="E98" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="33" t="inlineStr">
+        <is>
+          <t>Vertiv Acquires UtilityInnovation Group – Supplier Notification and Medium Risk Classification Queried (Eaton)</t>
+        </is>
+      </c>
+      <c r="G98" s="33" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="H98" s="33" t="inlineStr">
+        <is>
+          <t>Severity / consolidation handling concern</t>
+        </is>
+      </c>
+      <c r="I98" s="33" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="J98" s="33" t="inlineStr">
+        <is>
+          <t>Policy/Logic</t>
+        </is>
+      </c>
+      <c r="K98" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L98" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M98" s="33" t="inlineStr">
+        <is>
+          <t>Automated enforcement of the M&amp;A notification threshold so acquiring-side suppliers are excluded from impact-confirmation requests, plus a documented basis for the risk classification</t>
+        </is>
+      </c>
+      <c r="N98" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O98" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-38 (Open). Eaton queried WarRoom 37485945, 'Vertiv Acquires UtilityInnovation Group' (event date 08-Sep-2026, closed, severity Low). Two questions: why a Supplier Impact Confirmation Request was issued when the supplier is the acquiring party, which the latest Resilinc event-threshold guidance says does not require supplier notification; and why the event was classified Medium risk. The customer wants to know whether scenarios are being missed. A written explanation covering both was requested rather than an RCA.</t>
+        </is>
+      </c>
+      <c r="P98" s="33" t="n"/>
+      <c r="Q98" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R98" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S98" s="39" t="n"/>
+      <c r="T98" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U98" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="V98" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W98" s="33" t="inlineStr">
+        <is>
+          <t>EAO-38</t>
+        </is>
+      </c>
+      <c r="X98" s="33" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -14714,11 +15020,11 @@
       </c>
       <c r="B64" s="21" t="n" cm="1">
         <f t="array" ref="B64:B73">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A64))</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C64" s="23" t="n" cm="1">
         <f t="array" ref="C64:C73">_xlfn.ANCHORARRAY(B64)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.38271604938271603</v>
+        <v>0.3855421686746988</v>
       </c>
       <c r="D64" s="3" t="n"/>
       <c r="E64" s="18" t="inlineStr">
@@ -14759,7 +15065,7 @@
         <v>11</v>
       </c>
       <c r="C65" s="24" t="n">
-        <v>0.13580246913580246</v>
+        <v>0.13253012048192772</v>
       </c>
       <c r="D65" s="3" t="n"/>
       <c r="E65" s="20" t="inlineStr">
@@ -14801,7 +15107,7 @@
         <v>7</v>
       </c>
       <c r="C66" s="24" t="n">
-        <v>0.08641975308641975</v>
+        <v>0.08433734939759036</v>
       </c>
       <c r="D66" s="3" t="n"/>
       <c r="E66" s="20" t="inlineStr">
@@ -14843,7 +15149,7 @@
         <v>4</v>
       </c>
       <c r="C67" s="24" t="n">
-        <v>0.04938271604938271</v>
+        <v>0.04819277108433735</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="20" t="inlineStr">
@@ -14885,7 +15191,7 @@
         <v>4</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.04938271604938271</v>
+        <v>0.04819277108433735</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -14908,13 +15214,13 @@
         </is>
       </c>
       <c r="J68" s="76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K68" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -14927,7 +15233,7 @@
         <v>3</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.037037037037037035</v>
+        <v>0.03614457831325301</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -14969,7 +15275,7 @@
         <v>2</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.024691358024691357</v>
+        <v>0.024096385542168676</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -15011,7 +15317,7 @@
         <v>2</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.024691358024691357</v>
+        <v>0.024096385542168676</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -15053,7 +15359,7 @@
         <v>2</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.024691358024691357</v>
+        <v>0.024096385542168676</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -15095,7 +15401,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.012345679012345678</v>
+        <v>0.012048192771084338</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="25" t="inlineStr">
@@ -15261,10 +15567,10 @@
         <v>2</v>
       </c>
       <c r="K78" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" ht="23.25" customHeight="1">
@@ -15282,13 +15588,13 @@
         </is>
       </c>
       <c r="J79" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" s="76" t="n">
         <v>4</v>
       </c>
       <c r="L79" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" ht="23.25" customHeight="1">
@@ -15492,13 +15798,13 @@
         </is>
       </c>
       <c r="J87" s="77" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K87" s="77" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L87" s="77" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -3282,9 +3282,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:X104" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
-  <autoFilter ref="A1:X104"/>
-  <tableColumns count="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Y104" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="A1:Y104"/>
+  <tableColumns count="25">
     <tableColumn id="1" name="Month" dataDxfId="28">
       <calculatedColumnFormula>DATE(YEAR(B2),MONTH(B2),1)</calculatedColumnFormula>
     </tableColumn>
@@ -3332,14 +3332,15 @@
     </tableColumn>
     <tableColumn id="23" name="Jira Key"/>
     <tableColumn id="24" name="RCA Details"/>
+    <tableColumn id="25" name="Routed To"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E138" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A3:E138"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E139" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
     <tableColumn id="2" name="Term / Field" dataDxfId="3"/>
@@ -3642,7 +3643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X104"/>
+  <dimension ref="A1:Y104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -3776,6 +3777,11 @@
           <t>RCA Details</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Routed To</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="35" t="n">
@@ -3871,6 +3877,11 @@
         </is>
       </c>
       <c r="X2" s="33" t="n"/>
+      <c r="Y2" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="35" t="n">
@@ -3966,6 +3977,11 @@
         </is>
       </c>
       <c r="X3" s="33" t="n"/>
+      <c r="Y3" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="35" t="n">
@@ -4061,6 +4077,11 @@
         </is>
       </c>
       <c r="X4" s="33" t="n"/>
+      <c r="Y4" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="35" t="n">
@@ -4162,6 +4183,11 @@
         </is>
       </c>
       <c r="X5" s="33" t="n"/>
+      <c r="Y5" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="n">
@@ -4257,6 +4283,11 @@
         </is>
       </c>
       <c r="X6" s="33" t="n"/>
+      <c r="Y6" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="n">
@@ -4359,6 +4390,11 @@
         </is>
       </c>
       <c r="X7" s="33" t="n"/>
+      <c r="Y7" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="n">
@@ -4454,6 +4490,11 @@
         </is>
       </c>
       <c r="X8" s="33" t="n"/>
+      <c r="Y8" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="n">
@@ -4549,6 +4590,11 @@
         </is>
       </c>
       <c r="X9" s="33" t="n"/>
+      <c r="Y9" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="n">
@@ -4644,6 +4690,11 @@
         </is>
       </c>
       <c r="X10" s="33" t="n"/>
+      <c r="Y10" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="n">
@@ -4739,6 +4790,11 @@
         </is>
       </c>
       <c r="X11" s="33" t="n"/>
+      <c r="Y11" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="n">
@@ -4834,6 +4890,11 @@
         </is>
       </c>
       <c r="X12" s="33" t="n"/>
+      <c r="Y12" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="n">
@@ -4929,6 +4990,11 @@
         </is>
       </c>
       <c r="X13" s="33" t="n"/>
+      <c r="Y13" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="n">
@@ -5031,6 +5097,11 @@
         </is>
       </c>
       <c r="X14" s="33" t="n"/>
+      <c r="Y14" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="n">
@@ -5126,6 +5197,11 @@
         </is>
       </c>
       <c r="X15" s="33" t="n"/>
+      <c r="Y15" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="n">
@@ -5221,6 +5297,11 @@
         </is>
       </c>
       <c r="X16" s="33" t="n"/>
+      <c r="Y16" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="n">
@@ -5316,6 +5397,11 @@
         </is>
       </c>
       <c r="X17" s="33" t="n"/>
+      <c r="Y17" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="n">
@@ -5411,6 +5497,11 @@
         </is>
       </c>
       <c r="X18" s="33" t="n"/>
+      <c r="Y18" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="n">
@@ -5506,6 +5597,11 @@
         </is>
       </c>
       <c r="X19" s="33" t="n"/>
+      <c r="Y19" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="n">
@@ -5601,6 +5697,11 @@
         </is>
       </c>
       <c r="X20" s="33" t="n"/>
+      <c r="Y20" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="n">
@@ -5696,6 +5797,11 @@
         </is>
       </c>
       <c r="X21" s="33" t="n"/>
+      <c r="Y21" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="n">
@@ -5798,6 +5904,11 @@
         </is>
       </c>
       <c r="X22" s="33" t="n"/>
+      <c r="Y22" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="n">
@@ -5893,6 +6004,11 @@
         </is>
       </c>
       <c r="X23" s="33" t="n"/>
+      <c r="Y23" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="35" t="n">
@@ -5988,6 +6104,11 @@
         </is>
       </c>
       <c r="X24" s="33" t="n"/>
+      <c r="Y24" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="35" t="n">
@@ -6083,6 +6204,11 @@
         </is>
       </c>
       <c r="X25" s="33" t="n"/>
+      <c r="Y25" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="35" t="n">
@@ -6178,6 +6304,11 @@
         </is>
       </c>
       <c r="X26" s="33" t="n"/>
+      <c r="Y26" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="35" t="n">
@@ -6280,6 +6411,11 @@
         </is>
       </c>
       <c r="X27" s="33" t="n"/>
+      <c r="Y27" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="35" t="n">
@@ -6381,6 +6517,11 @@
         </is>
       </c>
       <c r="X28" s="33" t="n"/>
+      <c r="Y28" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="35" t="n">
@@ -6482,6 +6623,11 @@
         </is>
       </c>
       <c r="X29" s="33" t="n"/>
+      <c r="Y29" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="35" t="n">
@@ -6577,6 +6723,11 @@
         </is>
       </c>
       <c r="X30" s="33" t="n"/>
+      <c r="Y30" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="35" t="n">
@@ -6679,6 +6830,11 @@
         </is>
       </c>
       <c r="X31" s="33" t="n"/>
+      <c r="Y31" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="35" t="n">
@@ -6774,6 +6930,11 @@
         </is>
       </c>
       <c r="X32" s="33" t="n"/>
+      <c r="Y32" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="35" t="n">
@@ -6869,6 +7030,11 @@
         </is>
       </c>
       <c r="X33" s="33" t="n"/>
+      <c r="Y33" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="35" t="n">
@@ -6964,6 +7130,11 @@
         </is>
       </c>
       <c r="X34" s="33" t="n"/>
+      <c r="Y34" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="35" t="n">
@@ -7059,6 +7230,11 @@
         </is>
       </c>
       <c r="X35" s="33" t="n"/>
+      <c r="Y35" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="35" t="n">
@@ -7154,6 +7330,11 @@
         </is>
       </c>
       <c r="X36" s="33" t="n"/>
+      <c r="Y36" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="35" t="n">
@@ -7249,6 +7430,11 @@
         </is>
       </c>
       <c r="X37" s="33" t="n"/>
+      <c r="Y37" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="35" t="n">
@@ -7344,6 +7530,11 @@
         </is>
       </c>
       <c r="X38" s="33" t="n"/>
+      <c r="Y38" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="35" t="n">
@@ -7439,6 +7630,11 @@
         </is>
       </c>
       <c r="X39" s="33" t="n"/>
+      <c r="Y39" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="35" t="n">
@@ -7540,6 +7736,11 @@
         </is>
       </c>
       <c r="X40" s="33" t="n"/>
+      <c r="Y40" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="35" t="n">
@@ -7641,6 +7842,11 @@
         </is>
       </c>
       <c r="X41" s="33" t="n"/>
+      <c r="Y41" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="35" t="n">
@@ -7742,6 +7948,11 @@
         </is>
       </c>
       <c r="X42" s="33" t="n"/>
+      <c r="Y42" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="35" t="n">
@@ -7843,6 +8054,11 @@
         </is>
       </c>
       <c r="X43" s="33" t="n"/>
+      <c r="Y43" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="35" t="n">
@@ -7938,6 +8154,11 @@
         </is>
       </c>
       <c r="X44" s="33" t="n"/>
+      <c r="Y44" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="35" t="n">
@@ -8033,6 +8254,11 @@
         </is>
       </c>
       <c r="X45" s="33" t="n"/>
+      <c r="Y45" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="35" t="n">
@@ -8128,6 +8354,11 @@
         </is>
       </c>
       <c r="X46" s="33" t="n"/>
+      <c r="Y46" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="35" t="n">
@@ -8223,6 +8454,11 @@
         </is>
       </c>
       <c r="X47" s="33" t="n"/>
+      <c r="Y47" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="35" t="n">
@@ -8318,6 +8554,11 @@
         </is>
       </c>
       <c r="X48" s="33" t="n"/>
+      <c r="Y48" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="35" t="n">
@@ -8419,6 +8660,11 @@
         </is>
       </c>
       <c r="X49" s="33" t="n"/>
+      <c r="Y49" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="35" t="n">
@@ -8520,6 +8766,11 @@
         </is>
       </c>
       <c r="X50" s="33" t="n"/>
+      <c r="Y50" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="35" t="n">
@@ -8615,6 +8866,11 @@
         </is>
       </c>
       <c r="X51" s="33" t="n"/>
+      <c r="Y51" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="35" t="n">
@@ -8710,6 +8966,11 @@
         </is>
       </c>
       <c r="X52" s="33" t="n"/>
+      <c r="Y52" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="35" t="n">
@@ -8805,6 +9066,11 @@
         </is>
       </c>
       <c r="X53" s="33" t="n"/>
+      <c r="Y53" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="35" t="n">
@@ -8900,6 +9166,11 @@
         </is>
       </c>
       <c r="X54" s="33" t="n"/>
+      <c r="Y54" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="35" t="n">
@@ -9001,6 +9272,11 @@
         </is>
       </c>
       <c r="X55" s="33" t="n"/>
+      <c r="Y55" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="35" t="n">
@@ -9102,6 +9378,11 @@
         </is>
       </c>
       <c r="X56" s="33" t="n"/>
+      <c r="Y56" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="35" t="n">
@@ -9203,6 +9484,11 @@
         </is>
       </c>
       <c r="X57" s="33" t="n"/>
+      <c r="Y57" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="35" t="n">
@@ -9298,6 +9584,11 @@
         </is>
       </c>
       <c r="X58" s="33" t="n"/>
+      <c r="Y58" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="59" customFormat="1" s="29">
       <c r="A59" s="36" t="n">
@@ -9399,6 +9690,11 @@
         </is>
       </c>
       <c r="X59" s="33" t="n"/>
+      <c r="Y59" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="35" t="n">
@@ -9494,6 +9790,11 @@
         </is>
       </c>
       <c r="X60" s="33" t="n"/>
+      <c r="Y60" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="35" t="n">
@@ -9589,6 +9890,11 @@
         </is>
       </c>
       <c r="X61" s="33" t="n"/>
+      <c r="Y61" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="35" t="n">
@@ -9693,6 +9999,11 @@
           <t>Articles on the Burnstein von Seelen disruption did reach the portal, but the analyst classified the event Not Impactful and did not escalate it, so it never reached WarRoom consideration. Corrective: analyst coaching on law-enforcement, regulatory and workforce disruptions, plus an internal non-conformance raised against the reporting workflow. Preventive: extra review controls before a Not Impactful call on a monitored supplier, stronger supplier-context visibility during review, expanded audits of analyst overrides, and AI-assisted relevance work with Product/Data Science.</t>
         </is>
       </c>
+      <c r="Y62" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="35" t="n">
@@ -9795,6 +10106,11 @@
         </is>
       </c>
       <c r="X63" s="33" t="n"/>
+      <c r="Y63" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="35" t="n">
@@ -9899,6 +10215,11 @@
           <t>RCA approved and sent to the customer on 15-Jun-2026 as a PDF attached to EAO-4; the document text is not in the ticket.</t>
         </is>
       </c>
+      <c r="Y64" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="35" t="n">
@@ -9999,6 +10320,11 @@
         </is>
       </c>
       <c r="X65" s="33" t="n"/>
+      <c r="Y65" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="35" t="n">
@@ -10103,6 +10429,11 @@
           <t>The primary transaction participants were identified correctly, but Dana Holdings was omitted during the initial review of related corporate entities and supplier relationships; a WarRoom update was issued to add it. Preventive: mandatory secondary review for impacted-supplier assessments involving mergers, acquisitions, restructurings and other multi-entity transactions. RCA shared 13-Jul-2026.</t>
         </is>
       </c>
+      <c r="Y66" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="35" t="n">
@@ -10203,6 +10534,11 @@
         </is>
       </c>
       <c r="X67" s="33" t="n"/>
+      <c r="Y67" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="35" t="n">
@@ -10307,6 +10643,11 @@
           <t>RCA reviewed and sent to the customer as a PDF attached to EAO-10 (29-Jun-2026); the document text is not in the ticket.</t>
         </is>
       </c>
+      <c r="Y68" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="35" t="n">
@@ -10411,6 +10752,11 @@
           <t>RCA approved and sent to the customer on 25-Jun-2026 as a PDF attached to EAO-9; the document text is not in the ticket. The WarRoom itself was published before the RCA was issued.</t>
         </is>
       </c>
+      <c r="Y69" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="35" t="n">
@@ -10511,6 +10857,11 @@
         </is>
       </c>
       <c r="X70" s="33" t="n"/>
+      <c r="Y70" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="35" t="n">
@@ -10611,6 +10962,11 @@
         </is>
       </c>
       <c r="X71" s="33" t="n"/>
+      <c r="Y71" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="35" t="n">
@@ -10719,6 +11075,11 @@
           <t>Feeds covering the BorgWarner Vigo indefinite strike were in the public domain from 26-Jun-2026 but were not captured on the portal until 1 July; Engineering was asked to investigate why the 26-27 June sources were missed. RCA approved and shared 09-Jul-2026.</t>
         </is>
       </c>
+      <c r="Y72" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="35" t="n">
@@ -10819,6 +11180,11 @@
         </is>
       </c>
       <c r="X73" s="33" t="n"/>
+      <c r="Y73" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="35" t="n">
@@ -10923,6 +11289,11 @@
           <t>RCA approved and sent to the customer on 13-Jul-2026 as a PDF attached to EAO-14; the document text is not in the ticket.</t>
         </is>
       </c>
+      <c r="Y74" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="35" t="n">
@@ -11031,6 +11402,11 @@
           <t>The event met the Price Fluctuation reporting threshold and did qualify for a WarRoom; the failure came later, in customer-specific supplier normalization. The Samsung Electronics sites are normalized under Samsung for the affected customer, and that normalization was not applied during the impacted-site assessment, so the sites were never associated with the event and no customer WarRoom was created. This was not a parent-child modelling issue. Normalization is maintained outside the EventWatch editorial workflow, so the response is strengthened validation controls plus AI-assisted WarRoom generation rather than a guarantee. RCA shared 15-Jul-2026.</t>
         </is>
       </c>
+      <c r="Y75" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="35" t="n">
@@ -11133,6 +11509,11 @@
           <t>EventWatch captured multiple Philippines articles before the dedicated Philippines WarRoom was created, but they were assessed Not Impactful during reporting review, when available reports still described preparedness and localized impacts. Root cause: human assessment error underestimating the significance of the evolving Philippines impacts, which delayed WarRoom creation. Preventive: multi-country weather events assessed independently for each affected geography rather than inferred from the wider storm.</t>
         </is>
       </c>
+      <c r="Y76" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="35" t="n">
@@ -11235,6 +11616,11 @@
           <t>RCA reviewed and sent to the customer on 14-Jul-2026 as a PDF attached to EAO-17; the document text is not in the ticket.</t>
         </is>
       </c>
+      <c r="Y77" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="35" t="n">
@@ -11333,6 +11719,11 @@
         </is>
       </c>
       <c r="X78" s="33" t="n"/>
+      <c r="Y78" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="35" t="n">
@@ -11435,6 +11826,11 @@
           <t>Not a miss - an inquiry answered in full. EventWatch monitors power infrastructure continuously across utilities and transmission operators, government and emergency agencies, grid operators, news sources and official outage maps. Reporting is risk-based rather than every outage: mapped supplier sites in the affected region, impact on manufacturing hubs, ports, warehouses and logistics, expected outage duration, and public confirmation of operational disruption, all against regional reporting thresholds.</t>
         </is>
       </c>
+      <c r="Y79" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="35" t="n">
@@ -11537,6 +11933,11 @@
           <t>German-language sources reporting the ASSMANN WSW Components insolvency were not captured by the portal; Engineering was asked to investigate the feed gap. RCA reviewed and shared with the customer 20-Jul-2026.</t>
         </is>
       </c>
+      <c r="Y80" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="35" t="n">
@@ -11639,6 +12040,11 @@
           <t>RCA approved and sent to the customer on 21-Jul-2026 as a PDF attached to EAO-21; the document text is not in the ticket.</t>
         </is>
       </c>
+      <c r="Y81" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="35" t="n">
@@ -11737,6 +12143,11 @@
         </is>
       </c>
       <c r="X82" s="33" t="n"/>
+      <c r="Y82" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="35" t="n">
@@ -11837,6 +12248,11 @@
         </is>
       </c>
       <c r="X83" s="33" t="n"/>
+      <c r="Y83" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="35" t="n">
@@ -11939,6 +12355,11 @@
           <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
         </is>
       </c>
+      <c r="Y84" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="35" t="n">
@@ -12041,6 +12462,11 @@
           <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
         </is>
       </c>
+      <c r="Y85" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="35" t="n">
@@ -12143,6 +12569,11 @@
         </is>
       </c>
       <c r="X86" s="33" t="n"/>
+      <c r="Y86" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="35" t="n">
@@ -12247,6 +12678,11 @@
           <t>RCA approved and sent to the customer on 05-Aug-2026 as a PDF attached to EAO-23; the document text is not in the ticket.</t>
         </is>
       </c>
+      <c r="Y87" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="35" t="n">
@@ -12351,6 +12787,11 @@
           <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-27; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
         </is>
       </c>
+      <c r="Y88" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="35" t="n">
@@ -12453,6 +12894,11 @@
           <t>No RCA document issued - the team shares one only where there was a miss. Clarification given instead: EventWatch published the Kandla congestion event on reports of clearance delays up to 40 days and container shortages. The source article highlighted rice exports, but nothing indicated the congestion was confined to rice cargo, so mapped supplier sites within the impact area were sent Supplier Impact Confirmation requests as proactive validation. The outreach was not a statement that those suppliers were already impacted.</t>
         </is>
       </c>
+      <c r="Y89" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="35" t="n">
@@ -12557,6 +13003,11 @@
           <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-26; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
         </is>
       </c>
+      <c r="Y90" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="35" t="n">
@@ -12657,6 +13108,11 @@
         </is>
       </c>
       <c r="X91" s="33" t="n"/>
+      <c r="Y91" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="35" t="n">
@@ -12761,6 +13217,11 @@
           <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
         </is>
       </c>
+      <c r="Y92" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="35" t="n">
@@ -12865,6 +13326,11 @@
           <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
         </is>
       </c>
+      <c r="Y93" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="35" t="n">
@@ -12969,6 +13435,11 @@
           <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
         </is>
       </c>
+      <c r="Y94" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="35" t="n">
@@ -13069,6 +13540,11 @@
         </is>
       </c>
       <c r="X95" s="33" t="n"/>
+      <c r="Y95" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="35" t="n">
@@ -13173,6 +13649,11 @@
           <t>Feeds reporting the Qilin ransomware breach at Gindre India were not captured on the EventWatch portal; Engineering investigation requested 31-Aug-2026. RCA reviewed and shared with the customer 03-Sep-2026.</t>
         </is>
       </c>
+      <c r="Y96" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="35" t="n">
@@ -13268,6 +13749,11 @@
         </is>
       </c>
       <c r="X97" s="33" t="n"/>
+      <c r="Y97" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="35" t="n">
@@ -13363,6 +13849,11 @@
         </is>
       </c>
       <c r="X98" s="33" t="n"/>
+      <c r="Y98" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="35" t="n">
@@ -13461,6 +13952,11 @@
         </is>
       </c>
       <c r="X99" s="33" t="n"/>
+      <c r="Y99" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="35" t="n">
@@ -13559,6 +14055,11 @@
         </is>
       </c>
       <c r="X100" s="33" t="n"/>
+      <c r="Y100" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="35" t="n">
@@ -13657,6 +14158,11 @@
         </is>
       </c>
       <c r="X101" s="33" t="n"/>
+      <c r="Y101" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="35" t="n">
@@ -13759,6 +14265,11 @@
         </is>
       </c>
       <c r="X102" s="33" t="n"/>
+      <c r="Y102" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="35" t="n">
@@ -13861,6 +14372,11 @@
         </is>
       </c>
       <c r="X103" s="33" t="n"/>
+      <c r="Y103" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="35" t="n">
@@ -13963,6 +14479,11 @@
         </is>
       </c>
       <c r="X104" s="33" t="n"/>
+      <c r="Y104" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -16955,7 +17476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17654,30 +18175,30 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="30.75" customHeight="1">
+    <row r="28">
       <c r="A28" s="42" t="inlineStr">
         <is>
-          <t>Operational term</t>
+          <t>Field definition</t>
         </is>
       </c>
       <c r="B28" s="41" t="inlineStr">
         <is>
-          <t>EventWatch</t>
+          <t>Routed To</t>
         </is>
       </c>
       <c r="C28" s="41" t="inlineStr">
         <is>
-          <t>Operational monitoring service that identifies, assesses, and reports events relevant to customers.</t>
+          <t>Which team the record is directed to for action.</t>
         </is>
       </c>
       <c r="D28" s="41" t="inlineStr">
         <is>
-          <t>Common EventWatch terminology</t>
+          <t>EventWatch Ops - Nitin Rindhe for People- and Process-rooted records: analyst judgement, escalation, WarRoom decisions, threshold and methodology questions. Product &amp; Platform for Product-rooted records: ingestion, source coverage, keyword, clustering, mapping, visibility, platform and automation defects. Derived from Root Cause. EventWatch Ops still owns the customer-facing RCA on Product-routed records; routing says who investigates, not who replies.</t>
         </is>
       </c>
       <c r="E28" s="41" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>Routed To</t>
         </is>
       </c>
     </row>
@@ -17689,12 +18210,12 @@
       </c>
       <c r="B29" s="41" t="inlineStr">
         <is>
-          <t>WarRoom</t>
+          <t>EventWatch</t>
         </is>
       </c>
       <c r="C29" s="41" t="inlineStr">
         <is>
-          <t>Central event workspace used to publish, organize, and update an operational event.</t>
+          <t>Operational monitoring service that identifies, assesses, and reports events relevant to customers.</t>
         </is>
       </c>
       <c r="D29" s="41" t="inlineStr">
@@ -17716,12 +18237,12 @@
       </c>
       <c r="B30" s="41" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>WarRoom</t>
         </is>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
-          <t>Root Cause Analysis; a documented explanation of why an issue occurred and the corrective/preventive actions.</t>
+          <t>Central event workspace used to publish, organize, and update an operational event.</t>
         </is>
       </c>
       <c r="D30" s="41" t="inlineStr">
@@ -17743,12 +18264,12 @@
       </c>
       <c r="B31" s="41" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="C31" s="41" t="inlineStr">
         <is>
-          <t>Non-Conformance; an internal quality record raised when required process or control performance was not met.</t>
+          <t>Root Cause Analysis; a documented explanation of why an issue occurred and the corrective/preventive actions.</t>
         </is>
       </c>
       <c r="D31" s="41" t="inlineStr">
@@ -17770,12 +18291,12 @@
       </c>
       <c r="B32" s="41" t="inlineStr">
         <is>
-          <t>Not Impactful</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="C32" s="41" t="inlineStr">
         <is>
-          <t>Review outcome indicating that available evidence did not meet the threshold for EventWatch escalation.</t>
+          <t>Non-Conformance; an internal quality record raised when required process or control performance was not met.</t>
         </is>
       </c>
       <c r="D32" s="41" t="inlineStr">
@@ -17797,12 +18318,12 @@
       </c>
       <c r="B33" s="41" t="inlineStr">
         <is>
-          <t>Feed harvesting</t>
+          <t>Not Impactful</t>
         </is>
       </c>
       <c r="C33" s="41" t="inlineStr">
         <is>
-          <t>Automated collection of articles or reports from monitored information sources.</t>
+          <t>Review outcome indicating that available evidence did not meet the threshold for EventWatch escalation.</t>
         </is>
       </c>
       <c r="D33" s="41" t="inlineStr">
@@ -17824,12 +18345,12 @@
       </c>
       <c r="B34" s="41" t="inlineStr">
         <is>
-          <t>Source coverage</t>
+          <t>Feed harvesting</t>
         </is>
       </c>
       <c r="C34" s="41" t="inlineStr">
         <is>
-          <t>Availability and monitoring of relevant websites, feeds, registries, or publications.</t>
+          <t>Automated collection of articles or reports from monitored information sources.</t>
         </is>
       </c>
       <c r="D34" s="41" t="inlineStr">
@@ -17851,12 +18372,12 @@
       </c>
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Source coverage</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
         <is>
-          <t>Addition or refinement of search terms when available content was not identified correctly.</t>
+          <t>Availability and monitoring of relevant websites, feeds, registries, or publications.</t>
         </is>
       </c>
       <c r="D35" s="41" t="inlineStr">
@@ -17878,12 +18399,12 @@
       </c>
       <c r="B36" s="41" t="inlineStr">
         <is>
-          <t>Geofencing</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="C36" s="41" t="inlineStr">
         <is>
-          <t>Geographic impact logic used to associate an event area with customer or supplier locations.</t>
+          <t>Addition or refinement of search terms when available content was not identified correctly.</t>
         </is>
       </c>
       <c r="D36" s="41" t="inlineStr">
@@ -17905,12 +18426,12 @@
       </c>
       <c r="B37" s="41" t="inlineStr">
         <is>
-          <t>Cluster</t>
+          <t>Geofencing</t>
         </is>
       </c>
       <c r="C37" s="41" t="inlineStr">
         <is>
-          <t>Grouping of related articles or bulletins into one event record or WarRoom.</t>
+          <t>Geographic impact logic used to associate an event area with customer or supplier locations.</t>
         </is>
       </c>
       <c r="D37" s="41" t="inlineStr">
@@ -17932,12 +18453,12 @@
       </c>
       <c r="B38" s="41" t="inlineStr">
         <is>
-          <t>Human-in-the-loop review</t>
+          <t>Cluster</t>
         </is>
       </c>
       <c r="C38" s="41" t="inlineStr">
         <is>
-          <t>Analyst review that validates automated detection and decides whether to escalate or publish.</t>
+          <t>Grouping of related articles or bulletins into one event record or WarRoom.</t>
         </is>
       </c>
       <c r="D38" s="41" t="inlineStr">
@@ -17959,12 +18480,12 @@
       </c>
       <c r="B39" s="41" t="inlineStr">
         <is>
-          <t>Impacted supplier</t>
+          <t>Human-in-the-loop review</t>
         </is>
       </c>
       <c r="C39" s="41" t="inlineStr">
         <is>
-          <t>Customer-mapped supplier assessed as potentially affected by an event.</t>
+          <t>Analyst review that validates automated detection and decides whether to escalate or publish.</t>
         </is>
       </c>
       <c r="D39" s="41" t="inlineStr">
@@ -17981,233 +18502,233 @@
     <row r="40" ht="30.75" customHeight="1">
       <c r="A40" s="42" t="inlineStr">
         <is>
+          <t>Operational term</t>
+        </is>
+      </c>
+      <c r="B40" s="41" t="inlineStr">
+        <is>
+          <t>Impacted supplier</t>
+        </is>
+      </c>
+      <c r="C40" s="41" t="inlineStr">
+        <is>
+          <t>Customer-mapped supplier assessed as potentially affected by an event.</t>
+        </is>
+      </c>
+      <c r="D40" s="41" t="inlineStr">
+        <is>
+          <t>Common EventWatch terminology</t>
+        </is>
+      </c>
+      <c r="E40" s="41" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30.75" customHeight="1">
+      <c r="A41" s="42" t="inlineStr">
+        <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B40" s="41" t="inlineStr">
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>Bankruptcy</t>
         </is>
       </c>
-      <c r="C40" s="41" t="inlineStr">
+      <c r="C41" s="41" t="inlineStr">
         <is>
           <t>Formal insolvency, bankruptcy filing, restructuring, or equivalent proceeding.</t>
         </is>
       </c>
-      <c r="D40" s="41" t="inlineStr">
+      <c r="D41" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E40" s="41" t="inlineStr">
+      <c r="E41" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="42" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B41" s="41" t="inlineStr">
+      <c r="B42" s="41" t="inlineStr">
         <is>
           <t>Chemical Spill</t>
         </is>
       </c>
-      <c r="C41" s="41" t="inlineStr">
+      <c r="C42" s="41" t="inlineStr">
         <is>
           <t>Release or leak of a hazardous chemical substance.</t>
         </is>
       </c>
-      <c r="D41" s="41" t="inlineStr">
+      <c r="D42" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E41" s="41" t="inlineStr">
+      <c r="E42" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30.75" customHeight="1">
-      <c r="A42" s="42" t="inlineStr">
+    <row r="43" ht="30.75" customHeight="1">
+      <c r="A43" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B42" s="41" t="inlineStr">
+      <c r="B43" s="41" t="inlineStr">
         <is>
           <t>Cyber Attack</t>
         </is>
       </c>
-      <c r="C42" s="41" t="inlineStr">
+      <c r="C43" s="41" t="inlineStr">
         <is>
           <t>Cybersecurity incident such as ransomware, intrusion, compromise, or data breach.</t>
         </is>
       </c>
-      <c r="D42" s="41" t="inlineStr">
+      <c r="D43" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E42" s="41" t="inlineStr">
+      <c r="E43" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="42" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B43" s="41" t="inlineStr">
+      <c r="B44" s="41" t="inlineStr">
         <is>
           <t>Earthquake</t>
         </is>
       </c>
-      <c r="C43" s="41" t="inlineStr">
+      <c r="C44" s="41" t="inlineStr">
         <is>
           <t>Seismic event with potential operational or supply-chain impact.</t>
         </is>
       </c>
-      <c r="D43" s="41" t="inlineStr">
+      <c r="D44" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E43" s="41" t="inlineStr">
+      <c r="E44" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30.75" customHeight="1">
-      <c r="A44" s="42" t="inlineStr">
+    <row r="45" ht="30.75" customHeight="1">
+      <c r="A45" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B44" s="41" t="inlineStr">
+      <c r="B45" s="41" t="inlineStr">
         <is>
           <t>Extreme Weather</t>
         </is>
       </c>
-      <c r="C44" s="41" t="inlineStr">
+      <c r="C45" s="41" t="inlineStr">
         <is>
           <t>Severe weather such as storms, tornadoes, typhoons, flooding, or snowstorms.</t>
         </is>
       </c>
-      <c r="D44" s="41" t="inlineStr">
+      <c r="D45" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E44" s="41" t="inlineStr">
+      <c r="E45" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="42" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B45" s="41" t="inlineStr">
+      <c r="B46" s="41" t="inlineStr">
         <is>
           <t>Factory Closure</t>
         </is>
       </c>
-      <c r="C45" s="41" t="inlineStr">
+      <c r="C46" s="41" t="inlineStr">
         <is>
           <t>Planned or unplanned closure of a manufacturing facility.</t>
         </is>
       </c>
-      <c r="D45" s="41" t="inlineStr">
+      <c r="D46" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E45" s="41" t="inlineStr">
+      <c r="E46" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30.75" customHeight="1">
-      <c r="A46" s="42" t="inlineStr">
+    <row r="47" ht="30.75" customHeight="1">
+      <c r="A47" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B46" s="41" t="inlineStr">
+      <c r="B47" s="41" t="inlineStr">
         <is>
           <t>Factory Disruption</t>
         </is>
       </c>
-      <c r="C46" s="41" t="inlineStr">
+      <c r="C47" s="41" t="inlineStr">
         <is>
           <t>Operational interruption at a manufacturing facility that is not classified as closure or fire.</t>
         </is>
       </c>
-      <c r="D46" s="41" t="inlineStr">
+      <c r="D47" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E46" s="41" t="inlineStr">
+      <c r="E47" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="42" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B47" s="41" t="inlineStr">
+      <c r="B48" s="41" t="inlineStr">
         <is>
           <t>Factory Fire</t>
         </is>
       </c>
-      <c r="C47" s="41" t="inlineStr">
+      <c r="C48" s="41" t="inlineStr">
         <is>
           <t>Fire affecting a manufacturing, production, or storage facility.</t>
-        </is>
-      </c>
-      <c r="D47" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category</t>
-        </is>
-      </c>
-      <c r="E47" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30.75" customHeight="1">
-      <c r="A48" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B48" s="41" t="inlineStr">
-        <is>
-          <t>Financial Distress</t>
-        </is>
-      </c>
-      <c r="C48" s="41" t="inlineStr">
-        <is>
-          <t>Material financial difficulty that does not yet constitute a formal bankruptcy event.</t>
         </is>
       </c>
       <c r="D48" s="41" t="inlineStr">
@@ -18229,39 +18750,39 @@
       </c>
       <c r="B49" s="41" t="inlineStr">
         <is>
+          <t>Financial Distress</t>
+        </is>
+      </c>
+      <c r="C49" s="41" t="inlineStr">
+        <is>
+          <t>Material financial difficulty that does not yet constitute a formal bankruptcy event.</t>
+        </is>
+      </c>
+      <c r="D49" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category</t>
+        </is>
+      </c>
+      <c r="E49" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30.75" customHeight="1">
+      <c r="A50" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="inlineStr">
+        <is>
           <t>Geopolitical</t>
         </is>
       </c>
-      <c r="C49" s="41" t="inlineStr">
+      <c r="C50" s="41" t="inlineStr">
         <is>
           <t>Political, border, security, conflict, or humanitarian development affecting operations.</t>
-        </is>
-      </c>
-      <c r="D49" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category</t>
-        </is>
-      </c>
-      <c r="E49" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B50" s="41" t="inlineStr">
-        <is>
-          <t>Labor Disruption</t>
-        </is>
-      </c>
-      <c r="C50" s="41" t="inlineStr">
-        <is>
-          <t>Strike, work stoppage, industrial action, or labor-related disruption.</t>
         </is>
       </c>
       <c r="D50" s="41" t="inlineStr">
@@ -18283,12 +18804,12 @@
       </c>
       <c r="B51" s="41" t="inlineStr">
         <is>
-          <t>Leadership Transition</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>Change in senior executive or organizational leadership.</t>
+          <t>Strike, work stoppage, industrial action, or labor-related disruption.</t>
         </is>
       </c>
       <c r="D51" s="41" t="inlineStr">
@@ -18310,12 +18831,12 @@
       </c>
       <c r="B52" s="41" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Leadership Transition</t>
         </is>
       </c>
       <c r="C52" s="41" t="inlineStr">
         <is>
-          <t>Merger, acquisition, divestiture, or comparable corporate transaction.</t>
+          <t>Change in senior executive or organizational leadership.</t>
         </is>
       </c>
       <c r="D52" s="41" t="inlineStr">
@@ -18337,12 +18858,12 @@
       </c>
       <c r="B53" s="41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="C53" s="41" t="inlineStr">
         <is>
-          <t>No applicable event category, generally used for non-event inquiries.</t>
+          <t>Merger, acquisition, divestiture, or comparable corporate transaction.</t>
         </is>
       </c>
       <c r="D53" s="41" t="inlineStr">
@@ -18364,12 +18885,12 @@
       </c>
       <c r="B54" s="41" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C54" s="41" t="inlineStr">
         <is>
-          <t>Demonstration, civil unrest, riot, or blockade driven by protest activity.</t>
+          <t>No applicable event category, generally used for non-event inquiries.</t>
         </is>
       </c>
       <c r="D54" s="41" t="inlineStr">
@@ -18391,93 +18912,93 @@
       </c>
       <c r="B55" s="41" t="inlineStr">
         <is>
+          <t>Protest/Riot</t>
+        </is>
+      </c>
+      <c r="C55" s="41" t="inlineStr">
+        <is>
+          <t>Demonstration, civil unrest, riot, or blockade driven by protest activity.</t>
+        </is>
+      </c>
+      <c r="D55" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category</t>
+        </is>
+      </c>
+      <c r="E55" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="inlineStr">
+        <is>
           <t>Regulatory Change</t>
         </is>
       </c>
-      <c r="C55" s="41" t="inlineStr">
+      <c r="C56" s="41" t="inlineStr">
         <is>
           <t>Government rule, sanction, export control, or regulatory action.</t>
         </is>
       </c>
-      <c r="D55" s="41" t="inlineStr">
+      <c r="D56" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E55" s="41" t="inlineStr">
+      <c r="E56" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30.75" customHeight="1">
-      <c r="A56" s="42" t="inlineStr">
+    <row r="57" ht="30.75" customHeight="1">
+      <c r="A57" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B56" s="41" t="inlineStr">
+      <c r="B57" s="41" t="inlineStr">
         <is>
           <t>Supply Shortage</t>
         </is>
       </c>
-      <c r="C56" s="41" t="inlineStr">
+      <c r="C57" s="41" t="inlineStr">
         <is>
           <t>Shortage or constrained availability of materials, components, energy, or goods.</t>
         </is>
       </c>
-      <c r="D56" s="41" t="inlineStr">
+      <c r="D57" s="41" t="inlineStr">
         <is>
           <t>Standard event category</t>
         </is>
       </c>
-      <c r="E56" s="41" t="inlineStr">
+      <c r="E57" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="42" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="42" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>
       </c>
-      <c r="B57" s="41" t="inlineStr">
+      <c r="B58" s="41" t="inlineStr">
         <is>
           <t>Transport Disruption</t>
         </is>
       </c>
-      <c r="C57" s="41" t="inlineStr">
+      <c r="C58" s="41" t="inlineStr">
         <is>
           <t>Disruption to roads, bridges, ports, rail, air, or logistics routes.</t>
-        </is>
-      </c>
-      <c r="D57" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category</t>
-        </is>
-      </c>
-      <c r="E57" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30.75" customHeight="1">
-      <c r="A58" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B58" s="41" t="inlineStr">
-        <is>
-          <t>Wildfire</t>
-        </is>
-      </c>
-      <c r="C58" s="41" t="inlineStr">
-        <is>
-          <t>Uncontrolled vegetation fire with potential geographic or operational impact.</t>
         </is>
       </c>
       <c r="D58" s="41" t="inlineStr">
@@ -18494,27 +19015,27 @@
     <row r="59" ht="30.75" customHeight="1">
       <c r="A59" s="42" t="inlineStr">
         <is>
-          <t>Issue type</t>
+          <t>Event type</t>
         </is>
       </c>
       <c r="B59" s="41" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="C59" s="41" t="inlineStr">
         <is>
-          <t>Customer reports a service failure, miss, delay, incorrect action, or other concern.</t>
+          <t>Uncontrolled vegetation fire with potential geographic or operational impact.</t>
         </is>
       </c>
       <c r="D59" s="41" t="inlineStr">
         <is>
-          <t>Included in complaint metrics</t>
+          <t>Standard event category</t>
         </is>
       </c>
       <c r="E59" s="41" t="inlineStr">
         <is>
-          <t>Issue Type</t>
+          <t>Event type</t>
         </is>
       </c>
     </row>
@@ -18526,17 +19047,17 @@
       </c>
       <c r="B60" s="41" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="C60" s="41" t="inlineStr">
         <is>
-          <t>Customer requests verification, explanation, or information without a confirmed service failure.</t>
+          <t>Customer reports a service failure, miss, delay, incorrect action, or other concern.</t>
         </is>
       </c>
       <c r="D60" s="41" t="inlineStr">
         <is>
-          <t>Tracked separately from complaints</t>
+          <t>Included in complaint metrics</t>
         </is>
       </c>
       <c r="E60" s="41" t="inlineStr">
@@ -18548,27 +19069,27 @@
     <row r="61" ht="30.75" customHeight="1">
       <c r="A61" s="42" t="inlineStr">
         <is>
-          <t>Root cause</t>
+          <t>Issue type</t>
         </is>
       </c>
       <c r="B61" s="41" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="C61" s="41" t="inlineStr">
         <is>
-          <t>Human judgment, review, prioritization, publishing, or execution was the primary cause.</t>
+          <t>Customer requests verification, explanation, or information without a confirmed service failure.</t>
         </is>
       </c>
       <c r="D61" s="41" t="inlineStr">
         <is>
-          <t>Primary cause domain</t>
+          <t>Tracked separately from complaints</t>
         </is>
       </c>
       <c r="E61" s="41" t="inlineStr">
         <is>
-          <t>Root Cause</t>
+          <t>Issue Type</t>
         </is>
       </c>
     </row>
@@ -18580,12 +19101,12 @@
       </c>
       <c r="B62" s="41" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="C62" s="41" t="inlineStr">
         <is>
-          <t>Policy, workflow, threshold, mapping method, or procedural design was the primary cause.</t>
+          <t>Human judgment, review, prioritization, publishing, or execution was the primary cause.</t>
         </is>
       </c>
       <c r="D62" s="41" t="inlineStr">
@@ -18607,49 +19128,49 @@
       </c>
       <c r="B63" s="41" t="inlineStr">
         <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C63" s="41" t="inlineStr">
+        <is>
+          <t>Policy, workflow, threshold, mapping method, or procedural design was the primary cause.</t>
+        </is>
+      </c>
+      <c r="D63" s="41" t="inlineStr">
+        <is>
+          <t>Primary cause domain</t>
+        </is>
+      </c>
+      <c r="E63" s="41" t="inlineStr">
+        <is>
+          <t>Root Cause</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30.75" customHeight="1">
+      <c r="A64" s="42" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+      <c r="B64" s="41" t="inlineStr">
+        <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="C63" s="41" t="inlineStr">
+      <c r="C64" s="41" t="inlineStr">
         <is>
           <t>Technology, data ingestion, source coverage, detection, clustering, or platform behavior was the primary cause.</t>
         </is>
       </c>
-      <c r="D63" s="41" t="inlineStr">
+      <c r="D64" s="41" t="inlineStr">
         <is>
           <t>Primary cause domain</t>
         </is>
       </c>
-      <c r="E63" s="41" t="inlineStr">
+      <c r="E64" s="41" t="inlineStr">
         <is>
           <t>Root Cause</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B64" s="41" t="inlineStr">
-        <is>
-          <t>Captured Late</t>
-        </is>
-      </c>
-      <c r="C64" s="41" t="inlineStr">
-        <is>
-          <t>Relevant information entered the workflow later than required.</t>
-        </is>
-      </c>
-      <c r="D64" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E64" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
         </is>
       </c>
     </row>
@@ -18661,66 +19182,66 @@
       </c>
       <c r="B65" s="41" t="inlineStr">
         <is>
+          <t>Captured Late</t>
+        </is>
+      </c>
+      <c r="C65" s="41" t="inlineStr">
+        <is>
+          <t>Relevant information entered the workflow later than required.</t>
+        </is>
+      </c>
+      <c r="D65" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E65" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B66" s="41" t="inlineStr">
+        <is>
           <t>Duplication</t>
         </is>
       </c>
-      <c r="C65" s="41" t="inlineStr">
+      <c r="C66" s="41" t="inlineStr">
         <is>
           <t>Related content was split into duplicate WarRooms or event records.</t>
         </is>
       </c>
-      <c r="D65" s="41" t="inlineStr">
+      <c r="D66" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E65" s="41" t="inlineStr">
+      <c r="E66" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30.75" customHeight="1">
-      <c r="A66" s="42" t="inlineStr">
+    <row r="67" ht="30.75" customHeight="1">
+      <c r="A67" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B66" s="41" t="inlineStr">
+      <c r="B67" s="41" t="inlineStr">
         <is>
           <t>Event Identification</t>
         </is>
       </c>
-      <c r="C66" s="41" t="inlineStr">
+      <c r="C67" s="41" t="inlineStr">
         <is>
           <t>The relevant event was not recognized or converted into reportable coverage.</t>
-        </is>
-      </c>
-      <c r="D66" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E66" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B67" s="41" t="inlineStr">
-        <is>
-          <t>Industry selection</t>
-        </is>
-      </c>
-      <c r="C67" s="41" t="inlineStr">
-        <is>
-          <t>An incorrect or missing industry classification affected tracking.</t>
         </is>
       </c>
       <c r="D67" s="41" t="inlineStr">
@@ -18742,66 +19263,66 @@
       </c>
       <c r="B68" s="41" t="inlineStr">
         <is>
+          <t>Industry selection</t>
+        </is>
+      </c>
+      <c r="C68" s="41" t="inlineStr">
+        <is>
+          <t>An incorrect or missing industry classification affected tracking.</t>
+        </is>
+      </c>
+      <c r="D68" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E68" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B69" s="41" t="inlineStr">
+        <is>
           <t>Keyword Update</t>
         </is>
       </c>
-      <c r="C68" s="41" t="inlineStr">
+      <c r="C69" s="41" t="inlineStr">
         <is>
           <t>Search or detection terms required addition or refinement.</t>
         </is>
       </c>
-      <c r="D68" s="41" t="inlineStr">
+      <c r="D69" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E68" s="41" t="inlineStr">
+      <c r="E69" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30.75" customHeight="1">
-      <c r="A69" s="42" t="inlineStr">
+    <row r="70" ht="30.75" customHeight="1">
+      <c r="A70" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B69" s="41" t="inlineStr">
+      <c r="B70" s="41" t="inlineStr">
         <is>
           <t>Mapping</t>
         </is>
       </c>
-      <c r="C69" s="41" t="inlineStr">
+      <c r="C70" s="41" t="inlineStr">
         <is>
           <t>Customer, supplier, company, facility, or impact relationship was missing or incorrect.</t>
-        </is>
-      </c>
-      <c r="D69" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E69" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B70" s="41" t="inlineStr">
-        <is>
-          <t>Policy/Logic</t>
-        </is>
-      </c>
-      <c r="C70" s="41" t="inlineStr">
-        <is>
-          <t>A rule, threshold, or decision logic produced or explained the outcome.</t>
         </is>
       </c>
       <c r="D70" s="41" t="inlineStr">
@@ -18823,39 +19344,39 @@
       </c>
       <c r="B71" s="41" t="inlineStr">
         <is>
+          <t>Policy/Logic</t>
+        </is>
+      </c>
+      <c r="C71" s="41" t="inlineStr">
+        <is>
+          <t>A rule, threshold, or decision logic produced or explained the outcome.</t>
+        </is>
+      </c>
+      <c r="D71" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E71" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B72" s="41" t="inlineStr">
+        <is>
           <t>Prioritization</t>
         </is>
       </c>
-      <c r="C71" s="41" t="inlineStr">
+      <c r="C72" s="41" t="inlineStr">
         <is>
           <t>A detected item was not handled with the required urgency.</t>
-        </is>
-      </c>
-      <c r="D71" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E71" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="30.75" customHeight="1">
-      <c r="A72" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B72" s="41" t="inlineStr">
-        <is>
-          <t>Process Clarification</t>
-        </is>
-      </c>
-      <c r="C72" s="41" t="inlineStr">
-        <is>
-          <t>The case required explanation of policy, thresholds, or workflow rather than defect correction.</t>
         </is>
       </c>
       <c r="D72" s="41" t="inlineStr">
@@ -18877,93 +19398,93 @@
       </c>
       <c r="B73" s="41" t="inlineStr">
         <is>
+          <t>Process Clarification</t>
+        </is>
+      </c>
+      <c r="C73" s="41" t="inlineStr">
+        <is>
+          <t>The case required explanation of policy, thresholds, or workflow rather than defect correction.</t>
+        </is>
+      </c>
+      <c r="D73" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E73" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30.75" customHeight="1">
+      <c r="A74" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B74" s="41" t="inlineStr">
+        <is>
           <t>Relevancy</t>
         </is>
       </c>
-      <c r="C73" s="41" t="inlineStr">
+      <c r="C74" s="41" t="inlineStr">
         <is>
           <t>The item’s relevance to the customer or EventWatch scope was disputed or incorrectly assessed.</t>
         </is>
       </c>
-      <c r="D73" s="41" t="inlineStr">
+      <c r="D74" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E73" s="41" t="inlineStr">
+      <c r="E74" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="42" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B74" s="41" t="inlineStr">
+      <c r="B75" s="41" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="C74" s="41" t="inlineStr">
+      <c r="C75" s="41" t="inlineStr">
         <is>
           <t>Human assessment or quality review led to the issue.</t>
         </is>
       </c>
-      <c r="D74" s="41" t="inlineStr">
+      <c r="D75" s="41" t="inlineStr">
         <is>
           <t>Detailed cause/handling category</t>
         </is>
       </c>
-      <c r="E74" s="41" t="inlineStr">
+      <c r="E75" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="30.75" customHeight="1">
-      <c r="A75" s="42" t="inlineStr">
+    <row r="76" ht="30.75" customHeight="1">
+      <c r="A76" s="42" t="inlineStr">
         <is>
           <t>Sub-type</t>
         </is>
       </c>
-      <c r="B75" s="41" t="inlineStr">
+      <c r="B76" s="41" t="inlineStr">
         <is>
           <t>Source Coverage</t>
         </is>
       </c>
-      <c r="C75" s="41" t="inlineStr">
+      <c r="C76" s="41" t="inlineStr">
         <is>
           <t>The relevant source was unavailable, unmonitored, restricted, or not harvested.</t>
-        </is>
-      </c>
-      <c r="D75" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E75" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B76" s="41" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="C76" s="41" t="inlineStr">
-        <is>
-          <t>The concern relates to reporting or consolidation strategy.</t>
         </is>
       </c>
       <c r="D76" s="41" t="inlineStr">
@@ -18985,39 +19506,39 @@
       </c>
       <c r="B77" s="41" t="inlineStr">
         <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="C77" s="41" t="inlineStr">
+        <is>
+          <t>The concern relates to reporting or consolidation strategy.</t>
+        </is>
+      </c>
+      <c r="D77" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category</t>
+        </is>
+      </c>
+      <c r="E77" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B78" s="41" t="inlineStr">
+        <is>
           <t>Tagging</t>
         </is>
       </c>
-      <c r="C77" s="41" t="inlineStr">
+      <c r="C78" s="41" t="inlineStr">
         <is>
           <t>A required category or industry tag was missing or incorrect.</t>
-        </is>
-      </c>
-      <c r="D77" s="41" t="inlineStr">
-        <is>
-          <t>Detailed cause/handling category</t>
-        </is>
-      </c>
-      <c r="E77" s="41" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="30.75" customHeight="1">
-      <c r="A78" s="42" t="inlineStr">
-        <is>
-          <t>Sub-type</t>
-        </is>
-      </c>
-      <c r="B78" s="41" t="inlineStr">
-        <is>
-          <t>Visibility</t>
-        </is>
-      </c>
-      <c r="C78" s="41" t="inlineStr">
-        <is>
-          <t>Published content was not visible because of profile, portal, notification, or display conditions.</t>
         </is>
       </c>
       <c r="D78" s="41" t="inlineStr">
@@ -19039,12 +19560,12 @@
       </c>
       <c r="B79" s="41" t="inlineStr">
         <is>
-          <t>WarRoom Creation</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="C79" s="41" t="inlineStr">
         <is>
-          <t>A required WarRoom was not created despite available EventWatch coverage.</t>
+          <t>Published content was not visible because of profile, portal, notification, or display conditions.</t>
         </is>
       </c>
       <c r="D79" s="41" t="inlineStr">
@@ -19061,27 +19582,27 @@
     <row r="80" ht="30.75" customHeight="1">
       <c r="A80" s="42" t="inlineStr">
         <is>
-          <t>Improvement classification</t>
+          <t>Sub-type</t>
         </is>
       </c>
       <c r="B80" s="41" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>WarRoom Creation</t>
         </is>
       </c>
       <c r="C80" s="41" t="inlineStr">
         <is>
-          <t>Control, workflow, model, or monitoring enhancement rather than correction of a confirmed defect.</t>
+          <t>A required WarRoom was not created despite available EventWatch coverage.</t>
         </is>
       </c>
       <c r="D80" s="41" t="inlineStr">
         <is>
-          <t>Enhancement</t>
+          <t>Detailed cause/handling category</t>
         </is>
       </c>
       <c r="E80" s="41" t="inlineStr">
         <is>
-          <t>Improvement VS Bug</t>
+          <t>Sub-type</t>
         </is>
       </c>
     </row>
@@ -19093,49 +19614,49 @@
       </c>
       <c r="B81" s="41" t="inlineStr">
         <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="C81" s="41" t="inlineStr">
+        <is>
+          <t>Control, workflow, model, or monitoring enhancement rather than correction of a confirmed defect.</t>
+        </is>
+      </c>
+      <c r="D81" s="41" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E81" s="41" t="inlineStr">
+        <is>
+          <t>Improvement VS Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="30.75" customHeight="1">
+      <c r="A82" s="42" t="inlineStr">
+        <is>
+          <t>Improvement classification</t>
+        </is>
+      </c>
+      <c r="B82" s="41" t="inlineStr">
+        <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="C81" s="41" t="inlineStr">
+      <c r="C82" s="41" t="inlineStr">
         <is>
           <t>Confirmed product or engineering defect requiring correction.</t>
         </is>
       </c>
-      <c r="D81" s="41" t="inlineStr">
+      <c r="D82" s="41" t="inlineStr">
         <is>
           <t>Defect</t>
         </is>
       </c>
-      <c r="E81" s="41" t="inlineStr">
+      <c r="E82" s="41" t="inlineStr">
         <is>
           <t>Improvement VS Bug</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="42" t="inlineStr">
-        <is>
-          <t>Fix status</t>
-        </is>
-      </c>
-      <c r="B82" s="41" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C82" s="41" t="inlineStr">
-        <is>
-          <t>Immediate corrective action was completed.</t>
-        </is>
-      </c>
-      <c r="D82" s="41" t="inlineStr">
-        <is>
-          <t>Current resolution state</t>
-        </is>
-      </c>
-      <c r="E82" s="41" t="inlineStr">
-        <is>
-          <t>Short Term Fix Status</t>
         </is>
       </c>
     </row>
@@ -19147,76 +19668,76 @@
       </c>
       <c r="B83" s="41" t="inlineStr">
         <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C83" s="41" t="inlineStr">
+        <is>
+          <t>Immediate corrective action was completed.</t>
+        </is>
+      </c>
+      <c r="D83" s="41" t="inlineStr">
+        <is>
+          <t>Current resolution state</t>
+        </is>
+      </c>
+      <c r="E83" s="41" t="inlineStr">
+        <is>
+          <t>Short Term Fix Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="42" t="inlineStr">
+        <is>
+          <t>Fix status</t>
+        </is>
+      </c>
+      <c r="B84" s="41" t="inlineStr">
+        <is>
           <t>RCA Shared</t>
         </is>
       </c>
-      <c r="C83" s="41" t="inlineStr">
+      <c r="C84" s="41" t="inlineStr">
         <is>
           <t>The root cause analysis was completed and shared with the customer.</t>
         </is>
       </c>
-      <c r="D83" s="41" t="inlineStr">
+      <c r="D84" s="41" t="inlineStr">
         <is>
           <t>Current resolution state</t>
         </is>
       </c>
-      <c r="E83" s="41" t="inlineStr">
+      <c r="E84" s="41" t="inlineStr">
         <is>
           <t>Short Term Fix Status</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="30.75" customHeight="1">
-      <c r="A84" s="42" t="inlineStr">
+    <row r="85" ht="30.75" customHeight="1">
+      <c r="A85" s="42" t="inlineStr">
         <is>
           <t>Fix status</t>
         </is>
       </c>
-      <c r="B84" s="41" t="inlineStr">
+      <c r="B85" s="41" t="inlineStr">
         <is>
           <t>Clarification Provided</t>
         </is>
       </c>
-      <c r="C84" s="41" t="inlineStr">
+      <c r="C85" s="41" t="inlineStr">
         <is>
           <t>The customer received an explanation, verification result, or policy/process clarification.</t>
         </is>
       </c>
-      <c r="D84" s="41" t="inlineStr">
+      <c r="D85" s="41" t="inlineStr">
         <is>
           <t>Current resolution state</t>
         </is>
       </c>
-      <c r="E84" s="41" t="inlineStr">
+      <c r="E85" s="41" t="inlineStr">
         <is>
           <t>Short Term Fix Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="42" t="inlineStr">
-        <is>
-          <t>Boolean flag</t>
-        </is>
-      </c>
-      <c r="B85" s="41" t="inlineStr">
-        <is>
-          <t>Yes — RCA Requested</t>
-        </is>
-      </c>
-      <c r="C85" s="41" t="inlineStr">
-        <is>
-          <t>A formal root cause analysis was requested.</t>
-        </is>
-      </c>
-      <c r="D85" s="41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E85" s="41" t="inlineStr">
-        <is>
-          <t>RCA Requested</t>
         </is>
       </c>
     </row>
@@ -19228,49 +19749,49 @@
       </c>
       <c r="B86" s="41" t="inlineStr">
         <is>
+          <t>Yes — RCA Requested</t>
+        </is>
+      </c>
+      <c r="C86" s="41" t="inlineStr">
+        <is>
+          <t>A formal root cause analysis was requested.</t>
+        </is>
+      </c>
+      <c r="D86" s="41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E86" s="41" t="inlineStr">
+        <is>
+          <t>RCA Requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="42" t="inlineStr">
+        <is>
+          <t>Boolean flag</t>
+        </is>
+      </c>
+      <c r="B87" s="41" t="inlineStr">
+        <is>
           <t>No — RCA Requested</t>
         </is>
       </c>
-      <c r="C86" s="41" t="inlineStr">
+      <c r="C87" s="41" t="inlineStr">
         <is>
           <t>No formal root cause analysis was requested.</t>
         </is>
       </c>
-      <c r="D86" s="41" t="inlineStr">
+      <c r="D87" s="41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E86" s="41" t="inlineStr">
+      <c r="E87" s="41" t="inlineStr">
         <is>
           <t>RCA Requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="30.75" customHeight="1">
-      <c r="A87" s="42" t="inlineStr">
-        <is>
-          <t>Boolean flag</t>
-        </is>
-      </c>
-      <c r="B87" s="41" t="inlineStr">
-        <is>
-          <t>Yes — Missed_Flag</t>
-        </is>
-      </c>
-      <c r="C87" s="41" t="inlineStr">
-        <is>
-          <t>Expected coverage, alerting, escalation, or WarRoom action was missed or materially delayed.</t>
-        </is>
-      </c>
-      <c r="D87" s="41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E87" s="41" t="inlineStr">
-        <is>
-          <t>Missed_Flag</t>
         </is>
       </c>
     </row>
@@ -19282,49 +19803,49 @@
       </c>
       <c r="B88" s="41" t="inlineStr">
         <is>
+          <t>Yes — Missed_Flag</t>
+        </is>
+      </c>
+      <c r="C88" s="41" t="inlineStr">
+        <is>
+          <t>Expected coverage, alerting, escalation, or WarRoom action was missed or materially delayed.</t>
+        </is>
+      </c>
+      <c r="D88" s="41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E88" s="41" t="inlineStr">
+        <is>
+          <t>Missed_Flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="30.75" customHeight="1">
+      <c r="A89" s="42" t="inlineStr">
+        <is>
+          <t>Boolean flag</t>
+        </is>
+      </c>
+      <c r="B89" s="41" t="inlineStr">
+        <is>
           <t>No — Missed_Flag</t>
         </is>
       </c>
-      <c r="C88" s="41" t="inlineStr">
+      <c r="C89" s="41" t="inlineStr">
         <is>
           <t>No confirmed reporting miss; the case concerns clarification, relevancy, mapping, duplication, or another non-miss issue.</t>
         </is>
       </c>
-      <c r="D88" s="41" t="inlineStr">
+      <c r="D89" s="41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E88" s="41" t="inlineStr">
+      <c r="E89" s="41" t="inlineStr">
         <is>
           <t>Missed_Flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="42" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="B89" s="41" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C89" s="41" t="inlineStr">
-        <is>
-          <t>Material impact or priority requiring elevated management attention.</t>
-        </is>
-      </c>
-      <c r="D89" s="41" t="inlineStr">
-        <is>
-          <t>Priority level</t>
-        </is>
-      </c>
-      <c r="E89" s="41" t="inlineStr">
-        <is>
-          <t>Severity</t>
         </is>
       </c>
     </row>
@@ -19336,12 +19857,12 @@
       </c>
       <c r="B90" s="41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>Standard operational complaint or issue requiring tracked response.</t>
+          <t>Material impact or priority requiring elevated management attention.</t>
         </is>
       </c>
       <c r="D90" s="41" t="inlineStr">
@@ -19363,12 +19884,12 @@
       </c>
       <c r="B91" s="41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C91" s="41" t="inlineStr">
         <is>
-          <t>Limited-impact inquiry or quality issue with lower operational urgency.</t>
+          <t>Standard operational complaint or issue requiring tracked response.</t>
         </is>
       </c>
       <c r="D91" s="41" t="inlineStr">
@@ -19385,27 +19906,27 @@
     <row r="92">
       <c r="A92" s="42" t="inlineStr">
         <is>
-          <t>Automation focus</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="B92" s="41" t="inlineStr">
         <is>
-          <t>AI-Assisted Geofencing</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>Automate or improve impact-area creation and location validation.</t>
+          <t>Limited-impact inquiry or quality issue with lower operational urgency.</t>
         </is>
       </c>
       <c r="D92" s="41" t="inlineStr">
         <is>
-          <t>Standardized dashboard category</t>
+          <t>Priority level</t>
         </is>
       </c>
       <c r="E92" s="41" t="inlineStr">
         <is>
-          <t>Standard Automation Focus</t>
+          <t>Severity</t>
         </is>
       </c>
     </row>
@@ -19417,93 +19938,93 @@
       </c>
       <c r="B93" s="41" t="inlineStr">
         <is>
+          <t>AI-Assisted Geofencing</t>
+        </is>
+      </c>
+      <c r="C93" s="41" t="inlineStr">
+        <is>
+          <t>Automate or improve impact-area creation and location validation.</t>
+        </is>
+      </c>
+      <c r="D93" s="41" t="inlineStr">
+        <is>
+          <t>Standardized dashboard category</t>
+        </is>
+      </c>
+      <c r="E93" s="41" t="inlineStr">
+        <is>
+          <t>Standard Automation Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="42" t="inlineStr">
+        <is>
+          <t>Automation focus</t>
+        </is>
+      </c>
+      <c r="B94" s="41" t="inlineStr">
+        <is>
           <t>Automated Industry Tagging</t>
         </is>
       </c>
-      <c r="C93" s="41" t="inlineStr">
+      <c r="C94" s="41" t="inlineStr">
         <is>
           <t>Automatically assign and validate industry classifications.</t>
         </is>
       </c>
-      <c r="D93" s="41" t="inlineStr">
+      <c r="D94" s="41" t="inlineStr">
         <is>
           <t>Standardized dashboard category</t>
         </is>
       </c>
-      <c r="E93" s="41" t="inlineStr">
+      <c r="E94" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="30.75" customHeight="1">
-      <c r="A94" s="42" t="inlineStr">
+    <row r="95" ht="30.75" customHeight="1">
+      <c r="A95" s="42" t="inlineStr">
         <is>
           <t>Automation focus</t>
         </is>
       </c>
-      <c r="B94" s="41" t="inlineStr">
+      <c r="B95" s="41" t="inlineStr">
         <is>
           <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
-      <c r="C94" s="41" t="inlineStr">
+      <c r="C95" s="41" t="inlineStr">
         <is>
           <t>Detect duplicate/split clusters and preserve one coherent event sequence.</t>
         </is>
       </c>
-      <c r="D94" s="41" t="inlineStr">
+      <c r="D95" s="41" t="inlineStr">
         <is>
           <t>Standardized dashboard category</t>
         </is>
       </c>
-      <c r="E94" s="41" t="inlineStr">
+      <c r="E95" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="42" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="42" t="inlineStr">
         <is>
           <t>Automation focus</t>
         </is>
       </c>
-      <c r="B95" s="41" t="inlineStr">
+      <c r="B96" s="41" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="C95" s="41" t="inlineStr">
+      <c r="C96" s="41" t="inlineStr">
         <is>
           <t>Identify, onboard, and monitor new or missing sources dynamically.</t>
-        </is>
-      </c>
-      <c r="D95" s="41" t="inlineStr">
-        <is>
-          <t>Standardized dashboard category</t>
-        </is>
-      </c>
-      <c r="E95" s="41" t="inlineStr">
-        <is>
-          <t>Standard Automation Focus</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="30.75" customHeight="1">
-      <c r="A96" s="42" t="inlineStr">
-        <is>
-          <t>Automation focus</t>
-        </is>
-      </c>
-      <c r="B96" s="41" t="inlineStr">
-        <is>
-          <t>Entity &amp; Supplier Resolution</t>
-        </is>
-      </c>
-      <c r="C96" s="41" t="inlineStr">
-        <is>
-          <t>Resolve company, facility, supplier, and customer relationships accurately.</t>
         </is>
       </c>
       <c r="D96" s="41" t="inlineStr">
@@ -19525,12 +20046,12 @@
       </c>
       <c r="B97" s="41" t="inlineStr">
         <is>
-          <t>Multilingual Keyword Expansion</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="C97" s="41" t="inlineStr">
         <is>
-          <t>Expand and maintain detection terms across languages and regional variations.</t>
+          <t>Resolve company, facility, supplier, and customer relationships accurately.</t>
         </is>
       </c>
       <c r="D97" s="41" t="inlineStr">
@@ -19552,66 +20073,66 @@
       </c>
       <c r="B98" s="41" t="inlineStr">
         <is>
+          <t>Multilingual Keyword Expansion</t>
+        </is>
+      </c>
+      <c r="C98" s="41" t="inlineStr">
+        <is>
+          <t>Expand and maintain detection terms across languages and regional variations.</t>
+        </is>
+      </c>
+      <c r="D98" s="41" t="inlineStr">
+        <is>
+          <t>Standardized dashboard category</t>
+        </is>
+      </c>
+      <c r="E98" s="41" t="inlineStr">
+        <is>
+          <t>Standard Automation Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="30.75" customHeight="1">
+      <c r="A99" s="42" t="inlineStr">
+        <is>
+          <t>Automation focus</t>
+        </is>
+      </c>
+      <c r="B99" s="41" t="inlineStr">
+        <is>
           <t>Notification Visibility Monitoring</t>
         </is>
       </c>
-      <c r="C98" s="41" t="inlineStr">
+      <c r="C99" s="41" t="inlineStr">
         <is>
           <t>Monitor whether published alerts and WarRooms are visible and delivered to the customer.</t>
         </is>
       </c>
-      <c r="D98" s="41" t="inlineStr">
+      <c r="D99" s="41" t="inlineStr">
         <is>
           <t>Standardized dashboard category</t>
         </is>
       </c>
-      <c r="E98" s="41" t="inlineStr">
+      <c r="E99" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="42" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="42" t="inlineStr">
         <is>
           <t>Automation focus</t>
         </is>
       </c>
-      <c r="B99" s="41" t="inlineStr">
+      <c r="B100" s="41" t="inlineStr">
         <is>
           <t>Other Control Automation</t>
         </is>
       </c>
-      <c r="C99" s="41" t="inlineStr">
+      <c r="C100" s="41" t="inlineStr">
         <is>
           <t>Automation that does not fit another standardized focus category.</t>
-        </is>
-      </c>
-      <c r="D99" s="41" t="inlineStr">
-        <is>
-          <t>Standardized dashboard category</t>
-        </is>
-      </c>
-      <c r="E99" s="41" t="inlineStr">
-        <is>
-          <t>Standard Automation Focus</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="30.75" customHeight="1">
-      <c r="A100" s="42" t="inlineStr">
-        <is>
-          <t>Automation focus</t>
-        </is>
-      </c>
-      <c r="B100" s="41" t="inlineStr">
-        <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="C100" s="41" t="inlineStr">
-        <is>
-          <t>Validate impact decisions, escalation, publishing, and WarRoom creation.</t>
         </is>
       </c>
       <c r="D100" s="41" t="inlineStr">
@@ -19628,27 +20149,27 @@
     <row r="101" ht="30.75" customHeight="1">
       <c r="A101" s="42" t="inlineStr">
         <is>
-          <t>Reason label</t>
+          <t>Automation focus</t>
         </is>
       </c>
       <c r="B101" s="41" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="C101" s="41" t="inlineStr">
         <is>
-          <t>Customer requested confirmation of coverage, facts, or system behavior.</t>
+          <t>Validate impact decisions, escalation, publishing, and WarRoom creation.</t>
         </is>
       </c>
       <c r="D101" s="41" t="inlineStr">
         <is>
-          <t>Use only when supported by Comments and Missed_Flag</t>
+          <t>Standardized dashboard category</t>
         </is>
       </c>
       <c r="E101" s="41" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>
@@ -19660,7 +20181,7 @@
       </c>
       <c r="B102" s="41" t="inlineStr">
         <is>
-          <t>Customer Requested Verification</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="C102" s="41" t="inlineStr">
@@ -19687,12 +20208,12 @@
       </c>
       <c r="B103" s="41" t="inlineStr">
         <is>
-          <t>Customer Terminology Preference</t>
+          <t>Customer Requested Verification</t>
         </is>
       </c>
       <c r="C103" s="41" t="inlineStr">
         <is>
-          <t>Customer requested wording or naming alignment rather than correction of a reporting failure.</t>
+          <t>Customer requested confirmation of coverage, facts, or system behavior.</t>
         </is>
       </c>
       <c r="D103" s="41" t="inlineStr">
@@ -19714,12 +20235,12 @@
       </c>
       <c r="B104" s="41" t="inlineStr">
         <is>
-          <t>Delay in creating separate WarRoom / delayed escalation</t>
+          <t>Customer Terminology Preference</t>
         </is>
       </c>
       <c r="C104" s="41" t="inlineStr">
         <is>
-          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
+          <t>Customer requested wording or naming alignment rather than correction of a reporting failure.</t>
         </is>
       </c>
       <c r="D104" s="41" t="inlineStr">
@@ -19741,7 +20262,7 @@
       </c>
       <c r="B105" s="41" t="inlineStr">
         <is>
-          <t>Delayed / Missing WarRoom</t>
+          <t>Delay in creating separate WarRoom / delayed escalation</t>
         </is>
       </c>
       <c r="C105" s="41" t="inlineStr">
@@ -19768,7 +20289,7 @@
       </c>
       <c r="B106" s="41" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Delayed / Missing WarRoom</t>
         </is>
       </c>
       <c r="C106" s="41" t="inlineStr">
@@ -19795,7 +20316,7 @@
       </c>
       <c r="B107" s="41" t="inlineStr">
         <is>
-          <t>Delayed WarRoom</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="C107" s="41" t="inlineStr">
@@ -19822,7 +20343,7 @@
       </c>
       <c r="B108" s="41" t="inlineStr">
         <is>
-          <t>Delayed alert / WarRoom created late</t>
+          <t>Delayed WarRoom</t>
         </is>
       </c>
       <c r="C108" s="41" t="inlineStr">
@@ -19849,12 +20370,12 @@
       </c>
       <c r="B109" s="41" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms</t>
+          <t>Delayed alert / WarRoom created late</t>
         </is>
       </c>
       <c r="C109" s="41" t="inlineStr">
         <is>
-          <t>Related content was distributed across more than one WarRoom.</t>
+          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
         </is>
       </c>
       <c r="D109" s="41" t="inlineStr">
@@ -19876,12 +20397,12 @@
       </c>
       <c r="B110" s="41" t="inlineStr">
         <is>
-          <t>Event not triggered / not notified</t>
+          <t>Duplicate WarRooms</t>
         </is>
       </c>
       <c r="C110" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>Related content was distributed across more than one WarRoom.</t>
         </is>
       </c>
       <c r="D110" s="41" t="inlineStr">
@@ -19903,12 +20424,12 @@
       </c>
       <c r="B111" s="41" t="inlineStr">
         <is>
-          <t>Geographic Coverage Clarification</t>
+          <t>Event not triggered / not notified</t>
         </is>
       </c>
       <c r="C111" s="41" t="inlineStr">
         <is>
-          <t>Customer requested explanation of the geographic scope or impact-area method.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D111" s="41" t="inlineStr">
@@ -19930,12 +20451,12 @@
       </c>
       <c r="B112" s="41" t="inlineStr">
         <is>
-          <t>Geographic Misclassification</t>
+          <t>Geographic Coverage Clarification</t>
         </is>
       </c>
       <c r="C112" s="41" t="inlineStr">
         <is>
-          <t>An event or location was assigned to an incorrect geographic impact area.</t>
+          <t>Customer requested explanation of the geographic scope or impact-area method.</t>
         </is>
       </c>
       <c r="D112" s="41" t="inlineStr">
@@ -19957,12 +20478,12 @@
       </c>
       <c r="B113" s="41" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Geographic Misclassification</t>
         </is>
       </c>
       <c r="C113" s="41" t="inlineStr">
         <is>
-          <t>A relevant mapped supplier was omitted from the impacted-supplier selection.</t>
+          <t>An event or location was assigned to an incorrect geographic impact area.</t>
         </is>
       </c>
       <c r="D113" s="41" t="inlineStr">
@@ -19984,12 +20505,12 @@
       </c>
       <c r="B114" s="41" t="inlineStr">
         <is>
-          <t>Incorrect Action</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="C114" s="41" t="inlineStr">
         <is>
-          <t>EventWatch action or handling was incorrect even though the event itself may not have been missed.</t>
+          <t>A relevant mapped supplier was omitted from the impacted-supplier selection.</t>
         </is>
       </c>
       <c r="D114" s="41" t="inlineStr">
@@ -20011,12 +20532,12 @@
       </c>
       <c r="B115" s="41" t="inlineStr">
         <is>
-          <t>Incorrect Industry selection</t>
+          <t>Incorrect Action</t>
         </is>
       </c>
       <c r="C115" s="41" t="inlineStr">
         <is>
-          <t>The expected industry classification was missing or incorrect.</t>
+          <t>EventWatch action or handling was incorrect even though the event itself may not have been missed.</t>
         </is>
       </c>
       <c r="D115" s="41" t="inlineStr">
@@ -20038,12 +20559,12 @@
       </c>
       <c r="B116" s="41" t="inlineStr">
         <is>
-          <t>Missed + Delayed Reporting</t>
+          <t>Incorrect Industry selection</t>
         </is>
       </c>
       <c r="C116" s="41" t="inlineStr">
         <is>
-          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
+          <t>The expected industry classification was missing or incorrect.</t>
         </is>
       </c>
       <c r="D116" s="41" t="inlineStr">
@@ -20065,7 +20586,7 @@
       </c>
       <c r="B117" s="41" t="inlineStr">
         <is>
-          <t>Missed / Delayed Event</t>
+          <t>Missed + Delayed Reporting</t>
         </is>
       </c>
       <c r="C117" s="41" t="inlineStr">
@@ -20092,12 +20613,12 @@
       </c>
       <c r="B118" s="41" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed / Delayed Event</t>
         </is>
       </c>
       <c r="C118" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>Expected reporting, escalation, notification, or WarRoom creation occurred later than required.</t>
         </is>
       </c>
       <c r="D118" s="41" t="inlineStr">
@@ -20119,7 +20640,7 @@
       </c>
       <c r="B119" s="41" t="inlineStr">
         <is>
-          <t>Missed Relevant Event</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="C119" s="41" t="inlineStr">
@@ -20146,7 +20667,7 @@
       </c>
       <c r="B120" s="41" t="inlineStr">
         <is>
-          <t>Missed WarRoom</t>
+          <t>Missed Relevant Event</t>
         </is>
       </c>
       <c r="C120" s="41" t="inlineStr">
@@ -20173,7 +20694,7 @@
       </c>
       <c r="B121" s="41" t="inlineStr">
         <is>
-          <t>Missed WarRoom / No notification</t>
+          <t>Missed WarRoom</t>
         </is>
       </c>
       <c r="C121" s="41" t="inlineStr">
@@ -20200,7 +20721,7 @@
       </c>
       <c r="B122" s="41" t="inlineStr">
         <is>
-          <t>Missed alert / event not captured</t>
+          <t>Missed WarRoom / No notification</t>
         </is>
       </c>
       <c r="C122" s="41" t="inlineStr">
@@ -20227,7 +20748,7 @@
       </c>
       <c r="B123" s="41" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Missed alert / event not captured</t>
         </is>
       </c>
       <c r="C123" s="41" t="inlineStr">
@@ -20254,7 +20775,7 @@
       </c>
       <c r="B124" s="41" t="inlineStr">
         <is>
-          <t>Missed insolvency event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="C124" s="41" t="inlineStr">
@@ -20281,7 +20802,7 @@
       </c>
       <c r="B125" s="41" t="inlineStr">
         <is>
-          <t>Missed severe weather alert</t>
+          <t>Missed insolvency event</t>
         </is>
       </c>
       <c r="C125" s="41" t="inlineStr">
@@ -20308,12 +20829,12 @@
       </c>
       <c r="B126" s="41" t="inlineStr">
         <is>
-          <t>Missing Automotive industry tag (customer tracking missed it)</t>
+          <t>Missed severe weather alert</t>
         </is>
       </c>
       <c r="C126" s="41" t="inlineStr">
         <is>
-          <t>The expected industry classification was missing or incorrect.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D126" s="41" t="inlineStr">
@@ -20335,12 +20856,12 @@
       </c>
       <c r="B127" s="41" t="inlineStr">
         <is>
-          <t>Missing EventWatch coverage / feeds not captured</t>
+          <t>Missing Automotive industry tag (customer tracking missed it)</t>
         </is>
       </c>
       <c r="C127" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>The expected industry classification was missing or incorrect.</t>
         </is>
       </c>
       <c r="D127" s="41" t="inlineStr">
@@ -20362,7 +20883,7 @@
       </c>
       <c r="B128" s="41" t="inlineStr">
         <is>
-          <t>Missing Resilinc alert / insolvency not captured</t>
+          <t>Missing EventWatch coverage / feeds not captured</t>
         </is>
       </c>
       <c r="C128" s="41" t="inlineStr">
@@ -20389,12 +20910,12 @@
       </c>
       <c r="B129" s="41" t="inlineStr">
         <is>
-          <t>SEC notification not captured/provided on time</t>
+          <t>Missing Resilinc alert / insolvency not captured</t>
         </is>
       </c>
       <c r="C129" s="41" t="inlineStr">
         <is>
-          <t>Specific customer-reported reason recorded in the tracker.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D129" s="41" t="inlineStr">
@@ -20416,12 +20937,12 @@
       </c>
       <c r="B130" s="41" t="inlineStr">
         <is>
-          <t>Severity / consolidation handling concern</t>
+          <t>SEC notification not captured/provided on time</t>
         </is>
       </c>
       <c r="C130" s="41" t="inlineStr">
         <is>
-          <t>Customer questioned the severity level or consolidation of event coverage.</t>
+          <t>Specific customer-reported reason recorded in the tracker.</t>
         </is>
       </c>
       <c r="D130" s="41" t="inlineStr">
@@ -20443,12 +20964,12 @@
       </c>
       <c r="B131" s="41" t="inlineStr">
         <is>
-          <t>Supplier Impact Mapping Clarification</t>
+          <t>Severity / consolidation handling concern</t>
         </is>
       </c>
       <c r="C131" s="41" t="inlineStr">
         <is>
-          <t>Customer requested explanation of why suppliers were included or excluded from the impact area.</t>
+          <t>Customer questioned the severity level or consolidation of event coverage.</t>
         </is>
       </c>
       <c r="D131" s="41" t="inlineStr">
@@ -20470,12 +20991,12 @@
       </c>
       <c r="B132" s="41" t="inlineStr">
         <is>
-          <t>WarRoom not created despite nationwide disruption</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="C132" s="41" t="inlineStr">
         <is>
-          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
+          <t>Customer requested explanation of why suppliers were included or excluded from the impact area.</t>
         </is>
       </c>
       <c r="D132" s="41" t="inlineStr">
@@ -20497,12 +21018,12 @@
       </c>
       <c r="B133" s="41" t="inlineStr">
         <is>
-          <t>WarRoom not visible in customer profile</t>
+          <t>WarRoom not created despite nationwide disruption</t>
         </is>
       </c>
       <c r="C133" s="41" t="inlineStr">
         <is>
-          <t>Published content was not visible in the customer profile or portal.</t>
+          <t>Expected EventWatch coverage, alerting, notification, or WarRoom action did not occur.</t>
         </is>
       </c>
       <c r="D133" s="41" t="inlineStr">
@@ -20524,12 +21045,12 @@
       </c>
       <c r="B134" s="41" t="inlineStr">
         <is>
-          <t>WarRoom should have been created but was not</t>
+          <t>WarRoom not visible in customer profile</t>
         </is>
       </c>
       <c r="C134" s="41" t="inlineStr">
         <is>
-          <t>Available information met the escalation criteria, but the required WarRoom was not created.</t>
+          <t>Published content was not visible in the customer profile or portal.</t>
         </is>
       </c>
       <c r="D134" s="41" t="inlineStr">
@@ -20551,12 +21072,12 @@
       </c>
       <c r="B135" s="41" t="inlineStr">
         <is>
-          <t>WarRoom visibility affected by customer profile filters</t>
+          <t>WarRoom should have been created but was not</t>
         </is>
       </c>
       <c r="C135" s="41" t="inlineStr">
         <is>
-          <t>Published content was not visible in the customer profile or portal.</t>
+          <t>Available information met the escalation criteria, but the required WarRoom was not created.</t>
         </is>
       </c>
       <c r="D135" s="41" t="inlineStr">
@@ -20578,12 +21099,12 @@
       </c>
       <c r="B136" s="41" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>WarRoom visibility affected by customer profile filters</t>
         </is>
       </c>
       <c r="C136" s="41" t="inlineStr">
         <is>
-          <t>The relevance classification of an event or alert was disputed or incorrect.</t>
+          <t>Published content was not visible in the customer profile or portal.</t>
         </is>
       </c>
       <c r="D136" s="41" t="inlineStr">
@@ -20600,27 +21121,27 @@
     <row r="137" ht="30.75" customHeight="1">
       <c r="A137" s="42" t="inlineStr">
         <is>
-          <t>Event type</t>
+          <t>Reason label</t>
         </is>
       </c>
       <c r="B137" s="41" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="C137" s="41" t="inlineStr">
         <is>
-          <t>Tropical cyclone classified as a hurricane or typhoon, with potential geographic, operational, or supply-chain impact.</t>
+          <t>The relevance classification of an event or alert was disputed or incorrect.</t>
         </is>
       </c>
       <c r="D137" s="41" t="inlineStr">
         <is>
-          <t>Use specifically for hurricanes and typhoons rather than the broader Extreme Weather category.</t>
+          <t>Use only when supported by Comments and Missed_Flag</t>
         </is>
       </c>
       <c r="E137" s="41" t="inlineStr">
         <is>
-          <t>Event type</t>
+          <t>Reason</t>
         </is>
       </c>
     </row>
@@ -20632,20 +21153,47 @@
       </c>
       <c r="B138" s="41" t="inlineStr">
         <is>
+          <t>Hurricane/Typhoon</t>
+        </is>
+      </c>
+      <c r="C138" s="41" t="inlineStr">
+        <is>
+          <t>Tropical cyclone classified as a hurricane or typhoon, with potential geographic, operational, or supply-chain impact.</t>
+        </is>
+      </c>
+      <c r="D138" s="41" t="inlineStr">
+        <is>
+          <t>Use specifically for hurricanes and typhoons rather than the broader Extreme Weather category.</t>
+        </is>
+      </c>
+      <c r="E138" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="30.75" customHeight="1">
+      <c r="A139" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B139" s="41" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C138" s="41" t="inlineStr">
+      <c r="C139" s="41" t="inlineStr">
         <is>
           <t>Event or inquiry category that does not fit any available standardized Event type.</t>
         </is>
       </c>
-      <c r="D138" s="41" t="inlineStr">
+      <c r="D139" s="41" t="inlineStr">
         <is>
           <t>Use only when no specific standard category applies; explain the subject in the title and comments.</t>
         </is>
       </c>
-      <c r="E138" s="41" t="inlineStr">
+      <c r="E139" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1219,10 +1219,10 @@
           </marker>
           <cat>
             <numRef>
-              <f>Dashboard!$A$50:$A$58</f>
+              <f>Dashboard!$A$50:$A$61</f>
               <numCache>
                 <formatCode>mmm\ yyyy</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="12"/>
                 <pt idx="0">
                   <v>46023</v>
                 </pt>
@@ -1250,15 +1250,24 @@
                 <pt idx="8">
                   <v>46266</v>
                 </pt>
+                <pt idx="9">
+                  <v>46296</v>
+                </pt>
+                <pt idx="10">
+                  <v>46327</v>
+                </pt>
+                <pt idx="11">
+                  <v>46357</v>
+                </pt>
               </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>Dashboard!$B$50:$B$58</f>
+              <f>Dashboard!$B$50:$B$61</f>
               <numCache>
                 <formatCode>General</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="12"/>
                 <pt idx="0">
                   <v>4</v>
                 </pt>
@@ -1285,6 +1294,15 @@
                 </pt>
                 <pt idx="8">
                   <v>4</v>
+                </pt>
+                <pt idx="9">
+                  <v>0</v>
+                </pt>
+                <pt idx="10">
+                  <v>0</v>
+                </pt>
+                <pt idx="11">
+                  <v>0</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1323,10 +1341,10 @@
           </marker>
           <cat>
             <numRef>
-              <f>Dashboard!$A$50:$A$58</f>
+              <f>Dashboard!$A$50:$A$61</f>
               <numCache>
                 <formatCode>mmm\ yyyy</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="12"/>
                 <pt idx="0">
                   <v>46023</v>
                 </pt>
@@ -1354,15 +1372,24 @@
                 <pt idx="8">
                   <v>46266</v>
                 </pt>
+                <pt idx="9">
+                  <v>46296</v>
+                </pt>
+                <pt idx="10">
+                  <v>46327</v>
+                </pt>
+                <pt idx="11">
+                  <v>46357</v>
+                </pt>
               </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>Dashboard!$C$50:$C$58</f>
+              <f>Dashboard!$C$50:$C$61</f>
               <numCache>
                 <formatCode>General</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="12"/>
                 <pt idx="0">
                   <v>0</v>
                 </pt>
@@ -1389,6 +1416,15 @@
                 </pt>
                 <pt idx="8">
                   <v>1</v>
+                </pt>
+                <pt idx="9">
+                  <v>0</v>
+                </pt>
+                <pt idx="10">
+                  <v>0</v>
+                </pt>
+                <pt idx="11">
+                  <v>0</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2581,7 +2617,7 @@
           </dLbls>
           <cat>
             <strRef>
-              <f>Dashboard!$A$64:$A$74</f>
+              <f>Dashboard!$A$67:$A$77</f>
               <strCache>
                 <ptCount val="11"/>
                 <pt idx="0">
@@ -2622,7 +2658,7 @@
           </cat>
           <val>
             <numRef>
-              <f>Dashboard!$B$64:$B$74</f>
+              <f>Dashboard!$B$67:$B$77</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
@@ -2905,7 +2941,7 @@
           </dLbls>
           <cat>
             <strRef>
-              <f>Dashboard!$E$64:$E$72</f>
+              <f>Dashboard!$E$67:$E$75</f>
               <strCache>
                 <ptCount val="9"/>
                 <pt idx="0">
@@ -2940,7 +2976,7 @@
           </cat>
           <val>
             <numRef>
-              <f>Dashboard!$F$64:$F$72</f>
+              <f>Dashboard!$F$67:$F$75</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
@@ -14522,7 +14558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R110"/>
+  <dimension ref="A1:R113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.85546875" customWidth="1" min="1" max="1"/>
@@ -16004,17 +16040,15 @@
       <c r="R58" s="3" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B59" s="26">
-        <f>SUM(B50:B58)</f>
+      <c r="A59" s="19" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B59" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Month_Sort],ROW()-49)</f>
         <v/>
       </c>
-      <c r="C59" s="26">
-        <f>SUM(C50:C58)</f>
+      <c r="C59" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Inquiry",ComplaintTracker[Month_Sort],ROW()-49)</f>
         <v/>
       </c>
       <c r="D59" s="3" t="n"/>
@@ -16032,6 +16066,34 @@
       <c r="P59" s="3" t="n"/>
       <c r="Q59" s="3" t="n"/>
       <c r="R59" s="3" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="19" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B60" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Month_Sort],ROW()-49)</f>
+        <v/>
+      </c>
+      <c r="C60" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Inquiry",ComplaintTracker[Month_Sort],ROW()-49)</f>
+        <v/>
+      </c>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+      <c r="I60" s="3" t="n"/>
+      <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="n"/>
+      <c r="L60" s="3" t="n"/>
+      <c r="M60" s="3" t="n"/>
+      <c r="N60" s="3" t="n"/>
+      <c r="O60" s="3" t="n"/>
+      <c r="P60" s="3" t="n"/>
+      <c r="Q60" s="3" t="n"/>
+      <c r="R60" s="3" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="3" t="n"/>
@@ -16054,6 +16116,34 @@
       <c r="R60" s="3" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="19" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B61" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Month_Sort],ROW()-49)</f>
+        <v/>
+      </c>
+      <c r="C61" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Inquiry",ComplaintTracker[Month_Sort],ROW()-49)</f>
+        <v/>
+      </c>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="n"/>
+      <c r="L61" s="3" t="n"/>
+      <c r="M61" s="3" t="n"/>
+      <c r="N61" s="3" t="n"/>
+      <c r="O61" s="3" t="n"/>
+      <c r="P61" s="3" t="n"/>
+      <c r="Q61" s="3" t="n"/>
+      <c r="R61" s="3" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
       <c r="A61" s="3" t="n"/>
       <c r="B61" s="3" t="n"/>
       <c r="C61" s="3" t="n"/>
@@ -16073,263 +16163,167 @@
       <c r="Q61" s="3" t="n"/>
       <c r="R61" s="3" t="n"/>
     </row>
-    <row r="62" ht="23.25" customHeight="1">
-      <c r="A62" s="88" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B62" s="26">
+        <f>SUM(B50:B61)</f>
+        <v/>
+      </c>
+      <c r="C62" s="26">
+        <f>SUM(C50:C61)</f>
+        <v/>
+      </c>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="n"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="n"/>
+      <c r="L62" s="3" t="n"/>
+      <c r="M62" s="3" t="n"/>
+      <c r="N62" s="3" t="n"/>
+      <c r="O62" s="3" t="n"/>
+      <c r="P62" s="3" t="n"/>
+      <c r="Q62" s="3" t="n"/>
+      <c r="R62" s="3" t="n"/>
+    </row>
+    <row r="65" ht="23.25" customHeight="1">
+      <c r="A65" s="88" t="inlineStr">
         <is>
           <t>SOURCE 05 · Top customers</t>
         </is>
       </c>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="88" t="inlineStr">
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="88" t="inlineStr">
         <is>
           <t>SOURCE 06 · Automation focus</t>
         </is>
       </c>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="88" t="inlineStr">
+      <c r="H65" s="3" t="n"/>
+      <c r="I65" s="88" t="inlineStr">
         <is>
           <t>DETAIL · Event type workload</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="15" t="inlineStr">
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="15" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="B66" s="15" t="inlineStr">
         <is>
           <t>Complaints</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="C66" s="15" t="inlineStr">
         <is>
           <t>% of Complaints</t>
         </is>
       </c>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="15" t="inlineStr">
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="15" t="inlineStr">
         <is>
           <t>Automation Focus</t>
         </is>
       </c>
-      <c r="F63" s="15" t="inlineStr">
+      <c r="F66" s="15" t="inlineStr">
         <is>
           <t>Complaints</t>
         </is>
       </c>
-      <c r="G63" s="15" t="inlineStr">
+      <c r="G66" s="15" t="inlineStr">
         <is>
           <t>% of Complaints</t>
         </is>
       </c>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="15" t="inlineStr">
+      <c r="H66" s="3" t="n"/>
+      <c r="I66" s="15" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="J63" s="15" t="inlineStr">
+      <c r="J66" s="15" t="inlineStr">
         <is>
           <t>Complaints</t>
         </is>
       </c>
-      <c r="K63" s="15" t="inlineStr">
+      <c r="K66" s="15" t="inlineStr">
         <is>
           <t>Inquiries</t>
         </is>
       </c>
-      <c r="L63" s="16" t="inlineStr">
+      <c r="L66" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="23.25" customHeight="1">
-      <c r="A64" s="18" t="str" cm="1">
-        <f t="array" ref="A64:A73">_xlfn.LET(_xlpm.u,_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Customer],ComplaintTracker[Issue Type]="Complaint")),_xlfn.TAKE(_xlfn.SORTBY(_xlpm.u,COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlpm.u),-1,_xlpm.u,1),10))</f>
+    <row r="67" ht="23.25" customHeight="1">
+      <c r="A67" s="18" t="str" cm="1">
+        <f t="array" ref="A67:A76">_xlfn.LET(_xlpm.u,_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Customer],ComplaintTracker[Issue Type]="Complaint")),_xlfn.TAKE(_xlfn.SORTBY(_xlpm.u,COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlpm.u),-1,_xlpm.u,1),10))</f>
         <v>Ford</v>
       </c>
-      <c r="B64" s="21" t="n" cm="1">
-        <f t="array" ref="B64:B73">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A64))</f>
+      <c r="B67" s="21" t="n" cm="1">
+        <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
         <v>32</v>
       </c>
-      <c r="C64" s="23" t="n" cm="1">
-        <f t="array" ref="C64:C73">_xlfn.ANCHORARRAY(B64)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
+      <c r="C67" s="23" t="n" cm="1">
+        <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
         <v>0.35555555555555557</v>
       </c>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="18" t="inlineStr">
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="18" t="inlineStr">
         <is>
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="F64" s="21">
-        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Standard Automation Focus],E64)</f>
-        <v/>
-      </c>
-      <c r="G64" s="23">
-        <f>F64/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v/>
-      </c>
-      <c r="H64" s="3" t="n"/>
-      <c r="I64" s="18" t="str" cm="1">
-        <f t="array" ref="I64:L87">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
-        <v>Bankruptcy</v>
-      </c>
-      <c r="J64" s="75" t="n">
-        <v>10</v>
-      </c>
-      <c r="K64" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="75" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" ht="23.25" customHeight="1">
-      <c r="A65" s="20" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="B65" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="C65" s="24" t="n">
-        <v>0.13333333333333333</v>
-      </c>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="20" t="inlineStr">
-        <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="F65" s="22">
-        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Standard Automation Focus],E65)</f>
-        <v/>
-      </c>
-      <c r="G65" s="24">
-        <f>F65/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v/>
-      </c>
-      <c r="H65" s="3" t="n"/>
-      <c r="I65" s="20" t="inlineStr">
-        <is>
-          <t>Chemical Spill</t>
-        </is>
-      </c>
-      <c r="J65" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="76" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="20" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="B66" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="C66" s="24" t="n">
-        <v>0.07777777777777778</v>
-      </c>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="20" t="inlineStr">
-        <is>
-          <t>Multilingual Keyword Expansion</t>
-        </is>
-      </c>
-      <c r="F66" s="22">
-        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Standard Automation Focus],E66)</f>
-        <v/>
-      </c>
-      <c r="G66" s="24">
-        <f>F66/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v/>
-      </c>
-      <c r="H66" s="3" t="n"/>
-      <c r="I66" s="20" t="inlineStr">
-        <is>
-          <t>Cyber Attack</t>
-        </is>
-      </c>
-      <c r="J66" s="76" t="n">
-        <v>14</v>
-      </c>
-      <c r="K66" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="76" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" ht="23.25" customHeight="1">
-      <c r="A67" s="20" t="inlineStr">
-        <is>
-          <t>Collins Aerospace</t>
-        </is>
-      </c>
-      <c r="B67" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="C67" s="24" t="n">
-        <v>0.044444444444444446</v>
-      </c>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="20" t="inlineStr">
-        <is>
-          <t>Other Control Automation</t>
-        </is>
-      </c>
-      <c r="F67" s="22">
+      <c r="F67" s="21">
         <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Standard Automation Focus],E67)</f>
         <v/>
       </c>
-      <c r="G67" s="24">
+      <c r="G67" s="23">
         <f>F67/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
         <v/>
       </c>
       <c r="H67" s="3" t="n"/>
-      <c r="I67" s="20" t="inlineStr">
-        <is>
-          <t>Earthquake</t>
-        </is>
-      </c>
-      <c r="J67" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="K67" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="76" t="n">
-        <v>3</v>
+      <c r="I67" s="18" t="str" cm="1">
+        <f t="array" ref="I67:L90">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
+        <v>Bankruptcy</v>
+      </c>
+      <c r="J67" s="75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K67" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="75" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="68" ht="23.25" customHeight="1">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="B68" s="22" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.044444444444444446</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="F68" s="22">
@@ -16343,35 +16337,35 @@
       <c r="H68" s="3" t="n"/>
       <c r="I68" s="20" t="inlineStr">
         <is>
-          <t>Extreme Weather</t>
+          <t>Chemical Spill</t>
         </is>
       </c>
       <c r="J68" s="76" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K68" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="76" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="20" t="inlineStr">
         <is>
-          <t>Ford/GM</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="B69" s="22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.07777777777777778</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>AI-Assisted Geofencing</t>
+          <t>Multilingual Keyword Expansion</t>
         </is>
       </c>
       <c r="F69" s="22">
@@ -16385,35 +16379,35 @@
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="20" t="inlineStr">
         <is>
-          <t>Factory Closure</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="J69" s="76" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K69" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="76" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" ht="23.25" customHeight="1">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>Collins Aerospace</t>
         </is>
       </c>
       <c r="B70" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.022222222222222223</v>
+        <v>0.044444444444444446</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="F70" s="22">
@@ -16427,35 +16421,35 @@
       <c r="H70" s="3" t="n"/>
       <c r="I70" s="20" t="inlineStr">
         <is>
-          <t>Factory Disruption</t>
+          <t>Earthquake</t>
         </is>
       </c>
       <c r="J70" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="K70" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="K70" s="76" t="n">
-        <v>0</v>
-      </c>
       <c r="L70" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" ht="23.25" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B71" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.022222222222222223</v>
+        <v>0.044444444444444446</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>Automated Industry Tagging</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="F71" s="22">
@@ -16469,35 +16463,35 @@
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Extreme Weather</t>
         </is>
       </c>
       <c r="J71" s="76" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K71" s="76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" s="76" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Ford/GM</t>
         </is>
       </c>
       <c r="B72" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.022222222222222223</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>AI-Assisted Geofencing</t>
         </is>
       </c>
       <c r="F72" s="22">
@@ -16511,7 +16505,7 @@
       <c r="H72" s="3" t="n"/>
       <c r="I72" s="20" t="inlineStr">
         <is>
-          <t>Financial Distress</t>
+          <t>Factory Closure</t>
         </is>
       </c>
       <c r="J72" s="76" t="n">
@@ -16527,7 +16521,7 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>UVM Health Network</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
@@ -16537,131 +16531,175 @@
         <v>0.022222222222222223</v>
       </c>
       <c r="D73" s="3" t="n"/>
-      <c r="E73" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="F73" s="26">
-        <f>SUM(F64:F72)</f>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+        </is>
+      </c>
+      <c r="F73" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Standard Automation Focus],E73)</f>
         <v/>
       </c>
-      <c r="G73" s="27">
-        <f>SUM(G64:G72)</f>
+      <c r="G73" s="24">
+        <f>F73/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
         <v/>
       </c>
       <c r="H73" s="3" t="n"/>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Factory Disruption</t>
         </is>
       </c>
       <c r="J73" s="76" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K73" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="76" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>Other customers</t>
-        </is>
-      </c>
-      <c r="B74" s="22">
-        <f>COUNTIF(ComplaintTracker[Issue Type],"Complaint")-SUM(B64:B73)</f>
+          <t>Merck</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" s="24" t="n">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>Automated Industry Tagging</t>
+        </is>
+      </c>
+      <c r="F74" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Standard Automation Focus],E74)</f>
         <v/>
       </c>
-      <c r="C74" s="24">
-        <f>B74/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
+      <c r="G74" s="24">
+        <f>F74/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
         <v/>
       </c>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="3" t="n"/>
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="20" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="J74" s="76" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K74" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="76" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B75" s="26">
-        <f>SUM(B64:B74)</f>
+      <c r="A75" s="20" t="inlineStr">
+        <is>
+          <t>Schneider Electric</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="24" t="n">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="20" t="inlineStr">
+        <is>
+          <t>Notification Visibility Monitoring</t>
+        </is>
+      </c>
+      <c r="F75" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Standard Automation Focus],E75)</f>
         <v/>
       </c>
-      <c r="C75" s="27">
-        <f>SUM(C64:C74)</f>
+      <c r="G75" s="24">
+        <f>F75/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
         <v/>
       </c>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="3" t="n"/>
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>Labor Disruption</t>
+          <t>Financial Distress</t>
         </is>
       </c>
       <c r="J75" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K75" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" ht="23.25" customHeight="1">
-      <c r="A76" s="3" t="n"/>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
+      <c r="A76" s="20" t="inlineStr">
+        <is>
+          <t>UVM Health Network</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" s="24" t="n">
+        <v>0.022222222222222223</v>
+      </c>
       <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
+      <c r="E76" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F76" s="26">
+        <f>SUM(F67:F75)</f>
+        <v/>
+      </c>
+      <c r="G76" s="27">
+        <f>SUM(G67:G75)</f>
+        <v/>
+      </c>
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="20" t="inlineStr">
         <is>
-          <t>Leadership Transition</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="J76" s="76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K76" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" ht="23.25" customHeight="1">
-      <c r="A77" s="3" t="n"/>
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
+      <c r="A77" s="20" t="inlineStr">
+        <is>
+          <t>Other customers</t>
+        </is>
+      </c>
+      <c r="B77" s="22">
+        <f>COUNTIF(ComplaintTracker[Issue Type],"Complaint")-SUM(B67:B76)</f>
+        <v/>
+      </c>
+      <c r="C77" s="24">
+        <f>B77/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
+        <v/>
+      </c>
       <c r="D77" s="3" t="n"/>
       <c r="E77" s="3" t="n"/>
       <c r="F77" s="3" t="n"/>
@@ -16669,7 +16707,7 @@
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>Litigation/Legal</t>
+          <t>Hurricane/Typhoon</t>
         </is>
       </c>
       <c r="J77" s="76" t="n">
@@ -16683,9 +16721,19 @@
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="3" t="n"/>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
+      <c r="A78" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B78" s="26">
+        <f>SUM(B67:B77)</f>
+        <v/>
+      </c>
+      <c r="C78" s="27">
+        <f>SUM(C67:C77)</f>
+        <v/>
+      </c>
       <c r="D78" s="3" t="n"/>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n"/>
@@ -16693,17 +16741,17 @@
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="20" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="J78" s="76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K78" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" ht="23.25" customHeight="1">
@@ -16717,17 +16765,17 @@
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Leadership Transition</t>
         </is>
       </c>
       <c r="J79" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K79" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L79" s="76" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" ht="23.25" customHeight="1">
@@ -16741,17 +16789,17 @@
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="20" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>Litigation/Legal</t>
         </is>
       </c>
       <c r="J80" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K80" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -16765,17 +16813,17 @@
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>Regulatory Change</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="J81" s="76" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K81" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" ht="23.25" customHeight="1">
@@ -16789,7 +16837,7 @@
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="20" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="J82" s="76" t="n">
@@ -16813,17 +16861,17 @@
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Protest/Riot</t>
         </is>
       </c>
       <c r="J83" s="76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K83" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -16837,26 +16885,20 @@
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="20" t="inlineStr">
         <is>
-          <t>Transport Disruption</t>
+          <t>Regulatory Change</t>
         </is>
       </c>
       <c r="J84" s="76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K84" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="M84" s="3" t="n"/>
-      <c r="N84" s="3" t="n"/>
-      <c r="O84" s="3" t="n"/>
-      <c r="P84" s="3" t="n"/>
-      <c r="Q84" s="3" t="n"/>
-      <c r="R84" s="3" t="n"/>
-    </row>
-    <row r="85" ht="18" customHeight="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" ht="23.25" customHeight="1">
       <c r="A85" s="3" t="n"/>
       <c r="B85" s="3" t="n"/>
       <c r="C85" s="3" t="n"/>
@@ -16867,26 +16909,20 @@
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>WarRoom Operations</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="J85" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K85" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L85" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="M85" s="3" t="n"/>
-      <c r="N85" s="3" t="n"/>
-      <c r="O85" s="3" t="n"/>
-      <c r="P85" s="3" t="n"/>
-      <c r="Q85" s="3" t="n"/>
-      <c r="R85" s="3" t="n"/>
-    </row>
-    <row r="86" ht="18" customHeight="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" ht="23.25" customHeight="1">
       <c r="A86" s="3" t="n"/>
       <c r="B86" s="3" t="n"/>
       <c r="C86" s="3" t="n"/>
@@ -16897,24 +16933,18 @@
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="J86" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K86" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="L86" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="M86" s="3" t="n"/>
-      <c r="N86" s="3" t="n"/>
-      <c r="O86" s="3" t="n"/>
-      <c r="P86" s="3" t="n"/>
-      <c r="Q86" s="3" t="n"/>
-      <c r="R86" s="3" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="3" t="n"/>
@@ -16925,19 +16955,19 @@
       <c r="F87" s="3" t="n"/>
       <c r="G87" s="3" t="n"/>
       <c r="H87" s="3" t="n"/>
-      <c r="I87" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J87" s="77" t="n">
-        <v>90</v>
-      </c>
-      <c r="K87" s="77" t="n">
-        <v>13</v>
-      </c>
-      <c r="L87" s="77" t="n">
-        <v>103</v>
+      <c r="I87" s="20" t="inlineStr">
+        <is>
+          <t>Transport Disruption</t>
+        </is>
+      </c>
+      <c r="J87" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="76" t="n">
+        <v>2</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
@@ -16955,10 +16985,20 @@
       <c r="F88" s="3" t="n"/>
       <c r="G88" s="3" t="n"/>
       <c r="H88" s="3" t="n"/>
-      <c r="I88" s="3" t="n"/>
-      <c r="J88" s="78" t="n"/>
-      <c r="K88" s="78" t="n"/>
-      <c r="L88" s="78" t="n"/>
+      <c r="I88" s="20" t="inlineStr">
+        <is>
+          <t>WarRoom Operations</t>
+        </is>
+      </c>
+      <c r="J88" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="76" t="n">
+        <v>1</v>
+      </c>
       <c r="M88" s="3" t="n"/>
       <c r="N88" s="3" t="n"/>
       <c r="O88" s="3" t="n"/>
@@ -16975,10 +17015,20 @@
       <c r="F89" s="3" t="n"/>
       <c r="G89" s="3" t="n"/>
       <c r="H89" s="3" t="n"/>
-      <c r="I89" s="3" t="n"/>
-      <c r="J89" s="78" t="n"/>
-      <c r="K89" s="78" t="n"/>
-      <c r="L89" s="78" t="n"/>
+      <c r="I89" s="20" t="inlineStr">
+        <is>
+          <t>Wildfire</t>
+        </is>
+      </c>
+      <c r="J89" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K89" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="76" t="n">
+        <v>4</v>
+      </c>
       <c r="M89" s="3" t="n"/>
       <c r="N89" s="3" t="n"/>
       <c r="O89" s="3" t="n"/>
@@ -16995,10 +17045,20 @@
       <c r="F90" s="3" t="n"/>
       <c r="G90" s="3" t="n"/>
       <c r="H90" s="3" t="n"/>
-      <c r="I90" s="3" t="n"/>
-      <c r="J90" s="78" t="n"/>
-      <c r="K90" s="78" t="n"/>
-      <c r="L90" s="78" t="n"/>
+      <c r="I90" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J90" s="77" t="n">
+        <v>90</v>
+      </c>
+      <c r="K90" s="77" t="n">
+        <v>13</v>
+      </c>
+      <c r="L90" s="77" t="n">
+        <v>103</v>
+      </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
       <c r="O90" s="3" t="n"/>
@@ -17216,9 +17276,9 @@
       <c r="G101" s="3" t="n"/>
       <c r="H101" s="3" t="n"/>
       <c r="I101" s="3" t="n"/>
-      <c r="J101" s="3" t="n"/>
-      <c r="K101" s="3" t="n"/>
-      <c r="L101" s="3" t="n"/>
+      <c r="J101" s="78" t="n"/>
+      <c r="K101" s="78" t="n"/>
+      <c r="L101" s="78" t="n"/>
       <c r="M101" s="3" t="n"/>
       <c r="N101" s="3" t="n"/>
       <c r="O101" s="3" t="n"/>
@@ -17236,9 +17296,9 @@
       <c r="G102" s="3" t="n"/>
       <c r="H102" s="3" t="n"/>
       <c r="I102" s="3" t="n"/>
-      <c r="J102" s="3" t="n"/>
-      <c r="K102" s="3" t="n"/>
-      <c r="L102" s="3" t="n"/>
+      <c r="J102" s="78" t="n"/>
+      <c r="K102" s="78" t="n"/>
+      <c r="L102" s="78" t="n"/>
       <c r="M102" s="3" t="n"/>
       <c r="N102" s="3" t="n"/>
       <c r="O102" s="3" t="n"/>
@@ -17256,9 +17316,9 @@
       <c r="G103" s="3" t="n"/>
       <c r="H103" s="3" t="n"/>
       <c r="I103" s="3" t="n"/>
-      <c r="J103" s="3" t="n"/>
-      <c r="K103" s="3" t="n"/>
-      <c r="L103" s="3" t="n"/>
+      <c r="J103" s="78" t="n"/>
+      <c r="K103" s="78" t="n"/>
+      <c r="L103" s="78" t="n"/>
       <c r="M103" s="3" t="n"/>
       <c r="N103" s="3" t="n"/>
       <c r="O103" s="3" t="n"/>
@@ -17406,7 +17466,67 @@
       <c r="Q110" s="3" t="n"/>
       <c r="R110" s="3" t="n"/>
     </row>
-    <row r="132" ht="18.75" customHeight="1"/>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="3" t="n"/>
+      <c r="B111" s="3" t="n"/>
+      <c r="C111" s="3" t="n"/>
+      <c r="D111" s="3" t="n"/>
+      <c r="E111" s="3" t="n"/>
+      <c r="F111" s="3" t="n"/>
+      <c r="G111" s="3" t="n"/>
+      <c r="H111" s="3" t="n"/>
+      <c r="I111" s="3" t="n"/>
+      <c r="J111" s="3" t="n"/>
+      <c r="K111" s="3" t="n"/>
+      <c r="L111" s="3" t="n"/>
+      <c r="M111" s="3" t="n"/>
+      <c r="N111" s="3" t="n"/>
+      <c r="O111" s="3" t="n"/>
+      <c r="P111" s="3" t="n"/>
+      <c r="Q111" s="3" t="n"/>
+      <c r="R111" s="3" t="n"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="3" t="n"/>
+      <c r="B112" s="3" t="n"/>
+      <c r="C112" s="3" t="n"/>
+      <c r="D112" s="3" t="n"/>
+      <c r="E112" s="3" t="n"/>
+      <c r="F112" s="3" t="n"/>
+      <c r="G112" s="3" t="n"/>
+      <c r="H112" s="3" t="n"/>
+      <c r="I112" s="3" t="n"/>
+      <c r="J112" s="3" t="n"/>
+      <c r="K112" s="3" t="n"/>
+      <c r="L112" s="3" t="n"/>
+      <c r="M112" s="3" t="n"/>
+      <c r="N112" s="3" t="n"/>
+      <c r="O112" s="3" t="n"/>
+      <c r="P112" s="3" t="n"/>
+      <c r="Q112" s="3" t="n"/>
+      <c r="R112" s="3" t="n"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="3" t="n"/>
+      <c r="B113" s="3" t="n"/>
+      <c r="C113" s="3" t="n"/>
+      <c r="D113" s="3" t="n"/>
+      <c r="E113" s="3" t="n"/>
+      <c r="F113" s="3" t="n"/>
+      <c r="G113" s="3" t="n"/>
+      <c r="H113" s="3" t="n"/>
+      <c r="I113" s="3" t="n"/>
+      <c r="J113" s="3" t="n"/>
+      <c r="K113" s="3" t="n"/>
+      <c r="L113" s="3" t="n"/>
+      <c r="M113" s="3" t="n"/>
+      <c r="N113" s="3" t="n"/>
+      <c r="O113" s="3" t="n"/>
+      <c r="P113" s="3" t="n"/>
+      <c r="Q113" s="3" t="n"/>
+      <c r="R113" s="3" t="n"/>
+    </row>
+    <row r="135" ht="18.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
     <mergeCell ref="A27:F27"/>
@@ -17416,7 +17536,7 @@
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="I48:K48"/>
-    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A65:C65"/>
     <mergeCell ref="D5:F7"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="A4:C4"/>
@@ -17427,7 +17547,7 @@
     <mergeCell ref="G9:L9"/>
     <mergeCell ref="P4:R4"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E65:G65"/>
     <mergeCell ref="G27:L27"/>
     <mergeCell ref="J5:L7"/>
     <mergeCell ref="P5:R7"/>
@@ -17436,9 +17556,9 @@
     <mergeCell ref="M48:O48"/>
     <mergeCell ref="E48:G48"/>
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="I62:L62"/>
+    <mergeCell ref="I65:L65"/>
   </mergeCells>
-  <conditionalFormatting sqref="B64:B74">
+  <conditionalFormatting sqref="B67:B77">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -17447,7 +17567,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F64:F72">
+  <conditionalFormatting sqref="F67:F75">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -17456,7 +17576,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J64:J83">
+  <conditionalFormatting sqref="J67:J86">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2984,7 +2984,7 @@
                   <v>26</v>
                 </pt>
                 <pt idx="1">
-                  <v>31</v>
+                  <v>29</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -2999,7 +2999,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="6">
-                  <v>2</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="7">
                   <v>2</v>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="J84" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Duplication</t>
         </is>
       </c>
       <c r="K84" s="33" t="inlineStr">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="M84" s="33" t="inlineStr">
         <is>
-          <t>Chinese regional source coverage for sub-tier automotive lighting suppliers</t>
+          <t>Cluster-assignment validation so an article grouped into the wrong cluster is caught before analyst review</t>
         </is>
       </c>
       <c r="N84" s="33" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="V84" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
       <c r="W84" s="33" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="X84" s="33" t="inlineStr">
         <is>
-          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+          <t>Captured, but grouped into the wrong event cluster, so the analyst reviewing that cluster marked it Not Impactful and it never reached WarRoom consideration. The miss is a clustering defect rather than a source-coverage gap or an analyst-judgement failure: the article was in the system and the grouping put it in front of the wrong decision. The cluster logic has since been enhanced.</t>
         </is>
       </c>
       <c r="Y84" s="33" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="I85" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J85" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Duplication</t>
         </is>
       </c>
       <c r="K85" s="33" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="M85" s="33" t="inlineStr">
         <is>
-          <t>Escalation automation for localized-impact tornado/storm sub-events and named-facility (Trialco) impact confirmation</t>
+          <t>Cluster-assignment validation so an article grouped into the wrong cluster is caught before analyst review</t>
         </is>
       </c>
       <c r="N85" s="33" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="V85" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
       <c r="W85" s="33" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="X85" s="33" t="inlineStr">
         <is>
-          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+          <t>Captured, but grouped into the wrong event cluster, so the analyst reviewing that cluster marked it Not Impactful and it never reached WarRoom consideration. The miss is a clustering defect rather than a source-coverage gap or an analyst-judgement failure: the article was in the system and the grouping put it in front of the wrong decision. The cluster logic has since been enhanced.</t>
         </is>
       </c>
       <c r="Y85" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
     </row>
@@ -13987,7 +13987,11 @@
           <t>EAO-32</t>
         </is>
       </c>
-      <c r="X99" s="33" t="n"/>
+      <c r="X99" s="33" t="inlineStr">
+        <is>
+          <t>No RCA: an intelligence request, not a service miss. Liberty Blume asked for further detail on Ciena 400G optics counterfeit risk and the topic is under active monitoring. The record stays open until that monitoring produces something to share.</t>
+        </is>
+      </c>
       <c r="Y99" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -14036,7 +14040,7 @@
       </c>
       <c r="J100" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K100" s="33" t="inlineStr">
@@ -14090,7 +14094,11 @@
           <t>EAO-33</t>
         </is>
       </c>
-      <c r="X100" s="33" t="n"/>
+      <c r="X100" s="33" t="inlineStr">
+        <is>
+          <t>Human error. The analyst marked the event Not Impactful while clearing stories at pace, so it was never escalated for WarRoom consideration. The event was captured and available for review; ingestion, source coverage and mapping did not contribute.</t>
+        </is>
+      </c>
       <c r="Y100" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -14193,7 +14201,11 @@
           <t>EAO-34</t>
         </is>
       </c>
-      <c r="X101" s="33" t="n"/>
+      <c r="X101" s="33" t="inlineStr">
+        <is>
+          <t>Human error. The analyst marked the event Not Impactful while clearing stories at pace, so it was never escalated for WarRoom consideration. The event was captured and available for review; ingestion, source coverage and mapping did not contribute.</t>
+        </is>
+      </c>
       <c r="Y101" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -14344,12 +14356,12 @@
       </c>
       <c r="I103" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J103" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K103" s="33" t="inlineStr">
@@ -14364,7 +14376,7 @@
       </c>
       <c r="M103" s="33" t="inlineStr">
         <is>
-          <t>Japanese-language and regional weather source coverage for localized record-rainfall events</t>
+          <t>Pace controls on story clearing, and a second check before a Not Impactful classification where a monitored customer has sites in the affected area</t>
         </is>
       </c>
       <c r="N103" s="33" t="inlineStr">
@@ -14399,7 +14411,7 @@
       </c>
       <c r="V103" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W103" s="33" t="inlineStr">
@@ -14407,10 +14419,14 @@
           <t>EAO-37</t>
         </is>
       </c>
-      <c r="X103" s="33" t="n"/>
+      <c r="X103" s="33" t="inlineStr">
+        <is>
+          <t>Human error. The analyst marked the event Not Impactful while clearing stories at pace, so it was never escalated for WarRoom consideration. The event was captured and available for review; ingestion, source coverage and mapping did not contribute.</t>
+        </is>
+      </c>
       <c r="Y103" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
     </row>
@@ -14514,7 +14530,11 @@
           <t>EAO-38</t>
         </is>
       </c>
-      <c r="X104" s="33" t="n"/>
+      <c r="X104" s="33" t="inlineStr">
+        <is>
+          <t>Not a defect. The Supplier Impact Confirmation was issued in line with one of the customers mapped to that supplier, whose settings called for it, so the request was correct for that account even though Eaton reads the M&amp;A threshold as excluding an acquiring supplier. The answer to Eaton is an explanation of how supplier notification follows each mapped customer's own configuration, plus the basis for the risk grade.</t>
+        </is>
+      </c>
       <c r="Y104" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -12332,7 +12332,7 @@
       </c>
       <c r="J84" s="33" t="inlineStr">
         <is>
-          <t>Duplication</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K84" s="33" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="J85" s="33" t="inlineStr">
         <is>
-          <t>Duplication</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K85" s="33" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="H103" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="I103" s="33" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="J103" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Captured Late</t>
         </is>
       </c>
       <c r="K103" s="33" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="M103" s="33" t="inlineStr">
         <is>
-          <t>Pace controls on story clearing, and a second check before a Not Impactful classification where a monitored customer has sites in the affected area</t>
+          <t>Timeliness monitoring that flags a region already producing captured stories where a related event has not been published within the reporting window</t>
         </is>
       </c>
       <c r="N103" s="33" t="inlineStr">
@@ -14389,7 +14389,11 @@
           <t>Staged from Jira EAO-37 (Open). Sandisk was alerted internally to record heavy rain in Yokkaichi city, Japan and could find no news item or WarRoom for it, despite having loaded their own Yokkaichi sites as suppliers. The customer supplied no public source. CS verified the Sandisk org and then the database across all customer orgs and found no evidence the notification was ever generated, so the event did not enter the system at all rather than being filtered out. RCA requested.</t>
         </is>
       </c>
-      <c r="P103" s="33" t="n"/>
+      <c r="P103" s="33" t="inlineStr">
+        <is>
+          <t>~1 day (customer query 08-Sep-2026 -&gt; EventWatch report 09-Sep-2026)</t>
+        </is>
+      </c>
       <c r="Q103" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -14421,7 +14425,7 @@
       </c>
       <c r="X103" s="33" t="inlineStr">
         <is>
-          <t>Human error. The analyst marked the event Not Impactful while clearing stories at pace, so it was never escalated for WarRoom consideration. The event was captured and available for review; ingestion, source coverage and mapping did not contribute.</t>
+          <t>Not a coverage gap and not a Not Impactful call. The news was in the public domain and other Japan flooding stories were being captured on the analyst portal at the time; this one was delayed in reporting and only published on 09-Sep-2026, after the customer had raised the query on 08-Sep. Sandisk's complaint is that it never reached the notified section of their portal, which is the downstream effect of the reporting delay rather than a separate visibility defect.</t>
         </is>
       </c>
       <c r="Y103" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2984,7 +2984,7 @@
                   <v>26</v>
                 </pt>
                 <pt idx="1">
-                  <v>29</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -2999,7 +2999,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="6">
-                  <v>4</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="7">
                   <v>2</v>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Platform/Data Quality</t>
         </is>
       </c>
       <c r="D14" s="33" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Platform/Data Quality</t>
         </is>
       </c>
       <c r="D27" s="33" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="D67" s="33" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="V84" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W84" s="33" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="V85" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W85" s="33" t="inlineStr">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="C99" s="33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Counterfeit</t>
         </is>
       </c>
       <c r="D99" s="33" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C102" s="33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="D102" s="33" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="18" t="str" cm="1">
-        <f t="array" ref="I67:L90">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
+        <f t="array" ref="I67:L92">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
@@ -16403,17 +16403,17 @@
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="20" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Counterfeit</t>
         </is>
       </c>
       <c r="J69" s="76" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K69" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="76" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" ht="23.25" customHeight="1">
@@ -16445,17 +16445,17 @@
       <c r="H70" s="3" t="n"/>
       <c r="I70" s="20" t="inlineStr">
         <is>
-          <t>Earthquake</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="J70" s="76" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K70" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="76" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71" ht="23.25" customHeight="1">
@@ -16487,17 +16487,17 @@
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>Extreme Weather</t>
+          <t>Earthquake</t>
         </is>
       </c>
       <c r="J71" s="76" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K71" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="76" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -16529,17 +16529,17 @@
       <c r="H72" s="3" t="n"/>
       <c r="I72" s="20" t="inlineStr">
         <is>
-          <t>Factory Closure</t>
+          <t>Extreme Weather</t>
         </is>
       </c>
       <c r="J72" s="76" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K72" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="76" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" ht="23.25" customHeight="1">
@@ -16571,7 +16571,7 @@
       <c r="H73" s="3" t="n"/>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>Factory Disruption</t>
+          <t>Factory Closure</t>
         </is>
       </c>
       <c r="J73" s="76" t="n">
@@ -16613,17 +16613,17 @@
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="20" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Factory Disruption</t>
         </is>
       </c>
       <c r="J74" s="76" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K74" s="76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" s="76" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -16655,17 +16655,17 @@
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>Financial Distress</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="J75" s="76" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K75" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="76" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" ht="23.25" customHeight="1">
@@ -16697,17 +16697,17 @@
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="20" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Financial Distress</t>
         </is>
       </c>
       <c r="J76" s="76" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K76" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="76" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" ht="23.25" customHeight="1">
@@ -16731,17 +16731,17 @@
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="J77" s="76" t="n">
+        <v>6</v>
+      </c>
+      <c r="K77" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="K77" s="76" t="n">
-        <v>0</v>
-      </c>
       <c r="L77" s="76" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -16765,17 +16765,17 @@
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="20" t="inlineStr">
         <is>
-          <t>Labor Disruption</t>
+          <t>Hurricane/Typhoon</t>
         </is>
       </c>
       <c r="J78" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K78" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" ht="23.25" customHeight="1">
@@ -16789,17 +16789,17 @@
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>Leadership Transition</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="J79" s="76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K79" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" ht="23.25" customHeight="1">
@@ -16813,7 +16813,7 @@
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="20" t="inlineStr">
         <is>
-          <t>Litigation/Legal</t>
+          <t>Leadership Transition</t>
         </is>
       </c>
       <c r="J80" s="76" t="n">
@@ -16837,17 +16837,17 @@
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Litigation/Legal</t>
         </is>
       </c>
       <c r="J81" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K81" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="76" t="n">
         <v>1</v>
-      </c>
-      <c r="L81" s="76" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="82" ht="23.25" customHeight="1">
@@ -16861,17 +16861,17 @@
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="J82" s="76" t="n">
         <v>3</v>
       </c>
       <c r="K82" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L82" s="76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" ht="23.25" customHeight="1">
@@ -16885,17 +16885,17 @@
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>Platform/Data Quality</t>
         </is>
       </c>
       <c r="J83" s="76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K83" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -16909,17 +16909,17 @@
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="20" t="inlineStr">
         <is>
-          <t>Regulatory Change</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="J84" s="76" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K84" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="76" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" ht="23.25" customHeight="1">
@@ -16933,17 +16933,17 @@
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Protest/Riot</t>
         </is>
       </c>
       <c r="J85" s="76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K85" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L85" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" ht="23.25" customHeight="1">
@@ -16957,17 +16957,17 @@
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Regulatory Change</t>
         </is>
       </c>
       <c r="J86" s="76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K86" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16981,17 +16981,17 @@
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Transport Disruption</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="J87" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K87" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L87" s="76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
@@ -17011,14 +17011,14 @@
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="20" t="inlineStr">
         <is>
-          <t>WarRoom Operations</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="J88" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" s="76" t="n">
         <v>0</v>
-      </c>
-      <c r="K88" s="76" t="n">
-        <v>1</v>
       </c>
       <c r="L88" s="76" t="n">
         <v>1</v>
@@ -17041,17 +17041,17 @@
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Transport Disruption</t>
         </is>
       </c>
       <c r="J89" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K89" s="76" t="n">
         <v>1</v>
       </c>
       <c r="L89" s="76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M89" s="3" t="n"/>
       <c r="N89" s="3" t="n"/>
@@ -17069,19 +17069,19 @@
       <c r="F90" s="3" t="n"/>
       <c r="G90" s="3" t="n"/>
       <c r="H90" s="3" t="n"/>
-      <c r="I90" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J90" s="77" t="n">
-        <v>90</v>
-      </c>
-      <c r="K90" s="77" t="n">
-        <v>13</v>
-      </c>
-      <c r="L90" s="77" t="n">
-        <v>103</v>
+      <c r="I90" s="20" t="inlineStr">
+        <is>
+          <t>WarRoom Operations</t>
+        </is>
+      </c>
+      <c r="J90" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" s="76" t="n">
+        <v>1</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -17099,10 +17099,20 @@
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
       <c r="H91" s="3" t="n"/>
-      <c r="I91" s="3" t="n"/>
-      <c r="J91" s="78" t="n"/>
-      <c r="K91" s="78" t="n"/>
-      <c r="L91" s="78" t="n"/>
+      <c r="I91" s="20" t="inlineStr">
+        <is>
+          <t>Wildfire</t>
+        </is>
+      </c>
+      <c r="J91" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="76" t="n">
+        <v>4</v>
+      </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>
       <c r="O91" s="3" t="n"/>
@@ -17119,10 +17129,20 @@
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
       <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="78" t="n"/>
-      <c r="K92" s="78" t="n"/>
-      <c r="L92" s="78" t="n"/>
+      <c r="I92" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J92" s="77" t="n">
+        <v>90</v>
+      </c>
+      <c r="K92" s="77" t="n">
+        <v>13</v>
+      </c>
+      <c r="L92" s="77" t="n">
+        <v>103</v>
+      </c>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -3375,7 +3375,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E139" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E150" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -17640,7 +17640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E139"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21360,6 +21360,303 @@
       <c r="E139" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="30.75" customHeight="1">
+      <c r="A140" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B140" s="41" t="inlineStr">
+        <is>
+          <t>Counterfeit</t>
+        </is>
+      </c>
+      <c r="C140" s="41" t="inlineStr">
+        <is>
+          <t>Counterfeit, grey-market, or otherwise non-genuine goods entering the supply chain.</t>
+        </is>
+      </c>
+      <c r="D140" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category. Covers counterfeit-risk intelligence and advisory requests as well as confirmed incidents.</t>
+        </is>
+      </c>
+      <c r="E140" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="30.75" customHeight="1">
+      <c r="A141" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B141" s="41" t="inlineStr">
+        <is>
+          <t>Litigation/Legal</t>
+        </is>
+      </c>
+      <c r="C141" s="41" t="inlineStr">
+        <is>
+          <t>Lawsuit, legal proceeding, or enforcement action involving a supplier or customer-linked entity.</t>
+        </is>
+      </c>
+      <c r="D141" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category. Use where the legal action itself is the event; use Regulatory Change for a rule, sanction, or export-control change.</t>
+        </is>
+      </c>
+      <c r="E141" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="30.75" customHeight="1">
+      <c r="A142" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B142" s="41" t="inlineStr">
+        <is>
+          <t>Platform/Data Quality</t>
+        </is>
+      </c>
+      <c r="C142" s="41" t="inlineStr">
+        <is>
+          <t>Defect in what the EventWatch platform presents rather than an event in the outside world: irrelevant, unrecognized, or incorrectly displayed records reaching the customer.</t>
+        </is>
+      </c>
+      <c r="D142" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category. Use when the complaint concerns platform content or data quality, not an external event.</t>
+        </is>
+      </c>
+      <c r="E142" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="30.75" customHeight="1">
+      <c r="A143" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B143" s="41" t="inlineStr">
+        <is>
+          <t>Power Outage</t>
+        </is>
+      </c>
+      <c r="C143" s="41" t="inlineStr">
+        <is>
+          <t>Loss or failure of electrical power supply affecting a facility, region, or grid.</t>
+        </is>
+      </c>
+      <c r="D143" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category. Use for grid and utility failures; use Extreme Weather where the outage is incidental to a storm already being reported.</t>
+        </is>
+      </c>
+      <c r="E143" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="30.75" customHeight="1">
+      <c r="A144" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B144" s="41" t="inlineStr">
+        <is>
+          <t>Tornado</t>
+        </is>
+      </c>
+      <c r="C144" s="41" t="inlineStr">
+        <is>
+          <t>Tornado with potential geographic, operational, or supply-chain impact.</t>
+        </is>
+      </c>
+      <c r="D144" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category. Retained for records logged specifically as tornado events; Extreme Weather is the broader category and also names tornadoes.</t>
+        </is>
+      </c>
+      <c r="E144" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="30.75" customHeight="1">
+      <c r="A145" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B145" s="41" t="inlineStr">
+        <is>
+          <t>WarRoom Operations</t>
+        </is>
+      </c>
+      <c r="C145" s="41" t="inlineStr">
+        <is>
+          <t>The record concerns the operation of a WarRoom itself — its timing, triggering criteria, or handling — rather than the underlying event.</t>
+        </is>
+      </c>
+      <c r="D145" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category. Use for inquiries about WarRoom process; type the record by the underlying event where the event itself is the subject.</t>
+        </is>
+      </c>
+      <c r="E145" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="30.75" customHeight="1">
+      <c r="A146" s="42" t="inlineStr">
+        <is>
+          <t>Reason label</t>
+        </is>
+      </c>
+      <c r="B146" s="41" t="inlineStr">
+        <is>
+          <t>Intelligence/Advisory Request</t>
+        </is>
+      </c>
+      <c r="C146" s="41" t="inlineStr">
+        <is>
+          <t>Customer requested market, industry, or risk intelligence beyond the EventWatch reporting already provided.</t>
+        </is>
+      </c>
+      <c r="D146" s="41" t="inlineStr">
+        <is>
+          <t>Use only when supported by Comments and Missed_Flag</t>
+        </is>
+      </c>
+      <c r="E146" s="41" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="30.75" customHeight="1">
+      <c r="A147" s="42" t="inlineStr">
+        <is>
+          <t>Reason label</t>
+        </is>
+      </c>
+      <c r="B147" s="41" t="inlineStr">
+        <is>
+          <t>Monitoring Strategy RFI</t>
+        </is>
+      </c>
+      <c r="C147" s="41" t="inlineStr">
+        <is>
+          <t>Customer requested an explanation of how a class of event is monitored, detected, or prioritized.</t>
+        </is>
+      </c>
+      <c r="D147" s="41" t="inlineStr">
+        <is>
+          <t>Use only when supported by Comments and Missed_Flag</t>
+        </is>
+      </c>
+      <c r="E147" s="41" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="30.75" customHeight="1">
+      <c r="A148" s="42" t="inlineStr">
+        <is>
+          <t>Reason label</t>
+        </is>
+      </c>
+      <c r="B148" s="41" t="inlineStr">
+        <is>
+          <t>News dashboard visibility gap</t>
+        </is>
+      </c>
+      <c r="C148" s="41" t="inlineStr">
+        <is>
+          <t>Published content was not visible or searchable in the customer's EventWatch News Dashboard.</t>
+        </is>
+      </c>
+      <c r="D148" s="41" t="inlineStr">
+        <is>
+          <t>Use only when supported by Comments and Missed_Flag</t>
+        </is>
+      </c>
+      <c r="E148" s="41" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="30.75" customHeight="1">
+      <c r="A149" s="42" t="inlineStr">
+        <is>
+          <t>Reason label</t>
+        </is>
+      </c>
+      <c r="B149" s="41" t="inlineStr">
+        <is>
+          <t>WarRoom Timing/Trigger Criteria Clarification</t>
+        </is>
+      </c>
+      <c r="C149" s="41" t="inlineStr">
+        <is>
+          <t>Customer questioned when a WarRoom was activated or which criteria triggered it.</t>
+        </is>
+      </c>
+      <c r="D149" s="41" t="inlineStr">
+        <is>
+          <t>Use only when supported by Comments and Missed_Flag</t>
+        </is>
+      </c>
+      <c r="E149" s="41" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="30.75" customHeight="1">
+      <c r="A150" s="42" t="inlineStr">
+        <is>
+          <t>Fix status</t>
+        </is>
+      </c>
+      <c r="B150" s="41" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C150" s="41" t="inlineStr">
+        <is>
+          <t>The linked Jira ticket is still open; no fix, RCA, or clarification has yet been issued to the customer.</t>
+        </is>
+      </c>
+      <c r="D150" s="41" t="inlineStr">
+        <is>
+          <t>Current resolution state</t>
+        </is>
+      </c>
+      <c r="E150" s="41" t="inlineStr">
+        <is>
+          <t>Short Term Fix Status</t>
         </is>
       </c>
     </row>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -7787,7 +7787,7 @@
       </c>
       <c r="C41" s="33" t="inlineStr">
         <is>
-          <t>Extreme Weather</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="D41" s="33" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="C42" s="33" t="inlineStr">
         <is>
-          <t>Extreme Weather</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="D42" s="33" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Operations</t>
+          <t>Hurricane/Typhoon</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="18" t="str" cm="1">
-        <f t="array" ref="I67:L92">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
+        <f t="array" ref="I67:L91">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
@@ -16533,13 +16533,13 @@
         </is>
       </c>
       <c r="J72" s="76" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K72" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="76" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" ht="23.25" customHeight="1">
@@ -16772,10 +16772,10 @@
         <v>1</v>
       </c>
       <c r="K78" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" ht="23.25" customHeight="1">
@@ -17015,13 +17015,13 @@
         </is>
       </c>
       <c r="J88" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K88" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M88" s="3" t="n"/>
       <c r="N88" s="3" t="n"/>
@@ -17071,17 +17071,17 @@
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>WarRoom Operations</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="J90" s="76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K90" s="76" t="n">
         <v>1</v>
       </c>
       <c r="L90" s="76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -17099,19 +17099,19 @@
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
       <c r="H91" s="3" t="n"/>
-      <c r="I91" s="20" t="inlineStr">
-        <is>
-          <t>Wildfire</t>
-        </is>
-      </c>
-      <c r="J91" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="K91" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" s="76" t="n">
-        <v>4</v>
+      <c r="I91" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J91" s="77" t="n">
+        <v>90</v>
+      </c>
+      <c r="K91" s="77" t="n">
+        <v>13</v>
+      </c>
+      <c r="L91" s="77" t="n">
+        <v>103</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>
@@ -17129,20 +17129,10 @@
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
       <c r="H92" s="3" t="n"/>
-      <c r="I92" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J92" s="77" t="n">
-        <v>90</v>
-      </c>
-      <c r="K92" s="77" t="n">
-        <v>13</v>
-      </c>
-      <c r="L92" s="77" t="n">
-        <v>103</v>
-      </c>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="78" t="n"/>
+      <c r="K92" s="78" t="n"/>
+      <c r="L92" s="78" t="n"/>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="3" t="n"/>
@@ -18811,7 +18801,7 @@
       </c>
       <c r="C45" s="41" t="inlineStr">
         <is>
-          <t>Severe weather such as storms, tornadoes, typhoons, flooding, or snowstorms.</t>
+          <t>Severe weather such as storms, flooding, drought, heat, or snowstorms. Tornado and Hurricane/Typhoon are separate categories and take precedence.</t>
         </is>
       </c>
       <c r="D45" s="41" t="inlineStr">
@@ -21489,7 +21479,7 @@
       </c>
       <c r="D144" s="41" t="inlineStr">
         <is>
-          <t>Standard event category. Retained for records logged specifically as tornado events; Extreme Weather is the broader category and also names tornadoes.</t>
+          <t>Standard event category. A tornado event is typed here, not under Extreme Weather; the two are deliberately separate.</t>
         </is>
       </c>
       <c r="E144" s="41" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,13 +1771,13 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>21</v>
+                  <v>24</v>
                 </pt>
                 <pt idx="2">
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>7</v>
+                  <v>4</v>
                 </pt>
               </numCache>
             </numRef>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="L99" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M99" s="33" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="X99" s="33" t="inlineStr">
         <is>
-          <t>No RCA: an intelligence request, not a service miss. Liberty Blume asked for further detail on Ciena 400G optics counterfeit risk and the topic is under active monitoring. The record stays open until that monitoring produces something to share.</t>
+          <t>No RCA: an intelligence request, not a service miss. Liberty Blume asked for further detail on Ciena 400G optics counterfeit risk. EventWatch confirmed to the customer that no such reporting is available in the public domain and that the topic remains under active monitoring; the customer accepted that position, so the item is closed rather than open.</t>
         </is>
       </c>
       <c r="Y99" s="33" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="L100" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M100" s="33" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="L101" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M101" s="33" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="L103" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M103" s="33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="L104" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M104" s="33" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="X104" s="33" t="inlineStr">
         <is>
-          <t>Not a defect. The Supplier Impact Confirmation was issued in line with one of the customers mapped to that supplier, whose settings called for it, so the request was correct for that account even though Eaton reads the M&amp;A threshold as excluding an acquiring supplier. The answer to Eaton is an explanation of how supplier notification follows each mapped customer's own configuration, plus the basis for the risk grade.</t>
+          <t>Not a defect, and the rule has since changed. The Supplier Impact Confirmation was issued in line with one of the customers mapped to that supplier, whose settings called for it, so the request was correct for that account even though Eaton reads the M&amp;A threshold as excluding an acquiring supplier. Under the new process supplier impact is sent to all mapped customers regardless of which side of the transaction the supplier is on, and Eaton was given that explanation together with the basis for the risk grade.</t>
         </is>
       </c>
       <c r="Y104" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -3318,9 +3318,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Y104" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
-  <autoFilter ref="A1:Y104"/>
-  <tableColumns count="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z104" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="A1:Z104"/>
+  <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
       <calculatedColumnFormula>DATE(YEAR(B2),MONTH(B2),1)</calculatedColumnFormula>
     </tableColumn>
@@ -3369,13 +3369,14 @@
     <tableColumn id="23" name="Jira Key"/>
     <tableColumn id="24" name="RCA Details"/>
     <tableColumn id="25" name="Routed To"/>
+    <tableColumn id="26" name="Resolution Date"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E150" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E151" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -3679,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y104"/>
+  <dimension ref="A1:Z104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -3818,6 +3819,11 @@
           <t>Routed To</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Resolution Date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="35" t="n">
@@ -3918,6 +3924,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z2" s="37" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="35" t="n">
@@ -4018,6 +4025,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z3" s="37" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="35" t="n">
@@ -4118,6 +4126,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z4" s="37" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="n">
@@ -4224,6 +4233,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z5" s="37" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="n">
@@ -4324,6 +4334,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z6" s="37" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="n">
@@ -4431,6 +4442,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z7" s="37" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="n">
@@ -4531,6 +4543,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z8" s="37" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="n">
@@ -4631,6 +4644,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z9" s="37" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="n">
@@ -4731,6 +4745,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z10" s="37" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="n">
@@ -4831,6 +4846,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z11" s="37" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="35" t="n">
@@ -4931,6 +4947,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z12" s="37" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="35" t="n">
@@ -5031,6 +5048,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z13" s="37" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="35" t="n">
@@ -5138,6 +5156,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z14" s="37" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="35" t="n">
@@ -5238,6 +5257,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z15" s="37" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="35" t="n">
@@ -5338,6 +5358,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z16" s="37" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="35" t="n">
@@ -5438,6 +5459,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z17" s="37" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="35" t="n">
@@ -5538,6 +5560,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z18" s="37" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="35" t="n">
@@ -5638,6 +5661,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z19" s="37" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="35" t="n">
@@ -5738,6 +5762,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z20" s="37" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="35" t="n">
@@ -5838,6 +5863,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z21" s="37" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="35" t="n">
@@ -5945,6 +5971,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z22" s="37" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="35" t="n">
@@ -6045,6 +6072,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z23" s="37" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="35" t="n">
@@ -6145,6 +6173,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z24" s="37" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="35" t="n">
@@ -6245,6 +6274,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z25" s="37" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="35" t="n">
@@ -6345,6 +6375,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z26" s="37" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="35" t="n">
@@ -6452,6 +6483,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z27" s="37" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="35" t="n">
@@ -6558,6 +6590,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z28" s="37" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="35" t="n">
@@ -6664,6 +6697,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z29" s="37" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="35" t="n">
@@ -6764,6 +6798,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z30" s="37" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="35" t="n">
@@ -6871,6 +6906,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z31" s="37" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="35" t="n">
@@ -6971,6 +7007,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z32" s="37" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="35" t="n">
@@ -7071,6 +7108,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z33" s="37" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="35" t="n">
@@ -7171,6 +7209,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z34" s="37" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="35" t="n">
@@ -7271,6 +7310,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z35" s="37" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="35" t="n">
@@ -7371,6 +7411,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z36" s="37" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="35" t="n">
@@ -7471,6 +7512,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z37" s="37" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="35" t="n">
@@ -7571,6 +7613,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z38" s="37" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="35" t="n">
@@ -7671,6 +7714,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z39" s="37" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="35" t="n">
@@ -7777,6 +7821,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z40" s="37" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="35" t="n">
@@ -7883,6 +7928,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z41" s="37" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="35" t="n">
@@ -7989,6 +8035,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z42" s="37" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="35" t="n">
@@ -8095,6 +8142,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z43" s="37" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="35" t="n">
@@ -8195,6 +8243,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z44" s="37" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="35" t="n">
@@ -8295,6 +8344,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z45" s="37" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="35" t="n">
@@ -8395,6 +8445,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z46" s="37" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="35" t="n">
@@ -8495,6 +8546,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z47" s="37" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="35" t="n">
@@ -8595,6 +8647,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z48" s="37" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="35" t="n">
@@ -8701,6 +8754,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z49" s="37" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="35" t="n">
@@ -8807,6 +8861,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z50" s="37" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="35" t="n">
@@ -8907,6 +8962,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z51" s="37" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="35" t="n">
@@ -9007,6 +9063,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z52" s="37" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="35" t="n">
@@ -9107,6 +9164,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z53" s="37" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="35" t="n">
@@ -9207,6 +9265,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z54" s="37" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="35" t="n">
@@ -9313,6 +9372,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z55" s="37" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="35" t="n">
@@ -9419,6 +9479,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z56" s="37" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="35" t="n">
@@ -9525,6 +9586,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z57" s="37" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="35" t="n">
@@ -9625,6 +9687,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z58" s="37" t="n"/>
     </row>
     <row r="59" customFormat="1" s="29">
       <c r="A59" s="36" t="n">
@@ -9731,6 +9794,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z59" s="37" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="35" t="n">
@@ -9831,6 +9895,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z60" s="37" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="35" t="n">
@@ -9931,6 +9996,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z61" s="37" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="35" t="n">
@@ -10040,6 +10106,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z62" s="37" t="n">
+        <v>46181</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="35" t="n">
@@ -10147,6 +10216,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z63" s="37" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="35" t="n">
@@ -10256,6 +10326,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z64" s="37" t="n">
+        <v>46191</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="35" t="n">
@@ -10361,6 +10434,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z65" s="37" t="n">
+        <v>46202</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="35" t="n">
@@ -10470,6 +10546,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z66" s="37" t="n">
+        <v>46217</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="35" t="n">
@@ -10575,6 +10654,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z67" s="37" t="n">
+        <v>46198</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="35" t="n">
@@ -10684,6 +10766,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z68" s="37" t="n">
+        <v>46202</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="35" t="n">
@@ -10793,6 +10878,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z69" s="37" t="n">
+        <v>46202</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="35" t="n">
@@ -10898,6 +10986,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z70" s="37" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="35" t="n">
@@ -11003,6 +11092,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z71" s="37" t="n">
+        <v>46204</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="35" t="n">
@@ -11116,6 +11208,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z72" s="37" t="n">
+        <v>46216</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="35" t="n">
@@ -11221,6 +11316,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z73" s="37" t="n">
+        <v>46220</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="35" t="n">
@@ -11330,6 +11428,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z74" s="37" t="n">
+        <v>46217</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="35" t="n">
@@ -11443,6 +11544,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z75" s="37" t="n">
+        <v>46220</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="35" t="n">
@@ -11550,6 +11654,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z76" s="37" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="35" t="n">
@@ -11657,6 +11764,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z77" s="37" t="n">
+        <v>46217</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="35" t="n">
@@ -11760,6 +11870,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z78" s="37" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="35" t="n">
@@ -11867,6 +11980,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z79" s="37" t="n">
+        <v>46220</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="35" t="n">
@@ -11974,6 +12090,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z80" s="37" t="n">
+        <v>46224</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="35" t="n">
@@ -12081,6 +12200,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z81" s="37" t="n">
+        <v>46230</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="35" t="n">
@@ -12184,6 +12306,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z82" s="37" t="n">
+        <v>46232</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="35" t="n">
@@ -12289,6 +12414,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z83" s="37" t="n">
+        <v>46239</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="35" t="n">
@@ -12396,6 +12524,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z84" s="37" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="35" t="n">
@@ -12503,6 +12632,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z85" s="37" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="35" t="n">
@@ -12610,6 +12740,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z86" s="37" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="35" t="n">
@@ -12719,6 +12850,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z87" s="37" t="n">
+        <v>46252</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="35" t="n">
@@ -12828,6 +12962,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z88" s="37" t="n">
+        <v>46259</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="35" t="n">
@@ -12935,6 +13072,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z89" s="37" t="n">
+        <v>46259</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="35" t="n">
@@ -13044,6 +13184,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z90" s="37" t="n">
+        <v>46259</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="35" t="n">
@@ -13149,6 +13292,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z91" s="37" t="n">
+        <v>46272</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="35" t="n">
@@ -13258,6 +13404,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z92" s="37" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="35" t="n">
@@ -13367,6 +13514,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z93" s="37" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="35" t="n">
@@ -13476,6 +13624,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z94" s="37" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="35" t="n">
@@ -13581,6 +13730,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z95" s="37" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="35" t="n">
@@ -13690,6 +13840,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z96" s="37" t="n">
+        <v>46272</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="35" t="n">
@@ -13790,6 +13943,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z97" s="37" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="35" t="n">
@@ -13890,6 +14044,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z98" s="37" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="35" t="n">
@@ -13997,6 +14152,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z99" s="37" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="35" t="n">
@@ -14104,6 +14260,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z100" s="37" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="35" t="n">
@@ -14211,6 +14368,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z101" s="37" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="35" t="n">
@@ -14318,6 +14476,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
+      <c r="Z102" s="37" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="35" t="n">
@@ -14433,6 +14592,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z103" s="37" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="35" t="n">
@@ -14544,6 +14704,7 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
+      <c r="Z104" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -17630,7 +17791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21647,6 +21808,33 @@
       <c r="E150" s="41" t="inlineStr">
         <is>
           <t>Short Term Fix Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="30.75" customHeight="1">
+      <c r="A151" s="42" t="inlineStr">
+        <is>
+          <t>Field definition</t>
+        </is>
+      </c>
+      <c r="B151" s="41" t="inlineStr">
+        <is>
+          <t>Resolution Date</t>
+        </is>
+      </c>
+      <c r="C151" s="41" t="inlineStr">
+        <is>
+          <t>Date the record was closed out with the customer.</t>
+        </is>
+      </c>
+      <c r="D151" s="41" t="inlineStr">
+        <is>
+          <t>A true date in dd-mmm-yyyy format, taken from the linked Jira ticket's resolution date. Blank while the record is Pending, and blank on a closed record that carries no ticket to read a date from.</t>
+        </is>
+      </c>
+      <c r="E151" s="41" t="inlineStr">
+        <is>
+          <t>Resolution Date</t>
         </is>
       </c>
     </row>
